--- a/public/templates/monthly-treatment-report-template.xlsx
+++ b/public/templates/monthly-treatment-report-template.xlsx
@@ -10,19 +10,22 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId6" roundtripDataChecksum="fYAeZmF7azyJqfaPs0YH61Rolix2FXTbA6ZbGJf6XSY="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId6" roundtripDataChecksum="4cuHei8F1w80FoZa9V3pSUlQfUeduuCmAG9zUTE1mE4="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="24">
   <si>
     <t>Bridgeport Public Utility District - Monthly Treatment Report Field Test Result</t>
   </si>
   <si>
     <t>Month:</t>
+  </si>
+  <si>
+    <t>Apil 2026</t>
   </si>
   <si>
     <t>Field Test Category</t>
@@ -64,6 +67,15 @@
     <t>PH</t>
   </si>
   <si>
+    <t>Gallons Treated from Cain well (UG):</t>
+  </si>
+  <si>
+    <t>Gallons Treated from Twin Lakes well (UG):</t>
+  </si>
+  <si>
+    <t>Notes:</t>
+  </si>
+  <si>
     <t>Bridgeport Public Utility District</t>
   </si>
   <si>
@@ -87,7 +99,7 @@
     <numFmt numFmtId="164" formatCode="[$-409]mmmm\-yy"/>
     <numFmt numFmtId="165" formatCode="m/d/yy"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="12.0"/>
       <color theme="1"/>
@@ -130,12 +142,19 @@
     </font>
     <font>
       <b/>
+      <u/>
+      <sz val="12.0"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
       <sz val="12.0"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -166,8 +185,14 @@
         <bgColor rgb="FFD8D8D8"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC4BD97"/>
+        <bgColor rgb="FFC4BD97"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border/>
     <border>
       <left style="thin">
@@ -225,11 +250,23 @@
         <color rgb="FF000000"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="39">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -242,7 +279,7 @@
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf quotePrefix="1" borderId="0" fillId="0" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -311,11 +348,18 @@
     <xf borderId="1" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="6" fillId="6" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf borderId="3" fillId="6" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf quotePrefix="1" borderId="0" fillId="0" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left"/>
+    <xf borderId="1" fillId="6" fontId="4" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
@@ -564,7 +608,9 @@
       <c r="C2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="4"/>
+      <c r="D2" s="4" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="3">
       <c r="B3" s="2"/>
@@ -577,33 +623,33 @@
     </row>
     <row r="4" ht="36.75" customHeight="1">
       <c r="A4" s="5" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5" s="8"/>
       <c r="C5" s="9"/>
@@ -645,7 +691,7 @@
     </row>
     <row r="9">
       <c r="A9" s="14" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B9" s="15"/>
       <c r="C9" s="16"/>
@@ -687,20 +733,20 @@
     </row>
     <row r="13">
       <c r="A13" s="18" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B13" s="19"/>
       <c r="C13" s="20"/>
       <c r="D13" s="21"/>
       <c r="E13" s="21"/>
       <c r="F13" s="22" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G13" s="22" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H13" s="22" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14">
@@ -710,13 +756,13 @@
       <c r="D14" s="21"/>
       <c r="E14" s="21"/>
       <c r="F14" s="22" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G14" s="22" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H14" s="22" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -726,13 +772,13 @@
       <c r="D15" s="24"/>
       <c r="E15" s="21"/>
       <c r="F15" s="22" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G15" s="22" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H15" s="22" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16">
@@ -742,31 +788,31 @@
       <c r="D16" s="24"/>
       <c r="E16" s="21"/>
       <c r="F16" s="22" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G16" s="22" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H16" s="22" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B17" s="26"/>
       <c r="C17" s="27"/>
       <c r="D17" s="28"/>
       <c r="E17" s="28"/>
       <c r="F17" s="22" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G17" s="22" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H17" s="22" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18">
@@ -776,13 +822,13 @@
       <c r="D18" s="28"/>
       <c r="E18" s="28"/>
       <c r="F18" s="22" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G18" s="22" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H18" s="22" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19">
@@ -792,13 +838,13 @@
       <c r="D19" s="28"/>
       <c r="E19" s="28"/>
       <c r="F19" s="22" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G19" s="22" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H19" s="22" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="20">
@@ -808,13 +854,13 @@
       <c r="D20" s="28"/>
       <c r="E20" s="28"/>
       <c r="F20" s="22" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G20" s="22" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H20" s="22" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21">
@@ -827,8 +873,11 @@
       <c r="H21" s="2"/>
     </row>
     <row r="22">
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
+      <c r="A22" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="B22" s="30"/>
+      <c r="C22" s="31"/>
       <c r="D22" s="2"/>
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>
@@ -836,8 +885,11 @@
       <c r="H22" s="2"/>
     </row>
     <row r="23">
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
+      <c r="A23" s="29" t="s">
+        <v>17</v>
+      </c>
+      <c r="B23" s="30"/>
+      <c r="C23" s="31"/>
       <c r="D23" s="2"/>
       <c r="E23" s="2"/>
       <c r="F23" s="2"/>
@@ -846,66 +898,27 @@
     </row>
     <row r="24">
       <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
-      <c r="H24" s="2"/>
     </row>
     <row r="25">
+      <c r="A25" s="32" t="s">
+        <v>18</v>
+      </c>
       <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
-      <c r="H25" s="2"/>
     </row>
     <row r="26">
       <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
     </row>
     <row r="27">
       <c r="B27" s="2"/>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
-      <c r="E27" s="2"/>
-      <c r="F27" s="2"/>
-      <c r="G27" s="2"/>
-      <c r="H27" s="2"/>
     </row>
     <row r="28">
       <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
-      <c r="F28" s="2"/>
-      <c r="G28" s="2"/>
-      <c r="H28" s="2"/>
     </row>
     <row r="29">
       <c r="B29" s="2"/>
-      <c r="C29" s="2"/>
-      <c r="D29" s="2"/>
-      <c r="E29" s="2"/>
-      <c r="F29" s="2"/>
-      <c r="G29" s="2"/>
-      <c r="H29" s="2"/>
     </row>
     <row r="30">
       <c r="B30" s="2"/>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
-      <c r="E30" s="2"/>
-      <c r="F30" s="2"/>
-      <c r="G30" s="2"/>
-      <c r="H30" s="2"/>
     </row>
     <row r="31">
       <c r="B31" s="2"/>
@@ -9546,6 +9559,96 @@
       <c r="F990" s="2"/>
       <c r="G990" s="2"/>
       <c r="H990" s="2"/>
+    </row>
+    <row r="991">
+      <c r="B991" s="2"/>
+      <c r="C991" s="2"/>
+      <c r="D991" s="2"/>
+      <c r="E991" s="2"/>
+      <c r="F991" s="2"/>
+      <c r="G991" s="2"/>
+      <c r="H991" s="2"/>
+    </row>
+    <row r="992">
+      <c r="B992" s="2"/>
+      <c r="C992" s="2"/>
+      <c r="D992" s="2"/>
+      <c r="E992" s="2"/>
+      <c r="F992" s="2"/>
+      <c r="G992" s="2"/>
+      <c r="H992" s="2"/>
+    </row>
+    <row r="993">
+      <c r="B993" s="2"/>
+      <c r="C993" s="2"/>
+      <c r="D993" s="2"/>
+      <c r="E993" s="2"/>
+      <c r="F993" s="2"/>
+      <c r="G993" s="2"/>
+      <c r="H993" s="2"/>
+    </row>
+    <row r="994">
+      <c r="B994" s="2"/>
+      <c r="C994" s="2"/>
+      <c r="D994" s="2"/>
+      <c r="E994" s="2"/>
+      <c r="F994" s="2"/>
+      <c r="G994" s="2"/>
+      <c r="H994" s="2"/>
+    </row>
+    <row r="995">
+      <c r="B995" s="2"/>
+      <c r="C995" s="2"/>
+      <c r="D995" s="2"/>
+      <c r="E995" s="2"/>
+      <c r="F995" s="2"/>
+      <c r="G995" s="2"/>
+      <c r="H995" s="2"/>
+    </row>
+    <row r="996">
+      <c r="B996" s="2"/>
+      <c r="C996" s="2"/>
+      <c r="D996" s="2"/>
+      <c r="E996" s="2"/>
+      <c r="F996" s="2"/>
+      <c r="G996" s="2"/>
+      <c r="H996" s="2"/>
+    </row>
+    <row r="997">
+      <c r="B997" s="2"/>
+      <c r="C997" s="2"/>
+      <c r="D997" s="2"/>
+      <c r="E997" s="2"/>
+      <c r="F997" s="2"/>
+      <c r="G997" s="2"/>
+      <c r="H997" s="2"/>
+    </row>
+    <row r="998">
+      <c r="B998" s="2"/>
+      <c r="C998" s="2"/>
+      <c r="D998" s="2"/>
+      <c r="E998" s="2"/>
+      <c r="F998" s="2"/>
+      <c r="G998" s="2"/>
+      <c r="H998" s="2"/>
+    </row>
+    <row r="999">
+      <c r="B999" s="2"/>
+      <c r="C999" s="2"/>
+      <c r="D999" s="2"/>
+      <c r="E999" s="2"/>
+      <c r="F999" s="2"/>
+      <c r="G999" s="2"/>
+      <c r="H999" s="2"/>
+    </row>
+    <row r="1000">
+      <c r="B1000" s="2"/>
+      <c r="C1000" s="2"/>
+      <c r="D1000" s="2"/>
+      <c r="E1000" s="2"/>
+      <c r="F1000" s="2"/>
+      <c r="G1000" s="2"/>
+      <c r="H1000" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -9577,4218 +9680,4218 @@
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2">
       <c r="B2" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" ht="7.5" customHeight="1">
-      <c r="B3" s="29"/>
-      <c r="C3" s="29"/>
+      <c r="B3" s="33"/>
+      <c r="C3" s="33"/>
     </row>
     <row r="4">
       <c r="B4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="30" t="s">
-        <v>17</v>
+      <c r="C4" s="4" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="5" ht="6.75" customHeight="1">
       <c r="B5" s="2"/>
-      <c r="C5" s="31"/>
+      <c r="C5" s="34"/>
     </row>
     <row r="6">
-      <c r="B6" s="32" t="s">
-        <v>18</v>
+      <c r="B6" s="35" t="s">
+        <v>22</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="33">
+      <c r="B7" s="36">
         <v>46113.0</v>
       </c>
-      <c r="C7" s="34">
+      <c r="C7" s="37">
         <v>33.75</v>
       </c>
-      <c r="D7" s="35"/>
+      <c r="D7" s="38"/>
     </row>
     <row r="8">
-      <c r="B8" s="33">
+      <c r="B8" s="36">
         <f t="shared" ref="B8:B36" si="1">B7+1</f>
         <v>46114</v>
       </c>
-      <c r="C8" s="34">
+      <c r="C8" s="37">
         <v>33.5</v>
       </c>
-      <c r="D8" s="35"/>
+      <c r="D8" s="38"/>
     </row>
     <row r="9">
-      <c r="B9" s="33">
+      <c r="B9" s="36">
         <f t="shared" si="1"/>
         <v>46115</v>
       </c>
-      <c r="C9" s="34">
+      <c r="C9" s="37">
         <v>33.75</v>
       </c>
-      <c r="D9" s="35"/>
-      <c r="E9" s="35"/>
+      <c r="D9" s="38"/>
+      <c r="E9" s="38"/>
     </row>
     <row r="10">
-      <c r="B10" s="33">
+      <c r="B10" s="36">
         <f t="shared" si="1"/>
         <v>46116</v>
       </c>
-      <c r="C10" s="34">
+      <c r="C10" s="37">
         <v>32.5</v>
       </c>
-      <c r="D10" s="35"/>
-      <c r="E10" s="35"/>
+      <c r="D10" s="38"/>
+      <c r="E10" s="38"/>
     </row>
     <row r="11">
-      <c r="B11" s="33">
+      <c r="B11" s="36">
         <f t="shared" si="1"/>
         <v>46117</v>
       </c>
-      <c r="C11" s="34">
+      <c r="C11" s="37">
         <v>32.25</v>
       </c>
-      <c r="D11" s="35"/>
-      <c r="E11" s="35"/>
+      <c r="D11" s="38"/>
+      <c r="E11" s="38"/>
     </row>
     <row r="12">
-      <c r="B12" s="33">
+      <c r="B12" s="36">
         <f t="shared" si="1"/>
         <v>46118</v>
       </c>
-      <c r="C12" s="34">
+      <c r="C12" s="37">
         <v>31.75</v>
       </c>
-      <c r="D12" s="35"/>
-      <c r="E12" s="35"/>
+      <c r="D12" s="38"/>
+      <c r="E12" s="38"/>
     </row>
     <row r="13">
-      <c r="B13" s="33">
+      <c r="B13" s="36">
         <f t="shared" si="1"/>
         <v>46119</v>
       </c>
-      <c r="C13" s="34">
+      <c r="C13" s="37">
         <v>31.75</v>
       </c>
-      <c r="D13" s="35"/>
-      <c r="E13" s="35"/>
+      <c r="D13" s="38"/>
+      <c r="E13" s="38"/>
     </row>
     <row r="14">
-      <c r="B14" s="33">
+      <c r="B14" s="36">
         <f t="shared" si="1"/>
         <v>46120</v>
       </c>
-      <c r="C14" s="34">
+      <c r="C14" s="37">
         <v>30.75</v>
       </c>
-      <c r="D14" s="35"/>
-      <c r="E14" s="35"/>
+      <c r="D14" s="38"/>
+      <c r="E14" s="38"/>
     </row>
     <row r="15">
-      <c r="B15" s="33">
+      <c r="B15" s="36">
         <f t="shared" si="1"/>
         <v>46121</v>
       </c>
-      <c r="C15" s="34">
+      <c r="C15" s="37">
         <v>30.5</v>
       </c>
-      <c r="D15" s="35"/>
-      <c r="E15" s="35"/>
+      <c r="D15" s="38"/>
+      <c r="E15" s="38"/>
     </row>
     <row r="16">
-      <c r="B16" s="33">
+      <c r="B16" s="36">
         <f t="shared" si="1"/>
         <v>46122</v>
       </c>
-      <c r="C16" s="34">
+      <c r="C16" s="37">
         <v>30.0</v>
       </c>
-      <c r="D16" s="35"/>
-      <c r="E16" s="35"/>
+      <c r="D16" s="38"/>
+      <c r="E16" s="38"/>
     </row>
     <row r="17">
-      <c r="B17" s="33">
+      <c r="B17" s="36">
         <f t="shared" si="1"/>
         <v>46123</v>
       </c>
-      <c r="C17" s="34">
+      <c r="C17" s="37">
         <v>29.5</v>
       </c>
-      <c r="D17" s="35"/>
-      <c r="E17" s="35"/>
+      <c r="D17" s="38"/>
+      <c r="E17" s="38"/>
     </row>
     <row r="18">
-      <c r="B18" s="33">
+      <c r="B18" s="36">
         <f t="shared" si="1"/>
         <v>46124</v>
       </c>
-      <c r="C18" s="34">
+      <c r="C18" s="37">
         <v>28.75</v>
       </c>
-      <c r="D18" s="35"/>
-      <c r="E18" s="35"/>
+      <c r="D18" s="38"/>
+      <c r="E18" s="38"/>
     </row>
     <row r="19">
-      <c r="B19" s="33">
+      <c r="B19" s="36">
         <f t="shared" si="1"/>
         <v>46125</v>
       </c>
-      <c r="C19" s="34">
+      <c r="C19" s="37">
         <v>28.5</v>
       </c>
-      <c r="D19" s="35"/>
-      <c r="E19" s="35"/>
+      <c r="D19" s="38"/>
+      <c r="E19" s="38"/>
     </row>
     <row r="20">
-      <c r="B20" s="33">
+      <c r="B20" s="36">
         <f t="shared" si="1"/>
         <v>46126</v>
       </c>
-      <c r="C20" s="34">
+      <c r="C20" s="37">
         <v>28.0</v>
       </c>
-      <c r="D20" s="35"/>
-      <c r="E20" s="35"/>
+      <c r="D20" s="38"/>
+      <c r="E20" s="38"/>
     </row>
     <row r="21">
-      <c r="B21" s="33">
+      <c r="B21" s="36">
         <f t="shared" si="1"/>
         <v>46127</v>
       </c>
-      <c r="C21" s="34">
+      <c r="C21" s="37">
         <v>27.5</v>
       </c>
-      <c r="D21" s="35"/>
-      <c r="E21" s="35"/>
+      <c r="D21" s="38"/>
+      <c r="E21" s="38"/>
     </row>
     <row r="22">
-      <c r="B22" s="33">
+      <c r="B22" s="36">
         <f t="shared" si="1"/>
         <v>46128</v>
       </c>
-      <c r="C22" s="34">
+      <c r="C22" s="37">
         <v>27.0</v>
       </c>
-      <c r="D22" s="35"/>
-      <c r="E22" s="35"/>
+      <c r="D22" s="38"/>
+      <c r="E22" s="38"/>
     </row>
     <row r="23">
-      <c r="B23" s="33">
+      <c r="B23" s="36">
         <f t="shared" si="1"/>
         <v>46129</v>
       </c>
-      <c r="C23" s="34">
+      <c r="C23" s="37">
         <v>26.5</v>
       </c>
-      <c r="D23" s="35"/>
-      <c r="E23" s="35"/>
+      <c r="D23" s="38"/>
+      <c r="E23" s="38"/>
     </row>
     <row r="24">
-      <c r="B24" s="33">
+      <c r="B24" s="36">
         <f t="shared" si="1"/>
         <v>46130</v>
       </c>
-      <c r="C24" s="34">
+      <c r="C24" s="37">
         <v>24.75</v>
       </c>
-      <c r="D24" s="35"/>
-      <c r="E24" s="35"/>
+      <c r="D24" s="38"/>
+      <c r="E24" s="38"/>
     </row>
     <row r="25">
-      <c r="B25" s="33">
+      <c r="B25" s="36">
         <f t="shared" si="1"/>
         <v>46131</v>
       </c>
-      <c r="C25" s="34">
+      <c r="C25" s="37">
         <v>25.375</v>
       </c>
-      <c r="D25" s="35"/>
-      <c r="E25" s="35"/>
+      <c r="D25" s="38"/>
+      <c r="E25" s="38"/>
     </row>
     <row r="26">
-      <c r="B26" s="33">
+      <c r="B26" s="36">
         <f t="shared" si="1"/>
         <v>46132</v>
       </c>
-      <c r="C26" s="34">
+      <c r="C26" s="37">
         <v>24.75</v>
       </c>
-      <c r="D26" s="35"/>
-      <c r="E26" s="35"/>
+      <c r="D26" s="38"/>
+      <c r="E26" s="38"/>
     </row>
     <row r="27">
-      <c r="B27" s="33">
+      <c r="B27" s="36">
         <f t="shared" si="1"/>
         <v>46133</v>
       </c>
-      <c r="C27" s="34">
+      <c r="C27" s="37">
         <v>24.25</v>
       </c>
-      <c r="D27" s="35"/>
-      <c r="E27" s="35"/>
+      <c r="D27" s="38"/>
+      <c r="E27" s="38"/>
     </row>
     <row r="28">
-      <c r="B28" s="33">
+      <c r="B28" s="36">
         <f t="shared" si="1"/>
         <v>46134</v>
       </c>
-      <c r="C28" s="34">
+      <c r="C28" s="37">
         <v>23.75</v>
       </c>
-      <c r="D28" s="35"/>
-      <c r="E28" s="35"/>
+      <c r="D28" s="38"/>
+      <c r="E28" s="38"/>
     </row>
     <row r="29">
-      <c r="B29" s="33">
+      <c r="B29" s="36">
         <f t="shared" si="1"/>
         <v>46135</v>
       </c>
-      <c r="C29" s="34">
+      <c r="C29" s="37">
         <v>23.25</v>
       </c>
-      <c r="D29" s="35"/>
-      <c r="E29" s="35"/>
+      <c r="D29" s="38"/>
+      <c r="E29" s="38"/>
     </row>
     <row r="30">
-      <c r="B30" s="33">
+      <c r="B30" s="36">
         <f t="shared" si="1"/>
         <v>46136</v>
       </c>
-      <c r="C30" s="34">
+      <c r="C30" s="37">
         <v>22.5</v>
       </c>
-      <c r="D30" s="35"/>
-      <c r="E30" s="35"/>
+      <c r="D30" s="38"/>
+      <c r="E30" s="38"/>
     </row>
     <row r="31">
-      <c r="B31" s="33">
+      <c r="B31" s="36">
         <f t="shared" si="1"/>
         <v>46137</v>
       </c>
-      <c r="C31" s="34">
+      <c r="C31" s="37">
         <v>22.0</v>
       </c>
-      <c r="D31" s="35"/>
-      <c r="E31" s="35"/>
+      <c r="D31" s="38"/>
+      <c r="E31" s="38"/>
     </row>
     <row r="32">
-      <c r="B32" s="33">
+      <c r="B32" s="36">
         <f t="shared" si="1"/>
         <v>46138</v>
       </c>
-      <c r="C32" s="34">
+      <c r="C32" s="37">
         <v>21.5</v>
       </c>
-      <c r="D32" s="35"/>
-      <c r="E32" s="35"/>
+      <c r="D32" s="38"/>
+      <c r="E32" s="38"/>
     </row>
     <row r="33">
-      <c r="B33" s="33">
+      <c r="B33" s="36">
         <f t="shared" si="1"/>
         <v>46139</v>
       </c>
-      <c r="C33" s="34">
+      <c r="C33" s="37">
         <v>21.0</v>
       </c>
-      <c r="D33" s="35"/>
-      <c r="E33" s="35"/>
+      <c r="D33" s="38"/>
+      <c r="E33" s="38"/>
     </row>
     <row r="34">
-      <c r="B34" s="33">
+      <c r="B34" s="36">
         <f t="shared" si="1"/>
         <v>46140</v>
       </c>
-      <c r="C34" s="34">
+      <c r="C34" s="37">
         <v>20.5</v>
       </c>
-      <c r="D34" s="35"/>
-      <c r="E34" s="35"/>
+      <c r="D34" s="38"/>
+      <c r="E34" s="38"/>
     </row>
     <row r="35">
-      <c r="B35" s="33">
+      <c r="B35" s="36">
         <f t="shared" si="1"/>
         <v>46141</v>
       </c>
-      <c r="C35" s="34">
+      <c r="C35" s="37">
         <v>19.5</v>
       </c>
-      <c r="D35" s="35"/>
-      <c r="E35" s="35"/>
+      <c r="D35" s="38"/>
+      <c r="E35" s="38"/>
     </row>
     <row r="36">
-      <c r="B36" s="33">
+      <c r="B36" s="36">
         <f t="shared" si="1"/>
         <v>46142</v>
       </c>
-      <c r="C36" s="34">
+      <c r="C36" s="37">
         <v>18.75</v>
       </c>
     </row>
     <row r="37">
       <c r="B37" s="2"/>
-      <c r="C37" s="31"/>
+      <c r="C37" s="34"/>
     </row>
     <row r="38">
       <c r="B38" s="2"/>
-      <c r="C38" s="31"/>
+      <c r="C38" s="34"/>
     </row>
     <row r="39">
       <c r="B39" s="2"/>
-      <c r="C39" s="31"/>
+      <c r="C39" s="34"/>
     </row>
     <row r="40">
       <c r="B40" s="2"/>
-      <c r="C40" s="31"/>
+      <c r="C40" s="34"/>
     </row>
     <row r="41">
       <c r="B41" s="2"/>
-      <c r="C41" s="31"/>
+      <c r="C41" s="34"/>
     </row>
     <row r="42">
       <c r="B42" s="2"/>
-      <c r="C42" s="31"/>
+      <c r="C42" s="34"/>
     </row>
     <row r="43">
       <c r="B43" s="2"/>
-      <c r="C43" s="31"/>
+      <c r="C43" s="34"/>
     </row>
     <row r="44">
       <c r="B44" s="2"/>
-      <c r="C44" s="31"/>
+      <c r="C44" s="34"/>
     </row>
     <row r="45">
       <c r="B45" s="2"/>
-      <c r="C45" s="31"/>
+      <c r="C45" s="34"/>
     </row>
     <row r="46">
       <c r="B46" s="2"/>
-      <c r="C46" s="31"/>
+      <c r="C46" s="34"/>
     </row>
     <row r="47">
       <c r="B47" s="2"/>
-      <c r="C47" s="31"/>
+      <c r="C47" s="34"/>
     </row>
     <row r="48">
       <c r="B48" s="2"/>
-      <c r="C48" s="31"/>
+      <c r="C48" s="34"/>
     </row>
     <row r="49">
       <c r="B49" s="2"/>
-      <c r="C49" s="31"/>
+      <c r="C49" s="34"/>
     </row>
     <row r="50">
       <c r="B50" s="2"/>
-      <c r="C50" s="31"/>
+      <c r="C50" s="34"/>
     </row>
     <row r="51">
       <c r="B51" s="2"/>
-      <c r="C51" s="31"/>
+      <c r="C51" s="34"/>
     </row>
     <row r="52">
       <c r="B52" s="2"/>
-      <c r="C52" s="31"/>
+      <c r="C52" s="34"/>
     </row>
     <row r="53">
       <c r="B53" s="2"/>
-      <c r="C53" s="31"/>
+      <c r="C53" s="34"/>
     </row>
     <row r="54">
       <c r="B54" s="2"/>
-      <c r="C54" s="31"/>
+      <c r="C54" s="34"/>
     </row>
     <row r="55">
       <c r="B55" s="2"/>
-      <c r="C55" s="31"/>
+      <c r="C55" s="34"/>
     </row>
     <row r="56">
       <c r="B56" s="2"/>
-      <c r="C56" s="31"/>
+      <c r="C56" s="34"/>
     </row>
     <row r="57">
       <c r="B57" s="2"/>
-      <c r="C57" s="31"/>
+      <c r="C57" s="34"/>
     </row>
     <row r="58">
       <c r="B58" s="2"/>
-      <c r="C58" s="31"/>
+      <c r="C58" s="34"/>
     </row>
     <row r="59">
       <c r="B59" s="2"/>
-      <c r="C59" s="31"/>
+      <c r="C59" s="34"/>
     </row>
     <row r="60">
       <c r="B60" s="2"/>
-      <c r="C60" s="31"/>
+      <c r="C60" s="34"/>
     </row>
     <row r="61">
       <c r="B61" s="2"/>
-      <c r="C61" s="31"/>
+      <c r="C61" s="34"/>
     </row>
     <row r="62">
       <c r="B62" s="2"/>
-      <c r="C62" s="31"/>
+      <c r="C62" s="34"/>
     </row>
     <row r="63">
       <c r="B63" s="2"/>
-      <c r="C63" s="31"/>
+      <c r="C63" s="34"/>
     </row>
     <row r="64">
       <c r="B64" s="2"/>
-      <c r="C64" s="31"/>
+      <c r="C64" s="34"/>
     </row>
     <row r="65">
       <c r="B65" s="2"/>
-      <c r="C65" s="31"/>
+      <c r="C65" s="34"/>
     </row>
     <row r="66">
       <c r="B66" s="2"/>
-      <c r="C66" s="31"/>
+      <c r="C66" s="34"/>
     </row>
     <row r="67">
       <c r="B67" s="2"/>
-      <c r="C67" s="31"/>
+      <c r="C67" s="34"/>
     </row>
     <row r="68">
       <c r="B68" s="2"/>
-      <c r="C68" s="31"/>
+      <c r="C68" s="34"/>
     </row>
     <row r="69">
       <c r="B69" s="2"/>
-      <c r="C69" s="31"/>
+      <c r="C69" s="34"/>
     </row>
     <row r="70">
       <c r="B70" s="2"/>
-      <c r="C70" s="31"/>
+      <c r="C70" s="34"/>
     </row>
     <row r="71">
       <c r="B71" s="2"/>
-      <c r="C71" s="31"/>
+      <c r="C71" s="34"/>
     </row>
     <row r="72">
       <c r="B72" s="2"/>
-      <c r="C72" s="31"/>
+      <c r="C72" s="34"/>
     </row>
     <row r="73">
       <c r="B73" s="2"/>
-      <c r="C73" s="31"/>
+      <c r="C73" s="34"/>
     </row>
     <row r="74">
       <c r="B74" s="2"/>
-      <c r="C74" s="31"/>
+      <c r="C74" s="34"/>
     </row>
     <row r="75">
       <c r="B75" s="2"/>
-      <c r="C75" s="31"/>
+      <c r="C75" s="34"/>
     </row>
     <row r="76">
       <c r="B76" s="2"/>
-      <c r="C76" s="31"/>
+      <c r="C76" s="34"/>
     </row>
     <row r="77">
       <c r="B77" s="2"/>
-      <c r="C77" s="31"/>
+      <c r="C77" s="34"/>
     </row>
     <row r="78">
       <c r="B78" s="2"/>
-      <c r="C78" s="31"/>
+      <c r="C78" s="34"/>
     </row>
     <row r="79">
       <c r="B79" s="2"/>
-      <c r="C79" s="31"/>
+      <c r="C79" s="34"/>
     </row>
     <row r="80">
       <c r="B80" s="2"/>
-      <c r="C80" s="31"/>
+      <c r="C80" s="34"/>
     </row>
     <row r="81">
       <c r="B81" s="2"/>
-      <c r="C81" s="31"/>
+      <c r="C81" s="34"/>
     </row>
     <row r="82">
       <c r="B82" s="2"/>
-      <c r="C82" s="31"/>
+      <c r="C82" s="34"/>
     </row>
     <row r="83">
       <c r="B83" s="2"/>
-      <c r="C83" s="31"/>
+      <c r="C83" s="34"/>
     </row>
     <row r="84">
       <c r="B84" s="2"/>
-      <c r="C84" s="31"/>
+      <c r="C84" s="34"/>
     </row>
     <row r="85">
       <c r="B85" s="2"/>
-      <c r="C85" s="31"/>
+      <c r="C85" s="34"/>
     </row>
     <row r="86">
       <c r="B86" s="2"/>
-      <c r="C86" s="31"/>
+      <c r="C86" s="34"/>
     </row>
     <row r="87">
       <c r="B87" s="2"/>
-      <c r="C87" s="31"/>
+      <c r="C87" s="34"/>
     </row>
     <row r="88">
       <c r="B88" s="2"/>
-      <c r="C88" s="31"/>
+      <c r="C88" s="34"/>
     </row>
     <row r="89">
       <c r="B89" s="2"/>
-      <c r="C89" s="31"/>
+      <c r="C89" s="34"/>
     </row>
     <row r="90">
       <c r="B90" s="2"/>
-      <c r="C90" s="31"/>
+      <c r="C90" s="34"/>
     </row>
     <row r="91">
       <c r="B91" s="2"/>
-      <c r="C91" s="31"/>
+      <c r="C91" s="34"/>
     </row>
     <row r="92">
       <c r="B92" s="2"/>
-      <c r="C92" s="31"/>
+      <c r="C92" s="34"/>
     </row>
     <row r="93">
       <c r="B93" s="2"/>
-      <c r="C93" s="31"/>
+      <c r="C93" s="34"/>
     </row>
     <row r="94">
       <c r="B94" s="2"/>
-      <c r="C94" s="31"/>
+      <c r="C94" s="34"/>
     </row>
     <row r="95">
       <c r="B95" s="2"/>
-      <c r="C95" s="31"/>
+      <c r="C95" s="34"/>
     </row>
     <row r="96">
       <c r="B96" s="2"/>
-      <c r="C96" s="31"/>
+      <c r="C96" s="34"/>
     </row>
     <row r="97">
       <c r="B97" s="2"/>
-      <c r="C97" s="31"/>
+      <c r="C97" s="34"/>
     </row>
     <row r="98">
       <c r="B98" s="2"/>
-      <c r="C98" s="31"/>
+      <c r="C98" s="34"/>
     </row>
     <row r="99">
       <c r="B99" s="2"/>
-      <c r="C99" s="31"/>
+      <c r="C99" s="34"/>
     </row>
     <row r="100">
       <c r="B100" s="2"/>
-      <c r="C100" s="31"/>
+      <c r="C100" s="34"/>
     </row>
     <row r="101">
       <c r="B101" s="2"/>
-      <c r="C101" s="31"/>
+      <c r="C101" s="34"/>
     </row>
     <row r="102">
       <c r="B102" s="2"/>
-      <c r="C102" s="31"/>
+      <c r="C102" s="34"/>
     </row>
     <row r="103">
       <c r="B103" s="2"/>
-      <c r="C103" s="31"/>
+      <c r="C103" s="34"/>
     </row>
     <row r="104">
       <c r="B104" s="2"/>
-      <c r="C104" s="31"/>
+      <c r="C104" s="34"/>
     </row>
     <row r="105">
       <c r="B105" s="2"/>
-      <c r="C105" s="31"/>
+      <c r="C105" s="34"/>
     </row>
     <row r="106">
       <c r="B106" s="2"/>
-      <c r="C106" s="31"/>
+      <c r="C106" s="34"/>
     </row>
     <row r="107">
       <c r="B107" s="2"/>
-      <c r="C107" s="31"/>
+      <c r="C107" s="34"/>
     </row>
     <row r="108">
       <c r="B108" s="2"/>
-      <c r="C108" s="31"/>
+      <c r="C108" s="34"/>
     </row>
     <row r="109">
       <c r="B109" s="2"/>
-      <c r="C109" s="31"/>
+      <c r="C109" s="34"/>
     </row>
     <row r="110">
       <c r="B110" s="2"/>
-      <c r="C110" s="31"/>
+      <c r="C110" s="34"/>
     </row>
     <row r="111">
       <c r="B111" s="2"/>
-      <c r="C111" s="31"/>
+      <c r="C111" s="34"/>
     </row>
     <row r="112">
       <c r="B112" s="2"/>
-      <c r="C112" s="31"/>
+      <c r="C112" s="34"/>
     </row>
     <row r="113">
       <c r="B113" s="2"/>
-      <c r="C113" s="31"/>
+      <c r="C113" s="34"/>
     </row>
     <row r="114">
       <c r="B114" s="2"/>
-      <c r="C114" s="31"/>
+      <c r="C114" s="34"/>
     </row>
     <row r="115">
       <c r="B115" s="2"/>
-      <c r="C115" s="31"/>
+      <c r="C115" s="34"/>
     </row>
     <row r="116">
       <c r="B116" s="2"/>
-      <c r="C116" s="31"/>
+      <c r="C116" s="34"/>
     </row>
     <row r="117">
       <c r="B117" s="2"/>
-      <c r="C117" s="31"/>
+      <c r="C117" s="34"/>
     </row>
     <row r="118">
       <c r="B118" s="2"/>
-      <c r="C118" s="31"/>
+      <c r="C118" s="34"/>
     </row>
     <row r="119">
       <c r="B119" s="2"/>
-      <c r="C119" s="31"/>
+      <c r="C119" s="34"/>
     </row>
     <row r="120">
       <c r="B120" s="2"/>
-      <c r="C120" s="31"/>
+      <c r="C120" s="34"/>
     </row>
     <row r="121">
       <c r="B121" s="2"/>
-      <c r="C121" s="31"/>
+      <c r="C121" s="34"/>
     </row>
     <row r="122">
       <c r="B122" s="2"/>
-      <c r="C122" s="31"/>
+      <c r="C122" s="34"/>
     </row>
     <row r="123">
       <c r="B123" s="2"/>
-      <c r="C123" s="31"/>
+      <c r="C123" s="34"/>
     </row>
     <row r="124">
       <c r="B124" s="2"/>
-      <c r="C124" s="31"/>
+      <c r="C124" s="34"/>
     </row>
     <row r="125">
       <c r="B125" s="2"/>
-      <c r="C125" s="31"/>
+      <c r="C125" s="34"/>
     </row>
     <row r="126">
       <c r="B126" s="2"/>
-      <c r="C126" s="31"/>
+      <c r="C126" s="34"/>
     </row>
     <row r="127">
       <c r="B127" s="2"/>
-      <c r="C127" s="31"/>
+      <c r="C127" s="34"/>
     </row>
     <row r="128">
       <c r="B128" s="2"/>
-      <c r="C128" s="31"/>
+      <c r="C128" s="34"/>
     </row>
     <row r="129">
       <c r="B129" s="2"/>
-      <c r="C129" s="31"/>
+      <c r="C129" s="34"/>
     </row>
     <row r="130">
       <c r="B130" s="2"/>
-      <c r="C130" s="31"/>
+      <c r="C130" s="34"/>
     </row>
     <row r="131">
       <c r="B131" s="2"/>
-      <c r="C131" s="31"/>
+      <c r="C131" s="34"/>
     </row>
     <row r="132">
       <c r="B132" s="2"/>
-      <c r="C132" s="31"/>
+      <c r="C132" s="34"/>
     </row>
     <row r="133">
       <c r="B133" s="2"/>
-      <c r="C133" s="31"/>
+      <c r="C133" s="34"/>
     </row>
     <row r="134">
       <c r="B134" s="2"/>
-      <c r="C134" s="31"/>
+      <c r="C134" s="34"/>
     </row>
     <row r="135">
       <c r="B135" s="2"/>
-      <c r="C135" s="31"/>
+      <c r="C135" s="34"/>
     </row>
     <row r="136">
       <c r="B136" s="2"/>
-      <c r="C136" s="31"/>
+      <c r="C136" s="34"/>
     </row>
     <row r="137">
       <c r="B137" s="2"/>
-      <c r="C137" s="31"/>
+      <c r="C137" s="34"/>
     </row>
     <row r="138">
       <c r="B138" s="2"/>
-      <c r="C138" s="31"/>
+      <c r="C138" s="34"/>
     </row>
     <row r="139">
       <c r="B139" s="2"/>
-      <c r="C139" s="31"/>
+      <c r="C139" s="34"/>
     </row>
     <row r="140">
       <c r="B140" s="2"/>
-      <c r="C140" s="31"/>
+      <c r="C140" s="34"/>
     </row>
     <row r="141">
       <c r="B141" s="2"/>
-      <c r="C141" s="31"/>
+      <c r="C141" s="34"/>
     </row>
     <row r="142">
       <c r="B142" s="2"/>
-      <c r="C142" s="31"/>
+      <c r="C142" s="34"/>
     </row>
     <row r="143">
       <c r="B143" s="2"/>
-      <c r="C143" s="31"/>
+      <c r="C143" s="34"/>
     </row>
     <row r="144">
       <c r="B144" s="2"/>
-      <c r="C144" s="31"/>
+      <c r="C144" s="34"/>
     </row>
     <row r="145">
       <c r="B145" s="2"/>
-      <c r="C145" s="31"/>
+      <c r="C145" s="34"/>
     </row>
     <row r="146">
       <c r="B146" s="2"/>
-      <c r="C146" s="31"/>
+      <c r="C146" s="34"/>
     </row>
     <row r="147">
       <c r="B147" s="2"/>
-      <c r="C147" s="31"/>
+      <c r="C147" s="34"/>
     </row>
     <row r="148">
       <c r="B148" s="2"/>
-      <c r="C148" s="31"/>
+      <c r="C148" s="34"/>
     </row>
     <row r="149">
       <c r="B149" s="2"/>
-      <c r="C149" s="31"/>
+      <c r="C149" s="34"/>
     </row>
     <row r="150">
       <c r="B150" s="2"/>
-      <c r="C150" s="31"/>
+      <c r="C150" s="34"/>
     </row>
     <row r="151">
       <c r="B151" s="2"/>
-      <c r="C151" s="31"/>
+      <c r="C151" s="34"/>
     </row>
     <row r="152">
       <c r="B152" s="2"/>
-      <c r="C152" s="31"/>
+      <c r="C152" s="34"/>
     </row>
     <row r="153">
       <c r="B153" s="2"/>
-      <c r="C153" s="31"/>
+      <c r="C153" s="34"/>
     </row>
     <row r="154">
       <c r="B154" s="2"/>
-      <c r="C154" s="31"/>
+      <c r="C154" s="34"/>
     </row>
     <row r="155">
       <c r="B155" s="2"/>
-      <c r="C155" s="31"/>
+      <c r="C155" s="34"/>
     </row>
     <row r="156">
       <c r="B156" s="2"/>
-      <c r="C156" s="31"/>
+      <c r="C156" s="34"/>
     </row>
     <row r="157">
       <c r="B157" s="2"/>
-      <c r="C157" s="31"/>
+      <c r="C157" s="34"/>
     </row>
     <row r="158">
       <c r="B158" s="2"/>
-      <c r="C158" s="31"/>
+      <c r="C158" s="34"/>
     </row>
     <row r="159">
       <c r="B159" s="2"/>
-      <c r="C159" s="31"/>
+      <c r="C159" s="34"/>
     </row>
     <row r="160">
       <c r="B160" s="2"/>
-      <c r="C160" s="31"/>
+      <c r="C160" s="34"/>
     </row>
     <row r="161">
       <c r="B161" s="2"/>
-      <c r="C161" s="31"/>
+      <c r="C161" s="34"/>
     </row>
     <row r="162">
       <c r="B162" s="2"/>
-      <c r="C162" s="31"/>
+      <c r="C162" s="34"/>
     </row>
     <row r="163">
       <c r="B163" s="2"/>
-      <c r="C163" s="31"/>
+      <c r="C163" s="34"/>
     </row>
     <row r="164">
       <c r="B164" s="2"/>
-      <c r="C164" s="31"/>
+      <c r="C164" s="34"/>
     </row>
     <row r="165">
       <c r="B165" s="2"/>
-      <c r="C165" s="31"/>
+      <c r="C165" s="34"/>
     </row>
     <row r="166">
       <c r="B166" s="2"/>
-      <c r="C166" s="31"/>
+      <c r="C166" s="34"/>
     </row>
     <row r="167">
       <c r="B167" s="2"/>
-      <c r="C167" s="31"/>
+      <c r="C167" s="34"/>
     </row>
     <row r="168">
       <c r="B168" s="2"/>
-      <c r="C168" s="31"/>
+      <c r="C168" s="34"/>
     </row>
     <row r="169">
       <c r="B169" s="2"/>
-      <c r="C169" s="31"/>
+      <c r="C169" s="34"/>
     </row>
     <row r="170">
       <c r="B170" s="2"/>
-      <c r="C170" s="31"/>
+      <c r="C170" s="34"/>
     </row>
     <row r="171">
       <c r="B171" s="2"/>
-      <c r="C171" s="31"/>
+      <c r="C171" s="34"/>
     </row>
     <row r="172">
       <c r="B172" s="2"/>
-      <c r="C172" s="31"/>
+      <c r="C172" s="34"/>
     </row>
     <row r="173">
       <c r="B173" s="2"/>
-      <c r="C173" s="31"/>
+      <c r="C173" s="34"/>
     </row>
     <row r="174">
       <c r="B174" s="2"/>
-      <c r="C174" s="31"/>
+      <c r="C174" s="34"/>
     </row>
     <row r="175">
       <c r="B175" s="2"/>
-      <c r="C175" s="31"/>
+      <c r="C175" s="34"/>
     </row>
     <row r="176">
       <c r="B176" s="2"/>
-      <c r="C176" s="31"/>
+      <c r="C176" s="34"/>
     </row>
     <row r="177">
       <c r="B177" s="2"/>
-      <c r="C177" s="31"/>
+      <c r="C177" s="34"/>
     </row>
     <row r="178">
       <c r="B178" s="2"/>
-      <c r="C178" s="31"/>
+      <c r="C178" s="34"/>
     </row>
     <row r="179">
       <c r="B179" s="2"/>
-      <c r="C179" s="31"/>
+      <c r="C179" s="34"/>
     </row>
     <row r="180">
       <c r="B180" s="2"/>
-      <c r="C180" s="31"/>
+      <c r="C180" s="34"/>
     </row>
     <row r="181">
       <c r="B181" s="2"/>
-      <c r="C181" s="31"/>
+      <c r="C181" s="34"/>
     </row>
     <row r="182">
       <c r="B182" s="2"/>
-      <c r="C182" s="31"/>
+      <c r="C182" s="34"/>
     </row>
     <row r="183">
       <c r="B183" s="2"/>
-      <c r="C183" s="31"/>
+      <c r="C183" s="34"/>
     </row>
     <row r="184">
       <c r="B184" s="2"/>
-      <c r="C184" s="31"/>
+      <c r="C184" s="34"/>
     </row>
     <row r="185">
       <c r="B185" s="2"/>
-      <c r="C185" s="31"/>
+      <c r="C185" s="34"/>
     </row>
     <row r="186">
       <c r="B186" s="2"/>
-      <c r="C186" s="31"/>
+      <c r="C186" s="34"/>
     </row>
     <row r="187">
       <c r="B187" s="2"/>
-      <c r="C187" s="31"/>
+      <c r="C187" s="34"/>
     </row>
     <row r="188">
       <c r="B188" s="2"/>
-      <c r="C188" s="31"/>
+      <c r="C188" s="34"/>
     </row>
     <row r="189">
       <c r="B189" s="2"/>
-      <c r="C189" s="31"/>
+      <c r="C189" s="34"/>
     </row>
     <row r="190">
       <c r="B190" s="2"/>
-      <c r="C190" s="31"/>
+      <c r="C190" s="34"/>
     </row>
     <row r="191">
       <c r="B191" s="2"/>
-      <c r="C191" s="31"/>
+      <c r="C191" s="34"/>
     </row>
     <row r="192">
       <c r="B192" s="2"/>
-      <c r="C192" s="31"/>
+      <c r="C192" s="34"/>
     </row>
     <row r="193">
       <c r="B193" s="2"/>
-      <c r="C193" s="31"/>
+      <c r="C193" s="34"/>
     </row>
     <row r="194">
       <c r="B194" s="2"/>
-      <c r="C194" s="31"/>
+      <c r="C194" s="34"/>
     </row>
     <row r="195">
       <c r="B195" s="2"/>
-      <c r="C195" s="31"/>
+      <c r="C195" s="34"/>
     </row>
     <row r="196">
       <c r="B196" s="2"/>
-      <c r="C196" s="31"/>
+      <c r="C196" s="34"/>
     </row>
     <row r="197">
       <c r="B197" s="2"/>
-      <c r="C197" s="31"/>
+      <c r="C197" s="34"/>
     </row>
     <row r="198">
       <c r="B198" s="2"/>
-      <c r="C198" s="31"/>
+      <c r="C198" s="34"/>
     </row>
     <row r="199">
       <c r="B199" s="2"/>
-      <c r="C199" s="31"/>
+      <c r="C199" s="34"/>
     </row>
     <row r="200">
       <c r="B200" s="2"/>
-      <c r="C200" s="31"/>
+      <c r="C200" s="34"/>
     </row>
     <row r="201">
       <c r="B201" s="2"/>
-      <c r="C201" s="31"/>
+      <c r="C201" s="34"/>
     </row>
     <row r="202">
       <c r="B202" s="2"/>
-      <c r="C202" s="31"/>
+      <c r="C202" s="34"/>
     </row>
     <row r="203">
       <c r="B203" s="2"/>
-      <c r="C203" s="31"/>
+      <c r="C203" s="34"/>
     </row>
     <row r="204">
       <c r="B204" s="2"/>
-      <c r="C204" s="31"/>
+      <c r="C204" s="34"/>
     </row>
     <row r="205">
       <c r="B205" s="2"/>
-      <c r="C205" s="31"/>
+      <c r="C205" s="34"/>
     </row>
     <row r="206">
       <c r="B206" s="2"/>
-      <c r="C206" s="31"/>
+      <c r="C206" s="34"/>
     </row>
     <row r="207">
       <c r="B207" s="2"/>
-      <c r="C207" s="31"/>
+      <c r="C207" s="34"/>
     </row>
     <row r="208">
       <c r="B208" s="2"/>
-      <c r="C208" s="31"/>
+      <c r="C208" s="34"/>
     </row>
     <row r="209">
       <c r="B209" s="2"/>
-      <c r="C209" s="31"/>
+      <c r="C209" s="34"/>
     </row>
     <row r="210">
       <c r="B210" s="2"/>
-      <c r="C210" s="31"/>
+      <c r="C210" s="34"/>
     </row>
     <row r="211">
       <c r="B211" s="2"/>
-      <c r="C211" s="31"/>
+      <c r="C211" s="34"/>
     </row>
     <row r="212">
       <c r="B212" s="2"/>
-      <c r="C212" s="31"/>
+      <c r="C212" s="34"/>
     </row>
     <row r="213">
       <c r="B213" s="2"/>
-      <c r="C213" s="31"/>
+      <c r="C213" s="34"/>
     </row>
     <row r="214">
       <c r="B214" s="2"/>
-      <c r="C214" s="31"/>
+      <c r="C214" s="34"/>
     </row>
     <row r="215">
       <c r="B215" s="2"/>
-      <c r="C215" s="31"/>
+      <c r="C215" s="34"/>
     </row>
     <row r="216">
       <c r="B216" s="2"/>
-      <c r="C216" s="31"/>
+      <c r="C216" s="34"/>
     </row>
     <row r="217">
       <c r="B217" s="2"/>
-      <c r="C217" s="31"/>
+      <c r="C217" s="34"/>
     </row>
     <row r="218">
       <c r="B218" s="2"/>
-      <c r="C218" s="31"/>
+      <c r="C218" s="34"/>
     </row>
     <row r="219">
       <c r="B219" s="2"/>
-      <c r="C219" s="31"/>
+      <c r="C219" s="34"/>
     </row>
     <row r="220">
       <c r="B220" s="2"/>
-      <c r="C220" s="31"/>
+      <c r="C220" s="34"/>
     </row>
     <row r="221">
       <c r="B221" s="2"/>
-      <c r="C221" s="31"/>
+      <c r="C221" s="34"/>
     </row>
     <row r="222">
       <c r="B222" s="2"/>
-      <c r="C222" s="31"/>
+      <c r="C222" s="34"/>
     </row>
     <row r="223">
       <c r="B223" s="2"/>
-      <c r="C223" s="31"/>
+      <c r="C223" s="34"/>
     </row>
     <row r="224">
       <c r="B224" s="2"/>
-      <c r="C224" s="31"/>
+      <c r="C224" s="34"/>
     </row>
     <row r="225">
       <c r="B225" s="2"/>
-      <c r="C225" s="31"/>
+      <c r="C225" s="34"/>
     </row>
     <row r="226">
       <c r="B226" s="2"/>
-      <c r="C226" s="31"/>
+      <c r="C226" s="34"/>
     </row>
     <row r="227">
       <c r="B227" s="2"/>
-      <c r="C227" s="31"/>
+      <c r="C227" s="34"/>
     </row>
     <row r="228">
       <c r="B228" s="2"/>
-      <c r="C228" s="31"/>
+      <c r="C228" s="34"/>
     </row>
     <row r="229">
       <c r="B229" s="2"/>
-      <c r="C229" s="31"/>
+      <c r="C229" s="34"/>
     </row>
     <row r="230">
       <c r="B230" s="2"/>
-      <c r="C230" s="31"/>
+      <c r="C230" s="34"/>
     </row>
     <row r="231">
       <c r="B231" s="2"/>
-      <c r="C231" s="31"/>
+      <c r="C231" s="34"/>
     </row>
     <row r="232">
       <c r="B232" s="2"/>
-      <c r="C232" s="31"/>
+      <c r="C232" s="34"/>
     </row>
     <row r="233">
       <c r="B233" s="2"/>
-      <c r="C233" s="31"/>
+      <c r="C233" s="34"/>
     </row>
     <row r="234">
       <c r="B234" s="2"/>
-      <c r="C234" s="31"/>
+      <c r="C234" s="34"/>
     </row>
     <row r="235">
       <c r="B235" s="2"/>
-      <c r="C235" s="31"/>
+      <c r="C235" s="34"/>
     </row>
     <row r="236">
       <c r="B236" s="2"/>
-      <c r="C236" s="31"/>
+      <c r="C236" s="34"/>
     </row>
     <row r="237">
       <c r="B237" s="2"/>
-      <c r="C237" s="31"/>
+      <c r="C237" s="34"/>
     </row>
     <row r="238">
       <c r="B238" s="2"/>
-      <c r="C238" s="31"/>
+      <c r="C238" s="34"/>
     </row>
     <row r="239">
       <c r="B239" s="2"/>
-      <c r="C239" s="31"/>
+      <c r="C239" s="34"/>
     </row>
     <row r="240">
       <c r="B240" s="2"/>
-      <c r="C240" s="31"/>
+      <c r="C240" s="34"/>
     </row>
     <row r="241">
       <c r="B241" s="2"/>
-      <c r="C241" s="31"/>
+      <c r="C241" s="34"/>
     </row>
     <row r="242">
       <c r="B242" s="2"/>
-      <c r="C242" s="31"/>
+      <c r="C242" s="34"/>
     </row>
     <row r="243">
       <c r="B243" s="2"/>
-      <c r="C243" s="31"/>
+      <c r="C243" s="34"/>
     </row>
     <row r="244">
       <c r="B244" s="2"/>
-      <c r="C244" s="31"/>
+      <c r="C244" s="34"/>
     </row>
     <row r="245">
       <c r="B245" s="2"/>
-      <c r="C245" s="31"/>
+      <c r="C245" s="34"/>
     </row>
     <row r="246">
       <c r="B246" s="2"/>
-      <c r="C246" s="31"/>
+      <c r="C246" s="34"/>
     </row>
     <row r="247">
       <c r="B247" s="2"/>
-      <c r="C247" s="31"/>
+      <c r="C247" s="34"/>
     </row>
     <row r="248">
       <c r="B248" s="2"/>
-      <c r="C248" s="31"/>
+      <c r="C248" s="34"/>
     </row>
     <row r="249">
       <c r="B249" s="2"/>
-      <c r="C249" s="31"/>
+      <c r="C249" s="34"/>
     </row>
     <row r="250">
       <c r="B250" s="2"/>
-      <c r="C250" s="31"/>
+      <c r="C250" s="34"/>
     </row>
     <row r="251">
       <c r="B251" s="2"/>
-      <c r="C251" s="31"/>
+      <c r="C251" s="34"/>
     </row>
     <row r="252">
       <c r="B252" s="2"/>
-      <c r="C252" s="31"/>
+      <c r="C252" s="34"/>
     </row>
     <row r="253">
       <c r="B253" s="2"/>
-      <c r="C253" s="31"/>
+      <c r="C253" s="34"/>
     </row>
     <row r="254">
       <c r="B254" s="2"/>
-      <c r="C254" s="31"/>
+      <c r="C254" s="34"/>
     </row>
     <row r="255">
       <c r="B255" s="2"/>
-      <c r="C255" s="31"/>
+      <c r="C255" s="34"/>
     </row>
     <row r="256">
       <c r="B256" s="2"/>
-      <c r="C256" s="31"/>
+      <c r="C256" s="34"/>
     </row>
     <row r="257">
       <c r="B257" s="2"/>
-      <c r="C257" s="31"/>
+      <c r="C257" s="34"/>
     </row>
     <row r="258">
       <c r="B258" s="2"/>
-      <c r="C258" s="31"/>
+      <c r="C258" s="34"/>
     </row>
     <row r="259">
       <c r="B259" s="2"/>
-      <c r="C259" s="31"/>
+      <c r="C259" s="34"/>
     </row>
     <row r="260">
       <c r="B260" s="2"/>
-      <c r="C260" s="31"/>
+      <c r="C260" s="34"/>
     </row>
     <row r="261">
       <c r="B261" s="2"/>
-      <c r="C261" s="31"/>
+      <c r="C261" s="34"/>
     </row>
     <row r="262">
       <c r="B262" s="2"/>
-      <c r="C262" s="31"/>
+      <c r="C262" s="34"/>
     </row>
     <row r="263">
       <c r="B263" s="2"/>
-      <c r="C263" s="31"/>
+      <c r="C263" s="34"/>
     </row>
     <row r="264">
       <c r="B264" s="2"/>
-      <c r="C264" s="31"/>
+      <c r="C264" s="34"/>
     </row>
     <row r="265">
       <c r="B265" s="2"/>
-      <c r="C265" s="31"/>
+      <c r="C265" s="34"/>
     </row>
     <row r="266">
       <c r="B266" s="2"/>
-      <c r="C266" s="31"/>
+      <c r="C266" s="34"/>
     </row>
     <row r="267">
       <c r="B267" s="2"/>
-      <c r="C267" s="31"/>
+      <c r="C267" s="34"/>
     </row>
     <row r="268">
       <c r="B268" s="2"/>
-      <c r="C268" s="31"/>
+      <c r="C268" s="34"/>
     </row>
     <row r="269">
       <c r="B269" s="2"/>
-      <c r="C269" s="31"/>
+      <c r="C269" s="34"/>
     </row>
     <row r="270">
       <c r="B270" s="2"/>
-      <c r="C270" s="31"/>
+      <c r="C270" s="34"/>
     </row>
     <row r="271">
       <c r="B271" s="2"/>
-      <c r="C271" s="31"/>
+      <c r="C271" s="34"/>
     </row>
     <row r="272">
       <c r="B272" s="2"/>
-      <c r="C272" s="31"/>
+      <c r="C272" s="34"/>
     </row>
     <row r="273">
       <c r="B273" s="2"/>
-      <c r="C273" s="31"/>
+      <c r="C273" s="34"/>
     </row>
     <row r="274">
       <c r="B274" s="2"/>
-      <c r="C274" s="31"/>
+      <c r="C274" s="34"/>
     </row>
     <row r="275">
       <c r="B275" s="2"/>
-      <c r="C275" s="31"/>
+      <c r="C275" s="34"/>
     </row>
     <row r="276">
       <c r="B276" s="2"/>
-      <c r="C276" s="31"/>
+      <c r="C276" s="34"/>
     </row>
     <row r="277">
       <c r="B277" s="2"/>
-      <c r="C277" s="31"/>
+      <c r="C277" s="34"/>
     </row>
     <row r="278">
       <c r="B278" s="2"/>
-      <c r="C278" s="31"/>
+      <c r="C278" s="34"/>
     </row>
     <row r="279">
       <c r="B279" s="2"/>
-      <c r="C279" s="31"/>
+      <c r="C279" s="34"/>
     </row>
     <row r="280">
       <c r="B280" s="2"/>
-      <c r="C280" s="31"/>
+      <c r="C280" s="34"/>
     </row>
     <row r="281">
       <c r="B281" s="2"/>
-      <c r="C281" s="31"/>
+      <c r="C281" s="34"/>
     </row>
     <row r="282">
       <c r="B282" s="2"/>
-      <c r="C282" s="31"/>
+      <c r="C282" s="34"/>
     </row>
     <row r="283">
       <c r="B283" s="2"/>
-      <c r="C283" s="31"/>
+      <c r="C283" s="34"/>
     </row>
     <row r="284">
       <c r="B284" s="2"/>
-      <c r="C284" s="31"/>
+      <c r="C284" s="34"/>
     </row>
     <row r="285">
       <c r="B285" s="2"/>
-      <c r="C285" s="31"/>
+      <c r="C285" s="34"/>
     </row>
     <row r="286">
       <c r="B286" s="2"/>
-      <c r="C286" s="31"/>
+      <c r="C286" s="34"/>
     </row>
     <row r="287">
       <c r="B287" s="2"/>
-      <c r="C287" s="31"/>
+      <c r="C287" s="34"/>
     </row>
     <row r="288">
       <c r="B288" s="2"/>
-      <c r="C288" s="31"/>
+      <c r="C288" s="34"/>
     </row>
     <row r="289">
       <c r="B289" s="2"/>
-      <c r="C289" s="31"/>
+      <c r="C289" s="34"/>
     </row>
     <row r="290">
       <c r="B290" s="2"/>
-      <c r="C290" s="31"/>
+      <c r="C290" s="34"/>
     </row>
     <row r="291">
       <c r="B291" s="2"/>
-      <c r="C291" s="31"/>
+      <c r="C291" s="34"/>
     </row>
     <row r="292">
       <c r="B292" s="2"/>
-      <c r="C292" s="31"/>
+      <c r="C292" s="34"/>
     </row>
     <row r="293">
       <c r="B293" s="2"/>
-      <c r="C293" s="31"/>
+      <c r="C293" s="34"/>
     </row>
     <row r="294">
       <c r="B294" s="2"/>
-      <c r="C294" s="31"/>
+      <c r="C294" s="34"/>
     </row>
     <row r="295">
       <c r="B295" s="2"/>
-      <c r="C295" s="31"/>
+      <c r="C295" s="34"/>
     </row>
     <row r="296">
       <c r="B296" s="2"/>
-      <c r="C296" s="31"/>
+      <c r="C296" s="34"/>
     </row>
     <row r="297">
       <c r="B297" s="2"/>
-      <c r="C297" s="31"/>
+      <c r="C297" s="34"/>
     </row>
     <row r="298">
       <c r="B298" s="2"/>
-      <c r="C298" s="31"/>
+      <c r="C298" s="34"/>
     </row>
     <row r="299">
       <c r="B299" s="2"/>
-      <c r="C299" s="31"/>
+      <c r="C299" s="34"/>
     </row>
     <row r="300">
       <c r="B300" s="2"/>
-      <c r="C300" s="31"/>
+      <c r="C300" s="34"/>
     </row>
     <row r="301">
       <c r="B301" s="2"/>
-      <c r="C301" s="31"/>
+      <c r="C301" s="34"/>
     </row>
     <row r="302">
       <c r="B302" s="2"/>
-      <c r="C302" s="31"/>
+      <c r="C302" s="34"/>
     </row>
     <row r="303">
       <c r="B303" s="2"/>
-      <c r="C303" s="31"/>
+      <c r="C303" s="34"/>
     </row>
     <row r="304">
       <c r="B304" s="2"/>
-      <c r="C304" s="31"/>
+      <c r="C304" s="34"/>
     </row>
     <row r="305">
       <c r="B305" s="2"/>
-      <c r="C305" s="31"/>
+      <c r="C305" s="34"/>
     </row>
     <row r="306">
       <c r="B306" s="2"/>
-      <c r="C306" s="31"/>
+      <c r="C306" s="34"/>
     </row>
     <row r="307">
       <c r="B307" s="2"/>
-      <c r="C307" s="31"/>
+      <c r="C307" s="34"/>
     </row>
     <row r="308">
       <c r="B308" s="2"/>
-      <c r="C308" s="31"/>
+      <c r="C308" s="34"/>
     </row>
     <row r="309">
       <c r="B309" s="2"/>
-      <c r="C309" s="31"/>
+      <c r="C309" s="34"/>
     </row>
     <row r="310">
       <c r="B310" s="2"/>
-      <c r="C310" s="31"/>
+      <c r="C310" s="34"/>
     </row>
     <row r="311">
       <c r="B311" s="2"/>
-      <c r="C311" s="31"/>
+      <c r="C311" s="34"/>
     </row>
     <row r="312">
       <c r="B312" s="2"/>
-      <c r="C312" s="31"/>
+      <c r="C312" s="34"/>
     </row>
     <row r="313">
       <c r="B313" s="2"/>
-      <c r="C313" s="31"/>
+      <c r="C313" s="34"/>
     </row>
     <row r="314">
       <c r="B314" s="2"/>
-      <c r="C314" s="31"/>
+      <c r="C314" s="34"/>
     </row>
     <row r="315">
       <c r="B315" s="2"/>
-      <c r="C315" s="31"/>
+      <c r="C315" s="34"/>
     </row>
     <row r="316">
       <c r="B316" s="2"/>
-      <c r="C316" s="31"/>
+      <c r="C316" s="34"/>
     </row>
     <row r="317">
       <c r="B317" s="2"/>
-      <c r="C317" s="31"/>
+      <c r="C317" s="34"/>
     </row>
     <row r="318">
       <c r="B318" s="2"/>
-      <c r="C318" s="31"/>
+      <c r="C318" s="34"/>
     </row>
     <row r="319">
       <c r="B319" s="2"/>
-      <c r="C319" s="31"/>
+      <c r="C319" s="34"/>
     </row>
     <row r="320">
       <c r="B320" s="2"/>
-      <c r="C320" s="31"/>
+      <c r="C320" s="34"/>
     </row>
     <row r="321">
       <c r="B321" s="2"/>
-      <c r="C321" s="31"/>
+      <c r="C321" s="34"/>
     </row>
     <row r="322">
       <c r="B322" s="2"/>
-      <c r="C322" s="31"/>
+      <c r="C322" s="34"/>
     </row>
     <row r="323">
       <c r="B323" s="2"/>
-      <c r="C323" s="31"/>
+      <c r="C323" s="34"/>
     </row>
     <row r="324">
       <c r="B324" s="2"/>
-      <c r="C324" s="31"/>
+      <c r="C324" s="34"/>
     </row>
     <row r="325">
       <c r="B325" s="2"/>
-      <c r="C325" s="31"/>
+      <c r="C325" s="34"/>
     </row>
     <row r="326">
       <c r="B326" s="2"/>
-      <c r="C326" s="31"/>
+      <c r="C326" s="34"/>
     </row>
     <row r="327">
       <c r="B327" s="2"/>
-      <c r="C327" s="31"/>
+      <c r="C327" s="34"/>
     </row>
     <row r="328">
       <c r="B328" s="2"/>
-      <c r="C328" s="31"/>
+      <c r="C328" s="34"/>
     </row>
     <row r="329">
       <c r="B329" s="2"/>
-      <c r="C329" s="31"/>
+      <c r="C329" s="34"/>
     </row>
     <row r="330">
       <c r="B330" s="2"/>
-      <c r="C330" s="31"/>
+      <c r="C330" s="34"/>
     </row>
     <row r="331">
       <c r="B331" s="2"/>
-      <c r="C331" s="31"/>
+      <c r="C331" s="34"/>
     </row>
     <row r="332">
       <c r="B332" s="2"/>
-      <c r="C332" s="31"/>
+      <c r="C332" s="34"/>
     </row>
     <row r="333">
       <c r="B333" s="2"/>
-      <c r="C333" s="31"/>
+      <c r="C333" s="34"/>
     </row>
     <row r="334">
       <c r="B334" s="2"/>
-      <c r="C334" s="31"/>
+      <c r="C334" s="34"/>
     </row>
     <row r="335">
       <c r="B335" s="2"/>
-      <c r="C335" s="31"/>
+      <c r="C335" s="34"/>
     </row>
     <row r="336">
       <c r="B336" s="2"/>
-      <c r="C336" s="31"/>
+      <c r="C336" s="34"/>
     </row>
     <row r="337">
       <c r="B337" s="2"/>
-      <c r="C337" s="31"/>
+      <c r="C337" s="34"/>
     </row>
     <row r="338">
       <c r="B338" s="2"/>
-      <c r="C338" s="31"/>
+      <c r="C338" s="34"/>
     </row>
     <row r="339">
       <c r="B339" s="2"/>
-      <c r="C339" s="31"/>
+      <c r="C339" s="34"/>
     </row>
     <row r="340">
       <c r="B340" s="2"/>
-      <c r="C340" s="31"/>
+      <c r="C340" s="34"/>
     </row>
     <row r="341">
       <c r="B341" s="2"/>
-      <c r="C341" s="31"/>
+      <c r="C341" s="34"/>
     </row>
     <row r="342">
       <c r="B342" s="2"/>
-      <c r="C342" s="31"/>
+      <c r="C342" s="34"/>
     </row>
     <row r="343">
       <c r="B343" s="2"/>
-      <c r="C343" s="31"/>
+      <c r="C343" s="34"/>
     </row>
     <row r="344">
       <c r="B344" s="2"/>
-      <c r="C344" s="31"/>
+      <c r="C344" s="34"/>
     </row>
     <row r="345">
       <c r="B345" s="2"/>
-      <c r="C345" s="31"/>
+      <c r="C345" s="34"/>
     </row>
     <row r="346">
       <c r="B346" s="2"/>
-      <c r="C346" s="31"/>
+      <c r="C346" s="34"/>
     </row>
     <row r="347">
       <c r="B347" s="2"/>
-      <c r="C347" s="31"/>
+      <c r="C347" s="34"/>
     </row>
     <row r="348">
       <c r="B348" s="2"/>
-      <c r="C348" s="31"/>
+      <c r="C348" s="34"/>
     </row>
     <row r="349">
       <c r="B349" s="2"/>
-      <c r="C349" s="31"/>
+      <c r="C349" s="34"/>
     </row>
     <row r="350">
       <c r="B350" s="2"/>
-      <c r="C350" s="31"/>
+      <c r="C350" s="34"/>
     </row>
     <row r="351">
       <c r="B351" s="2"/>
-      <c r="C351" s="31"/>
+      <c r="C351" s="34"/>
     </row>
     <row r="352">
       <c r="B352" s="2"/>
-      <c r="C352" s="31"/>
+      <c r="C352" s="34"/>
     </row>
     <row r="353">
       <c r="B353" s="2"/>
-      <c r="C353" s="31"/>
+      <c r="C353" s="34"/>
     </row>
     <row r="354">
       <c r="B354" s="2"/>
-      <c r="C354" s="31"/>
+      <c r="C354" s="34"/>
     </row>
     <row r="355">
       <c r="B355" s="2"/>
-      <c r="C355" s="31"/>
+      <c r="C355" s="34"/>
     </row>
     <row r="356">
       <c r="B356" s="2"/>
-      <c r="C356" s="31"/>
+      <c r="C356" s="34"/>
     </row>
     <row r="357">
       <c r="B357" s="2"/>
-      <c r="C357" s="31"/>
+      <c r="C357" s="34"/>
     </row>
     <row r="358">
       <c r="B358" s="2"/>
-      <c r="C358" s="31"/>
+      <c r="C358" s="34"/>
     </row>
     <row r="359">
       <c r="B359" s="2"/>
-      <c r="C359" s="31"/>
+      <c r="C359" s="34"/>
     </row>
     <row r="360">
       <c r="B360" s="2"/>
-      <c r="C360" s="31"/>
+      <c r="C360" s="34"/>
     </row>
     <row r="361">
       <c r="B361" s="2"/>
-      <c r="C361" s="31"/>
+      <c r="C361" s="34"/>
     </row>
     <row r="362">
       <c r="B362" s="2"/>
-      <c r="C362" s="31"/>
+      <c r="C362" s="34"/>
     </row>
     <row r="363">
       <c r="B363" s="2"/>
-      <c r="C363" s="31"/>
+      <c r="C363" s="34"/>
     </row>
     <row r="364">
       <c r="B364" s="2"/>
-      <c r="C364" s="31"/>
+      <c r="C364" s="34"/>
     </row>
     <row r="365">
       <c r="B365" s="2"/>
-      <c r="C365" s="31"/>
+      <c r="C365" s="34"/>
     </row>
     <row r="366">
       <c r="B366" s="2"/>
-      <c r="C366" s="31"/>
+      <c r="C366" s="34"/>
     </row>
     <row r="367">
       <c r="B367" s="2"/>
-      <c r="C367" s="31"/>
+      <c r="C367" s="34"/>
     </row>
     <row r="368">
       <c r="B368" s="2"/>
-      <c r="C368" s="31"/>
+      <c r="C368" s="34"/>
     </row>
     <row r="369">
       <c r="B369" s="2"/>
-      <c r="C369" s="31"/>
+      <c r="C369" s="34"/>
     </row>
     <row r="370">
       <c r="B370" s="2"/>
-      <c r="C370" s="31"/>
+      <c r="C370" s="34"/>
     </row>
     <row r="371">
       <c r="B371" s="2"/>
-      <c r="C371" s="31"/>
+      <c r="C371" s="34"/>
     </row>
     <row r="372">
       <c r="B372" s="2"/>
-      <c r="C372" s="31"/>
+      <c r="C372" s="34"/>
     </row>
     <row r="373">
       <c r="B373" s="2"/>
-      <c r="C373" s="31"/>
+      <c r="C373" s="34"/>
     </row>
     <row r="374">
       <c r="B374" s="2"/>
-      <c r="C374" s="31"/>
+      <c r="C374" s="34"/>
     </row>
     <row r="375">
       <c r="B375" s="2"/>
-      <c r="C375" s="31"/>
+      <c r="C375" s="34"/>
     </row>
     <row r="376">
       <c r="B376" s="2"/>
-      <c r="C376" s="31"/>
+      <c r="C376" s="34"/>
     </row>
     <row r="377">
       <c r="B377" s="2"/>
-      <c r="C377" s="31"/>
+      <c r="C377" s="34"/>
     </row>
     <row r="378">
       <c r="B378" s="2"/>
-      <c r="C378" s="31"/>
+      <c r="C378" s="34"/>
     </row>
     <row r="379">
       <c r="B379" s="2"/>
-      <c r="C379" s="31"/>
+      <c r="C379" s="34"/>
     </row>
     <row r="380">
       <c r="B380" s="2"/>
-      <c r="C380" s="31"/>
+      <c r="C380" s="34"/>
     </row>
     <row r="381">
       <c r="B381" s="2"/>
-      <c r="C381" s="31"/>
+      <c r="C381" s="34"/>
     </row>
     <row r="382">
       <c r="B382" s="2"/>
-      <c r="C382" s="31"/>
+      <c r="C382" s="34"/>
     </row>
     <row r="383">
       <c r="B383" s="2"/>
-      <c r="C383" s="31"/>
+      <c r="C383" s="34"/>
     </row>
     <row r="384">
       <c r="B384" s="2"/>
-      <c r="C384" s="31"/>
+      <c r="C384" s="34"/>
     </row>
     <row r="385">
       <c r="B385" s="2"/>
-      <c r="C385" s="31"/>
+      <c r="C385" s="34"/>
     </row>
     <row r="386">
       <c r="B386" s="2"/>
-      <c r="C386" s="31"/>
+      <c r="C386" s="34"/>
     </row>
     <row r="387">
       <c r="B387" s="2"/>
-      <c r="C387" s="31"/>
+      <c r="C387" s="34"/>
     </row>
     <row r="388">
       <c r="B388" s="2"/>
-      <c r="C388" s="31"/>
+      <c r="C388" s="34"/>
     </row>
     <row r="389">
       <c r="B389" s="2"/>
-      <c r="C389" s="31"/>
+      <c r="C389" s="34"/>
     </row>
     <row r="390">
       <c r="B390" s="2"/>
-      <c r="C390" s="31"/>
+      <c r="C390" s="34"/>
     </row>
     <row r="391">
       <c r="B391" s="2"/>
-      <c r="C391" s="31"/>
+      <c r="C391" s="34"/>
     </row>
     <row r="392">
       <c r="B392" s="2"/>
-      <c r="C392" s="31"/>
+      <c r="C392" s="34"/>
     </row>
     <row r="393">
       <c r="B393" s="2"/>
-      <c r="C393" s="31"/>
+      <c r="C393" s="34"/>
     </row>
     <row r="394">
       <c r="B394" s="2"/>
-      <c r="C394" s="31"/>
+      <c r="C394" s="34"/>
     </row>
     <row r="395">
       <c r="B395" s="2"/>
-      <c r="C395" s="31"/>
+      <c r="C395" s="34"/>
     </row>
     <row r="396">
       <c r="B396" s="2"/>
-      <c r="C396" s="31"/>
+      <c r="C396" s="34"/>
     </row>
     <row r="397">
       <c r="B397" s="2"/>
-      <c r="C397" s="31"/>
+      <c r="C397" s="34"/>
     </row>
     <row r="398">
       <c r="B398" s="2"/>
-      <c r="C398" s="31"/>
+      <c r="C398" s="34"/>
     </row>
     <row r="399">
       <c r="B399" s="2"/>
-      <c r="C399" s="31"/>
+      <c r="C399" s="34"/>
     </row>
     <row r="400">
       <c r="B400" s="2"/>
-      <c r="C400" s="31"/>
+      <c r="C400" s="34"/>
     </row>
     <row r="401">
       <c r="B401" s="2"/>
-      <c r="C401" s="31"/>
+      <c r="C401" s="34"/>
     </row>
     <row r="402">
       <c r="B402" s="2"/>
-      <c r="C402" s="31"/>
+      <c r="C402" s="34"/>
     </row>
     <row r="403">
       <c r="B403" s="2"/>
-      <c r="C403" s="31"/>
+      <c r="C403" s="34"/>
     </row>
     <row r="404">
       <c r="B404" s="2"/>
-      <c r="C404" s="31"/>
+      <c r="C404" s="34"/>
     </row>
     <row r="405">
       <c r="B405" s="2"/>
-      <c r="C405" s="31"/>
+      <c r="C405" s="34"/>
     </row>
     <row r="406">
       <c r="B406" s="2"/>
-      <c r="C406" s="31"/>
+      <c r="C406" s="34"/>
     </row>
     <row r="407">
       <c r="B407" s="2"/>
-      <c r="C407" s="31"/>
+      <c r="C407" s="34"/>
     </row>
     <row r="408">
       <c r="B408" s="2"/>
-      <c r="C408" s="31"/>
+      <c r="C408" s="34"/>
     </row>
     <row r="409">
       <c r="B409" s="2"/>
-      <c r="C409" s="31"/>
+      <c r="C409" s="34"/>
     </row>
     <row r="410">
       <c r="B410" s="2"/>
-      <c r="C410" s="31"/>
+      <c r="C410" s="34"/>
     </row>
     <row r="411">
       <c r="B411" s="2"/>
-      <c r="C411" s="31"/>
+      <c r="C411" s="34"/>
     </row>
     <row r="412">
       <c r="B412" s="2"/>
-      <c r="C412" s="31"/>
+      <c r="C412" s="34"/>
     </row>
     <row r="413">
       <c r="B413" s="2"/>
-      <c r="C413" s="31"/>
+      <c r="C413" s="34"/>
     </row>
     <row r="414">
       <c r="B414" s="2"/>
-      <c r="C414" s="31"/>
+      <c r="C414" s="34"/>
     </row>
     <row r="415">
       <c r="B415" s="2"/>
-      <c r="C415" s="31"/>
+      <c r="C415" s="34"/>
     </row>
     <row r="416">
       <c r="B416" s="2"/>
-      <c r="C416" s="31"/>
+      <c r="C416" s="34"/>
     </row>
     <row r="417">
       <c r="B417" s="2"/>
-      <c r="C417" s="31"/>
+      <c r="C417" s="34"/>
     </row>
     <row r="418">
       <c r="B418" s="2"/>
-      <c r="C418" s="31"/>
+      <c r="C418" s="34"/>
     </row>
     <row r="419">
       <c r="B419" s="2"/>
-      <c r="C419" s="31"/>
+      <c r="C419" s="34"/>
     </row>
     <row r="420">
       <c r="B420" s="2"/>
-      <c r="C420" s="31"/>
+      <c r="C420" s="34"/>
     </row>
     <row r="421">
       <c r="B421" s="2"/>
-      <c r="C421" s="31"/>
+      <c r="C421" s="34"/>
     </row>
     <row r="422">
       <c r="B422" s="2"/>
-      <c r="C422" s="31"/>
+      <c r="C422" s="34"/>
     </row>
     <row r="423">
       <c r="B423" s="2"/>
-      <c r="C423" s="31"/>
+      <c r="C423" s="34"/>
     </row>
     <row r="424">
       <c r="B424" s="2"/>
-      <c r="C424" s="31"/>
+      <c r="C424" s="34"/>
     </row>
     <row r="425">
       <c r="B425" s="2"/>
-      <c r="C425" s="31"/>
+      <c r="C425" s="34"/>
     </row>
     <row r="426">
       <c r="B426" s="2"/>
-      <c r="C426" s="31"/>
+      <c r="C426" s="34"/>
     </row>
     <row r="427">
       <c r="B427" s="2"/>
-      <c r="C427" s="31"/>
+      <c r="C427" s="34"/>
     </row>
     <row r="428">
       <c r="B428" s="2"/>
-      <c r="C428" s="31"/>
+      <c r="C428" s="34"/>
     </row>
     <row r="429">
       <c r="B429" s="2"/>
-      <c r="C429" s="31"/>
+      <c r="C429" s="34"/>
     </row>
     <row r="430">
       <c r="B430" s="2"/>
-      <c r="C430" s="31"/>
+      <c r="C430" s="34"/>
     </row>
     <row r="431">
       <c r="B431" s="2"/>
-      <c r="C431" s="31"/>
+      <c r="C431" s="34"/>
     </row>
     <row r="432">
       <c r="B432" s="2"/>
-      <c r="C432" s="31"/>
+      <c r="C432" s="34"/>
     </row>
     <row r="433">
       <c r="B433" s="2"/>
-      <c r="C433" s="31"/>
+      <c r="C433" s="34"/>
     </row>
     <row r="434">
       <c r="B434" s="2"/>
-      <c r="C434" s="31"/>
+      <c r="C434" s="34"/>
     </row>
     <row r="435">
       <c r="B435" s="2"/>
-      <c r="C435" s="31"/>
+      <c r="C435" s="34"/>
     </row>
     <row r="436">
       <c r="B436" s="2"/>
-      <c r="C436" s="31"/>
+      <c r="C436" s="34"/>
     </row>
     <row r="437">
       <c r="B437" s="2"/>
-      <c r="C437" s="31"/>
+      <c r="C437" s="34"/>
     </row>
     <row r="438">
       <c r="B438" s="2"/>
-      <c r="C438" s="31"/>
+      <c r="C438" s="34"/>
     </row>
     <row r="439">
       <c r="B439" s="2"/>
-      <c r="C439" s="31"/>
+      <c r="C439" s="34"/>
     </row>
     <row r="440">
       <c r="B440" s="2"/>
-      <c r="C440" s="31"/>
+      <c r="C440" s="34"/>
     </row>
     <row r="441">
       <c r="B441" s="2"/>
-      <c r="C441" s="31"/>
+      <c r="C441" s="34"/>
     </row>
     <row r="442">
       <c r="B442" s="2"/>
-      <c r="C442" s="31"/>
+      <c r="C442" s="34"/>
     </row>
     <row r="443">
       <c r="B443" s="2"/>
-      <c r="C443" s="31"/>
+      <c r="C443" s="34"/>
     </row>
     <row r="444">
       <c r="B444" s="2"/>
-      <c r="C444" s="31"/>
+      <c r="C444" s="34"/>
     </row>
     <row r="445">
       <c r="B445" s="2"/>
-      <c r="C445" s="31"/>
+      <c r="C445" s="34"/>
     </row>
     <row r="446">
       <c r="B446" s="2"/>
-      <c r="C446" s="31"/>
+      <c r="C446" s="34"/>
     </row>
     <row r="447">
       <c r="B447" s="2"/>
-      <c r="C447" s="31"/>
+      <c r="C447" s="34"/>
     </row>
     <row r="448">
       <c r="B448" s="2"/>
-      <c r="C448" s="31"/>
+      <c r="C448" s="34"/>
     </row>
     <row r="449">
       <c r="B449" s="2"/>
-      <c r="C449" s="31"/>
+      <c r="C449" s="34"/>
     </row>
     <row r="450">
       <c r="B450" s="2"/>
-      <c r="C450" s="31"/>
+      <c r="C450" s="34"/>
     </row>
     <row r="451">
       <c r="B451" s="2"/>
-      <c r="C451" s="31"/>
+      <c r="C451" s="34"/>
     </row>
     <row r="452">
       <c r="B452" s="2"/>
-      <c r="C452" s="31"/>
+      <c r="C452" s="34"/>
     </row>
     <row r="453">
       <c r="B453" s="2"/>
-      <c r="C453" s="31"/>
+      <c r="C453" s="34"/>
     </row>
     <row r="454">
       <c r="B454" s="2"/>
-      <c r="C454" s="31"/>
+      <c r="C454" s="34"/>
     </row>
     <row r="455">
       <c r="B455" s="2"/>
-      <c r="C455" s="31"/>
+      <c r="C455" s="34"/>
     </row>
     <row r="456">
       <c r="B456" s="2"/>
-      <c r="C456" s="31"/>
+      <c r="C456" s="34"/>
     </row>
     <row r="457">
       <c r="B457" s="2"/>
-      <c r="C457" s="31"/>
+      <c r="C457" s="34"/>
     </row>
     <row r="458">
       <c r="B458" s="2"/>
-      <c r="C458" s="31"/>
+      <c r="C458" s="34"/>
     </row>
     <row r="459">
       <c r="B459" s="2"/>
-      <c r="C459" s="31"/>
+      <c r="C459" s="34"/>
     </row>
     <row r="460">
       <c r="B460" s="2"/>
-      <c r="C460" s="31"/>
+      <c r="C460" s="34"/>
     </row>
     <row r="461">
       <c r="B461" s="2"/>
-      <c r="C461" s="31"/>
+      <c r="C461" s="34"/>
     </row>
     <row r="462">
       <c r="B462" s="2"/>
-      <c r="C462" s="31"/>
+      <c r="C462" s="34"/>
     </row>
     <row r="463">
       <c r="B463" s="2"/>
-      <c r="C463" s="31"/>
+      <c r="C463" s="34"/>
     </row>
     <row r="464">
       <c r="B464" s="2"/>
-      <c r="C464" s="31"/>
+      <c r="C464" s="34"/>
     </row>
     <row r="465">
       <c r="B465" s="2"/>
-      <c r="C465" s="31"/>
+      <c r="C465" s="34"/>
     </row>
     <row r="466">
       <c r="B466" s="2"/>
-      <c r="C466" s="31"/>
+      <c r="C466" s="34"/>
     </row>
     <row r="467">
       <c r="B467" s="2"/>
-      <c r="C467" s="31"/>
+      <c r="C467" s="34"/>
     </row>
     <row r="468">
       <c r="B468" s="2"/>
-      <c r="C468" s="31"/>
+      <c r="C468" s="34"/>
     </row>
     <row r="469">
       <c r="B469" s="2"/>
-      <c r="C469" s="31"/>
+      <c r="C469" s="34"/>
     </row>
     <row r="470">
       <c r="B470" s="2"/>
-      <c r="C470" s="31"/>
+      <c r="C470" s="34"/>
     </row>
     <row r="471">
       <c r="B471" s="2"/>
-      <c r="C471" s="31"/>
+      <c r="C471" s="34"/>
     </row>
     <row r="472">
       <c r="B472" s="2"/>
-      <c r="C472" s="31"/>
+      <c r="C472" s="34"/>
     </row>
     <row r="473">
       <c r="B473" s="2"/>
-      <c r="C473" s="31"/>
+      <c r="C473" s="34"/>
     </row>
     <row r="474">
       <c r="B474" s="2"/>
-      <c r="C474" s="31"/>
+      <c r="C474" s="34"/>
     </row>
     <row r="475">
       <c r="B475" s="2"/>
-      <c r="C475" s="31"/>
+      <c r="C475" s="34"/>
     </row>
     <row r="476">
       <c r="B476" s="2"/>
-      <c r="C476" s="31"/>
+      <c r="C476" s="34"/>
     </row>
     <row r="477">
       <c r="B477" s="2"/>
-      <c r="C477" s="31"/>
+      <c r="C477" s="34"/>
     </row>
     <row r="478">
       <c r="B478" s="2"/>
-      <c r="C478" s="31"/>
+      <c r="C478" s="34"/>
     </row>
     <row r="479">
       <c r="B479" s="2"/>
-      <c r="C479" s="31"/>
+      <c r="C479" s="34"/>
     </row>
     <row r="480">
       <c r="B480" s="2"/>
-      <c r="C480" s="31"/>
+      <c r="C480" s="34"/>
     </row>
     <row r="481">
       <c r="B481" s="2"/>
-      <c r="C481" s="31"/>
+      <c r="C481" s="34"/>
     </row>
     <row r="482">
       <c r="B482" s="2"/>
-      <c r="C482" s="31"/>
+      <c r="C482" s="34"/>
     </row>
     <row r="483">
       <c r="B483" s="2"/>
-      <c r="C483" s="31"/>
+      <c r="C483" s="34"/>
     </row>
     <row r="484">
       <c r="B484" s="2"/>
-      <c r="C484" s="31"/>
+      <c r="C484" s="34"/>
     </row>
     <row r="485">
       <c r="B485" s="2"/>
-      <c r="C485" s="31"/>
+      <c r="C485" s="34"/>
     </row>
     <row r="486">
       <c r="B486" s="2"/>
-      <c r="C486" s="31"/>
+      <c r="C486" s="34"/>
     </row>
     <row r="487">
       <c r="B487" s="2"/>
-      <c r="C487" s="31"/>
+      <c r="C487" s="34"/>
     </row>
     <row r="488">
       <c r="B488" s="2"/>
-      <c r="C488" s="31"/>
+      <c r="C488" s="34"/>
     </row>
     <row r="489">
       <c r="B489" s="2"/>
-      <c r="C489" s="31"/>
+      <c r="C489" s="34"/>
     </row>
     <row r="490">
       <c r="B490" s="2"/>
-      <c r="C490" s="31"/>
+      <c r="C490" s="34"/>
     </row>
     <row r="491">
       <c r="B491" s="2"/>
-      <c r="C491" s="31"/>
+      <c r="C491" s="34"/>
     </row>
     <row r="492">
       <c r="B492" s="2"/>
-      <c r="C492" s="31"/>
+      <c r="C492" s="34"/>
     </row>
     <row r="493">
       <c r="B493" s="2"/>
-      <c r="C493" s="31"/>
+      <c r="C493" s="34"/>
     </row>
     <row r="494">
       <c r="B494" s="2"/>
-      <c r="C494" s="31"/>
+      <c r="C494" s="34"/>
     </row>
     <row r="495">
       <c r="B495" s="2"/>
-      <c r="C495" s="31"/>
+      <c r="C495" s="34"/>
     </row>
     <row r="496">
       <c r="B496" s="2"/>
-      <c r="C496" s="31"/>
+      <c r="C496" s="34"/>
     </row>
     <row r="497">
       <c r="B497" s="2"/>
-      <c r="C497" s="31"/>
+      <c r="C497" s="34"/>
     </row>
     <row r="498">
       <c r="B498" s="2"/>
-      <c r="C498" s="31"/>
+      <c r="C498" s="34"/>
     </row>
     <row r="499">
       <c r="B499" s="2"/>
-      <c r="C499" s="31"/>
+      <c r="C499" s="34"/>
     </row>
     <row r="500">
       <c r="B500" s="2"/>
-      <c r="C500" s="31"/>
+      <c r="C500" s="34"/>
     </row>
     <row r="501">
       <c r="B501" s="2"/>
-      <c r="C501" s="31"/>
+      <c r="C501" s="34"/>
     </row>
     <row r="502">
       <c r="B502" s="2"/>
-      <c r="C502" s="31"/>
+      <c r="C502" s="34"/>
     </row>
     <row r="503">
       <c r="B503" s="2"/>
-      <c r="C503" s="31"/>
+      <c r="C503" s="34"/>
     </row>
     <row r="504">
       <c r="B504" s="2"/>
-      <c r="C504" s="31"/>
+      <c r="C504" s="34"/>
     </row>
     <row r="505">
       <c r="B505" s="2"/>
-      <c r="C505" s="31"/>
+      <c r="C505" s="34"/>
     </row>
     <row r="506">
       <c r="B506" s="2"/>
-      <c r="C506" s="31"/>
+      <c r="C506" s="34"/>
     </row>
     <row r="507">
       <c r="B507" s="2"/>
-      <c r="C507" s="31"/>
+      <c r="C507" s="34"/>
     </row>
     <row r="508">
       <c r="B508" s="2"/>
-      <c r="C508" s="31"/>
+      <c r="C508" s="34"/>
     </row>
     <row r="509">
       <c r="B509" s="2"/>
-      <c r="C509" s="31"/>
+      <c r="C509" s="34"/>
     </row>
     <row r="510">
       <c r="B510" s="2"/>
-      <c r="C510" s="31"/>
+      <c r="C510" s="34"/>
     </row>
     <row r="511">
       <c r="B511" s="2"/>
-      <c r="C511" s="31"/>
+      <c r="C511" s="34"/>
     </row>
     <row r="512">
       <c r="B512" s="2"/>
-      <c r="C512" s="31"/>
+      <c r="C512" s="34"/>
     </row>
     <row r="513">
       <c r="B513" s="2"/>
-      <c r="C513" s="31"/>
+      <c r="C513" s="34"/>
     </row>
     <row r="514">
       <c r="B514" s="2"/>
-      <c r="C514" s="31"/>
+      <c r="C514" s="34"/>
     </row>
     <row r="515">
       <c r="B515" s="2"/>
-      <c r="C515" s="31"/>
+      <c r="C515" s="34"/>
     </row>
     <row r="516">
       <c r="B516" s="2"/>
-      <c r="C516" s="31"/>
+      <c r="C516" s="34"/>
     </row>
     <row r="517">
       <c r="B517" s="2"/>
-      <c r="C517" s="31"/>
+      <c r="C517" s="34"/>
     </row>
     <row r="518">
       <c r="B518" s="2"/>
-      <c r="C518" s="31"/>
+      <c r="C518" s="34"/>
     </row>
     <row r="519">
       <c r="B519" s="2"/>
-      <c r="C519" s="31"/>
+      <c r="C519" s="34"/>
     </row>
     <row r="520">
       <c r="B520" s="2"/>
-      <c r="C520" s="31"/>
+      <c r="C520" s="34"/>
     </row>
     <row r="521">
       <c r="B521" s="2"/>
-      <c r="C521" s="31"/>
+      <c r="C521" s="34"/>
     </row>
     <row r="522">
       <c r="B522" s="2"/>
-      <c r="C522" s="31"/>
+      <c r="C522" s="34"/>
     </row>
     <row r="523">
       <c r="B523" s="2"/>
-      <c r="C523" s="31"/>
+      <c r="C523" s="34"/>
     </row>
     <row r="524">
       <c r="B524" s="2"/>
-      <c r="C524" s="31"/>
+      <c r="C524" s="34"/>
     </row>
     <row r="525">
       <c r="B525" s="2"/>
-      <c r="C525" s="31"/>
+      <c r="C525" s="34"/>
     </row>
     <row r="526">
       <c r="B526" s="2"/>
-      <c r="C526" s="31"/>
+      <c r="C526" s="34"/>
     </row>
     <row r="527">
       <c r="B527" s="2"/>
-      <c r="C527" s="31"/>
+      <c r="C527" s="34"/>
     </row>
     <row r="528">
       <c r="B528" s="2"/>
-      <c r="C528" s="31"/>
+      <c r="C528" s="34"/>
     </row>
     <row r="529">
       <c r="B529" s="2"/>
-      <c r="C529" s="31"/>
+      <c r="C529" s="34"/>
     </row>
     <row r="530">
       <c r="B530" s="2"/>
-      <c r="C530" s="31"/>
+      <c r="C530" s="34"/>
     </row>
     <row r="531">
       <c r="B531" s="2"/>
-      <c r="C531" s="31"/>
+      <c r="C531" s="34"/>
     </row>
     <row r="532">
       <c r="B532" s="2"/>
-      <c r="C532" s="31"/>
+      <c r="C532" s="34"/>
     </row>
     <row r="533">
       <c r="B533" s="2"/>
-      <c r="C533" s="31"/>
+      <c r="C533" s="34"/>
     </row>
     <row r="534">
       <c r="B534" s="2"/>
-      <c r="C534" s="31"/>
+      <c r="C534" s="34"/>
     </row>
     <row r="535">
       <c r="B535" s="2"/>
-      <c r="C535" s="31"/>
+      <c r="C535" s="34"/>
     </row>
     <row r="536">
       <c r="B536" s="2"/>
-      <c r="C536" s="31"/>
+      <c r="C536" s="34"/>
     </row>
     <row r="537">
       <c r="B537" s="2"/>
-      <c r="C537" s="31"/>
+      <c r="C537" s="34"/>
     </row>
     <row r="538">
       <c r="B538" s="2"/>
-      <c r="C538" s="31"/>
+      <c r="C538" s="34"/>
     </row>
     <row r="539">
       <c r="B539" s="2"/>
-      <c r="C539" s="31"/>
+      <c r="C539" s="34"/>
     </row>
     <row r="540">
       <c r="B540" s="2"/>
-      <c r="C540" s="31"/>
+      <c r="C540" s="34"/>
     </row>
     <row r="541">
       <c r="B541" s="2"/>
-      <c r="C541" s="31"/>
+      <c r="C541" s="34"/>
     </row>
     <row r="542">
       <c r="B542" s="2"/>
-      <c r="C542" s="31"/>
+      <c r="C542" s="34"/>
     </row>
     <row r="543">
       <c r="B543" s="2"/>
-      <c r="C543" s="31"/>
+      <c r="C543" s="34"/>
     </row>
     <row r="544">
       <c r="B544" s="2"/>
-      <c r="C544" s="31"/>
+      <c r="C544" s="34"/>
     </row>
     <row r="545">
       <c r="B545" s="2"/>
-      <c r="C545" s="31"/>
+      <c r="C545" s="34"/>
     </row>
     <row r="546">
       <c r="B546" s="2"/>
-      <c r="C546" s="31"/>
+      <c r="C546" s="34"/>
     </row>
     <row r="547">
       <c r="B547" s="2"/>
-      <c r="C547" s="31"/>
+      <c r="C547" s="34"/>
     </row>
     <row r="548">
       <c r="B548" s="2"/>
-      <c r="C548" s="31"/>
+      <c r="C548" s="34"/>
     </row>
     <row r="549">
       <c r="B549" s="2"/>
-      <c r="C549" s="31"/>
+      <c r="C549" s="34"/>
     </row>
     <row r="550">
       <c r="B550" s="2"/>
-      <c r="C550" s="31"/>
+      <c r="C550" s="34"/>
     </row>
     <row r="551">
       <c r="B551" s="2"/>
-      <c r="C551" s="31"/>
+      <c r="C551" s="34"/>
     </row>
     <row r="552">
       <c r="B552" s="2"/>
-      <c r="C552" s="31"/>
+      <c r="C552" s="34"/>
     </row>
     <row r="553">
       <c r="B553" s="2"/>
-      <c r="C553" s="31"/>
+      <c r="C553" s="34"/>
     </row>
     <row r="554">
       <c r="B554" s="2"/>
-      <c r="C554" s="31"/>
+      <c r="C554" s="34"/>
     </row>
     <row r="555">
       <c r="B555" s="2"/>
-      <c r="C555" s="31"/>
+      <c r="C555" s="34"/>
     </row>
     <row r="556">
       <c r="B556" s="2"/>
-      <c r="C556" s="31"/>
+      <c r="C556" s="34"/>
     </row>
     <row r="557">
       <c r="B557" s="2"/>
-      <c r="C557" s="31"/>
+      <c r="C557" s="34"/>
     </row>
     <row r="558">
       <c r="B558" s="2"/>
-      <c r="C558" s="31"/>
+      <c r="C558" s="34"/>
     </row>
     <row r="559">
       <c r="B559" s="2"/>
-      <c r="C559" s="31"/>
+      <c r="C559" s="34"/>
     </row>
     <row r="560">
       <c r="B560" s="2"/>
-      <c r="C560" s="31"/>
+      <c r="C560" s="34"/>
     </row>
     <row r="561">
       <c r="B561" s="2"/>
-      <c r="C561" s="31"/>
+      <c r="C561" s="34"/>
     </row>
     <row r="562">
       <c r="B562" s="2"/>
-      <c r="C562" s="31"/>
+      <c r="C562" s="34"/>
     </row>
     <row r="563">
       <c r="B563" s="2"/>
-      <c r="C563" s="31"/>
+      <c r="C563" s="34"/>
     </row>
     <row r="564">
       <c r="B564" s="2"/>
-      <c r="C564" s="31"/>
+      <c r="C564" s="34"/>
     </row>
     <row r="565">
       <c r="B565" s="2"/>
-      <c r="C565" s="31"/>
+      <c r="C565" s="34"/>
     </row>
     <row r="566">
       <c r="B566" s="2"/>
-      <c r="C566" s="31"/>
+      <c r="C566" s="34"/>
     </row>
     <row r="567">
       <c r="B567" s="2"/>
-      <c r="C567" s="31"/>
+      <c r="C567" s="34"/>
     </row>
     <row r="568">
       <c r="B568" s="2"/>
-      <c r="C568" s="31"/>
+      <c r="C568" s="34"/>
     </row>
     <row r="569">
       <c r="B569" s="2"/>
-      <c r="C569" s="31"/>
+      <c r="C569" s="34"/>
     </row>
     <row r="570">
       <c r="B570" s="2"/>
-      <c r="C570" s="31"/>
+      <c r="C570" s="34"/>
     </row>
     <row r="571">
       <c r="B571" s="2"/>
-      <c r="C571" s="31"/>
+      <c r="C571" s="34"/>
     </row>
     <row r="572">
       <c r="B572" s="2"/>
-      <c r="C572" s="31"/>
+      <c r="C572" s="34"/>
     </row>
     <row r="573">
       <c r="B573" s="2"/>
-      <c r="C573" s="31"/>
+      <c r="C573" s="34"/>
     </row>
     <row r="574">
       <c r="B574" s="2"/>
-      <c r="C574" s="31"/>
+      <c r="C574" s="34"/>
     </row>
     <row r="575">
       <c r="B575" s="2"/>
-      <c r="C575" s="31"/>
+      <c r="C575" s="34"/>
     </row>
     <row r="576">
       <c r="B576" s="2"/>
-      <c r="C576" s="31"/>
+      <c r="C576" s="34"/>
     </row>
     <row r="577">
       <c r="B577" s="2"/>
-      <c r="C577" s="31"/>
+      <c r="C577" s="34"/>
     </row>
     <row r="578">
       <c r="B578" s="2"/>
-      <c r="C578" s="31"/>
+      <c r="C578" s="34"/>
     </row>
     <row r="579">
       <c r="B579" s="2"/>
-      <c r="C579" s="31"/>
+      <c r="C579" s="34"/>
     </row>
     <row r="580">
       <c r="B580" s="2"/>
-      <c r="C580" s="31"/>
+      <c r="C580" s="34"/>
     </row>
     <row r="581">
       <c r="B581" s="2"/>
-      <c r="C581" s="31"/>
+      <c r="C581" s="34"/>
     </row>
     <row r="582">
       <c r="B582" s="2"/>
-      <c r="C582" s="31"/>
+      <c r="C582" s="34"/>
     </row>
     <row r="583">
       <c r="B583" s="2"/>
-      <c r="C583" s="31"/>
+      <c r="C583" s="34"/>
     </row>
     <row r="584">
       <c r="B584" s="2"/>
-      <c r="C584" s="31"/>
+      <c r="C584" s="34"/>
     </row>
     <row r="585">
       <c r="B585" s="2"/>
-      <c r="C585" s="31"/>
+      <c r="C585" s="34"/>
     </row>
     <row r="586">
       <c r="B586" s="2"/>
-      <c r="C586" s="31"/>
+      <c r="C586" s="34"/>
     </row>
     <row r="587">
       <c r="B587" s="2"/>
-      <c r="C587" s="31"/>
+      <c r="C587" s="34"/>
     </row>
     <row r="588">
       <c r="B588" s="2"/>
-      <c r="C588" s="31"/>
+      <c r="C588" s="34"/>
     </row>
     <row r="589">
       <c r="B589" s="2"/>
-      <c r="C589" s="31"/>
+      <c r="C589" s="34"/>
     </row>
     <row r="590">
       <c r="B590" s="2"/>
-      <c r="C590" s="31"/>
+      <c r="C590" s="34"/>
     </row>
     <row r="591">
       <c r="B591" s="2"/>
-      <c r="C591" s="31"/>
+      <c r="C591" s="34"/>
     </row>
     <row r="592">
       <c r="B592" s="2"/>
-      <c r="C592" s="31"/>
+      <c r="C592" s="34"/>
     </row>
     <row r="593">
       <c r="B593" s="2"/>
-      <c r="C593" s="31"/>
+      <c r="C593" s="34"/>
     </row>
     <row r="594">
       <c r="B594" s="2"/>
-      <c r="C594" s="31"/>
+      <c r="C594" s="34"/>
     </row>
     <row r="595">
       <c r="B595" s="2"/>
-      <c r="C595" s="31"/>
+      <c r="C595" s="34"/>
     </row>
     <row r="596">
       <c r="B596" s="2"/>
-      <c r="C596" s="31"/>
+      <c r="C596" s="34"/>
     </row>
     <row r="597">
       <c r="B597" s="2"/>
-      <c r="C597" s="31"/>
+      <c r="C597" s="34"/>
     </row>
     <row r="598">
       <c r="B598" s="2"/>
-      <c r="C598" s="31"/>
+      <c r="C598" s="34"/>
     </row>
     <row r="599">
       <c r="B599" s="2"/>
-      <c r="C599" s="31"/>
+      <c r="C599" s="34"/>
     </row>
     <row r="600">
       <c r="B600" s="2"/>
-      <c r="C600" s="31"/>
+      <c r="C600" s="34"/>
     </row>
     <row r="601">
       <c r="B601" s="2"/>
-      <c r="C601" s="31"/>
+      <c r="C601" s="34"/>
     </row>
     <row r="602">
       <c r="B602" s="2"/>
-      <c r="C602" s="31"/>
+      <c r="C602" s="34"/>
     </row>
     <row r="603">
       <c r="B603" s="2"/>
-      <c r="C603" s="31"/>
+      <c r="C603" s="34"/>
     </row>
     <row r="604">
       <c r="B604" s="2"/>
-      <c r="C604" s="31"/>
+      <c r="C604" s="34"/>
     </row>
     <row r="605">
       <c r="B605" s="2"/>
-      <c r="C605" s="31"/>
+      <c r="C605" s="34"/>
     </row>
     <row r="606">
       <c r="B606" s="2"/>
-      <c r="C606" s="31"/>
+      <c r="C606" s="34"/>
     </row>
     <row r="607">
       <c r="B607" s="2"/>
-      <c r="C607" s="31"/>
+      <c r="C607" s="34"/>
     </row>
     <row r="608">
       <c r="B608" s="2"/>
-      <c r="C608" s="31"/>
+      <c r="C608" s="34"/>
     </row>
     <row r="609">
       <c r="B609" s="2"/>
-      <c r="C609" s="31"/>
+      <c r="C609" s="34"/>
     </row>
     <row r="610">
       <c r="B610" s="2"/>
-      <c r="C610" s="31"/>
+      <c r="C610" s="34"/>
     </row>
     <row r="611">
       <c r="B611" s="2"/>
-      <c r="C611" s="31"/>
+      <c r="C611" s="34"/>
     </row>
     <row r="612">
       <c r="B612" s="2"/>
-      <c r="C612" s="31"/>
+      <c r="C612" s="34"/>
     </row>
     <row r="613">
       <c r="B613" s="2"/>
-      <c r="C613" s="31"/>
+      <c r="C613" s="34"/>
     </row>
     <row r="614">
       <c r="B614" s="2"/>
-      <c r="C614" s="31"/>
+      <c r="C614" s="34"/>
     </row>
     <row r="615">
       <c r="B615" s="2"/>
-      <c r="C615" s="31"/>
+      <c r="C615" s="34"/>
     </row>
     <row r="616">
       <c r="B616" s="2"/>
-      <c r="C616" s="31"/>
+      <c r="C616" s="34"/>
     </row>
     <row r="617">
       <c r="B617" s="2"/>
-      <c r="C617" s="31"/>
+      <c r="C617" s="34"/>
     </row>
     <row r="618">
       <c r="B618" s="2"/>
-      <c r="C618" s="31"/>
+      <c r="C618" s="34"/>
     </row>
     <row r="619">
       <c r="B619" s="2"/>
-      <c r="C619" s="31"/>
+      <c r="C619" s="34"/>
     </row>
     <row r="620">
       <c r="B620" s="2"/>
-      <c r="C620" s="31"/>
+      <c r="C620" s="34"/>
     </row>
     <row r="621">
       <c r="B621" s="2"/>
-      <c r="C621" s="31"/>
+      <c r="C621" s="34"/>
     </row>
     <row r="622">
       <c r="B622" s="2"/>
-      <c r="C622" s="31"/>
+      <c r="C622" s="34"/>
     </row>
     <row r="623">
       <c r="B623" s="2"/>
-      <c r="C623" s="31"/>
+      <c r="C623" s="34"/>
     </row>
     <row r="624">
       <c r="B624" s="2"/>
-      <c r="C624" s="31"/>
+      <c r="C624" s="34"/>
     </row>
     <row r="625">
       <c r="B625" s="2"/>
-      <c r="C625" s="31"/>
+      <c r="C625" s="34"/>
     </row>
     <row r="626">
       <c r="B626" s="2"/>
-      <c r="C626" s="31"/>
+      <c r="C626" s="34"/>
     </row>
     <row r="627">
       <c r="B627" s="2"/>
-      <c r="C627" s="31"/>
+      <c r="C627" s="34"/>
     </row>
     <row r="628">
       <c r="B628" s="2"/>
-      <c r="C628" s="31"/>
+      <c r="C628" s="34"/>
     </row>
     <row r="629">
       <c r="B629" s="2"/>
-      <c r="C629" s="31"/>
+      <c r="C629" s="34"/>
     </row>
     <row r="630">
       <c r="B630" s="2"/>
-      <c r="C630" s="31"/>
+      <c r="C630" s="34"/>
     </row>
     <row r="631">
       <c r="B631" s="2"/>
-      <c r="C631" s="31"/>
+      <c r="C631" s="34"/>
     </row>
     <row r="632">
       <c r="B632" s="2"/>
-      <c r="C632" s="31"/>
+      <c r="C632" s="34"/>
     </row>
     <row r="633">
       <c r="B633" s="2"/>
-      <c r="C633" s="31"/>
+      <c r="C633" s="34"/>
     </row>
     <row r="634">
       <c r="B634" s="2"/>
-      <c r="C634" s="31"/>
+      <c r="C634" s="34"/>
     </row>
     <row r="635">
       <c r="B635" s="2"/>
-      <c r="C635" s="31"/>
+      <c r="C635" s="34"/>
     </row>
     <row r="636">
       <c r="B636" s="2"/>
-      <c r="C636" s="31"/>
+      <c r="C636" s="34"/>
     </row>
     <row r="637">
       <c r="B637" s="2"/>
-      <c r="C637" s="31"/>
+      <c r="C637" s="34"/>
     </row>
     <row r="638">
       <c r="B638" s="2"/>
-      <c r="C638" s="31"/>
+      <c r="C638" s="34"/>
     </row>
     <row r="639">
       <c r="B639" s="2"/>
-      <c r="C639" s="31"/>
+      <c r="C639" s="34"/>
     </row>
     <row r="640">
       <c r="B640" s="2"/>
-      <c r="C640" s="31"/>
+      <c r="C640" s="34"/>
     </row>
     <row r="641">
       <c r="B641" s="2"/>
-      <c r="C641" s="31"/>
+      <c r="C641" s="34"/>
     </row>
     <row r="642">
       <c r="B642" s="2"/>
-      <c r="C642" s="31"/>
+      <c r="C642" s="34"/>
     </row>
     <row r="643">
       <c r="B643" s="2"/>
-      <c r="C643" s="31"/>
+      <c r="C643" s="34"/>
     </row>
     <row r="644">
       <c r="B644" s="2"/>
-      <c r="C644" s="31"/>
+      <c r="C644" s="34"/>
     </row>
     <row r="645">
       <c r="B645" s="2"/>
-      <c r="C645" s="31"/>
+      <c r="C645" s="34"/>
     </row>
     <row r="646">
       <c r="B646" s="2"/>
-      <c r="C646" s="31"/>
+      <c r="C646" s="34"/>
     </row>
     <row r="647">
       <c r="B647" s="2"/>
-      <c r="C647" s="31"/>
+      <c r="C647" s="34"/>
     </row>
     <row r="648">
       <c r="B648" s="2"/>
-      <c r="C648" s="31"/>
+      <c r="C648" s="34"/>
     </row>
     <row r="649">
       <c r="B649" s="2"/>
-      <c r="C649" s="31"/>
+      <c r="C649" s="34"/>
     </row>
     <row r="650">
       <c r="B650" s="2"/>
-      <c r="C650" s="31"/>
+      <c r="C650" s="34"/>
     </row>
     <row r="651">
       <c r="B651" s="2"/>
-      <c r="C651" s="31"/>
+      <c r="C651" s="34"/>
     </row>
     <row r="652">
       <c r="B652" s="2"/>
-      <c r="C652" s="31"/>
+      <c r="C652" s="34"/>
     </row>
     <row r="653">
       <c r="B653" s="2"/>
-      <c r="C653" s="31"/>
+      <c r="C653" s="34"/>
     </row>
     <row r="654">
       <c r="B654" s="2"/>
-      <c r="C654" s="31"/>
+      <c r="C654" s="34"/>
     </row>
     <row r="655">
       <c r="B655" s="2"/>
-      <c r="C655" s="31"/>
+      <c r="C655" s="34"/>
     </row>
     <row r="656">
       <c r="B656" s="2"/>
-      <c r="C656" s="31"/>
+      <c r="C656" s="34"/>
     </row>
     <row r="657">
       <c r="B657" s="2"/>
-      <c r="C657" s="31"/>
+      <c r="C657" s="34"/>
     </row>
     <row r="658">
       <c r="B658" s="2"/>
-      <c r="C658" s="31"/>
+      <c r="C658" s="34"/>
     </row>
     <row r="659">
       <c r="B659" s="2"/>
-      <c r="C659" s="31"/>
+      <c r="C659" s="34"/>
     </row>
     <row r="660">
       <c r="B660" s="2"/>
-      <c r="C660" s="31"/>
+      <c r="C660" s="34"/>
     </row>
     <row r="661">
       <c r="B661" s="2"/>
-      <c r="C661" s="31"/>
+      <c r="C661" s="34"/>
     </row>
     <row r="662">
       <c r="B662" s="2"/>
-      <c r="C662" s="31"/>
+      <c r="C662" s="34"/>
     </row>
     <row r="663">
       <c r="B663" s="2"/>
-      <c r="C663" s="31"/>
+      <c r="C663" s="34"/>
     </row>
     <row r="664">
       <c r="B664" s="2"/>
-      <c r="C664" s="31"/>
+      <c r="C664" s="34"/>
     </row>
     <row r="665">
       <c r="B665" s="2"/>
-      <c r="C665" s="31"/>
+      <c r="C665" s="34"/>
     </row>
     <row r="666">
       <c r="B666" s="2"/>
-      <c r="C666" s="31"/>
+      <c r="C666" s="34"/>
     </row>
     <row r="667">
       <c r="B667" s="2"/>
-      <c r="C667" s="31"/>
+      <c r="C667" s="34"/>
     </row>
     <row r="668">
       <c r="B668" s="2"/>
-      <c r="C668" s="31"/>
+      <c r="C668" s="34"/>
     </row>
     <row r="669">
       <c r="B669" s="2"/>
-      <c r="C669" s="31"/>
+      <c r="C669" s="34"/>
     </row>
     <row r="670">
       <c r="B670" s="2"/>
-      <c r="C670" s="31"/>
+      <c r="C670" s="34"/>
     </row>
     <row r="671">
       <c r="B671" s="2"/>
-      <c r="C671" s="31"/>
+      <c r="C671" s="34"/>
     </row>
     <row r="672">
       <c r="B672" s="2"/>
-      <c r="C672" s="31"/>
+      <c r="C672" s="34"/>
     </row>
     <row r="673">
       <c r="B673" s="2"/>
-      <c r="C673" s="31"/>
+      <c r="C673" s="34"/>
     </row>
     <row r="674">
       <c r="B674" s="2"/>
-      <c r="C674" s="31"/>
+      <c r="C674" s="34"/>
     </row>
     <row r="675">
       <c r="B675" s="2"/>
-      <c r="C675" s="31"/>
+      <c r="C675" s="34"/>
     </row>
     <row r="676">
       <c r="B676" s="2"/>
-      <c r="C676" s="31"/>
+      <c r="C676" s="34"/>
     </row>
     <row r="677">
       <c r="B677" s="2"/>
-      <c r="C677" s="31"/>
+      <c r="C677" s="34"/>
     </row>
     <row r="678">
       <c r="B678" s="2"/>
-      <c r="C678" s="31"/>
+      <c r="C678" s="34"/>
     </row>
     <row r="679">
       <c r="B679" s="2"/>
-      <c r="C679" s="31"/>
+      <c r="C679" s="34"/>
     </row>
     <row r="680">
       <c r="B680" s="2"/>
-      <c r="C680" s="31"/>
+      <c r="C680" s="34"/>
     </row>
     <row r="681">
       <c r="B681" s="2"/>
-      <c r="C681" s="31"/>
+      <c r="C681" s="34"/>
     </row>
     <row r="682">
       <c r="B682" s="2"/>
-      <c r="C682" s="31"/>
+      <c r="C682" s="34"/>
     </row>
     <row r="683">
       <c r="B683" s="2"/>
-      <c r="C683" s="31"/>
+      <c r="C683" s="34"/>
     </row>
     <row r="684">
       <c r="B684" s="2"/>
-      <c r="C684" s="31"/>
+      <c r="C684" s="34"/>
     </row>
     <row r="685">
       <c r="B685" s="2"/>
-      <c r="C685" s="31"/>
+      <c r="C685" s="34"/>
     </row>
     <row r="686">
       <c r="B686" s="2"/>
-      <c r="C686" s="31"/>
+      <c r="C686" s="34"/>
     </row>
     <row r="687">
       <c r="B687" s="2"/>
-      <c r="C687" s="31"/>
+      <c r="C687" s="34"/>
     </row>
     <row r="688">
       <c r="B688" s="2"/>
-      <c r="C688" s="31"/>
+      <c r="C688" s="34"/>
     </row>
     <row r="689">
       <c r="B689" s="2"/>
-      <c r="C689" s="31"/>
+      <c r="C689" s="34"/>
     </row>
     <row r="690">
       <c r="B690" s="2"/>
-      <c r="C690" s="31"/>
+      <c r="C690" s="34"/>
     </row>
     <row r="691">
       <c r="B691" s="2"/>
-      <c r="C691" s="31"/>
+      <c r="C691" s="34"/>
     </row>
     <row r="692">
       <c r="B692" s="2"/>
-      <c r="C692" s="31"/>
+      <c r="C692" s="34"/>
     </row>
     <row r="693">
       <c r="B693" s="2"/>
-      <c r="C693" s="31"/>
+      <c r="C693" s="34"/>
     </row>
     <row r="694">
       <c r="B694" s="2"/>
-      <c r="C694" s="31"/>
+      <c r="C694" s="34"/>
     </row>
     <row r="695">
       <c r="B695" s="2"/>
-      <c r="C695" s="31"/>
+      <c r="C695" s="34"/>
     </row>
     <row r="696">
       <c r="B696" s="2"/>
-      <c r="C696" s="31"/>
+      <c r="C696" s="34"/>
     </row>
     <row r="697">
       <c r="B697" s="2"/>
-      <c r="C697" s="31"/>
+      <c r="C697" s="34"/>
     </row>
     <row r="698">
       <c r="B698" s="2"/>
-      <c r="C698" s="31"/>
+      <c r="C698" s="34"/>
     </row>
     <row r="699">
       <c r="B699" s="2"/>
-      <c r="C699" s="31"/>
+      <c r="C699" s="34"/>
     </row>
     <row r="700">
       <c r="B700" s="2"/>
-      <c r="C700" s="31"/>
+      <c r="C700" s="34"/>
     </row>
     <row r="701">
       <c r="B701" s="2"/>
-      <c r="C701" s="31"/>
+      <c r="C701" s="34"/>
     </row>
     <row r="702">
       <c r="B702" s="2"/>
-      <c r="C702" s="31"/>
+      <c r="C702" s="34"/>
     </row>
     <row r="703">
       <c r="B703" s="2"/>
-      <c r="C703" s="31"/>
+      <c r="C703" s="34"/>
     </row>
     <row r="704">
       <c r="B704" s="2"/>
-      <c r="C704" s="31"/>
+      <c r="C704" s="34"/>
     </row>
     <row r="705">
       <c r="B705" s="2"/>
-      <c r="C705" s="31"/>
+      <c r="C705" s="34"/>
     </row>
     <row r="706">
       <c r="B706" s="2"/>
-      <c r="C706" s="31"/>
+      <c r="C706" s="34"/>
     </row>
     <row r="707">
       <c r="B707" s="2"/>
-      <c r="C707" s="31"/>
+      <c r="C707" s="34"/>
     </row>
     <row r="708">
       <c r="B708" s="2"/>
-      <c r="C708" s="31"/>
+      <c r="C708" s="34"/>
     </row>
     <row r="709">
       <c r="B709" s="2"/>
-      <c r="C709" s="31"/>
+      <c r="C709" s="34"/>
     </row>
     <row r="710">
       <c r="B710" s="2"/>
-      <c r="C710" s="31"/>
+      <c r="C710" s="34"/>
     </row>
     <row r="711">
       <c r="B711" s="2"/>
-      <c r="C711" s="31"/>
+      <c r="C711" s="34"/>
     </row>
     <row r="712">
       <c r="B712" s="2"/>
-      <c r="C712" s="31"/>
+      <c r="C712" s="34"/>
     </row>
     <row r="713">
       <c r="B713" s="2"/>
-      <c r="C713" s="31"/>
+      <c r="C713" s="34"/>
     </row>
     <row r="714">
       <c r="B714" s="2"/>
-      <c r="C714" s="31"/>
+      <c r="C714" s="34"/>
     </row>
     <row r="715">
       <c r="B715" s="2"/>
-      <c r="C715" s="31"/>
+      <c r="C715" s="34"/>
     </row>
     <row r="716">
       <c r="B716" s="2"/>
-      <c r="C716" s="31"/>
+      <c r="C716" s="34"/>
     </row>
     <row r="717">
       <c r="B717" s="2"/>
-      <c r="C717" s="31"/>
+      <c r="C717" s="34"/>
     </row>
     <row r="718">
       <c r="B718" s="2"/>
-      <c r="C718" s="31"/>
+      <c r="C718" s="34"/>
     </row>
     <row r="719">
       <c r="B719" s="2"/>
-      <c r="C719" s="31"/>
+      <c r="C719" s="34"/>
     </row>
     <row r="720">
       <c r="B720" s="2"/>
-      <c r="C720" s="31"/>
+      <c r="C720" s="34"/>
     </row>
     <row r="721">
       <c r="B721" s="2"/>
-      <c r="C721" s="31"/>
+      <c r="C721" s="34"/>
     </row>
     <row r="722">
       <c r="B722" s="2"/>
-      <c r="C722" s="31"/>
+      <c r="C722" s="34"/>
     </row>
     <row r="723">
       <c r="B723" s="2"/>
-      <c r="C723" s="31"/>
+      <c r="C723" s="34"/>
     </row>
     <row r="724">
       <c r="B724" s="2"/>
-      <c r="C724" s="31"/>
+      <c r="C724" s="34"/>
     </row>
     <row r="725">
       <c r="B725" s="2"/>
-      <c r="C725" s="31"/>
+      <c r="C725" s="34"/>
     </row>
     <row r="726">
       <c r="B726" s="2"/>
-      <c r="C726" s="31"/>
+      <c r="C726" s="34"/>
     </row>
     <row r="727">
       <c r="B727" s="2"/>
-      <c r="C727" s="31"/>
+      <c r="C727" s="34"/>
     </row>
     <row r="728">
       <c r="B728" s="2"/>
-      <c r="C728" s="31"/>
+      <c r="C728" s="34"/>
     </row>
     <row r="729">
       <c r="B729" s="2"/>
-      <c r="C729" s="31"/>
+      <c r="C729" s="34"/>
     </row>
     <row r="730">
       <c r="B730" s="2"/>
-      <c r="C730" s="31"/>
+      <c r="C730" s="34"/>
     </row>
     <row r="731">
       <c r="B731" s="2"/>
-      <c r="C731" s="31"/>
+      <c r="C731" s="34"/>
     </row>
     <row r="732">
       <c r="B732" s="2"/>
-      <c r="C732" s="31"/>
+      <c r="C732" s="34"/>
     </row>
     <row r="733">
       <c r="B733" s="2"/>
-      <c r="C733" s="31"/>
+      <c r="C733" s="34"/>
     </row>
     <row r="734">
       <c r="B734" s="2"/>
-      <c r="C734" s="31"/>
+      <c r="C734" s="34"/>
     </row>
     <row r="735">
       <c r="B735" s="2"/>
-      <c r="C735" s="31"/>
+      <c r="C735" s="34"/>
     </row>
     <row r="736">
       <c r="B736" s="2"/>
-      <c r="C736" s="31"/>
+      <c r="C736" s="34"/>
     </row>
     <row r="737">
       <c r="B737" s="2"/>
-      <c r="C737" s="31"/>
+      <c r="C737" s="34"/>
     </row>
     <row r="738">
       <c r="B738" s="2"/>
-      <c r="C738" s="31"/>
+      <c r="C738" s="34"/>
     </row>
     <row r="739">
       <c r="B739" s="2"/>
-      <c r="C739" s="31"/>
+      <c r="C739" s="34"/>
     </row>
     <row r="740">
       <c r="B740" s="2"/>
-      <c r="C740" s="31"/>
+      <c r="C740" s="34"/>
     </row>
     <row r="741">
       <c r="B741" s="2"/>
-      <c r="C741" s="31"/>
+      <c r="C741" s="34"/>
     </row>
     <row r="742">
       <c r="B742" s="2"/>
-      <c r="C742" s="31"/>
+      <c r="C742" s="34"/>
     </row>
     <row r="743">
       <c r="B743" s="2"/>
-      <c r="C743" s="31"/>
+      <c r="C743" s="34"/>
     </row>
     <row r="744">
       <c r="B744" s="2"/>
-      <c r="C744" s="31"/>
+      <c r="C744" s="34"/>
     </row>
     <row r="745">
       <c r="B745" s="2"/>
-      <c r="C745" s="31"/>
+      <c r="C745" s="34"/>
     </row>
     <row r="746">
       <c r="B746" s="2"/>
-      <c r="C746" s="31"/>
+      <c r="C746" s="34"/>
     </row>
     <row r="747">
       <c r="B747" s="2"/>
-      <c r="C747" s="31"/>
+      <c r="C747" s="34"/>
     </row>
     <row r="748">
       <c r="B748" s="2"/>
-      <c r="C748" s="31"/>
+      <c r="C748" s="34"/>
     </row>
     <row r="749">
       <c r="B749" s="2"/>
-      <c r="C749" s="31"/>
+      <c r="C749" s="34"/>
     </row>
     <row r="750">
       <c r="B750" s="2"/>
-      <c r="C750" s="31"/>
+      <c r="C750" s="34"/>
     </row>
     <row r="751">
       <c r="B751" s="2"/>
-      <c r="C751" s="31"/>
+      <c r="C751" s="34"/>
     </row>
     <row r="752">
       <c r="B752" s="2"/>
-      <c r="C752" s="31"/>
+      <c r="C752" s="34"/>
     </row>
     <row r="753">
       <c r="B753" s="2"/>
-      <c r="C753" s="31"/>
+      <c r="C753" s="34"/>
     </row>
     <row r="754">
       <c r="B754" s="2"/>
-      <c r="C754" s="31"/>
+      <c r="C754" s="34"/>
     </row>
     <row r="755">
       <c r="B755" s="2"/>
-      <c r="C755" s="31"/>
+      <c r="C755" s="34"/>
     </row>
     <row r="756">
       <c r="B756" s="2"/>
-      <c r="C756" s="31"/>
+      <c r="C756" s="34"/>
     </row>
     <row r="757">
       <c r="B757" s="2"/>
-      <c r="C757" s="31"/>
+      <c r="C757" s="34"/>
     </row>
     <row r="758">
       <c r="B758" s="2"/>
-      <c r="C758" s="31"/>
+      <c r="C758" s="34"/>
     </row>
     <row r="759">
       <c r="B759" s="2"/>
-      <c r="C759" s="31"/>
+      <c r="C759" s="34"/>
     </row>
     <row r="760">
       <c r="B760" s="2"/>
-      <c r="C760" s="31"/>
+      <c r="C760" s="34"/>
     </row>
     <row r="761">
       <c r="B761" s="2"/>
-      <c r="C761" s="31"/>
+      <c r="C761" s="34"/>
     </row>
     <row r="762">
       <c r="B762" s="2"/>
-      <c r="C762" s="31"/>
+      <c r="C762" s="34"/>
     </row>
     <row r="763">
       <c r="B763" s="2"/>
-      <c r="C763" s="31"/>
+      <c r="C763" s="34"/>
     </row>
     <row r="764">
       <c r="B764" s="2"/>
-      <c r="C764" s="31"/>
+      <c r="C764" s="34"/>
     </row>
     <row r="765">
       <c r="B765" s="2"/>
-      <c r="C765" s="31"/>
+      <c r="C765" s="34"/>
     </row>
     <row r="766">
       <c r="B766" s="2"/>
-      <c r="C766" s="31"/>
+      <c r="C766" s="34"/>
     </row>
     <row r="767">
       <c r="B767" s="2"/>
-      <c r="C767" s="31"/>
+      <c r="C767" s="34"/>
     </row>
     <row r="768">
       <c r="B768" s="2"/>
-      <c r="C768" s="31"/>
+      <c r="C768" s="34"/>
     </row>
     <row r="769">
       <c r="B769" s="2"/>
-      <c r="C769" s="31"/>
+      <c r="C769" s="34"/>
     </row>
     <row r="770">
       <c r="B770" s="2"/>
-      <c r="C770" s="31"/>
+      <c r="C770" s="34"/>
     </row>
     <row r="771">
       <c r="B771" s="2"/>
-      <c r="C771" s="31"/>
+      <c r="C771" s="34"/>
     </row>
     <row r="772">
       <c r="B772" s="2"/>
-      <c r="C772" s="31"/>
+      <c r="C772" s="34"/>
     </row>
     <row r="773">
       <c r="B773" s="2"/>
-      <c r="C773" s="31"/>
+      <c r="C773" s="34"/>
     </row>
     <row r="774">
       <c r="B774" s="2"/>
-      <c r="C774" s="31"/>
+      <c r="C774" s="34"/>
     </row>
     <row r="775">
       <c r="B775" s="2"/>
-      <c r="C775" s="31"/>
+      <c r="C775" s="34"/>
     </row>
     <row r="776">
       <c r="B776" s="2"/>
-      <c r="C776" s="31"/>
+      <c r="C776" s="34"/>
     </row>
     <row r="777">
       <c r="B777" s="2"/>
-      <c r="C777" s="31"/>
+      <c r="C777" s="34"/>
     </row>
     <row r="778">
       <c r="B778" s="2"/>
-      <c r="C778" s="31"/>
+      <c r="C778" s="34"/>
     </row>
     <row r="779">
       <c r="B779" s="2"/>
-      <c r="C779" s="31"/>
+      <c r="C779" s="34"/>
     </row>
     <row r="780">
       <c r="B780" s="2"/>
-      <c r="C780" s="31"/>
+      <c r="C780" s="34"/>
     </row>
     <row r="781">
       <c r="B781" s="2"/>
-      <c r="C781" s="31"/>
+      <c r="C781" s="34"/>
     </row>
     <row r="782">
       <c r="B782" s="2"/>
-      <c r="C782" s="31"/>
+      <c r="C782" s="34"/>
     </row>
     <row r="783">
       <c r="B783" s="2"/>
-      <c r="C783" s="31"/>
+      <c r="C783" s="34"/>
     </row>
     <row r="784">
       <c r="B784" s="2"/>
-      <c r="C784" s="31"/>
+      <c r="C784" s="34"/>
     </row>
     <row r="785">
       <c r="B785" s="2"/>
-      <c r="C785" s="31"/>
+      <c r="C785" s="34"/>
     </row>
     <row r="786">
       <c r="B786" s="2"/>
-      <c r="C786" s="31"/>
+      <c r="C786" s="34"/>
     </row>
     <row r="787">
       <c r="B787" s="2"/>
-      <c r="C787" s="31"/>
+      <c r="C787" s="34"/>
     </row>
     <row r="788">
       <c r="B788" s="2"/>
-      <c r="C788" s="31"/>
+      <c r="C788" s="34"/>
     </row>
     <row r="789">
       <c r="B789" s="2"/>
-      <c r="C789" s="31"/>
+      <c r="C789" s="34"/>
     </row>
     <row r="790">
       <c r="B790" s="2"/>
-      <c r="C790" s="31"/>
+      <c r="C790" s="34"/>
     </row>
     <row r="791">
       <c r="B791" s="2"/>
-      <c r="C791" s="31"/>
+      <c r="C791" s="34"/>
     </row>
     <row r="792">
       <c r="B792" s="2"/>
-      <c r="C792" s="31"/>
+      <c r="C792" s="34"/>
     </row>
     <row r="793">
       <c r="B793" s="2"/>
-      <c r="C793" s="31"/>
+      <c r="C793" s="34"/>
     </row>
     <row r="794">
       <c r="B794" s="2"/>
-      <c r="C794" s="31"/>
+      <c r="C794" s="34"/>
     </row>
     <row r="795">
       <c r="B795" s="2"/>
-      <c r="C795" s="31"/>
+      <c r="C795" s="34"/>
     </row>
     <row r="796">
       <c r="B796" s="2"/>
-      <c r="C796" s="31"/>
+      <c r="C796" s="34"/>
     </row>
     <row r="797">
       <c r="B797" s="2"/>
-      <c r="C797" s="31"/>
+      <c r="C797" s="34"/>
     </row>
     <row r="798">
       <c r="B798" s="2"/>
-      <c r="C798" s="31"/>
+      <c r="C798" s="34"/>
     </row>
     <row r="799">
       <c r="B799" s="2"/>
-      <c r="C799" s="31"/>
+      <c r="C799" s="34"/>
     </row>
     <row r="800">
       <c r="B800" s="2"/>
-      <c r="C800" s="31"/>
+      <c r="C800" s="34"/>
     </row>
     <row r="801">
       <c r="B801" s="2"/>
-      <c r="C801" s="31"/>
+      <c r="C801" s="34"/>
     </row>
     <row r="802">
       <c r="B802" s="2"/>
-      <c r="C802" s="31"/>
+      <c r="C802" s="34"/>
     </row>
     <row r="803">
       <c r="B803" s="2"/>
-      <c r="C803" s="31"/>
+      <c r="C803" s="34"/>
     </row>
     <row r="804">
       <c r="B804" s="2"/>
-      <c r="C804" s="31"/>
+      <c r="C804" s="34"/>
     </row>
     <row r="805">
       <c r="B805" s="2"/>
-      <c r="C805" s="31"/>
+      <c r="C805" s="34"/>
     </row>
     <row r="806">
       <c r="B806" s="2"/>
-      <c r="C806" s="31"/>
+      <c r="C806" s="34"/>
     </row>
     <row r="807">
       <c r="B807" s="2"/>
-      <c r="C807" s="31"/>
+      <c r="C807" s="34"/>
     </row>
     <row r="808">
       <c r="B808" s="2"/>
-      <c r="C808" s="31"/>
+      <c r="C808" s="34"/>
     </row>
     <row r="809">
       <c r="B809" s="2"/>
-      <c r="C809" s="31"/>
+      <c r="C809" s="34"/>
     </row>
     <row r="810">
       <c r="B810" s="2"/>
-      <c r="C810" s="31"/>
+      <c r="C810" s="34"/>
     </row>
     <row r="811">
       <c r="B811" s="2"/>
-      <c r="C811" s="31"/>
+      <c r="C811" s="34"/>
     </row>
     <row r="812">
       <c r="B812" s="2"/>
-      <c r="C812" s="31"/>
+      <c r="C812" s="34"/>
     </row>
     <row r="813">
       <c r="B813" s="2"/>
-      <c r="C813" s="31"/>
+      <c r="C813" s="34"/>
     </row>
     <row r="814">
       <c r="B814" s="2"/>
-      <c r="C814" s="31"/>
+      <c r="C814" s="34"/>
     </row>
     <row r="815">
       <c r="B815" s="2"/>
-      <c r="C815" s="31"/>
+      <c r="C815" s="34"/>
     </row>
     <row r="816">
       <c r="B816" s="2"/>
-      <c r="C816" s="31"/>
+      <c r="C816" s="34"/>
     </row>
     <row r="817">
       <c r="B817" s="2"/>
-      <c r="C817" s="31"/>
+      <c r="C817" s="34"/>
     </row>
     <row r="818">
       <c r="B818" s="2"/>
-      <c r="C818" s="31"/>
+      <c r="C818" s="34"/>
     </row>
     <row r="819">
       <c r="B819" s="2"/>
-      <c r="C819" s="31"/>
+      <c r="C819" s="34"/>
     </row>
     <row r="820">
       <c r="B820" s="2"/>
-      <c r="C820" s="31"/>
+      <c r="C820" s="34"/>
     </row>
     <row r="821">
       <c r="B821" s="2"/>
-      <c r="C821" s="31"/>
+      <c r="C821" s="34"/>
     </row>
     <row r="822">
       <c r="B822" s="2"/>
-      <c r="C822" s="31"/>
+      <c r="C822" s="34"/>
     </row>
     <row r="823">
       <c r="B823" s="2"/>
-      <c r="C823" s="31"/>
+      <c r="C823" s="34"/>
     </row>
     <row r="824">
       <c r="B824" s="2"/>
-      <c r="C824" s="31"/>
+      <c r="C824" s="34"/>
     </row>
     <row r="825">
       <c r="B825" s="2"/>
-      <c r="C825" s="31"/>
+      <c r="C825" s="34"/>
     </row>
     <row r="826">
       <c r="B826" s="2"/>
-      <c r="C826" s="31"/>
+      <c r="C826" s="34"/>
     </row>
     <row r="827">
       <c r="B827" s="2"/>
-      <c r="C827" s="31"/>
+      <c r="C827" s="34"/>
     </row>
     <row r="828">
       <c r="B828" s="2"/>
-      <c r="C828" s="31"/>
+      <c r="C828" s="34"/>
     </row>
     <row r="829">
       <c r="B829" s="2"/>
-      <c r="C829" s="31"/>
+      <c r="C829" s="34"/>
     </row>
     <row r="830">
       <c r="B830" s="2"/>
-      <c r="C830" s="31"/>
+      <c r="C830" s="34"/>
     </row>
     <row r="831">
       <c r="B831" s="2"/>
-      <c r="C831" s="31"/>
+      <c r="C831" s="34"/>
     </row>
     <row r="832">
       <c r="B832" s="2"/>
-      <c r="C832" s="31"/>
+      <c r="C832" s="34"/>
     </row>
     <row r="833">
       <c r="B833" s="2"/>
-      <c r="C833" s="31"/>
+      <c r="C833" s="34"/>
     </row>
     <row r="834">
       <c r="B834" s="2"/>
-      <c r="C834" s="31"/>
+      <c r="C834" s="34"/>
     </row>
     <row r="835">
       <c r="B835" s="2"/>
-      <c r="C835" s="31"/>
+      <c r="C835" s="34"/>
     </row>
     <row r="836">
       <c r="B836" s="2"/>
-      <c r="C836" s="31"/>
+      <c r="C836" s="34"/>
     </row>
     <row r="837">
       <c r="B837" s="2"/>
-      <c r="C837" s="31"/>
+      <c r="C837" s="34"/>
     </row>
     <row r="838">
       <c r="B838" s="2"/>
-      <c r="C838" s="31"/>
+      <c r="C838" s="34"/>
     </row>
     <row r="839">
       <c r="B839" s="2"/>
-      <c r="C839" s="31"/>
+      <c r="C839" s="34"/>
     </row>
     <row r="840">
       <c r="B840" s="2"/>
-      <c r="C840" s="31"/>
+      <c r="C840" s="34"/>
     </row>
     <row r="841">
       <c r="B841" s="2"/>
-      <c r="C841" s="31"/>
+      <c r="C841" s="34"/>
     </row>
     <row r="842">
       <c r="B842" s="2"/>
-      <c r="C842" s="31"/>
+      <c r="C842" s="34"/>
     </row>
     <row r="843">
       <c r="B843" s="2"/>
-      <c r="C843" s="31"/>
+      <c r="C843" s="34"/>
     </row>
     <row r="844">
       <c r="B844" s="2"/>
-      <c r="C844" s="31"/>
+      <c r="C844" s="34"/>
     </row>
     <row r="845">
       <c r="B845" s="2"/>
-      <c r="C845" s="31"/>
+      <c r="C845" s="34"/>
     </row>
     <row r="846">
       <c r="B846" s="2"/>
-      <c r="C846" s="31"/>
+      <c r="C846" s="34"/>
     </row>
     <row r="847">
       <c r="B847" s="2"/>
-      <c r="C847" s="31"/>
+      <c r="C847" s="34"/>
     </row>
     <row r="848">
       <c r="B848" s="2"/>
-      <c r="C848" s="31"/>
+      <c r="C848" s="34"/>
     </row>
     <row r="849">
       <c r="B849" s="2"/>
-      <c r="C849" s="31"/>
+      <c r="C849" s="34"/>
     </row>
     <row r="850">
       <c r="B850" s="2"/>
-      <c r="C850" s="31"/>
+      <c r="C850" s="34"/>
     </row>
     <row r="851">
       <c r="B851" s="2"/>
-      <c r="C851" s="31"/>
+      <c r="C851" s="34"/>
     </row>
     <row r="852">
       <c r="B852" s="2"/>
-      <c r="C852" s="31"/>
+      <c r="C852" s="34"/>
     </row>
     <row r="853">
       <c r="B853" s="2"/>
-      <c r="C853" s="31"/>
+      <c r="C853" s="34"/>
     </row>
     <row r="854">
       <c r="B854" s="2"/>
-      <c r="C854" s="31"/>
+      <c r="C854" s="34"/>
     </row>
     <row r="855">
       <c r="B855" s="2"/>
-      <c r="C855" s="31"/>
+      <c r="C855" s="34"/>
     </row>
     <row r="856">
       <c r="B856" s="2"/>
-      <c r="C856" s="31"/>
+      <c r="C856" s="34"/>
     </row>
     <row r="857">
       <c r="B857" s="2"/>
-      <c r="C857" s="31"/>
+      <c r="C857" s="34"/>
     </row>
     <row r="858">
       <c r="B858" s="2"/>
-      <c r="C858" s="31"/>
+      <c r="C858" s="34"/>
     </row>
     <row r="859">
       <c r="B859" s="2"/>
-      <c r="C859" s="31"/>
+      <c r="C859" s="34"/>
     </row>
     <row r="860">
       <c r="B860" s="2"/>
-      <c r="C860" s="31"/>
+      <c r="C860" s="34"/>
     </row>
     <row r="861">
       <c r="B861" s="2"/>
-      <c r="C861" s="31"/>
+      <c r="C861" s="34"/>
     </row>
     <row r="862">
       <c r="B862" s="2"/>
-      <c r="C862" s="31"/>
+      <c r="C862" s="34"/>
     </row>
     <row r="863">
       <c r="B863" s="2"/>
-      <c r="C863" s="31"/>
+      <c r="C863" s="34"/>
     </row>
     <row r="864">
       <c r="B864" s="2"/>
-      <c r="C864" s="31"/>
+      <c r="C864" s="34"/>
     </row>
     <row r="865">
       <c r="B865" s="2"/>
-      <c r="C865" s="31"/>
+      <c r="C865" s="34"/>
     </row>
     <row r="866">
       <c r="B866" s="2"/>
-      <c r="C866" s="31"/>
+      <c r="C866" s="34"/>
     </row>
     <row r="867">
       <c r="B867" s="2"/>
-      <c r="C867" s="31"/>
+      <c r="C867" s="34"/>
     </row>
     <row r="868">
       <c r="B868" s="2"/>
-      <c r="C868" s="31"/>
+      <c r="C868" s="34"/>
     </row>
     <row r="869">
       <c r="B869" s="2"/>
-      <c r="C869" s="31"/>
+      <c r="C869" s="34"/>
     </row>
     <row r="870">
       <c r="B870" s="2"/>
-      <c r="C870" s="31"/>
+      <c r="C870" s="34"/>
     </row>
     <row r="871">
       <c r="B871" s="2"/>
-      <c r="C871" s="31"/>
+      <c r="C871" s="34"/>
     </row>
     <row r="872">
       <c r="B872" s="2"/>
-      <c r="C872" s="31"/>
+      <c r="C872" s="34"/>
     </row>
     <row r="873">
       <c r="B873" s="2"/>
-      <c r="C873" s="31"/>
+      <c r="C873" s="34"/>
     </row>
     <row r="874">
       <c r="B874" s="2"/>
-      <c r="C874" s="31"/>
+      <c r="C874" s="34"/>
     </row>
     <row r="875">
       <c r="B875" s="2"/>
-      <c r="C875" s="31"/>
+      <c r="C875" s="34"/>
     </row>
     <row r="876">
       <c r="B876" s="2"/>
-      <c r="C876" s="31"/>
+      <c r="C876" s="34"/>
     </row>
     <row r="877">
       <c r="B877" s="2"/>
-      <c r="C877" s="31"/>
+      <c r="C877" s="34"/>
     </row>
     <row r="878">
       <c r="B878" s="2"/>
-      <c r="C878" s="31"/>
+      <c r="C878" s="34"/>
     </row>
     <row r="879">
       <c r="B879" s="2"/>
-      <c r="C879" s="31"/>
+      <c r="C879" s="34"/>
     </row>
     <row r="880">
       <c r="B880" s="2"/>
-      <c r="C880" s="31"/>
+      <c r="C880" s="34"/>
     </row>
     <row r="881">
       <c r="B881" s="2"/>
-      <c r="C881" s="31"/>
+      <c r="C881" s="34"/>
     </row>
     <row r="882">
       <c r="B882" s="2"/>
-      <c r="C882" s="31"/>
+      <c r="C882" s="34"/>
     </row>
     <row r="883">
       <c r="B883" s="2"/>
-      <c r="C883" s="31"/>
+      <c r="C883" s="34"/>
     </row>
     <row r="884">
       <c r="B884" s="2"/>
-      <c r="C884" s="31"/>
+      <c r="C884" s="34"/>
     </row>
     <row r="885">
       <c r="B885" s="2"/>
-      <c r="C885" s="31"/>
+      <c r="C885" s="34"/>
     </row>
     <row r="886">
       <c r="B886" s="2"/>
-      <c r="C886" s="31"/>
+      <c r="C886" s="34"/>
     </row>
     <row r="887">
       <c r="B887" s="2"/>
-      <c r="C887" s="31"/>
+      <c r="C887" s="34"/>
     </row>
     <row r="888">
       <c r="B888" s="2"/>
-      <c r="C888" s="31"/>
+      <c r="C888" s="34"/>
     </row>
     <row r="889">
       <c r="B889" s="2"/>
-      <c r="C889" s="31"/>
+      <c r="C889" s="34"/>
     </row>
     <row r="890">
       <c r="B890" s="2"/>
-      <c r="C890" s="31"/>
+      <c r="C890" s="34"/>
     </row>
     <row r="891">
       <c r="B891" s="2"/>
-      <c r="C891" s="31"/>
+      <c r="C891" s="34"/>
     </row>
     <row r="892">
       <c r="B892" s="2"/>
-      <c r="C892" s="31"/>
+      <c r="C892" s="34"/>
     </row>
     <row r="893">
       <c r="B893" s="2"/>
-      <c r="C893" s="31"/>
+      <c r="C893" s="34"/>
     </row>
     <row r="894">
       <c r="B894" s="2"/>
-      <c r="C894" s="31"/>
+      <c r="C894" s="34"/>
     </row>
     <row r="895">
       <c r="B895" s="2"/>
-      <c r="C895" s="31"/>
+      <c r="C895" s="34"/>
     </row>
     <row r="896">
       <c r="B896" s="2"/>
-      <c r="C896" s="31"/>
+      <c r="C896" s="34"/>
     </row>
     <row r="897">
       <c r="B897" s="2"/>
-      <c r="C897" s="31"/>
+      <c r="C897" s="34"/>
     </row>
     <row r="898">
       <c r="B898" s="2"/>
-      <c r="C898" s="31"/>
+      <c r="C898" s="34"/>
     </row>
     <row r="899">
       <c r="B899" s="2"/>
-      <c r="C899" s="31"/>
+      <c r="C899" s="34"/>
     </row>
     <row r="900">
       <c r="B900" s="2"/>
-      <c r="C900" s="31"/>
+      <c r="C900" s="34"/>
     </row>
     <row r="901">
       <c r="B901" s="2"/>
-      <c r="C901" s="31"/>
+      <c r="C901" s="34"/>
     </row>
     <row r="902">
       <c r="B902" s="2"/>
-      <c r="C902" s="31"/>
+      <c r="C902" s="34"/>
     </row>
     <row r="903">
       <c r="B903" s="2"/>
-      <c r="C903" s="31"/>
+      <c r="C903" s="34"/>
     </row>
     <row r="904">
       <c r="B904" s="2"/>
-      <c r="C904" s="31"/>
+      <c r="C904" s="34"/>
     </row>
     <row r="905">
       <c r="B905" s="2"/>
-      <c r="C905" s="31"/>
+      <c r="C905" s="34"/>
     </row>
     <row r="906">
       <c r="B906" s="2"/>
-      <c r="C906" s="31"/>
+      <c r="C906" s="34"/>
     </row>
     <row r="907">
       <c r="B907" s="2"/>
-      <c r="C907" s="31"/>
+      <c r="C907" s="34"/>
     </row>
     <row r="908">
       <c r="B908" s="2"/>
-      <c r="C908" s="31"/>
+      <c r="C908" s="34"/>
     </row>
     <row r="909">
       <c r="B909" s="2"/>
-      <c r="C909" s="31"/>
+      <c r="C909" s="34"/>
     </row>
     <row r="910">
       <c r="B910" s="2"/>
-      <c r="C910" s="31"/>
+      <c r="C910" s="34"/>
     </row>
     <row r="911">
       <c r="B911" s="2"/>
-      <c r="C911" s="31"/>
+      <c r="C911" s="34"/>
     </row>
     <row r="912">
       <c r="B912" s="2"/>
-      <c r="C912" s="31"/>
+      <c r="C912" s="34"/>
     </row>
     <row r="913">
       <c r="B913" s="2"/>
-      <c r="C913" s="31"/>
+      <c r="C913" s="34"/>
     </row>
     <row r="914">
       <c r="B914" s="2"/>
-      <c r="C914" s="31"/>
+      <c r="C914" s="34"/>
     </row>
     <row r="915">
       <c r="B915" s="2"/>
-      <c r="C915" s="31"/>
+      <c r="C915" s="34"/>
     </row>
     <row r="916">
       <c r="B916" s="2"/>
-      <c r="C916" s="31"/>
+      <c r="C916" s="34"/>
     </row>
     <row r="917">
       <c r="B917" s="2"/>
-      <c r="C917" s="31"/>
+      <c r="C917" s="34"/>
     </row>
     <row r="918">
       <c r="B918" s="2"/>
-      <c r="C918" s="31"/>
+      <c r="C918" s="34"/>
     </row>
     <row r="919">
       <c r="B919" s="2"/>
-      <c r="C919" s="31"/>
+      <c r="C919" s="34"/>
     </row>
     <row r="920">
       <c r="B920" s="2"/>
-      <c r="C920" s="31"/>
+      <c r="C920" s="34"/>
     </row>
     <row r="921">
       <c r="B921" s="2"/>
-      <c r="C921" s="31"/>
+      <c r="C921" s="34"/>
     </row>
     <row r="922">
       <c r="B922" s="2"/>
-      <c r="C922" s="31"/>
+      <c r="C922" s="34"/>
     </row>
     <row r="923">
       <c r="B923" s="2"/>
-      <c r="C923" s="31"/>
+      <c r="C923" s="34"/>
     </row>
     <row r="924">
       <c r="B924" s="2"/>
-      <c r="C924" s="31"/>
+      <c r="C924" s="34"/>
     </row>
     <row r="925">
       <c r="B925" s="2"/>
-      <c r="C925" s="31"/>
+      <c r="C925" s="34"/>
     </row>
     <row r="926">
       <c r="B926" s="2"/>
-      <c r="C926" s="31"/>
+      <c r="C926" s="34"/>
     </row>
     <row r="927">
       <c r="B927" s="2"/>
-      <c r="C927" s="31"/>
+      <c r="C927" s="34"/>
     </row>
     <row r="928">
       <c r="B928" s="2"/>
-      <c r="C928" s="31"/>
+      <c r="C928" s="34"/>
     </row>
     <row r="929">
       <c r="B929" s="2"/>
-      <c r="C929" s="31"/>
+      <c r="C929" s="34"/>
     </row>
     <row r="930">
       <c r="B930" s="2"/>
-      <c r="C930" s="31"/>
+      <c r="C930" s="34"/>
     </row>
     <row r="931">
       <c r="B931" s="2"/>
-      <c r="C931" s="31"/>
+      <c r="C931" s="34"/>
     </row>
     <row r="932">
       <c r="B932" s="2"/>
-      <c r="C932" s="31"/>
+      <c r="C932" s="34"/>
     </row>
     <row r="933">
       <c r="B933" s="2"/>
-      <c r="C933" s="31"/>
+      <c r="C933" s="34"/>
     </row>
     <row r="934">
       <c r="B934" s="2"/>
-      <c r="C934" s="31"/>
+      <c r="C934" s="34"/>
     </row>
     <row r="935">
       <c r="B935" s="2"/>
-      <c r="C935" s="31"/>
+      <c r="C935" s="34"/>
     </row>
     <row r="936">
       <c r="B936" s="2"/>
-      <c r="C936" s="31"/>
+      <c r="C936" s="34"/>
     </row>
     <row r="937">
       <c r="B937" s="2"/>
-      <c r="C937" s="31"/>
+      <c r="C937" s="34"/>
     </row>
     <row r="938">
       <c r="B938" s="2"/>
-      <c r="C938" s="31"/>
+      <c r="C938" s="34"/>
     </row>
     <row r="939">
       <c r="B939" s="2"/>
-      <c r="C939" s="31"/>
+      <c r="C939" s="34"/>
     </row>
     <row r="940">
       <c r="B940" s="2"/>
-      <c r="C940" s="31"/>
+      <c r="C940" s="34"/>
     </row>
     <row r="941">
       <c r="B941" s="2"/>
-      <c r="C941" s="31"/>
+      <c r="C941" s="34"/>
     </row>
     <row r="942">
       <c r="B942" s="2"/>
-      <c r="C942" s="31"/>
+      <c r="C942" s="34"/>
     </row>
     <row r="943">
       <c r="B943" s="2"/>
-      <c r="C943" s="31"/>
+      <c r="C943" s="34"/>
     </row>
     <row r="944">
       <c r="B944" s="2"/>
-      <c r="C944" s="31"/>
+      <c r="C944" s="34"/>
     </row>
     <row r="945">
       <c r="B945" s="2"/>
-      <c r="C945" s="31"/>
+      <c r="C945" s="34"/>
     </row>
     <row r="946">
       <c r="B946" s="2"/>
-      <c r="C946" s="31"/>
+      <c r="C946" s="34"/>
     </row>
     <row r="947">
       <c r="B947" s="2"/>
-      <c r="C947" s="31"/>
+      <c r="C947" s="34"/>
     </row>
     <row r="948">
       <c r="B948" s="2"/>
-      <c r="C948" s="31"/>
+      <c r="C948" s="34"/>
     </row>
     <row r="949">
       <c r="B949" s="2"/>
-      <c r="C949" s="31"/>
+      <c r="C949" s="34"/>
     </row>
     <row r="950">
       <c r="B950" s="2"/>
-      <c r="C950" s="31"/>
+      <c r="C950" s="34"/>
     </row>
     <row r="951">
       <c r="B951" s="2"/>
-      <c r="C951" s="31"/>
+      <c r="C951" s="34"/>
     </row>
     <row r="952">
       <c r="B952" s="2"/>
-      <c r="C952" s="31"/>
+      <c r="C952" s="34"/>
     </row>
     <row r="953">
       <c r="B953" s="2"/>
-      <c r="C953" s="31"/>
+      <c r="C953" s="34"/>
     </row>
     <row r="954">
       <c r="B954" s="2"/>
-      <c r="C954" s="31"/>
+      <c r="C954" s="34"/>
     </row>
     <row r="955">
       <c r="B955" s="2"/>
-      <c r="C955" s="31"/>
+      <c r="C955" s="34"/>
     </row>
     <row r="956">
       <c r="B956" s="2"/>
-      <c r="C956" s="31"/>
+      <c r="C956" s="34"/>
     </row>
     <row r="957">
       <c r="B957" s="2"/>
-      <c r="C957" s="31"/>
+      <c r="C957" s="34"/>
     </row>
     <row r="958">
       <c r="B958" s="2"/>
-      <c r="C958" s="31"/>
+      <c r="C958" s="34"/>
     </row>
     <row r="959">
       <c r="B959" s="2"/>
-      <c r="C959" s="31"/>
+      <c r="C959" s="34"/>
     </row>
     <row r="960">
       <c r="B960" s="2"/>
-      <c r="C960" s="31"/>
+      <c r="C960" s="34"/>
     </row>
     <row r="961">
       <c r="B961" s="2"/>
-      <c r="C961" s="31"/>
+      <c r="C961" s="34"/>
     </row>
     <row r="962">
       <c r="B962" s="2"/>
-      <c r="C962" s="31"/>
+      <c r="C962" s="34"/>
     </row>
     <row r="963">
       <c r="B963" s="2"/>
-      <c r="C963" s="31"/>
+      <c r="C963" s="34"/>
     </row>
     <row r="964">
       <c r="B964" s="2"/>
-      <c r="C964" s="31"/>
+      <c r="C964" s="34"/>
     </row>
     <row r="965">
       <c r="B965" s="2"/>
-      <c r="C965" s="31"/>
+      <c r="C965" s="34"/>
     </row>
     <row r="966">
       <c r="B966" s="2"/>
-      <c r="C966" s="31"/>
+      <c r="C966" s="34"/>
     </row>
     <row r="967">
       <c r="B967" s="2"/>
-      <c r="C967" s="31"/>
+      <c r="C967" s="34"/>
     </row>
     <row r="968">
       <c r="B968" s="2"/>
-      <c r="C968" s="31"/>
+      <c r="C968" s="34"/>
     </row>
     <row r="969">
       <c r="B969" s="2"/>
-      <c r="C969" s="31"/>
+      <c r="C969" s="34"/>
     </row>
     <row r="970">
       <c r="B970" s="2"/>
-      <c r="C970" s="31"/>
+      <c r="C970" s="34"/>
     </row>
     <row r="971">
       <c r="B971" s="2"/>
-      <c r="C971" s="31"/>
+      <c r="C971" s="34"/>
     </row>
     <row r="972">
       <c r="B972" s="2"/>
-      <c r="C972" s="31"/>
+      <c r="C972" s="34"/>
     </row>
     <row r="973">
       <c r="B973" s="2"/>
-      <c r="C973" s="31"/>
+      <c r="C973" s="34"/>
     </row>
     <row r="974">
       <c r="B974" s="2"/>
-      <c r="C974" s="31"/>
+      <c r="C974" s="34"/>
     </row>
     <row r="975">
       <c r="B975" s="2"/>
-      <c r="C975" s="31"/>
+      <c r="C975" s="34"/>
     </row>
     <row r="976">
       <c r="B976" s="2"/>
-      <c r="C976" s="31"/>
+      <c r="C976" s="34"/>
     </row>
     <row r="977">
       <c r="B977" s="2"/>
-      <c r="C977" s="31"/>
+      <c r="C977" s="34"/>
     </row>
     <row r="978">
       <c r="B978" s="2"/>
-      <c r="C978" s="31"/>
+      <c r="C978" s="34"/>
     </row>
     <row r="979">
       <c r="B979" s="2"/>
-      <c r="C979" s="31"/>
+      <c r="C979" s="34"/>
     </row>
     <row r="980">
       <c r="B980" s="2"/>
-      <c r="C980" s="31"/>
+      <c r="C980" s="34"/>
     </row>
     <row r="981">
       <c r="B981" s="2"/>
-      <c r="C981" s="31"/>
+      <c r="C981" s="34"/>
     </row>
     <row r="982">
       <c r="B982" s="2"/>
-      <c r="C982" s="31"/>
+      <c r="C982" s="34"/>
     </row>
     <row r="983">
       <c r="B983" s="2"/>
-      <c r="C983" s="31"/>
+      <c r="C983" s="34"/>
     </row>
     <row r="984">
       <c r="B984" s="2"/>
-      <c r="C984" s="31"/>
+      <c r="C984" s="34"/>
     </row>
     <row r="985">
       <c r="B985" s="2"/>
-      <c r="C985" s="31"/>
+      <c r="C985" s="34"/>
     </row>
     <row r="986">
       <c r="B986" s="2"/>
-      <c r="C986" s="31"/>
+      <c r="C986" s="34"/>
     </row>
     <row r="987">
       <c r="B987" s="2"/>
-      <c r="C987" s="31"/>
+      <c r="C987" s="34"/>
     </row>
     <row r="988">
       <c r="B988" s="2"/>
-      <c r="C988" s="31"/>
+      <c r="C988" s="34"/>
     </row>
     <row r="989">
       <c r="B989" s="2"/>
-      <c r="C989" s="31"/>
+      <c r="C989" s="34"/>
     </row>
     <row r="990">
       <c r="B990" s="2"/>
-      <c r="C990" s="31"/>
+      <c r="C990" s="34"/>
     </row>
     <row r="991">
       <c r="B991" s="2"/>
-      <c r="C991" s="31"/>
+      <c r="C991" s="34"/>
     </row>
     <row r="992">
       <c r="B992" s="2"/>
-      <c r="C992" s="31"/>
+      <c r="C992" s="34"/>
     </row>
     <row r="993">
       <c r="B993" s="2"/>
-      <c r="C993" s="31"/>
+      <c r="C993" s="34"/>
     </row>
     <row r="994">
       <c r="B994" s="2"/>
-      <c r="C994" s="31"/>
+      <c r="C994" s="34"/>
     </row>
     <row r="995">
       <c r="B995" s="2"/>
-      <c r="C995" s="31"/>
+      <c r="C995" s="34"/>
     </row>
     <row r="996">
       <c r="B996" s="2"/>
-      <c r="C996" s="31"/>
+      <c r="C996" s="34"/>
     </row>
     <row r="997">
       <c r="B997" s="2"/>
-      <c r="C997" s="31"/>
+      <c r="C997" s="34"/>
     </row>
     <row r="998">
       <c r="B998" s="2"/>
-      <c r="C998" s="31"/>
+      <c r="C998" s="34"/>
     </row>
     <row r="999">
       <c r="B999" s="2"/>
-      <c r="C999" s="31"/>
+      <c r="C999" s="34"/>
     </row>
     <row r="1000">
       <c r="B1000" s="2"/>
-      <c r="C1000" s="31"/>
+      <c r="C1000" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/public/templates/monthly-treatment-report-template.xlsx
+++ b/public/templates/monthly-treatment-report-template.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="29">
   <si>
     <t>Bridgeport Public Utility District - Monthly Treatment Report Field Test Result</t>
   </si>
@@ -34,22 +34,22 @@
     <t>DATE</t>
   </si>
   <si>
-    <t>Weekly Influent  Cain Well #4</t>
+    <t>Influent  From Cain Well</t>
   </si>
   <si>
-    <t>Weekly Influent Twin Well #2</t>
+    <t>Influent From Twin Lakes</t>
   </si>
   <si>
-    <t>Weekly Effluent</t>
+    <t>Skid Effluent</t>
   </si>
   <si>
-    <t>Effluent Vessel #1</t>
+    <t xml:space="preserve">Vessel #1 Effluent </t>
   </si>
   <si>
-    <t>Effluent Vessel #2</t>
+    <t xml:space="preserve">Vessel #2 Effluent </t>
   </si>
   <si>
-    <t>Effluent Vessel #3</t>
+    <t xml:space="preserve">Vessel #3 Effluent </t>
   </si>
   <si>
     <t>Chlorine Residual</t>
@@ -76,6 +76,21 @@
     <t>Notes:</t>
   </si>
   <si>
+    <t>Observations:</t>
+  </si>
+  <si>
+    <t>Twin Well - 2610003-002</t>
+  </si>
+  <si>
+    <t>Twin Treated- 2610003-800</t>
+  </si>
+  <si>
+    <t>Cain Well - 2610003-004</t>
+  </si>
+  <si>
+    <t>Cain Treated - 2610003-801</t>
+  </si>
+  <si>
     <t>Bridgeport Public Utility District</t>
   </si>
   <si>
@@ -99,7 +114,7 @@
     <numFmt numFmtId="164" formatCode="[$-409]mmmm\-yy"/>
     <numFmt numFmtId="165" formatCode="m/d/yy"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="12.0"/>
       <color theme="1"/>
@@ -148,6 +163,11 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <sz val="12.0"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
       <b/>
       <sz val="12.0"/>
       <color rgb="FFFF0000"/>
@@ -192,7 +212,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="18">
     <border/>
     <border>
       <left style="thin">
@@ -262,11 +282,105 @@
         <color rgb="FF000000"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF9A9A9A"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+    </border>
+    <border>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF9A9A9A"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF9A9A9A"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF9A9A9A"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="51">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -287,6 +401,9 @@
     </xf>
     <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="2" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -357,8 +474,29 @@
     <xf borderId="1" fillId="6" fontId="4" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="7" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="8" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="9" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="10" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="11" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="12" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="13" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="14" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="15" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="16" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="17" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -591,8 +729,8 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="22.22"/>
-    <col customWidth="1" min="2" max="2" width="15.33"/>
+    <col customWidth="1" min="1" max="1" width="24.33"/>
+    <col customWidth="1" min="2" max="2" width="21.89"/>
     <col customWidth="1" min="3" max="4" width="14.67"/>
     <col customWidth="1" min="5" max="8" width="10.67"/>
     <col customWidth="1" min="9" max="26" width="8.56"/>
@@ -628,238 +766,238 @@
       <c r="B4" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="G4" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="H4" s="7" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="8"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="10"/>
-      <c r="H5" s="10"/>
+      <c r="B5" s="9"/>
+      <c r="C5" s="10"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11"/>
     </row>
     <row r="6">
-      <c r="A6" s="11"/>
-      <c r="B6" s="8"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10"/>
+      <c r="A6" s="12"/>
+      <c r="B6" s="9"/>
+      <c r="C6" s="10"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
     </row>
     <row r="7">
-      <c r="A7" s="11"/>
-      <c r="B7" s="8"/>
-      <c r="C7" s="12"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="10"/>
-      <c r="H7" s="10"/>
+      <c r="A7" s="12"/>
+      <c r="B7" s="9"/>
+      <c r="C7" s="13"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="11"/>
     </row>
     <row r="8">
-      <c r="A8" s="13"/>
-      <c r="B8" s="8"/>
-      <c r="C8" s="12"/>
-      <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="10"/>
-      <c r="G8" s="10"/>
-      <c r="H8" s="10"/>
+      <c r="A8" s="14"/>
+      <c r="B8" s="9"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="11"/>
     </row>
     <row r="9">
-      <c r="A9" s="14" t="s">
+      <c r="A9" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="15"/>
-      <c r="C9" s="16"/>
-      <c r="D9" s="17"/>
-      <c r="E9" s="16"/>
-      <c r="F9" s="16"/>
-      <c r="G9" s="16"/>
-      <c r="H9" s="16"/>
+      <c r="B9" s="16"/>
+      <c r="C9" s="17"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="17"/>
+      <c r="F9" s="17"/>
+      <c r="G9" s="17"/>
+      <c r="H9" s="17"/>
     </row>
     <row r="10">
-      <c r="A10" s="11"/>
-      <c r="B10" s="15"/>
-      <c r="C10" s="16"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="16"/>
-      <c r="F10" s="16"/>
-      <c r="G10" s="16"/>
-      <c r="H10" s="16"/>
+      <c r="A10" s="12"/>
+      <c r="B10" s="16"/>
+      <c r="C10" s="17"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="17"/>
+      <c r="F10" s="17"/>
+      <c r="G10" s="17"/>
+      <c r="H10" s="17"/>
     </row>
     <row r="11">
-      <c r="A11" s="11"/>
-      <c r="B11" s="15"/>
-      <c r="C11" s="16"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="16"/>
-      <c r="F11" s="16"/>
-      <c r="G11" s="16"/>
-      <c r="H11" s="16"/>
+      <c r="A11" s="12"/>
+      <c r="B11" s="16"/>
+      <c r="C11" s="17"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="17"/>
+      <c r="F11" s="17"/>
+      <c r="G11" s="17"/>
+      <c r="H11" s="17"/>
     </row>
     <row r="12">
-      <c r="A12" s="13"/>
-      <c r="B12" s="15"/>
-      <c r="C12" s="16"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="16"/>
-      <c r="F12" s="16"/>
-      <c r="G12" s="16"/>
-      <c r="H12" s="16"/>
+      <c r="A12" s="14"/>
+      <c r="B12" s="16"/>
+      <c r="C12" s="17"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="17"/>
+      <c r="G12" s="17"/>
+      <c r="H12" s="17"/>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="s">
+      <c r="A13" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="19"/>
-      <c r="C13" s="20"/>
-      <c r="D13" s="21"/>
-      <c r="E13" s="21"/>
-      <c r="F13" s="22" t="s">
+      <c r="B13" s="20"/>
+      <c r="C13" s="21"/>
+      <c r="D13" s="22"/>
+      <c r="E13" s="22"/>
+      <c r="F13" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="G13" s="22" t="s">
+      <c r="G13" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H13" s="22" t="s">
+      <c r="H13" s="23" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="11"/>
-      <c r="B14" s="19"/>
-      <c r="C14" s="20"/>
-      <c r="D14" s="21"/>
-      <c r="E14" s="21"/>
-      <c r="F14" s="22" t="s">
+      <c r="A14" s="12"/>
+      <c r="B14" s="20"/>
+      <c r="C14" s="21"/>
+      <c r="D14" s="22"/>
+      <c r="E14" s="22"/>
+      <c r="F14" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="G14" s="22" t="s">
+      <c r="G14" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H14" s="22" t="s">
+      <c r="H14" s="23" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="11"/>
-      <c r="B15" s="19"/>
-      <c r="C15" s="23"/>
-      <c r="D15" s="24"/>
-      <c r="E15" s="21"/>
-      <c r="F15" s="22" t="s">
+      <c r="A15" s="12"/>
+      <c r="B15" s="20"/>
+      <c r="C15" s="24"/>
+      <c r="D15" s="25"/>
+      <c r="E15" s="22"/>
+      <c r="F15" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="G15" s="22" t="s">
+      <c r="G15" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H15" s="22" t="s">
+      <c r="H15" s="23" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="13"/>
-      <c r="B16" s="19"/>
-      <c r="C16" s="23"/>
-      <c r="D16" s="24"/>
-      <c r="E16" s="21"/>
-      <c r="F16" s="22" t="s">
+      <c r="A16" s="14"/>
+      <c r="B16" s="20"/>
+      <c r="C16" s="24"/>
+      <c r="D16" s="25"/>
+      <c r="E16" s="22"/>
+      <c r="F16" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="G16" s="22" t="s">
+      <c r="G16" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H16" s="22" t="s">
+      <c r="H16" s="23" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="25" t="s">
+      <c r="A17" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="26"/>
-      <c r="C17" s="27"/>
-      <c r="D17" s="28"/>
-      <c r="E17" s="28"/>
-      <c r="F17" s="22" t="s">
+      <c r="B17" s="27"/>
+      <c r="C17" s="28"/>
+      <c r="D17" s="29"/>
+      <c r="E17" s="29"/>
+      <c r="F17" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="G17" s="22" t="s">
+      <c r="G17" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H17" s="22" t="s">
+      <c r="H17" s="23" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="11"/>
-      <c r="B18" s="26"/>
-      <c r="C18" s="27"/>
-      <c r="D18" s="28"/>
-      <c r="E18" s="28"/>
-      <c r="F18" s="22" t="s">
+      <c r="A18" s="12"/>
+      <c r="B18" s="27"/>
+      <c r="C18" s="28"/>
+      <c r="D18" s="29"/>
+      <c r="E18" s="29"/>
+      <c r="F18" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="G18" s="22" t="s">
+      <c r="G18" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H18" s="22" t="s">
+      <c r="H18" s="23" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="11"/>
-      <c r="B19" s="26"/>
-      <c r="C19" s="28"/>
-      <c r="D19" s="28"/>
-      <c r="E19" s="28"/>
-      <c r="F19" s="22" t="s">
+      <c r="A19" s="12"/>
+      <c r="B19" s="27"/>
+      <c r="C19" s="29"/>
+      <c r="D19" s="29"/>
+      <c r="E19" s="29"/>
+      <c r="F19" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="G19" s="22" t="s">
+      <c r="G19" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H19" s="22" t="s">
+      <c r="H19" s="23" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="13"/>
-      <c r="B20" s="26"/>
-      <c r="C20" s="28"/>
-      <c r="D20" s="28"/>
-      <c r="E20" s="28"/>
-      <c r="F20" s="22" t="s">
+      <c r="A20" s="14"/>
+      <c r="B20" s="27"/>
+      <c r="C20" s="29"/>
+      <c r="D20" s="29"/>
+      <c r="E20" s="29"/>
+      <c r="F20" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="G20" s="22" t="s">
+      <c r="G20" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H20" s="22" t="s">
+      <c r="H20" s="23" t="s">
         <v>14</v>
       </c>
     </row>
@@ -873,11 +1011,11 @@
       <c r="H21" s="2"/>
     </row>
     <row r="22">
-      <c r="A22" s="29" t="s">
+      <c r="A22" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="B22" s="30"/>
-      <c r="C22" s="31"/>
+      <c r="B22" s="31"/>
+      <c r="C22" s="32"/>
       <c r="D22" s="2"/>
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>
@@ -885,11 +1023,11 @@
       <c r="H22" s="2"/>
     </row>
     <row r="23">
-      <c r="A23" s="29" t="s">
+      <c r="A23" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="B23" s="30"/>
-      <c r="C23" s="31"/>
+      <c r="B23" s="31"/>
+      <c r="C23" s="32"/>
       <c r="D23" s="2"/>
       <c r="E23" s="2"/>
       <c r="F23" s="2"/>
@@ -900,25 +1038,58 @@
       <c r="B24" s="2"/>
     </row>
     <row r="25">
-      <c r="A25" s="32" t="s">
+      <c r="A25" s="33" t="s">
         <v>18</v>
       </c>
       <c r="B25" s="2"/>
+      <c r="D25" s="34" t="s">
+        <v>19</v>
+      </c>
+      <c r="E25" s="35"/>
+      <c r="F25" s="35"/>
+      <c r="G25" s="35"/>
+      <c r="H25" s="36"/>
     </row>
     <row r="26">
+      <c r="A26" s="37" t="s">
+        <v>20</v>
+      </c>
       <c r="B26" s="2"/>
+      <c r="D26" s="38"/>
+      <c r="H26" s="39"/>
     </row>
     <row r="27">
+      <c r="A27" s="37" t="s">
+        <v>21</v>
+      </c>
       <c r="B27" s="2"/>
+      <c r="D27" s="38"/>
+      <c r="H27" s="39"/>
     </row>
     <row r="28">
+      <c r="A28" s="37" t="s">
+        <v>22</v>
+      </c>
       <c r="B28" s="2"/>
+      <c r="D28" s="38"/>
+      <c r="H28" s="39"/>
     </row>
     <row r="29">
+      <c r="A29" s="40" t="s">
+        <v>23</v>
+      </c>
       <c r="B29" s="2"/>
+      <c r="D29" s="38"/>
+      <c r="H29" s="39"/>
     </row>
     <row r="30">
+      <c r="A30" s="41"/>
       <c r="B30" s="2"/>
+      <c r="D30" s="42"/>
+      <c r="E30" s="43"/>
+      <c r="F30" s="43"/>
+      <c r="G30" s="43"/>
+      <c r="H30" s="44"/>
     </row>
     <row r="31">
       <c r="B31" s="2"/>
@@ -9680,4218 +9851,4218 @@
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2">
       <c r="B2" s="1" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" ht="7.5" customHeight="1">
-      <c r="B3" s="33"/>
-      <c r="C3" s="33"/>
+      <c r="B3" s="45"/>
+      <c r="C3" s="45"/>
     </row>
     <row r="4">
       <c r="B4" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" ht="6.75" customHeight="1">
       <c r="B5" s="2"/>
-      <c r="C5" s="34"/>
+      <c r="C5" s="46"/>
     </row>
     <row r="6">
-      <c r="B6" s="35" t="s">
-        <v>22</v>
+      <c r="B6" s="47" t="s">
+        <v>27</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="36">
+      <c r="B7" s="48">
         <v>46113.0</v>
       </c>
-      <c r="C7" s="37">
+      <c r="C7" s="49">
         <v>33.75</v>
       </c>
-      <c r="D7" s="38"/>
+      <c r="D7" s="50"/>
     </row>
     <row r="8">
-      <c r="B8" s="36">
+      <c r="B8" s="48">
         <f t="shared" ref="B8:B36" si="1">B7+1</f>
         <v>46114</v>
       </c>
-      <c r="C8" s="37">
+      <c r="C8" s="49">
         <v>33.5</v>
       </c>
-      <c r="D8" s="38"/>
+      <c r="D8" s="50"/>
     </row>
     <row r="9">
-      <c r="B9" s="36">
+      <c r="B9" s="48">
         <f t="shared" si="1"/>
         <v>46115</v>
       </c>
-      <c r="C9" s="37">
+      <c r="C9" s="49">
         <v>33.75</v>
       </c>
-      <c r="D9" s="38"/>
-      <c r="E9" s="38"/>
+      <c r="D9" s="50"/>
+      <c r="E9" s="50"/>
     </row>
     <row r="10">
-      <c r="B10" s="36">
+      <c r="B10" s="48">
         <f t="shared" si="1"/>
         <v>46116</v>
       </c>
-      <c r="C10" s="37">
+      <c r="C10" s="49">
         <v>32.5</v>
       </c>
-      <c r="D10" s="38"/>
-      <c r="E10" s="38"/>
+      <c r="D10" s="50"/>
+      <c r="E10" s="50"/>
     </row>
     <row r="11">
-      <c r="B11" s="36">
+      <c r="B11" s="48">
         <f t="shared" si="1"/>
         <v>46117</v>
       </c>
-      <c r="C11" s="37">
+      <c r="C11" s="49">
         <v>32.25</v>
       </c>
-      <c r="D11" s="38"/>
-      <c r="E11" s="38"/>
+      <c r="D11" s="50"/>
+      <c r="E11" s="50"/>
     </row>
     <row r="12">
-      <c r="B12" s="36">
+      <c r="B12" s="48">
         <f t="shared" si="1"/>
         <v>46118</v>
       </c>
-      <c r="C12" s="37">
+      <c r="C12" s="49">
         <v>31.75</v>
       </c>
-      <c r="D12" s="38"/>
-      <c r="E12" s="38"/>
+      <c r="D12" s="50"/>
+      <c r="E12" s="50"/>
     </row>
     <row r="13">
-      <c r="B13" s="36">
+      <c r="B13" s="48">
         <f t="shared" si="1"/>
         <v>46119</v>
       </c>
-      <c r="C13" s="37">
+      <c r="C13" s="49">
         <v>31.75</v>
       </c>
-      <c r="D13" s="38"/>
-      <c r="E13" s="38"/>
+      <c r="D13" s="50"/>
+      <c r="E13" s="50"/>
     </row>
     <row r="14">
-      <c r="B14" s="36">
+      <c r="B14" s="48">
         <f t="shared" si="1"/>
         <v>46120</v>
       </c>
-      <c r="C14" s="37">
+      <c r="C14" s="49">
         <v>30.75</v>
       </c>
-      <c r="D14" s="38"/>
-      <c r="E14" s="38"/>
+      <c r="D14" s="50"/>
+      <c r="E14" s="50"/>
     </row>
     <row r="15">
-      <c r="B15" s="36">
+      <c r="B15" s="48">
         <f t="shared" si="1"/>
         <v>46121</v>
       </c>
-      <c r="C15" s="37">
+      <c r="C15" s="49">
         <v>30.5</v>
       </c>
-      <c r="D15" s="38"/>
-      <c r="E15" s="38"/>
+      <c r="D15" s="50"/>
+      <c r="E15" s="50"/>
     </row>
     <row r="16">
-      <c r="B16" s="36">
+      <c r="B16" s="48">
         <f t="shared" si="1"/>
         <v>46122</v>
       </c>
-      <c r="C16" s="37">
+      <c r="C16" s="49">
         <v>30.0</v>
       </c>
-      <c r="D16" s="38"/>
-      <c r="E16" s="38"/>
+      <c r="D16" s="50"/>
+      <c r="E16" s="50"/>
     </row>
     <row r="17">
-      <c r="B17" s="36">
+      <c r="B17" s="48">
         <f t="shared" si="1"/>
         <v>46123</v>
       </c>
-      <c r="C17" s="37">
+      <c r="C17" s="49">
         <v>29.5</v>
       </c>
-      <c r="D17" s="38"/>
-      <c r="E17" s="38"/>
+      <c r="D17" s="50"/>
+      <c r="E17" s="50"/>
     </row>
     <row r="18">
-      <c r="B18" s="36">
+      <c r="B18" s="48">
         <f t="shared" si="1"/>
         <v>46124</v>
       </c>
-      <c r="C18" s="37">
+      <c r="C18" s="49">
         <v>28.75</v>
       </c>
-      <c r="D18" s="38"/>
-      <c r="E18" s="38"/>
+      <c r="D18" s="50"/>
+      <c r="E18" s="50"/>
     </row>
     <row r="19">
-      <c r="B19" s="36">
+      <c r="B19" s="48">
         <f t="shared" si="1"/>
         <v>46125</v>
       </c>
-      <c r="C19" s="37">
+      <c r="C19" s="49">
         <v>28.5</v>
       </c>
-      <c r="D19" s="38"/>
-      <c r="E19" s="38"/>
+      <c r="D19" s="50"/>
+      <c r="E19" s="50"/>
     </row>
     <row r="20">
-      <c r="B20" s="36">
+      <c r="B20" s="48">
         <f t="shared" si="1"/>
         <v>46126</v>
       </c>
-      <c r="C20" s="37">
+      <c r="C20" s="49">
         <v>28.0</v>
       </c>
-      <c r="D20" s="38"/>
-      <c r="E20" s="38"/>
+      <c r="D20" s="50"/>
+      <c r="E20" s="50"/>
     </row>
     <row r="21">
-      <c r="B21" s="36">
+      <c r="B21" s="48">
         <f t="shared" si="1"/>
         <v>46127</v>
       </c>
-      <c r="C21" s="37">
+      <c r="C21" s="49">
         <v>27.5</v>
       </c>
-      <c r="D21" s="38"/>
-      <c r="E21" s="38"/>
+      <c r="D21" s="50"/>
+      <c r="E21" s="50"/>
     </row>
     <row r="22">
-      <c r="B22" s="36">
+      <c r="B22" s="48">
         <f t="shared" si="1"/>
         <v>46128</v>
       </c>
-      <c r="C22" s="37">
+      <c r="C22" s="49">
         <v>27.0</v>
       </c>
-      <c r="D22" s="38"/>
-      <c r="E22" s="38"/>
+      <c r="D22" s="50"/>
+      <c r="E22" s="50"/>
     </row>
     <row r="23">
-      <c r="B23" s="36">
+      <c r="B23" s="48">
         <f t="shared" si="1"/>
         <v>46129</v>
       </c>
-      <c r="C23" s="37">
+      <c r="C23" s="49">
         <v>26.5</v>
       </c>
-      <c r="D23" s="38"/>
-      <c r="E23" s="38"/>
+      <c r="D23" s="50"/>
+      <c r="E23" s="50"/>
     </row>
     <row r="24">
-      <c r="B24" s="36">
+      <c r="B24" s="48">
         <f t="shared" si="1"/>
         <v>46130</v>
       </c>
-      <c r="C24" s="37">
+      <c r="C24" s="49">
         <v>24.75</v>
       </c>
-      <c r="D24" s="38"/>
-      <c r="E24" s="38"/>
+      <c r="D24" s="50"/>
+      <c r="E24" s="50"/>
     </row>
     <row r="25">
-      <c r="B25" s="36">
+      <c r="B25" s="48">
         <f t="shared" si="1"/>
         <v>46131</v>
       </c>
-      <c r="C25" s="37">
+      <c r="C25" s="49">
         <v>25.375</v>
       </c>
-      <c r="D25" s="38"/>
-      <c r="E25" s="38"/>
+      <c r="D25" s="50"/>
+      <c r="E25" s="50"/>
     </row>
     <row r="26">
-      <c r="B26" s="36">
+      <c r="B26" s="48">
         <f t="shared" si="1"/>
         <v>46132</v>
       </c>
-      <c r="C26" s="37">
+      <c r="C26" s="49">
         <v>24.75</v>
       </c>
-      <c r="D26" s="38"/>
-      <c r="E26" s="38"/>
+      <c r="D26" s="50"/>
+      <c r="E26" s="50"/>
     </row>
     <row r="27">
-      <c r="B27" s="36">
+      <c r="B27" s="48">
         <f t="shared" si="1"/>
         <v>46133</v>
       </c>
-      <c r="C27" s="37">
+      <c r="C27" s="49">
         <v>24.25</v>
       </c>
-      <c r="D27" s="38"/>
-      <c r="E27" s="38"/>
+      <c r="D27" s="50"/>
+      <c r="E27" s="50"/>
     </row>
     <row r="28">
-      <c r="B28" s="36">
+      <c r="B28" s="48">
         <f t="shared" si="1"/>
         <v>46134</v>
       </c>
-      <c r="C28" s="37">
+      <c r="C28" s="49">
         <v>23.75</v>
       </c>
-      <c r="D28" s="38"/>
-      <c r="E28" s="38"/>
+      <c r="D28" s="50"/>
+      <c r="E28" s="50"/>
     </row>
     <row r="29">
-      <c r="B29" s="36">
+      <c r="B29" s="48">
         <f t="shared" si="1"/>
         <v>46135</v>
       </c>
-      <c r="C29" s="37">
+      <c r="C29" s="49">
         <v>23.25</v>
       </c>
-      <c r="D29" s="38"/>
-      <c r="E29" s="38"/>
+      <c r="D29" s="50"/>
+      <c r="E29" s="50"/>
     </row>
     <row r="30">
-      <c r="B30" s="36">
+      <c r="B30" s="48">
         <f t="shared" si="1"/>
         <v>46136</v>
       </c>
-      <c r="C30" s="37">
+      <c r="C30" s="49">
         <v>22.5</v>
       </c>
-      <c r="D30" s="38"/>
-      <c r="E30" s="38"/>
+      <c r="D30" s="50"/>
+      <c r="E30" s="50"/>
     </row>
     <row r="31">
-      <c r="B31" s="36">
+      <c r="B31" s="48">
         <f t="shared" si="1"/>
         <v>46137</v>
       </c>
-      <c r="C31" s="37">
+      <c r="C31" s="49">
         <v>22.0</v>
       </c>
-      <c r="D31" s="38"/>
-      <c r="E31" s="38"/>
+      <c r="D31" s="50"/>
+      <c r="E31" s="50"/>
     </row>
     <row r="32">
-      <c r="B32" s="36">
+      <c r="B32" s="48">
         <f t="shared" si="1"/>
         <v>46138</v>
       </c>
-      <c r="C32" s="37">
+      <c r="C32" s="49">
         <v>21.5</v>
       </c>
-      <c r="D32" s="38"/>
-      <c r="E32" s="38"/>
+      <c r="D32" s="50"/>
+      <c r="E32" s="50"/>
     </row>
     <row r="33">
-      <c r="B33" s="36">
+      <c r="B33" s="48">
         <f t="shared" si="1"/>
         <v>46139</v>
       </c>
-      <c r="C33" s="37">
+      <c r="C33" s="49">
         <v>21.0</v>
       </c>
-      <c r="D33" s="38"/>
-      <c r="E33" s="38"/>
+      <c r="D33" s="50"/>
+      <c r="E33" s="50"/>
     </row>
     <row r="34">
-      <c r="B34" s="36">
+      <c r="B34" s="48">
         <f t="shared" si="1"/>
         <v>46140</v>
       </c>
-      <c r="C34" s="37">
+      <c r="C34" s="49">
         <v>20.5</v>
       </c>
-      <c r="D34" s="38"/>
-      <c r="E34" s="38"/>
+      <c r="D34" s="50"/>
+      <c r="E34" s="50"/>
     </row>
     <row r="35">
-      <c r="B35" s="36">
+      <c r="B35" s="48">
         <f t="shared" si="1"/>
         <v>46141</v>
       </c>
-      <c r="C35" s="37">
+      <c r="C35" s="49">
         <v>19.5</v>
       </c>
-      <c r="D35" s="38"/>
-      <c r="E35" s="38"/>
+      <c r="D35" s="50"/>
+      <c r="E35" s="50"/>
     </row>
     <row r="36">
-      <c r="B36" s="36">
+      <c r="B36" s="48">
         <f t="shared" si="1"/>
         <v>46142</v>
       </c>
-      <c r="C36" s="37">
+      <c r="C36" s="49">
         <v>18.75</v>
       </c>
     </row>
     <row r="37">
       <c r="B37" s="2"/>
-      <c r="C37" s="34"/>
+      <c r="C37" s="46"/>
     </row>
     <row r="38">
       <c r="B38" s="2"/>
-      <c r="C38" s="34"/>
+      <c r="C38" s="46"/>
     </row>
     <row r="39">
       <c r="B39" s="2"/>
-      <c r="C39" s="34"/>
+      <c r="C39" s="46"/>
     </row>
     <row r="40">
       <c r="B40" s="2"/>
-      <c r="C40" s="34"/>
+      <c r="C40" s="46"/>
     </row>
     <row r="41">
       <c r="B41" s="2"/>
-      <c r="C41" s="34"/>
+      <c r="C41" s="46"/>
     </row>
     <row r="42">
       <c r="B42" s="2"/>
-      <c r="C42" s="34"/>
+      <c r="C42" s="46"/>
     </row>
     <row r="43">
       <c r="B43" s="2"/>
-      <c r="C43" s="34"/>
+      <c r="C43" s="46"/>
     </row>
     <row r="44">
       <c r="B44" s="2"/>
-      <c r="C44" s="34"/>
+      <c r="C44" s="46"/>
     </row>
     <row r="45">
       <c r="B45" s="2"/>
-      <c r="C45" s="34"/>
+      <c r="C45" s="46"/>
     </row>
     <row r="46">
       <c r="B46" s="2"/>
-      <c r="C46" s="34"/>
+      <c r="C46" s="46"/>
     </row>
     <row r="47">
       <c r="B47" s="2"/>
-      <c r="C47" s="34"/>
+      <c r="C47" s="46"/>
     </row>
     <row r="48">
       <c r="B48" s="2"/>
-      <c r="C48" s="34"/>
+      <c r="C48" s="46"/>
     </row>
     <row r="49">
       <c r="B49" s="2"/>
-      <c r="C49" s="34"/>
+      <c r="C49" s="46"/>
     </row>
     <row r="50">
       <c r="B50" s="2"/>
-      <c r="C50" s="34"/>
+      <c r="C50" s="46"/>
     </row>
     <row r="51">
       <c r="B51" s="2"/>
-      <c r="C51" s="34"/>
+      <c r="C51" s="46"/>
     </row>
     <row r="52">
       <c r="B52" s="2"/>
-      <c r="C52" s="34"/>
+      <c r="C52" s="46"/>
     </row>
     <row r="53">
       <c r="B53" s="2"/>
-      <c r="C53" s="34"/>
+      <c r="C53" s="46"/>
     </row>
     <row r="54">
       <c r="B54" s="2"/>
-      <c r="C54" s="34"/>
+      <c r="C54" s="46"/>
     </row>
     <row r="55">
       <c r="B55" s="2"/>
-      <c r="C55" s="34"/>
+      <c r="C55" s="46"/>
     </row>
     <row r="56">
       <c r="B56" s="2"/>
-      <c r="C56" s="34"/>
+      <c r="C56" s="46"/>
     </row>
     <row r="57">
       <c r="B57" s="2"/>
-      <c r="C57" s="34"/>
+      <c r="C57" s="46"/>
     </row>
     <row r="58">
       <c r="B58" s="2"/>
-      <c r="C58" s="34"/>
+      <c r="C58" s="46"/>
     </row>
     <row r="59">
       <c r="B59" s="2"/>
-      <c r="C59" s="34"/>
+      <c r="C59" s="46"/>
     </row>
     <row r="60">
       <c r="B60" s="2"/>
-      <c r="C60" s="34"/>
+      <c r="C60" s="46"/>
     </row>
     <row r="61">
       <c r="B61" s="2"/>
-      <c r="C61" s="34"/>
+      <c r="C61" s="46"/>
     </row>
     <row r="62">
       <c r="B62" s="2"/>
-      <c r="C62" s="34"/>
+      <c r="C62" s="46"/>
     </row>
     <row r="63">
       <c r="B63" s="2"/>
-      <c r="C63" s="34"/>
+      <c r="C63" s="46"/>
     </row>
     <row r="64">
       <c r="B64" s="2"/>
-      <c r="C64" s="34"/>
+      <c r="C64" s="46"/>
     </row>
     <row r="65">
       <c r="B65" s="2"/>
-      <c r="C65" s="34"/>
+      <c r="C65" s="46"/>
     </row>
     <row r="66">
       <c r="B66" s="2"/>
-      <c r="C66" s="34"/>
+      <c r="C66" s="46"/>
     </row>
     <row r="67">
       <c r="B67" s="2"/>
-      <c r="C67" s="34"/>
+      <c r="C67" s="46"/>
     </row>
     <row r="68">
       <c r="B68" s="2"/>
-      <c r="C68" s="34"/>
+      <c r="C68" s="46"/>
     </row>
     <row r="69">
       <c r="B69" s="2"/>
-      <c r="C69" s="34"/>
+      <c r="C69" s="46"/>
     </row>
     <row r="70">
       <c r="B70" s="2"/>
-      <c r="C70" s="34"/>
+      <c r="C70" s="46"/>
     </row>
     <row r="71">
       <c r="B71" s="2"/>
-      <c r="C71" s="34"/>
+      <c r="C71" s="46"/>
     </row>
     <row r="72">
       <c r="B72" s="2"/>
-      <c r="C72" s="34"/>
+      <c r="C72" s="46"/>
     </row>
     <row r="73">
       <c r="B73" s="2"/>
-      <c r="C73" s="34"/>
+      <c r="C73" s="46"/>
     </row>
     <row r="74">
       <c r="B74" s="2"/>
-      <c r="C74" s="34"/>
+      <c r="C74" s="46"/>
     </row>
     <row r="75">
       <c r="B75" s="2"/>
-      <c r="C75" s="34"/>
+      <c r="C75" s="46"/>
     </row>
     <row r="76">
       <c r="B76" s="2"/>
-      <c r="C76" s="34"/>
+      <c r="C76" s="46"/>
     </row>
     <row r="77">
       <c r="B77" s="2"/>
-      <c r="C77" s="34"/>
+      <c r="C77" s="46"/>
     </row>
     <row r="78">
       <c r="B78" s="2"/>
-      <c r="C78" s="34"/>
+      <c r="C78" s="46"/>
     </row>
     <row r="79">
       <c r="B79" s="2"/>
-      <c r="C79" s="34"/>
+      <c r="C79" s="46"/>
     </row>
     <row r="80">
       <c r="B80" s="2"/>
-      <c r="C80" s="34"/>
+      <c r="C80" s="46"/>
     </row>
     <row r="81">
       <c r="B81" s="2"/>
-      <c r="C81" s="34"/>
+      <c r="C81" s="46"/>
     </row>
     <row r="82">
       <c r="B82" s="2"/>
-      <c r="C82" s="34"/>
+      <c r="C82" s="46"/>
     </row>
     <row r="83">
       <c r="B83" s="2"/>
-      <c r="C83" s="34"/>
+      <c r="C83" s="46"/>
     </row>
     <row r="84">
       <c r="B84" s="2"/>
-      <c r="C84" s="34"/>
+      <c r="C84" s="46"/>
     </row>
     <row r="85">
       <c r="B85" s="2"/>
-      <c r="C85" s="34"/>
+      <c r="C85" s="46"/>
     </row>
     <row r="86">
       <c r="B86" s="2"/>
-      <c r="C86" s="34"/>
+      <c r="C86" s="46"/>
     </row>
     <row r="87">
       <c r="B87" s="2"/>
-      <c r="C87" s="34"/>
+      <c r="C87" s="46"/>
     </row>
     <row r="88">
       <c r="B88" s="2"/>
-      <c r="C88" s="34"/>
+      <c r="C88" s="46"/>
     </row>
     <row r="89">
       <c r="B89" s="2"/>
-      <c r="C89" s="34"/>
+      <c r="C89" s="46"/>
     </row>
     <row r="90">
       <c r="B90" s="2"/>
-      <c r="C90" s="34"/>
+      <c r="C90" s="46"/>
     </row>
     <row r="91">
       <c r="B91" s="2"/>
-      <c r="C91" s="34"/>
+      <c r="C91" s="46"/>
     </row>
     <row r="92">
       <c r="B92" s="2"/>
-      <c r="C92" s="34"/>
+      <c r="C92" s="46"/>
     </row>
     <row r="93">
       <c r="B93" s="2"/>
-      <c r="C93" s="34"/>
+      <c r="C93" s="46"/>
     </row>
     <row r="94">
       <c r="B94" s="2"/>
-      <c r="C94" s="34"/>
+      <c r="C94" s="46"/>
     </row>
     <row r="95">
       <c r="B95" s="2"/>
-      <c r="C95" s="34"/>
+      <c r="C95" s="46"/>
     </row>
     <row r="96">
       <c r="B96" s="2"/>
-      <c r="C96" s="34"/>
+      <c r="C96" s="46"/>
     </row>
     <row r="97">
       <c r="B97" s="2"/>
-      <c r="C97" s="34"/>
+      <c r="C97" s="46"/>
     </row>
     <row r="98">
       <c r="B98" s="2"/>
-      <c r="C98" s="34"/>
+      <c r="C98" s="46"/>
     </row>
     <row r="99">
       <c r="B99" s="2"/>
-      <c r="C99" s="34"/>
+      <c r="C99" s="46"/>
     </row>
     <row r="100">
       <c r="B100" s="2"/>
-      <c r="C100" s="34"/>
+      <c r="C100" s="46"/>
     </row>
     <row r="101">
       <c r="B101" s="2"/>
-      <c r="C101" s="34"/>
+      <c r="C101" s="46"/>
     </row>
     <row r="102">
       <c r="B102" s="2"/>
-      <c r="C102" s="34"/>
+      <c r="C102" s="46"/>
     </row>
     <row r="103">
       <c r="B103" s="2"/>
-      <c r="C103" s="34"/>
+      <c r="C103" s="46"/>
     </row>
     <row r="104">
       <c r="B104" s="2"/>
-      <c r="C104" s="34"/>
+      <c r="C104" s="46"/>
     </row>
     <row r="105">
       <c r="B105" s="2"/>
-      <c r="C105" s="34"/>
+      <c r="C105" s="46"/>
     </row>
     <row r="106">
       <c r="B106" s="2"/>
-      <c r="C106" s="34"/>
+      <c r="C106" s="46"/>
     </row>
     <row r="107">
       <c r="B107" s="2"/>
-      <c r="C107" s="34"/>
+      <c r="C107" s="46"/>
     </row>
     <row r="108">
       <c r="B108" s="2"/>
-      <c r="C108" s="34"/>
+      <c r="C108" s="46"/>
     </row>
     <row r="109">
       <c r="B109" s="2"/>
-      <c r="C109" s="34"/>
+      <c r="C109" s="46"/>
     </row>
     <row r="110">
       <c r="B110" s="2"/>
-      <c r="C110" s="34"/>
+      <c r="C110" s="46"/>
     </row>
     <row r="111">
       <c r="B111" s="2"/>
-      <c r="C111" s="34"/>
+      <c r="C111" s="46"/>
     </row>
     <row r="112">
       <c r="B112" s="2"/>
-      <c r="C112" s="34"/>
+      <c r="C112" s="46"/>
     </row>
     <row r="113">
       <c r="B113" s="2"/>
-      <c r="C113" s="34"/>
+      <c r="C113" s="46"/>
     </row>
     <row r="114">
       <c r="B114" s="2"/>
-      <c r="C114" s="34"/>
+      <c r="C114" s="46"/>
     </row>
     <row r="115">
       <c r="B115" s="2"/>
-      <c r="C115" s="34"/>
+      <c r="C115" s="46"/>
     </row>
     <row r="116">
       <c r="B116" s="2"/>
-      <c r="C116" s="34"/>
+      <c r="C116" s="46"/>
     </row>
     <row r="117">
       <c r="B117" s="2"/>
-      <c r="C117" s="34"/>
+      <c r="C117" s="46"/>
     </row>
     <row r="118">
       <c r="B118" s="2"/>
-      <c r="C118" s="34"/>
+      <c r="C118" s="46"/>
     </row>
     <row r="119">
       <c r="B119" s="2"/>
-      <c r="C119" s="34"/>
+      <c r="C119" s="46"/>
     </row>
     <row r="120">
       <c r="B120" s="2"/>
-      <c r="C120" s="34"/>
+      <c r="C120" s="46"/>
     </row>
     <row r="121">
       <c r="B121" s="2"/>
-      <c r="C121" s="34"/>
+      <c r="C121" s="46"/>
     </row>
     <row r="122">
       <c r="B122" s="2"/>
-      <c r="C122" s="34"/>
+      <c r="C122" s="46"/>
     </row>
     <row r="123">
       <c r="B123" s="2"/>
-      <c r="C123" s="34"/>
+      <c r="C123" s="46"/>
     </row>
     <row r="124">
       <c r="B124" s="2"/>
-      <c r="C124" s="34"/>
+      <c r="C124" s="46"/>
     </row>
     <row r="125">
       <c r="B125" s="2"/>
-      <c r="C125" s="34"/>
+      <c r="C125" s="46"/>
     </row>
     <row r="126">
       <c r="B126" s="2"/>
-      <c r="C126" s="34"/>
+      <c r="C126" s="46"/>
     </row>
     <row r="127">
       <c r="B127" s="2"/>
-      <c r="C127" s="34"/>
+      <c r="C127" s="46"/>
     </row>
     <row r="128">
       <c r="B128" s="2"/>
-      <c r="C128" s="34"/>
+      <c r="C128" s="46"/>
     </row>
     <row r="129">
       <c r="B129" s="2"/>
-      <c r="C129" s="34"/>
+      <c r="C129" s="46"/>
     </row>
     <row r="130">
       <c r="B130" s="2"/>
-      <c r="C130" s="34"/>
+      <c r="C130" s="46"/>
     </row>
     <row r="131">
       <c r="B131" s="2"/>
-      <c r="C131" s="34"/>
+      <c r="C131" s="46"/>
     </row>
     <row r="132">
       <c r="B132" s="2"/>
-      <c r="C132" s="34"/>
+      <c r="C132" s="46"/>
     </row>
     <row r="133">
       <c r="B133" s="2"/>
-      <c r="C133" s="34"/>
+      <c r="C133" s="46"/>
     </row>
     <row r="134">
       <c r="B134" s="2"/>
-      <c r="C134" s="34"/>
+      <c r="C134" s="46"/>
     </row>
     <row r="135">
       <c r="B135" s="2"/>
-      <c r="C135" s="34"/>
+      <c r="C135" s="46"/>
     </row>
     <row r="136">
       <c r="B136" s="2"/>
-      <c r="C136" s="34"/>
+      <c r="C136" s="46"/>
     </row>
     <row r="137">
       <c r="B137" s="2"/>
-      <c r="C137" s="34"/>
+      <c r="C137" s="46"/>
     </row>
     <row r="138">
       <c r="B138" s="2"/>
-      <c r="C138" s="34"/>
+      <c r="C138" s="46"/>
     </row>
     <row r="139">
       <c r="B139" s="2"/>
-      <c r="C139" s="34"/>
+      <c r="C139" s="46"/>
     </row>
     <row r="140">
       <c r="B140" s="2"/>
-      <c r="C140" s="34"/>
+      <c r="C140" s="46"/>
     </row>
     <row r="141">
       <c r="B141" s="2"/>
-      <c r="C141" s="34"/>
+      <c r="C141" s="46"/>
     </row>
     <row r="142">
       <c r="B142" s="2"/>
-      <c r="C142" s="34"/>
+      <c r="C142" s="46"/>
     </row>
     <row r="143">
       <c r="B143" s="2"/>
-      <c r="C143" s="34"/>
+      <c r="C143" s="46"/>
     </row>
     <row r="144">
       <c r="B144" s="2"/>
-      <c r="C144" s="34"/>
+      <c r="C144" s="46"/>
     </row>
     <row r="145">
       <c r="B145" s="2"/>
-      <c r="C145" s="34"/>
+      <c r="C145" s="46"/>
     </row>
     <row r="146">
       <c r="B146" s="2"/>
-      <c r="C146" s="34"/>
+      <c r="C146" s="46"/>
     </row>
     <row r="147">
       <c r="B147" s="2"/>
-      <c r="C147" s="34"/>
+      <c r="C147" s="46"/>
     </row>
     <row r="148">
       <c r="B148" s="2"/>
-      <c r="C148" s="34"/>
+      <c r="C148" s="46"/>
     </row>
     <row r="149">
       <c r="B149" s="2"/>
-      <c r="C149" s="34"/>
+      <c r="C149" s="46"/>
     </row>
     <row r="150">
       <c r="B150" s="2"/>
-      <c r="C150" s="34"/>
+      <c r="C150" s="46"/>
     </row>
     <row r="151">
       <c r="B151" s="2"/>
-      <c r="C151" s="34"/>
+      <c r="C151" s="46"/>
     </row>
     <row r="152">
       <c r="B152" s="2"/>
-      <c r="C152" s="34"/>
+      <c r="C152" s="46"/>
     </row>
     <row r="153">
       <c r="B153" s="2"/>
-      <c r="C153" s="34"/>
+      <c r="C153" s="46"/>
     </row>
     <row r="154">
       <c r="B154" s="2"/>
-      <c r="C154" s="34"/>
+      <c r="C154" s="46"/>
     </row>
     <row r="155">
       <c r="B155" s="2"/>
-      <c r="C155" s="34"/>
+      <c r="C155" s="46"/>
     </row>
     <row r="156">
       <c r="B156" s="2"/>
-      <c r="C156" s="34"/>
+      <c r="C156" s="46"/>
     </row>
     <row r="157">
       <c r="B157" s="2"/>
-      <c r="C157" s="34"/>
+      <c r="C157" s="46"/>
     </row>
     <row r="158">
       <c r="B158" s="2"/>
-      <c r="C158" s="34"/>
+      <c r="C158" s="46"/>
     </row>
     <row r="159">
       <c r="B159" s="2"/>
-      <c r="C159" s="34"/>
+      <c r="C159" s="46"/>
     </row>
     <row r="160">
       <c r="B160" s="2"/>
-      <c r="C160" s="34"/>
+      <c r="C160" s="46"/>
     </row>
     <row r="161">
       <c r="B161" s="2"/>
-      <c r="C161" s="34"/>
+      <c r="C161" s="46"/>
     </row>
     <row r="162">
       <c r="B162" s="2"/>
-      <c r="C162" s="34"/>
+      <c r="C162" s="46"/>
     </row>
     <row r="163">
       <c r="B163" s="2"/>
-      <c r="C163" s="34"/>
+      <c r="C163" s="46"/>
     </row>
     <row r="164">
       <c r="B164" s="2"/>
-      <c r="C164" s="34"/>
+      <c r="C164" s="46"/>
     </row>
     <row r="165">
       <c r="B165" s="2"/>
-      <c r="C165" s="34"/>
+      <c r="C165" s="46"/>
     </row>
     <row r="166">
       <c r="B166" s="2"/>
-      <c r="C166" s="34"/>
+      <c r="C166" s="46"/>
     </row>
     <row r="167">
       <c r="B167" s="2"/>
-      <c r="C167" s="34"/>
+      <c r="C167" s="46"/>
     </row>
     <row r="168">
       <c r="B168" s="2"/>
-      <c r="C168" s="34"/>
+      <c r="C168" s="46"/>
     </row>
     <row r="169">
       <c r="B169" s="2"/>
-      <c r="C169" s="34"/>
+      <c r="C169" s="46"/>
     </row>
     <row r="170">
       <c r="B170" s="2"/>
-      <c r="C170" s="34"/>
+      <c r="C170" s="46"/>
     </row>
     <row r="171">
       <c r="B171" s="2"/>
-      <c r="C171" s="34"/>
+      <c r="C171" s="46"/>
     </row>
     <row r="172">
       <c r="B172" s="2"/>
-      <c r="C172" s="34"/>
+      <c r="C172" s="46"/>
     </row>
     <row r="173">
       <c r="B173" s="2"/>
-      <c r="C173" s="34"/>
+      <c r="C173" s="46"/>
     </row>
     <row r="174">
       <c r="B174" s="2"/>
-      <c r="C174" s="34"/>
+      <c r="C174" s="46"/>
     </row>
     <row r="175">
       <c r="B175" s="2"/>
-      <c r="C175" s="34"/>
+      <c r="C175" s="46"/>
     </row>
     <row r="176">
       <c r="B176" s="2"/>
-      <c r="C176" s="34"/>
+      <c r="C176" s="46"/>
     </row>
     <row r="177">
       <c r="B177" s="2"/>
-      <c r="C177" s="34"/>
+      <c r="C177" s="46"/>
     </row>
     <row r="178">
       <c r="B178" s="2"/>
-      <c r="C178" s="34"/>
+      <c r="C178" s="46"/>
     </row>
     <row r="179">
       <c r="B179" s="2"/>
-      <c r="C179" s="34"/>
+      <c r="C179" s="46"/>
     </row>
     <row r="180">
       <c r="B180" s="2"/>
-      <c r="C180" s="34"/>
+      <c r="C180" s="46"/>
     </row>
     <row r="181">
       <c r="B181" s="2"/>
-      <c r="C181" s="34"/>
+      <c r="C181" s="46"/>
     </row>
     <row r="182">
       <c r="B182" s="2"/>
-      <c r="C182" s="34"/>
+      <c r="C182" s="46"/>
     </row>
     <row r="183">
       <c r="B183" s="2"/>
-      <c r="C183" s="34"/>
+      <c r="C183" s="46"/>
     </row>
     <row r="184">
       <c r="B184" s="2"/>
-      <c r="C184" s="34"/>
+      <c r="C184" s="46"/>
     </row>
     <row r="185">
       <c r="B185" s="2"/>
-      <c r="C185" s="34"/>
+      <c r="C185" s="46"/>
     </row>
     <row r="186">
       <c r="B186" s="2"/>
-      <c r="C186" s="34"/>
+      <c r="C186" s="46"/>
     </row>
     <row r="187">
       <c r="B187" s="2"/>
-      <c r="C187" s="34"/>
+      <c r="C187" s="46"/>
     </row>
     <row r="188">
       <c r="B188" s="2"/>
-      <c r="C188" s="34"/>
+      <c r="C188" s="46"/>
     </row>
     <row r="189">
       <c r="B189" s="2"/>
-      <c r="C189" s="34"/>
+      <c r="C189" s="46"/>
     </row>
     <row r="190">
       <c r="B190" s="2"/>
-      <c r="C190" s="34"/>
+      <c r="C190" s="46"/>
     </row>
     <row r="191">
       <c r="B191" s="2"/>
-      <c r="C191" s="34"/>
+      <c r="C191" s="46"/>
     </row>
     <row r="192">
       <c r="B192" s="2"/>
-      <c r="C192" s="34"/>
+      <c r="C192" s="46"/>
     </row>
     <row r="193">
       <c r="B193" s="2"/>
-      <c r="C193" s="34"/>
+      <c r="C193" s="46"/>
     </row>
     <row r="194">
       <c r="B194" s="2"/>
-      <c r="C194" s="34"/>
+      <c r="C194" s="46"/>
     </row>
     <row r="195">
       <c r="B195" s="2"/>
-      <c r="C195" s="34"/>
+      <c r="C195" s="46"/>
     </row>
     <row r="196">
       <c r="B196" s="2"/>
-      <c r="C196" s="34"/>
+      <c r="C196" s="46"/>
     </row>
     <row r="197">
       <c r="B197" s="2"/>
-      <c r="C197" s="34"/>
+      <c r="C197" s="46"/>
     </row>
     <row r="198">
       <c r="B198" s="2"/>
-      <c r="C198" s="34"/>
+      <c r="C198" s="46"/>
     </row>
     <row r="199">
       <c r="B199" s="2"/>
-      <c r="C199" s="34"/>
+      <c r="C199" s="46"/>
     </row>
     <row r="200">
       <c r="B200" s="2"/>
-      <c r="C200" s="34"/>
+      <c r="C200" s="46"/>
     </row>
     <row r="201">
       <c r="B201" s="2"/>
-      <c r="C201" s="34"/>
+      <c r="C201" s="46"/>
     </row>
     <row r="202">
       <c r="B202" s="2"/>
-      <c r="C202" s="34"/>
+      <c r="C202" s="46"/>
     </row>
     <row r="203">
       <c r="B203" s="2"/>
-      <c r="C203" s="34"/>
+      <c r="C203" s="46"/>
     </row>
     <row r="204">
       <c r="B204" s="2"/>
-      <c r="C204" s="34"/>
+      <c r="C204" s="46"/>
     </row>
     <row r="205">
       <c r="B205" s="2"/>
-      <c r="C205" s="34"/>
+      <c r="C205" s="46"/>
     </row>
     <row r="206">
       <c r="B206" s="2"/>
-      <c r="C206" s="34"/>
+      <c r="C206" s="46"/>
     </row>
     <row r="207">
       <c r="B207" s="2"/>
-      <c r="C207" s="34"/>
+      <c r="C207" s="46"/>
     </row>
     <row r="208">
       <c r="B208" s="2"/>
-      <c r="C208" s="34"/>
+      <c r="C208" s="46"/>
     </row>
     <row r="209">
       <c r="B209" s="2"/>
-      <c r="C209" s="34"/>
+      <c r="C209" s="46"/>
     </row>
     <row r="210">
       <c r="B210" s="2"/>
-      <c r="C210" s="34"/>
+      <c r="C210" s="46"/>
     </row>
     <row r="211">
       <c r="B211" s="2"/>
-      <c r="C211" s="34"/>
+      <c r="C211" s="46"/>
     </row>
     <row r="212">
       <c r="B212" s="2"/>
-      <c r="C212" s="34"/>
+      <c r="C212" s="46"/>
     </row>
     <row r="213">
       <c r="B213" s="2"/>
-      <c r="C213" s="34"/>
+      <c r="C213" s="46"/>
     </row>
     <row r="214">
       <c r="B214" s="2"/>
-      <c r="C214" s="34"/>
+      <c r="C214" s="46"/>
     </row>
     <row r="215">
       <c r="B215" s="2"/>
-      <c r="C215" s="34"/>
+      <c r="C215" s="46"/>
     </row>
     <row r="216">
       <c r="B216" s="2"/>
-      <c r="C216" s="34"/>
+      <c r="C216" s="46"/>
     </row>
     <row r="217">
       <c r="B217" s="2"/>
-      <c r="C217" s="34"/>
+      <c r="C217" s="46"/>
     </row>
     <row r="218">
       <c r="B218" s="2"/>
-      <c r="C218" s="34"/>
+      <c r="C218" s="46"/>
     </row>
     <row r="219">
       <c r="B219" s="2"/>
-      <c r="C219" s="34"/>
+      <c r="C219" s="46"/>
     </row>
     <row r="220">
       <c r="B220" s="2"/>
-      <c r="C220" s="34"/>
+      <c r="C220" s="46"/>
     </row>
     <row r="221">
       <c r="B221" s="2"/>
-      <c r="C221" s="34"/>
+      <c r="C221" s="46"/>
     </row>
     <row r="222">
       <c r="B222" s="2"/>
-      <c r="C222" s="34"/>
+      <c r="C222" s="46"/>
     </row>
     <row r="223">
       <c r="B223" s="2"/>
-      <c r="C223" s="34"/>
+      <c r="C223" s="46"/>
     </row>
     <row r="224">
       <c r="B224" s="2"/>
-      <c r="C224" s="34"/>
+      <c r="C224" s="46"/>
     </row>
     <row r="225">
       <c r="B225" s="2"/>
-      <c r="C225" s="34"/>
+      <c r="C225" s="46"/>
     </row>
     <row r="226">
       <c r="B226" s="2"/>
-      <c r="C226" s="34"/>
+      <c r="C226" s="46"/>
     </row>
     <row r="227">
       <c r="B227" s="2"/>
-      <c r="C227" s="34"/>
+      <c r="C227" s="46"/>
     </row>
     <row r="228">
       <c r="B228" s="2"/>
-      <c r="C228" s="34"/>
+      <c r="C228" s="46"/>
     </row>
     <row r="229">
       <c r="B229" s="2"/>
-      <c r="C229" s="34"/>
+      <c r="C229" s="46"/>
     </row>
     <row r="230">
       <c r="B230" s="2"/>
-      <c r="C230" s="34"/>
+      <c r="C230" s="46"/>
     </row>
     <row r="231">
       <c r="B231" s="2"/>
-      <c r="C231" s="34"/>
+      <c r="C231" s="46"/>
     </row>
     <row r="232">
       <c r="B232" s="2"/>
-      <c r="C232" s="34"/>
+      <c r="C232" s="46"/>
     </row>
     <row r="233">
       <c r="B233" s="2"/>
-      <c r="C233" s="34"/>
+      <c r="C233" s="46"/>
     </row>
     <row r="234">
       <c r="B234" s="2"/>
-      <c r="C234" s="34"/>
+      <c r="C234" s="46"/>
     </row>
     <row r="235">
       <c r="B235" s="2"/>
-      <c r="C235" s="34"/>
+      <c r="C235" s="46"/>
     </row>
     <row r="236">
       <c r="B236" s="2"/>
-      <c r="C236" s="34"/>
+      <c r="C236" s="46"/>
     </row>
     <row r="237">
       <c r="B237" s="2"/>
-      <c r="C237" s="34"/>
+      <c r="C237" s="46"/>
     </row>
     <row r="238">
       <c r="B238" s="2"/>
-      <c r="C238" s="34"/>
+      <c r="C238" s="46"/>
     </row>
     <row r="239">
       <c r="B239" s="2"/>
-      <c r="C239" s="34"/>
+      <c r="C239" s="46"/>
     </row>
     <row r="240">
       <c r="B240" s="2"/>
-      <c r="C240" s="34"/>
+      <c r="C240" s="46"/>
     </row>
     <row r="241">
       <c r="B241" s="2"/>
-      <c r="C241" s="34"/>
+      <c r="C241" s="46"/>
     </row>
     <row r="242">
       <c r="B242" s="2"/>
-      <c r="C242" s="34"/>
+      <c r="C242" s="46"/>
     </row>
     <row r="243">
       <c r="B243" s="2"/>
-      <c r="C243" s="34"/>
+      <c r="C243" s="46"/>
     </row>
     <row r="244">
       <c r="B244" s="2"/>
-      <c r="C244" s="34"/>
+      <c r="C244" s="46"/>
     </row>
     <row r="245">
       <c r="B245" s="2"/>
-      <c r="C245" s="34"/>
+      <c r="C245" s="46"/>
     </row>
     <row r="246">
       <c r="B246" s="2"/>
-      <c r="C246" s="34"/>
+      <c r="C246" s="46"/>
     </row>
     <row r="247">
       <c r="B247" s="2"/>
-      <c r="C247" s="34"/>
+      <c r="C247" s="46"/>
     </row>
     <row r="248">
       <c r="B248" s="2"/>
-      <c r="C248" s="34"/>
+      <c r="C248" s="46"/>
     </row>
     <row r="249">
       <c r="B249" s="2"/>
-      <c r="C249" s="34"/>
+      <c r="C249" s="46"/>
     </row>
     <row r="250">
       <c r="B250" s="2"/>
-      <c r="C250" s="34"/>
+      <c r="C250" s="46"/>
     </row>
     <row r="251">
       <c r="B251" s="2"/>
-      <c r="C251" s="34"/>
+      <c r="C251" s="46"/>
     </row>
     <row r="252">
       <c r="B252" s="2"/>
-      <c r="C252" s="34"/>
+      <c r="C252" s="46"/>
     </row>
     <row r="253">
       <c r="B253" s="2"/>
-      <c r="C253" s="34"/>
+      <c r="C253" s="46"/>
     </row>
     <row r="254">
       <c r="B254" s="2"/>
-      <c r="C254" s="34"/>
+      <c r="C254" s="46"/>
     </row>
     <row r="255">
       <c r="B255" s="2"/>
-      <c r="C255" s="34"/>
+      <c r="C255" s="46"/>
     </row>
     <row r="256">
       <c r="B256" s="2"/>
-      <c r="C256" s="34"/>
+      <c r="C256" s="46"/>
     </row>
     <row r="257">
       <c r="B257" s="2"/>
-      <c r="C257" s="34"/>
+      <c r="C257" s="46"/>
     </row>
     <row r="258">
       <c r="B258" s="2"/>
-      <c r="C258" s="34"/>
+      <c r="C258" s="46"/>
     </row>
     <row r="259">
       <c r="B259" s="2"/>
-      <c r="C259" s="34"/>
+      <c r="C259" s="46"/>
     </row>
     <row r="260">
       <c r="B260" s="2"/>
-      <c r="C260" s="34"/>
+      <c r="C260" s="46"/>
     </row>
     <row r="261">
       <c r="B261" s="2"/>
-      <c r="C261" s="34"/>
+      <c r="C261" s="46"/>
     </row>
     <row r="262">
       <c r="B262" s="2"/>
-      <c r="C262" s="34"/>
+      <c r="C262" s="46"/>
     </row>
     <row r="263">
       <c r="B263" s="2"/>
-      <c r="C263" s="34"/>
+      <c r="C263" s="46"/>
     </row>
     <row r="264">
       <c r="B264" s="2"/>
-      <c r="C264" s="34"/>
+      <c r="C264" s="46"/>
     </row>
     <row r="265">
       <c r="B265" s="2"/>
-      <c r="C265" s="34"/>
+      <c r="C265" s="46"/>
     </row>
     <row r="266">
       <c r="B266" s="2"/>
-      <c r="C266" s="34"/>
+      <c r="C266" s="46"/>
     </row>
     <row r="267">
       <c r="B267" s="2"/>
-      <c r="C267" s="34"/>
+      <c r="C267" s="46"/>
     </row>
     <row r="268">
       <c r="B268" s="2"/>
-      <c r="C268" s="34"/>
+      <c r="C268" s="46"/>
     </row>
     <row r="269">
       <c r="B269" s="2"/>
-      <c r="C269" s="34"/>
+      <c r="C269" s="46"/>
     </row>
     <row r="270">
       <c r="B270" s="2"/>
-      <c r="C270" s="34"/>
+      <c r="C270" s="46"/>
     </row>
     <row r="271">
       <c r="B271" s="2"/>
-      <c r="C271" s="34"/>
+      <c r="C271" s="46"/>
     </row>
     <row r="272">
       <c r="B272" s="2"/>
-      <c r="C272" s="34"/>
+      <c r="C272" s="46"/>
     </row>
     <row r="273">
       <c r="B273" s="2"/>
-      <c r="C273" s="34"/>
+      <c r="C273" s="46"/>
     </row>
     <row r="274">
       <c r="B274" s="2"/>
-      <c r="C274" s="34"/>
+      <c r="C274" s="46"/>
     </row>
     <row r="275">
       <c r="B275" s="2"/>
-      <c r="C275" s="34"/>
+      <c r="C275" s="46"/>
     </row>
     <row r="276">
       <c r="B276" s="2"/>
-      <c r="C276" s="34"/>
+      <c r="C276" s="46"/>
     </row>
     <row r="277">
       <c r="B277" s="2"/>
-      <c r="C277" s="34"/>
+      <c r="C277" s="46"/>
     </row>
     <row r="278">
       <c r="B278" s="2"/>
-      <c r="C278" s="34"/>
+      <c r="C278" s="46"/>
     </row>
     <row r="279">
       <c r="B279" s="2"/>
-      <c r="C279" s="34"/>
+      <c r="C279" s="46"/>
     </row>
     <row r="280">
       <c r="B280" s="2"/>
-      <c r="C280" s="34"/>
+      <c r="C280" s="46"/>
     </row>
     <row r="281">
       <c r="B281" s="2"/>
-      <c r="C281" s="34"/>
+      <c r="C281" s="46"/>
     </row>
     <row r="282">
       <c r="B282" s="2"/>
-      <c r="C282" s="34"/>
+      <c r="C282" s="46"/>
     </row>
     <row r="283">
       <c r="B283" s="2"/>
-      <c r="C283" s="34"/>
+      <c r="C283" s="46"/>
     </row>
     <row r="284">
       <c r="B284" s="2"/>
-      <c r="C284" s="34"/>
+      <c r="C284" s="46"/>
     </row>
     <row r="285">
       <c r="B285" s="2"/>
-      <c r="C285" s="34"/>
+      <c r="C285" s="46"/>
     </row>
     <row r="286">
       <c r="B286" s="2"/>
-      <c r="C286" s="34"/>
+      <c r="C286" s="46"/>
     </row>
     <row r="287">
       <c r="B287" s="2"/>
-      <c r="C287" s="34"/>
+      <c r="C287" s="46"/>
     </row>
     <row r="288">
       <c r="B288" s="2"/>
-      <c r="C288" s="34"/>
+      <c r="C288" s="46"/>
     </row>
     <row r="289">
       <c r="B289" s="2"/>
-      <c r="C289" s="34"/>
+      <c r="C289" s="46"/>
     </row>
     <row r="290">
       <c r="B290" s="2"/>
-      <c r="C290" s="34"/>
+      <c r="C290" s="46"/>
     </row>
     <row r="291">
       <c r="B291" s="2"/>
-      <c r="C291" s="34"/>
+      <c r="C291" s="46"/>
     </row>
     <row r="292">
       <c r="B292" s="2"/>
-      <c r="C292" s="34"/>
+      <c r="C292" s="46"/>
     </row>
     <row r="293">
       <c r="B293" s="2"/>
-      <c r="C293" s="34"/>
+      <c r="C293" s="46"/>
     </row>
     <row r="294">
       <c r="B294" s="2"/>
-      <c r="C294" s="34"/>
+      <c r="C294" s="46"/>
     </row>
     <row r="295">
       <c r="B295" s="2"/>
-      <c r="C295" s="34"/>
+      <c r="C295" s="46"/>
     </row>
     <row r="296">
       <c r="B296" s="2"/>
-      <c r="C296" s="34"/>
+      <c r="C296" s="46"/>
     </row>
     <row r="297">
       <c r="B297" s="2"/>
-      <c r="C297" s="34"/>
+      <c r="C297" s="46"/>
     </row>
     <row r="298">
       <c r="B298" s="2"/>
-      <c r="C298" s="34"/>
+      <c r="C298" s="46"/>
     </row>
     <row r="299">
       <c r="B299" s="2"/>
-      <c r="C299" s="34"/>
+      <c r="C299" s="46"/>
     </row>
     <row r="300">
       <c r="B300" s="2"/>
-      <c r="C300" s="34"/>
+      <c r="C300" s="46"/>
     </row>
     <row r="301">
       <c r="B301" s="2"/>
-      <c r="C301" s="34"/>
+      <c r="C301" s="46"/>
     </row>
     <row r="302">
       <c r="B302" s="2"/>
-      <c r="C302" s="34"/>
+      <c r="C302" s="46"/>
     </row>
     <row r="303">
       <c r="B303" s="2"/>
-      <c r="C303" s="34"/>
+      <c r="C303" s="46"/>
     </row>
     <row r="304">
       <c r="B304" s="2"/>
-      <c r="C304" s="34"/>
+      <c r="C304" s="46"/>
     </row>
     <row r="305">
       <c r="B305" s="2"/>
-      <c r="C305" s="34"/>
+      <c r="C305" s="46"/>
     </row>
     <row r="306">
       <c r="B306" s="2"/>
-      <c r="C306" s="34"/>
+      <c r="C306" s="46"/>
     </row>
     <row r="307">
       <c r="B307" s="2"/>
-      <c r="C307" s="34"/>
+      <c r="C307" s="46"/>
     </row>
     <row r="308">
       <c r="B308" s="2"/>
-      <c r="C308" s="34"/>
+      <c r="C308" s="46"/>
     </row>
     <row r="309">
       <c r="B309" s="2"/>
-      <c r="C309" s="34"/>
+      <c r="C309" s="46"/>
     </row>
     <row r="310">
       <c r="B310" s="2"/>
-      <c r="C310" s="34"/>
+      <c r="C310" s="46"/>
     </row>
     <row r="311">
       <c r="B311" s="2"/>
-      <c r="C311" s="34"/>
+      <c r="C311" s="46"/>
     </row>
     <row r="312">
       <c r="B312" s="2"/>
-      <c r="C312" s="34"/>
+      <c r="C312" s="46"/>
     </row>
     <row r="313">
       <c r="B313" s="2"/>
-      <c r="C313" s="34"/>
+      <c r="C313" s="46"/>
     </row>
     <row r="314">
       <c r="B314" s="2"/>
-      <c r="C314" s="34"/>
+      <c r="C314" s="46"/>
     </row>
     <row r="315">
       <c r="B315" s="2"/>
-      <c r="C315" s="34"/>
+      <c r="C315" s="46"/>
     </row>
     <row r="316">
       <c r="B316" s="2"/>
-      <c r="C316" s="34"/>
+      <c r="C316" s="46"/>
     </row>
     <row r="317">
       <c r="B317" s="2"/>
-      <c r="C317" s="34"/>
+      <c r="C317" s="46"/>
     </row>
     <row r="318">
       <c r="B318" s="2"/>
-      <c r="C318" s="34"/>
+      <c r="C318" s="46"/>
     </row>
     <row r="319">
       <c r="B319" s="2"/>
-      <c r="C319" s="34"/>
+      <c r="C319" s="46"/>
     </row>
     <row r="320">
       <c r="B320" s="2"/>
-      <c r="C320" s="34"/>
+      <c r="C320" s="46"/>
     </row>
     <row r="321">
       <c r="B321" s="2"/>
-      <c r="C321" s="34"/>
+      <c r="C321" s="46"/>
     </row>
     <row r="322">
       <c r="B322" s="2"/>
-      <c r="C322" s="34"/>
+      <c r="C322" s="46"/>
     </row>
     <row r="323">
       <c r="B323" s="2"/>
-      <c r="C323" s="34"/>
+      <c r="C323" s="46"/>
     </row>
     <row r="324">
       <c r="B324" s="2"/>
-      <c r="C324" s="34"/>
+      <c r="C324" s="46"/>
     </row>
     <row r="325">
       <c r="B325" s="2"/>
-      <c r="C325" s="34"/>
+      <c r="C325" s="46"/>
     </row>
     <row r="326">
       <c r="B326" s="2"/>
-      <c r="C326" s="34"/>
+      <c r="C326" s="46"/>
     </row>
     <row r="327">
       <c r="B327" s="2"/>
-      <c r="C327" s="34"/>
+      <c r="C327" s="46"/>
     </row>
     <row r="328">
       <c r="B328" s="2"/>
-      <c r="C328" s="34"/>
+      <c r="C328" s="46"/>
     </row>
     <row r="329">
       <c r="B329" s="2"/>
-      <c r="C329" s="34"/>
+      <c r="C329" s="46"/>
     </row>
     <row r="330">
       <c r="B330" s="2"/>
-      <c r="C330" s="34"/>
+      <c r="C330" s="46"/>
     </row>
     <row r="331">
       <c r="B331" s="2"/>
-      <c r="C331" s="34"/>
+      <c r="C331" s="46"/>
     </row>
     <row r="332">
       <c r="B332" s="2"/>
-      <c r="C332" s="34"/>
+      <c r="C332" s="46"/>
     </row>
     <row r="333">
       <c r="B333" s="2"/>
-      <c r="C333" s="34"/>
+      <c r="C333" s="46"/>
     </row>
     <row r="334">
       <c r="B334" s="2"/>
-      <c r="C334" s="34"/>
+      <c r="C334" s="46"/>
     </row>
     <row r="335">
       <c r="B335" s="2"/>
-      <c r="C335" s="34"/>
+      <c r="C335" s="46"/>
     </row>
     <row r="336">
       <c r="B336" s="2"/>
-      <c r="C336" s="34"/>
+      <c r="C336" s="46"/>
     </row>
     <row r="337">
       <c r="B337" s="2"/>
-      <c r="C337" s="34"/>
+      <c r="C337" s="46"/>
     </row>
     <row r="338">
       <c r="B338" s="2"/>
-      <c r="C338" s="34"/>
+      <c r="C338" s="46"/>
     </row>
     <row r="339">
       <c r="B339" s="2"/>
-      <c r="C339" s="34"/>
+      <c r="C339" s="46"/>
     </row>
     <row r="340">
       <c r="B340" s="2"/>
-      <c r="C340" s="34"/>
+      <c r="C340" s="46"/>
     </row>
     <row r="341">
       <c r="B341" s="2"/>
-      <c r="C341" s="34"/>
+      <c r="C341" s="46"/>
     </row>
     <row r="342">
       <c r="B342" s="2"/>
-      <c r="C342" s="34"/>
+      <c r="C342" s="46"/>
     </row>
     <row r="343">
       <c r="B343" s="2"/>
-      <c r="C343" s="34"/>
+      <c r="C343" s="46"/>
     </row>
     <row r="344">
       <c r="B344" s="2"/>
-      <c r="C344" s="34"/>
+      <c r="C344" s="46"/>
     </row>
     <row r="345">
       <c r="B345" s="2"/>
-      <c r="C345" s="34"/>
+      <c r="C345" s="46"/>
     </row>
     <row r="346">
       <c r="B346" s="2"/>
-      <c r="C346" s="34"/>
+      <c r="C346" s="46"/>
     </row>
     <row r="347">
       <c r="B347" s="2"/>
-      <c r="C347" s="34"/>
+      <c r="C347" s="46"/>
     </row>
     <row r="348">
       <c r="B348" s="2"/>
-      <c r="C348" s="34"/>
+      <c r="C348" s="46"/>
     </row>
     <row r="349">
       <c r="B349" s="2"/>
-      <c r="C349" s="34"/>
+      <c r="C349" s="46"/>
     </row>
     <row r="350">
       <c r="B350" s="2"/>
-      <c r="C350" s="34"/>
+      <c r="C350" s="46"/>
     </row>
     <row r="351">
       <c r="B351" s="2"/>
-      <c r="C351" s="34"/>
+      <c r="C351" s="46"/>
     </row>
     <row r="352">
       <c r="B352" s="2"/>
-      <c r="C352" s="34"/>
+      <c r="C352" s="46"/>
     </row>
     <row r="353">
       <c r="B353" s="2"/>
-      <c r="C353" s="34"/>
+      <c r="C353" s="46"/>
     </row>
     <row r="354">
       <c r="B354" s="2"/>
-      <c r="C354" s="34"/>
+      <c r="C354" s="46"/>
     </row>
     <row r="355">
       <c r="B355" s="2"/>
-      <c r="C355" s="34"/>
+      <c r="C355" s="46"/>
     </row>
     <row r="356">
       <c r="B356" s="2"/>
-      <c r="C356" s="34"/>
+      <c r="C356" s="46"/>
     </row>
     <row r="357">
       <c r="B357" s="2"/>
-      <c r="C357" s="34"/>
+      <c r="C357" s="46"/>
     </row>
     <row r="358">
       <c r="B358" s="2"/>
-      <c r="C358" s="34"/>
+      <c r="C358" s="46"/>
     </row>
     <row r="359">
       <c r="B359" s="2"/>
-      <c r="C359" s="34"/>
+      <c r="C359" s="46"/>
     </row>
     <row r="360">
       <c r="B360" s="2"/>
-      <c r="C360" s="34"/>
+      <c r="C360" s="46"/>
     </row>
     <row r="361">
       <c r="B361" s="2"/>
-      <c r="C361" s="34"/>
+      <c r="C361" s="46"/>
     </row>
     <row r="362">
       <c r="B362" s="2"/>
-      <c r="C362" s="34"/>
+      <c r="C362" s="46"/>
     </row>
     <row r="363">
       <c r="B363" s="2"/>
-      <c r="C363" s="34"/>
+      <c r="C363" s="46"/>
     </row>
     <row r="364">
       <c r="B364" s="2"/>
-      <c r="C364" s="34"/>
+      <c r="C364" s="46"/>
     </row>
     <row r="365">
       <c r="B365" s="2"/>
-      <c r="C365" s="34"/>
+      <c r="C365" s="46"/>
     </row>
     <row r="366">
       <c r="B366" s="2"/>
-      <c r="C366" s="34"/>
+      <c r="C366" s="46"/>
     </row>
     <row r="367">
       <c r="B367" s="2"/>
-      <c r="C367" s="34"/>
+      <c r="C367" s="46"/>
     </row>
     <row r="368">
       <c r="B368" s="2"/>
-      <c r="C368" s="34"/>
+      <c r="C368" s="46"/>
     </row>
     <row r="369">
       <c r="B369" s="2"/>
-      <c r="C369" s="34"/>
+      <c r="C369" s="46"/>
     </row>
     <row r="370">
       <c r="B370" s="2"/>
-      <c r="C370" s="34"/>
+      <c r="C370" s="46"/>
     </row>
     <row r="371">
       <c r="B371" s="2"/>
-      <c r="C371" s="34"/>
+      <c r="C371" s="46"/>
     </row>
     <row r="372">
       <c r="B372" s="2"/>
-      <c r="C372" s="34"/>
+      <c r="C372" s="46"/>
     </row>
     <row r="373">
       <c r="B373" s="2"/>
-      <c r="C373" s="34"/>
+      <c r="C373" s="46"/>
     </row>
     <row r="374">
       <c r="B374" s="2"/>
-      <c r="C374" s="34"/>
+      <c r="C374" s="46"/>
     </row>
     <row r="375">
       <c r="B375" s="2"/>
-      <c r="C375" s="34"/>
+      <c r="C375" s="46"/>
     </row>
     <row r="376">
       <c r="B376" s="2"/>
-      <c r="C376" s="34"/>
+      <c r="C376" s="46"/>
     </row>
     <row r="377">
       <c r="B377" s="2"/>
-      <c r="C377" s="34"/>
+      <c r="C377" s="46"/>
     </row>
     <row r="378">
       <c r="B378" s="2"/>
-      <c r="C378" s="34"/>
+      <c r="C378" s="46"/>
     </row>
     <row r="379">
       <c r="B379" s="2"/>
-      <c r="C379" s="34"/>
+      <c r="C379" s="46"/>
     </row>
     <row r="380">
       <c r="B380" s="2"/>
-      <c r="C380" s="34"/>
+      <c r="C380" s="46"/>
     </row>
     <row r="381">
       <c r="B381" s="2"/>
-      <c r="C381" s="34"/>
+      <c r="C381" s="46"/>
     </row>
     <row r="382">
       <c r="B382" s="2"/>
-      <c r="C382" s="34"/>
+      <c r="C382" s="46"/>
     </row>
     <row r="383">
       <c r="B383" s="2"/>
-      <c r="C383" s="34"/>
+      <c r="C383" s="46"/>
     </row>
     <row r="384">
       <c r="B384" s="2"/>
-      <c r="C384" s="34"/>
+      <c r="C384" s="46"/>
     </row>
     <row r="385">
       <c r="B385" s="2"/>
-      <c r="C385" s="34"/>
+      <c r="C385" s="46"/>
     </row>
     <row r="386">
       <c r="B386" s="2"/>
-      <c r="C386" s="34"/>
+      <c r="C386" s="46"/>
     </row>
     <row r="387">
       <c r="B387" s="2"/>
-      <c r="C387" s="34"/>
+      <c r="C387" s="46"/>
     </row>
     <row r="388">
       <c r="B388" s="2"/>
-      <c r="C388" s="34"/>
+      <c r="C388" s="46"/>
     </row>
     <row r="389">
       <c r="B389" s="2"/>
-      <c r="C389" s="34"/>
+      <c r="C389" s="46"/>
     </row>
     <row r="390">
       <c r="B390" s="2"/>
-      <c r="C390" s="34"/>
+      <c r="C390" s="46"/>
     </row>
     <row r="391">
       <c r="B391" s="2"/>
-      <c r="C391" s="34"/>
+      <c r="C391" s="46"/>
     </row>
     <row r="392">
       <c r="B392" s="2"/>
-      <c r="C392" s="34"/>
+      <c r="C392" s="46"/>
     </row>
     <row r="393">
       <c r="B393" s="2"/>
-      <c r="C393" s="34"/>
+      <c r="C393" s="46"/>
     </row>
     <row r="394">
       <c r="B394" s="2"/>
-      <c r="C394" s="34"/>
+      <c r="C394" s="46"/>
     </row>
     <row r="395">
       <c r="B395" s="2"/>
-      <c r="C395" s="34"/>
+      <c r="C395" s="46"/>
     </row>
     <row r="396">
       <c r="B396" s="2"/>
-      <c r="C396" s="34"/>
+      <c r="C396" s="46"/>
     </row>
     <row r="397">
       <c r="B397" s="2"/>
-      <c r="C397" s="34"/>
+      <c r="C397" s="46"/>
     </row>
     <row r="398">
       <c r="B398" s="2"/>
-      <c r="C398" s="34"/>
+      <c r="C398" s="46"/>
     </row>
     <row r="399">
       <c r="B399" s="2"/>
-      <c r="C399" s="34"/>
+      <c r="C399" s="46"/>
     </row>
     <row r="400">
       <c r="B400" s="2"/>
-      <c r="C400" s="34"/>
+      <c r="C400" s="46"/>
     </row>
     <row r="401">
       <c r="B401" s="2"/>
-      <c r="C401" s="34"/>
+      <c r="C401" s="46"/>
     </row>
     <row r="402">
       <c r="B402" s="2"/>
-      <c r="C402" s="34"/>
+      <c r="C402" s="46"/>
     </row>
     <row r="403">
       <c r="B403" s="2"/>
-      <c r="C403" s="34"/>
+      <c r="C403" s="46"/>
     </row>
     <row r="404">
       <c r="B404" s="2"/>
-      <c r="C404" s="34"/>
+      <c r="C404" s="46"/>
     </row>
     <row r="405">
       <c r="B405" s="2"/>
-      <c r="C405" s="34"/>
+      <c r="C405" s="46"/>
     </row>
     <row r="406">
       <c r="B406" s="2"/>
-      <c r="C406" s="34"/>
+      <c r="C406" s="46"/>
     </row>
     <row r="407">
       <c r="B407" s="2"/>
-      <c r="C407" s="34"/>
+      <c r="C407" s="46"/>
     </row>
     <row r="408">
       <c r="B408" s="2"/>
-      <c r="C408" s="34"/>
+      <c r="C408" s="46"/>
     </row>
     <row r="409">
       <c r="B409" s="2"/>
-      <c r="C409" s="34"/>
+      <c r="C409" s="46"/>
     </row>
     <row r="410">
       <c r="B410" s="2"/>
-      <c r="C410" s="34"/>
+      <c r="C410" s="46"/>
     </row>
     <row r="411">
       <c r="B411" s="2"/>
-      <c r="C411" s="34"/>
+      <c r="C411" s="46"/>
     </row>
     <row r="412">
       <c r="B412" s="2"/>
-      <c r="C412" s="34"/>
+      <c r="C412" s="46"/>
     </row>
     <row r="413">
       <c r="B413" s="2"/>
-      <c r="C413" s="34"/>
+      <c r="C413" s="46"/>
     </row>
     <row r="414">
       <c r="B414" s="2"/>
-      <c r="C414" s="34"/>
+      <c r="C414" s="46"/>
     </row>
     <row r="415">
       <c r="B415" s="2"/>
-      <c r="C415" s="34"/>
+      <c r="C415" s="46"/>
     </row>
     <row r="416">
       <c r="B416" s="2"/>
-      <c r="C416" s="34"/>
+      <c r="C416" s="46"/>
     </row>
     <row r="417">
       <c r="B417" s="2"/>
-      <c r="C417" s="34"/>
+      <c r="C417" s="46"/>
     </row>
     <row r="418">
       <c r="B418" s="2"/>
-      <c r="C418" s="34"/>
+      <c r="C418" s="46"/>
     </row>
     <row r="419">
       <c r="B419" s="2"/>
-      <c r="C419" s="34"/>
+      <c r="C419" s="46"/>
     </row>
     <row r="420">
       <c r="B420" s="2"/>
-      <c r="C420" s="34"/>
+      <c r="C420" s="46"/>
     </row>
     <row r="421">
       <c r="B421" s="2"/>
-      <c r="C421" s="34"/>
+      <c r="C421" s="46"/>
     </row>
     <row r="422">
       <c r="B422" s="2"/>
-      <c r="C422" s="34"/>
+      <c r="C422" s="46"/>
     </row>
     <row r="423">
       <c r="B423" s="2"/>
-      <c r="C423" s="34"/>
+      <c r="C423" s="46"/>
     </row>
     <row r="424">
       <c r="B424" s="2"/>
-      <c r="C424" s="34"/>
+      <c r="C424" s="46"/>
     </row>
     <row r="425">
       <c r="B425" s="2"/>
-      <c r="C425" s="34"/>
+      <c r="C425" s="46"/>
     </row>
     <row r="426">
       <c r="B426" s="2"/>
-      <c r="C426" s="34"/>
+      <c r="C426" s="46"/>
     </row>
     <row r="427">
       <c r="B427" s="2"/>
-      <c r="C427" s="34"/>
+      <c r="C427" s="46"/>
     </row>
     <row r="428">
       <c r="B428" s="2"/>
-      <c r="C428" s="34"/>
+      <c r="C428" s="46"/>
     </row>
     <row r="429">
       <c r="B429" s="2"/>
-      <c r="C429" s="34"/>
+      <c r="C429" s="46"/>
     </row>
     <row r="430">
       <c r="B430" s="2"/>
-      <c r="C430" s="34"/>
+      <c r="C430" s="46"/>
     </row>
     <row r="431">
       <c r="B431" s="2"/>
-      <c r="C431" s="34"/>
+      <c r="C431" s="46"/>
     </row>
     <row r="432">
       <c r="B432" s="2"/>
-      <c r="C432" s="34"/>
+      <c r="C432" s="46"/>
     </row>
     <row r="433">
       <c r="B433" s="2"/>
-      <c r="C433" s="34"/>
+      <c r="C433" s="46"/>
     </row>
     <row r="434">
       <c r="B434" s="2"/>
-      <c r="C434" s="34"/>
+      <c r="C434" s="46"/>
     </row>
     <row r="435">
       <c r="B435" s="2"/>
-      <c r="C435" s="34"/>
+      <c r="C435" s="46"/>
     </row>
     <row r="436">
       <c r="B436" s="2"/>
-      <c r="C436" s="34"/>
+      <c r="C436" s="46"/>
     </row>
     <row r="437">
       <c r="B437" s="2"/>
-      <c r="C437" s="34"/>
+      <c r="C437" s="46"/>
     </row>
     <row r="438">
       <c r="B438" s="2"/>
-      <c r="C438" s="34"/>
+      <c r="C438" s="46"/>
     </row>
     <row r="439">
       <c r="B439" s="2"/>
-      <c r="C439" s="34"/>
+      <c r="C439" s="46"/>
     </row>
     <row r="440">
       <c r="B440" s="2"/>
-      <c r="C440" s="34"/>
+      <c r="C440" s="46"/>
     </row>
     <row r="441">
       <c r="B441" s="2"/>
-      <c r="C441" s="34"/>
+      <c r="C441" s="46"/>
     </row>
     <row r="442">
       <c r="B442" s="2"/>
-      <c r="C442" s="34"/>
+      <c r="C442" s="46"/>
     </row>
     <row r="443">
       <c r="B443" s="2"/>
-      <c r="C443" s="34"/>
+      <c r="C443" s="46"/>
     </row>
     <row r="444">
       <c r="B444" s="2"/>
-      <c r="C444" s="34"/>
+      <c r="C444" s="46"/>
     </row>
     <row r="445">
       <c r="B445" s="2"/>
-      <c r="C445" s="34"/>
+      <c r="C445" s="46"/>
     </row>
     <row r="446">
       <c r="B446" s="2"/>
-      <c r="C446" s="34"/>
+      <c r="C446" s="46"/>
     </row>
     <row r="447">
       <c r="B447" s="2"/>
-      <c r="C447" s="34"/>
+      <c r="C447" s="46"/>
     </row>
     <row r="448">
       <c r="B448" s="2"/>
-      <c r="C448" s="34"/>
+      <c r="C448" s="46"/>
     </row>
     <row r="449">
       <c r="B449" s="2"/>
-      <c r="C449" s="34"/>
+      <c r="C449" s="46"/>
     </row>
     <row r="450">
       <c r="B450" s="2"/>
-      <c r="C450" s="34"/>
+      <c r="C450" s="46"/>
     </row>
     <row r="451">
       <c r="B451" s="2"/>
-      <c r="C451" s="34"/>
+      <c r="C451" s="46"/>
     </row>
     <row r="452">
       <c r="B452" s="2"/>
-      <c r="C452" s="34"/>
+      <c r="C452" s="46"/>
     </row>
     <row r="453">
       <c r="B453" s="2"/>
-      <c r="C453" s="34"/>
+      <c r="C453" s="46"/>
     </row>
     <row r="454">
       <c r="B454" s="2"/>
-      <c r="C454" s="34"/>
+      <c r="C454" s="46"/>
     </row>
     <row r="455">
       <c r="B455" s="2"/>
-      <c r="C455" s="34"/>
+      <c r="C455" s="46"/>
     </row>
     <row r="456">
       <c r="B456" s="2"/>
-      <c r="C456" s="34"/>
+      <c r="C456" s="46"/>
     </row>
     <row r="457">
       <c r="B457" s="2"/>
-      <c r="C457" s="34"/>
+      <c r="C457" s="46"/>
     </row>
     <row r="458">
       <c r="B458" s="2"/>
-      <c r="C458" s="34"/>
+      <c r="C458" s="46"/>
     </row>
     <row r="459">
       <c r="B459" s="2"/>
-      <c r="C459" s="34"/>
+      <c r="C459" s="46"/>
     </row>
     <row r="460">
       <c r="B460" s="2"/>
-      <c r="C460" s="34"/>
+      <c r="C460" s="46"/>
     </row>
     <row r="461">
       <c r="B461" s="2"/>
-      <c r="C461" s="34"/>
+      <c r="C461" s="46"/>
     </row>
     <row r="462">
       <c r="B462" s="2"/>
-      <c r="C462" s="34"/>
+      <c r="C462" s="46"/>
     </row>
     <row r="463">
       <c r="B463" s="2"/>
-      <c r="C463" s="34"/>
+      <c r="C463" s="46"/>
     </row>
     <row r="464">
       <c r="B464" s="2"/>
-      <c r="C464" s="34"/>
+      <c r="C464" s="46"/>
     </row>
     <row r="465">
       <c r="B465" s="2"/>
-      <c r="C465" s="34"/>
+      <c r="C465" s="46"/>
     </row>
     <row r="466">
       <c r="B466" s="2"/>
-      <c r="C466" s="34"/>
+      <c r="C466" s="46"/>
     </row>
     <row r="467">
       <c r="B467" s="2"/>
-      <c r="C467" s="34"/>
+      <c r="C467" s="46"/>
     </row>
     <row r="468">
       <c r="B468" s="2"/>
-      <c r="C468" s="34"/>
+      <c r="C468" s="46"/>
     </row>
     <row r="469">
       <c r="B469" s="2"/>
-      <c r="C469" s="34"/>
+      <c r="C469" s="46"/>
     </row>
     <row r="470">
       <c r="B470" s="2"/>
-      <c r="C470" s="34"/>
+      <c r="C470" s="46"/>
     </row>
     <row r="471">
       <c r="B471" s="2"/>
-      <c r="C471" s="34"/>
+      <c r="C471" s="46"/>
     </row>
     <row r="472">
       <c r="B472" s="2"/>
-      <c r="C472" s="34"/>
+      <c r="C472" s="46"/>
     </row>
     <row r="473">
       <c r="B473" s="2"/>
-      <c r="C473" s="34"/>
+      <c r="C473" s="46"/>
     </row>
     <row r="474">
       <c r="B474" s="2"/>
-      <c r="C474" s="34"/>
+      <c r="C474" s="46"/>
     </row>
     <row r="475">
       <c r="B475" s="2"/>
-      <c r="C475" s="34"/>
+      <c r="C475" s="46"/>
     </row>
     <row r="476">
       <c r="B476" s="2"/>
-      <c r="C476" s="34"/>
+      <c r="C476" s="46"/>
     </row>
     <row r="477">
       <c r="B477" s="2"/>
-      <c r="C477" s="34"/>
+      <c r="C477" s="46"/>
     </row>
     <row r="478">
       <c r="B478" s="2"/>
-      <c r="C478" s="34"/>
+      <c r="C478" s="46"/>
     </row>
     <row r="479">
       <c r="B479" s="2"/>
-      <c r="C479" s="34"/>
+      <c r="C479" s="46"/>
     </row>
     <row r="480">
       <c r="B480" s="2"/>
-      <c r="C480" s="34"/>
+      <c r="C480" s="46"/>
     </row>
     <row r="481">
       <c r="B481" s="2"/>
-      <c r="C481" s="34"/>
+      <c r="C481" s="46"/>
     </row>
     <row r="482">
       <c r="B482" s="2"/>
-      <c r="C482" s="34"/>
+      <c r="C482" s="46"/>
     </row>
     <row r="483">
       <c r="B483" s="2"/>
-      <c r="C483" s="34"/>
+      <c r="C483" s="46"/>
     </row>
     <row r="484">
       <c r="B484" s="2"/>
-      <c r="C484" s="34"/>
+      <c r="C484" s="46"/>
     </row>
     <row r="485">
       <c r="B485" s="2"/>
-      <c r="C485" s="34"/>
+      <c r="C485" s="46"/>
     </row>
     <row r="486">
       <c r="B486" s="2"/>
-      <c r="C486" s="34"/>
+      <c r="C486" s="46"/>
     </row>
     <row r="487">
       <c r="B487" s="2"/>
-      <c r="C487" s="34"/>
+      <c r="C487" s="46"/>
     </row>
     <row r="488">
       <c r="B488" s="2"/>
-      <c r="C488" s="34"/>
+      <c r="C488" s="46"/>
     </row>
     <row r="489">
       <c r="B489" s="2"/>
-      <c r="C489" s="34"/>
+      <c r="C489" s="46"/>
     </row>
     <row r="490">
       <c r="B490" s="2"/>
-      <c r="C490" s="34"/>
+      <c r="C490" s="46"/>
     </row>
     <row r="491">
       <c r="B491" s="2"/>
-      <c r="C491" s="34"/>
+      <c r="C491" s="46"/>
     </row>
     <row r="492">
       <c r="B492" s="2"/>
-      <c r="C492" s="34"/>
+      <c r="C492" s="46"/>
     </row>
     <row r="493">
       <c r="B493" s="2"/>
-      <c r="C493" s="34"/>
+      <c r="C493" s="46"/>
     </row>
     <row r="494">
       <c r="B494" s="2"/>
-      <c r="C494" s="34"/>
+      <c r="C494" s="46"/>
     </row>
     <row r="495">
       <c r="B495" s="2"/>
-      <c r="C495" s="34"/>
+      <c r="C495" s="46"/>
     </row>
     <row r="496">
       <c r="B496" s="2"/>
-      <c r="C496" s="34"/>
+      <c r="C496" s="46"/>
     </row>
     <row r="497">
       <c r="B497" s="2"/>
-      <c r="C497" s="34"/>
+      <c r="C497" s="46"/>
     </row>
     <row r="498">
       <c r="B498" s="2"/>
-      <c r="C498" s="34"/>
+      <c r="C498" s="46"/>
     </row>
     <row r="499">
       <c r="B499" s="2"/>
-      <c r="C499" s="34"/>
+      <c r="C499" s="46"/>
     </row>
     <row r="500">
       <c r="B500" s="2"/>
-      <c r="C500" s="34"/>
+      <c r="C500" s="46"/>
     </row>
     <row r="501">
       <c r="B501" s="2"/>
-      <c r="C501" s="34"/>
+      <c r="C501" s="46"/>
     </row>
     <row r="502">
       <c r="B502" s="2"/>
-      <c r="C502" s="34"/>
+      <c r="C502" s="46"/>
     </row>
     <row r="503">
       <c r="B503" s="2"/>
-      <c r="C503" s="34"/>
+      <c r="C503" s="46"/>
     </row>
     <row r="504">
       <c r="B504" s="2"/>
-      <c r="C504" s="34"/>
+      <c r="C504" s="46"/>
     </row>
     <row r="505">
       <c r="B505" s="2"/>
-      <c r="C505" s="34"/>
+      <c r="C505" s="46"/>
     </row>
     <row r="506">
       <c r="B506" s="2"/>
-      <c r="C506" s="34"/>
+      <c r="C506" s="46"/>
     </row>
     <row r="507">
       <c r="B507" s="2"/>
-      <c r="C507" s="34"/>
+      <c r="C507" s="46"/>
     </row>
     <row r="508">
       <c r="B508" s="2"/>
-      <c r="C508" s="34"/>
+      <c r="C508" s="46"/>
     </row>
     <row r="509">
       <c r="B509" s="2"/>
-      <c r="C509" s="34"/>
+      <c r="C509" s="46"/>
     </row>
     <row r="510">
       <c r="B510" s="2"/>
-      <c r="C510" s="34"/>
+      <c r="C510" s="46"/>
     </row>
     <row r="511">
       <c r="B511" s="2"/>
-      <c r="C511" s="34"/>
+      <c r="C511" s="46"/>
     </row>
     <row r="512">
       <c r="B512" s="2"/>
-      <c r="C512" s="34"/>
+      <c r="C512" s="46"/>
     </row>
     <row r="513">
       <c r="B513" s="2"/>
-      <c r="C513" s="34"/>
+      <c r="C513" s="46"/>
     </row>
     <row r="514">
       <c r="B514" s="2"/>
-      <c r="C514" s="34"/>
+      <c r="C514" s="46"/>
     </row>
     <row r="515">
       <c r="B515" s="2"/>
-      <c r="C515" s="34"/>
+      <c r="C515" s="46"/>
     </row>
     <row r="516">
       <c r="B516" s="2"/>
-      <c r="C516" s="34"/>
+      <c r="C516" s="46"/>
     </row>
     <row r="517">
       <c r="B517" s="2"/>
-      <c r="C517" s="34"/>
+      <c r="C517" s="46"/>
     </row>
     <row r="518">
       <c r="B518" s="2"/>
-      <c r="C518" s="34"/>
+      <c r="C518" s="46"/>
     </row>
     <row r="519">
       <c r="B519" s="2"/>
-      <c r="C519" s="34"/>
+      <c r="C519" s="46"/>
     </row>
     <row r="520">
       <c r="B520" s="2"/>
-      <c r="C520" s="34"/>
+      <c r="C520" s="46"/>
     </row>
     <row r="521">
       <c r="B521" s="2"/>
-      <c r="C521" s="34"/>
+      <c r="C521" s="46"/>
     </row>
     <row r="522">
       <c r="B522" s="2"/>
-      <c r="C522" s="34"/>
+      <c r="C522" s="46"/>
     </row>
     <row r="523">
       <c r="B523" s="2"/>
-      <c r="C523" s="34"/>
+      <c r="C523" s="46"/>
     </row>
     <row r="524">
       <c r="B524" s="2"/>
-      <c r="C524" s="34"/>
+      <c r="C524" s="46"/>
     </row>
     <row r="525">
       <c r="B525" s="2"/>
-      <c r="C525" s="34"/>
+      <c r="C525" s="46"/>
     </row>
     <row r="526">
       <c r="B526" s="2"/>
-      <c r="C526" s="34"/>
+      <c r="C526" s="46"/>
     </row>
     <row r="527">
       <c r="B527" s="2"/>
-      <c r="C527" s="34"/>
+      <c r="C527" s="46"/>
     </row>
     <row r="528">
       <c r="B528" s="2"/>
-      <c r="C528" s="34"/>
+      <c r="C528" s="46"/>
     </row>
     <row r="529">
       <c r="B529" s="2"/>
-      <c r="C529" s="34"/>
+      <c r="C529" s="46"/>
     </row>
     <row r="530">
       <c r="B530" s="2"/>
-      <c r="C530" s="34"/>
+      <c r="C530" s="46"/>
     </row>
     <row r="531">
       <c r="B531" s="2"/>
-      <c r="C531" s="34"/>
+      <c r="C531" s="46"/>
     </row>
     <row r="532">
       <c r="B532" s="2"/>
-      <c r="C532" s="34"/>
+      <c r="C532" s="46"/>
     </row>
     <row r="533">
       <c r="B533" s="2"/>
-      <c r="C533" s="34"/>
+      <c r="C533" s="46"/>
     </row>
     <row r="534">
       <c r="B534" s="2"/>
-      <c r="C534" s="34"/>
+      <c r="C534" s="46"/>
     </row>
     <row r="535">
       <c r="B535" s="2"/>
-      <c r="C535" s="34"/>
+      <c r="C535" s="46"/>
     </row>
     <row r="536">
       <c r="B536" s="2"/>
-      <c r="C536" s="34"/>
+      <c r="C536" s="46"/>
     </row>
     <row r="537">
       <c r="B537" s="2"/>
-      <c r="C537" s="34"/>
+      <c r="C537" s="46"/>
     </row>
     <row r="538">
       <c r="B538" s="2"/>
-      <c r="C538" s="34"/>
+      <c r="C538" s="46"/>
     </row>
     <row r="539">
       <c r="B539" s="2"/>
-      <c r="C539" s="34"/>
+      <c r="C539" s="46"/>
     </row>
     <row r="540">
       <c r="B540" s="2"/>
-      <c r="C540" s="34"/>
+      <c r="C540" s="46"/>
     </row>
     <row r="541">
       <c r="B541" s="2"/>
-      <c r="C541" s="34"/>
+      <c r="C541" s="46"/>
     </row>
     <row r="542">
       <c r="B542" s="2"/>
-      <c r="C542" s="34"/>
+      <c r="C542" s="46"/>
     </row>
     <row r="543">
       <c r="B543" s="2"/>
-      <c r="C543" s="34"/>
+      <c r="C543" s="46"/>
     </row>
     <row r="544">
       <c r="B544" s="2"/>
-      <c r="C544" s="34"/>
+      <c r="C544" s="46"/>
     </row>
     <row r="545">
       <c r="B545" s="2"/>
-      <c r="C545" s="34"/>
+      <c r="C545" s="46"/>
     </row>
     <row r="546">
       <c r="B546" s="2"/>
-      <c r="C546" s="34"/>
+      <c r="C546" s="46"/>
     </row>
     <row r="547">
       <c r="B547" s="2"/>
-      <c r="C547" s="34"/>
+      <c r="C547" s="46"/>
     </row>
     <row r="548">
       <c r="B548" s="2"/>
-      <c r="C548" s="34"/>
+      <c r="C548" s="46"/>
     </row>
     <row r="549">
       <c r="B549" s="2"/>
-      <c r="C549" s="34"/>
+      <c r="C549" s="46"/>
     </row>
     <row r="550">
       <c r="B550" s="2"/>
-      <c r="C550" s="34"/>
+      <c r="C550" s="46"/>
     </row>
     <row r="551">
       <c r="B551" s="2"/>
-      <c r="C551" s="34"/>
+      <c r="C551" s="46"/>
     </row>
     <row r="552">
       <c r="B552" s="2"/>
-      <c r="C552" s="34"/>
+      <c r="C552" s="46"/>
     </row>
     <row r="553">
       <c r="B553" s="2"/>
-      <c r="C553" s="34"/>
+      <c r="C553" s="46"/>
     </row>
     <row r="554">
       <c r="B554" s="2"/>
-      <c r="C554" s="34"/>
+      <c r="C554" s="46"/>
     </row>
     <row r="555">
       <c r="B555" s="2"/>
-      <c r="C555" s="34"/>
+      <c r="C555" s="46"/>
     </row>
     <row r="556">
       <c r="B556" s="2"/>
-      <c r="C556" s="34"/>
+      <c r="C556" s="46"/>
     </row>
     <row r="557">
       <c r="B557" s="2"/>
-      <c r="C557" s="34"/>
+      <c r="C557" s="46"/>
     </row>
     <row r="558">
       <c r="B558" s="2"/>
-      <c r="C558" s="34"/>
+      <c r="C558" s="46"/>
     </row>
     <row r="559">
       <c r="B559" s="2"/>
-      <c r="C559" s="34"/>
+      <c r="C559" s="46"/>
     </row>
     <row r="560">
       <c r="B560" s="2"/>
-      <c r="C560" s="34"/>
+      <c r="C560" s="46"/>
     </row>
     <row r="561">
       <c r="B561" s="2"/>
-      <c r="C561" s="34"/>
+      <c r="C561" s="46"/>
     </row>
     <row r="562">
       <c r="B562" s="2"/>
-      <c r="C562" s="34"/>
+      <c r="C562" s="46"/>
     </row>
     <row r="563">
       <c r="B563" s="2"/>
-      <c r="C563" s="34"/>
+      <c r="C563" s="46"/>
     </row>
     <row r="564">
       <c r="B564" s="2"/>
-      <c r="C564" s="34"/>
+      <c r="C564" s="46"/>
     </row>
     <row r="565">
       <c r="B565" s="2"/>
-      <c r="C565" s="34"/>
+      <c r="C565" s="46"/>
     </row>
     <row r="566">
       <c r="B566" s="2"/>
-      <c r="C566" s="34"/>
+      <c r="C566" s="46"/>
     </row>
     <row r="567">
       <c r="B567" s="2"/>
-      <c r="C567" s="34"/>
+      <c r="C567" s="46"/>
     </row>
     <row r="568">
       <c r="B568" s="2"/>
-      <c r="C568" s="34"/>
+      <c r="C568" s="46"/>
     </row>
     <row r="569">
       <c r="B569" s="2"/>
-      <c r="C569" s="34"/>
+      <c r="C569" s="46"/>
     </row>
     <row r="570">
       <c r="B570" s="2"/>
-      <c r="C570" s="34"/>
+      <c r="C570" s="46"/>
     </row>
     <row r="571">
       <c r="B571" s="2"/>
-      <c r="C571" s="34"/>
+      <c r="C571" s="46"/>
     </row>
     <row r="572">
       <c r="B572" s="2"/>
-      <c r="C572" s="34"/>
+      <c r="C572" s="46"/>
     </row>
     <row r="573">
       <c r="B573" s="2"/>
-      <c r="C573" s="34"/>
+      <c r="C573" s="46"/>
     </row>
     <row r="574">
       <c r="B574" s="2"/>
-      <c r="C574" s="34"/>
+      <c r="C574" s="46"/>
     </row>
     <row r="575">
       <c r="B575" s="2"/>
-      <c r="C575" s="34"/>
+      <c r="C575" s="46"/>
     </row>
     <row r="576">
       <c r="B576" s="2"/>
-      <c r="C576" s="34"/>
+      <c r="C576" s="46"/>
     </row>
     <row r="577">
       <c r="B577" s="2"/>
-      <c r="C577" s="34"/>
+      <c r="C577" s="46"/>
     </row>
     <row r="578">
       <c r="B578" s="2"/>
-      <c r="C578" s="34"/>
+      <c r="C578" s="46"/>
     </row>
     <row r="579">
       <c r="B579" s="2"/>
-      <c r="C579" s="34"/>
+      <c r="C579" s="46"/>
     </row>
     <row r="580">
       <c r="B580" s="2"/>
-      <c r="C580" s="34"/>
+      <c r="C580" s="46"/>
     </row>
     <row r="581">
       <c r="B581" s="2"/>
-      <c r="C581" s="34"/>
+      <c r="C581" s="46"/>
     </row>
     <row r="582">
       <c r="B582" s="2"/>
-      <c r="C582" s="34"/>
+      <c r="C582" s="46"/>
     </row>
     <row r="583">
       <c r="B583" s="2"/>
-      <c r="C583" s="34"/>
+      <c r="C583" s="46"/>
     </row>
     <row r="584">
       <c r="B584" s="2"/>
-      <c r="C584" s="34"/>
+      <c r="C584" s="46"/>
     </row>
     <row r="585">
       <c r="B585" s="2"/>
-      <c r="C585" s="34"/>
+      <c r="C585" s="46"/>
     </row>
     <row r="586">
       <c r="B586" s="2"/>
-      <c r="C586" s="34"/>
+      <c r="C586" s="46"/>
     </row>
     <row r="587">
       <c r="B587" s="2"/>
-      <c r="C587" s="34"/>
+      <c r="C587" s="46"/>
     </row>
     <row r="588">
       <c r="B588" s="2"/>
-      <c r="C588" s="34"/>
+      <c r="C588" s="46"/>
     </row>
     <row r="589">
       <c r="B589" s="2"/>
-      <c r="C589" s="34"/>
+      <c r="C589" s="46"/>
     </row>
     <row r="590">
       <c r="B590" s="2"/>
-      <c r="C590" s="34"/>
+      <c r="C590" s="46"/>
     </row>
     <row r="591">
       <c r="B591" s="2"/>
-      <c r="C591" s="34"/>
+      <c r="C591" s="46"/>
     </row>
     <row r="592">
       <c r="B592" s="2"/>
-      <c r="C592" s="34"/>
+      <c r="C592" s="46"/>
     </row>
     <row r="593">
       <c r="B593" s="2"/>
-      <c r="C593" s="34"/>
+      <c r="C593" s="46"/>
     </row>
     <row r="594">
       <c r="B594" s="2"/>
-      <c r="C594" s="34"/>
+      <c r="C594" s="46"/>
     </row>
     <row r="595">
       <c r="B595" s="2"/>
-      <c r="C595" s="34"/>
+      <c r="C595" s="46"/>
     </row>
     <row r="596">
       <c r="B596" s="2"/>
-      <c r="C596" s="34"/>
+      <c r="C596" s="46"/>
     </row>
     <row r="597">
       <c r="B597" s="2"/>
-      <c r="C597" s="34"/>
+      <c r="C597" s="46"/>
     </row>
     <row r="598">
       <c r="B598" s="2"/>
-      <c r="C598" s="34"/>
+      <c r="C598" s="46"/>
     </row>
     <row r="599">
       <c r="B599" s="2"/>
-      <c r="C599" s="34"/>
+      <c r="C599" s="46"/>
     </row>
     <row r="600">
       <c r="B600" s="2"/>
-      <c r="C600" s="34"/>
+      <c r="C600" s="46"/>
     </row>
     <row r="601">
       <c r="B601" s="2"/>
-      <c r="C601" s="34"/>
+      <c r="C601" s="46"/>
     </row>
     <row r="602">
       <c r="B602" s="2"/>
-      <c r="C602" s="34"/>
+      <c r="C602" s="46"/>
     </row>
     <row r="603">
       <c r="B603" s="2"/>
-      <c r="C603" s="34"/>
+      <c r="C603" s="46"/>
     </row>
     <row r="604">
       <c r="B604" s="2"/>
-      <c r="C604" s="34"/>
+      <c r="C604" s="46"/>
     </row>
     <row r="605">
       <c r="B605" s="2"/>
-      <c r="C605" s="34"/>
+      <c r="C605" s="46"/>
     </row>
     <row r="606">
       <c r="B606" s="2"/>
-      <c r="C606" s="34"/>
+      <c r="C606" s="46"/>
     </row>
     <row r="607">
       <c r="B607" s="2"/>
-      <c r="C607" s="34"/>
+      <c r="C607" s="46"/>
     </row>
     <row r="608">
       <c r="B608" s="2"/>
-      <c r="C608" s="34"/>
+      <c r="C608" s="46"/>
     </row>
     <row r="609">
       <c r="B609" s="2"/>
-      <c r="C609" s="34"/>
+      <c r="C609" s="46"/>
     </row>
     <row r="610">
       <c r="B610" s="2"/>
-      <c r="C610" s="34"/>
+      <c r="C610" s="46"/>
     </row>
     <row r="611">
       <c r="B611" s="2"/>
-      <c r="C611" s="34"/>
+      <c r="C611" s="46"/>
     </row>
     <row r="612">
       <c r="B612" s="2"/>
-      <c r="C612" s="34"/>
+      <c r="C612" s="46"/>
     </row>
     <row r="613">
       <c r="B613" s="2"/>
-      <c r="C613" s="34"/>
+      <c r="C613" s="46"/>
     </row>
     <row r="614">
       <c r="B614" s="2"/>
-      <c r="C614" s="34"/>
+      <c r="C614" s="46"/>
     </row>
     <row r="615">
       <c r="B615" s="2"/>
-      <c r="C615" s="34"/>
+      <c r="C615" s="46"/>
     </row>
     <row r="616">
       <c r="B616" s="2"/>
-      <c r="C616" s="34"/>
+      <c r="C616" s="46"/>
     </row>
     <row r="617">
       <c r="B617" s="2"/>
-      <c r="C617" s="34"/>
+      <c r="C617" s="46"/>
     </row>
     <row r="618">
       <c r="B618" s="2"/>
-      <c r="C618" s="34"/>
+      <c r="C618" s="46"/>
     </row>
     <row r="619">
       <c r="B619" s="2"/>
-      <c r="C619" s="34"/>
+      <c r="C619" s="46"/>
     </row>
     <row r="620">
       <c r="B620" s="2"/>
-      <c r="C620" s="34"/>
+      <c r="C620" s="46"/>
     </row>
     <row r="621">
       <c r="B621" s="2"/>
-      <c r="C621" s="34"/>
+      <c r="C621" s="46"/>
     </row>
     <row r="622">
       <c r="B622" s="2"/>
-      <c r="C622" s="34"/>
+      <c r="C622" s="46"/>
     </row>
     <row r="623">
       <c r="B623" s="2"/>
-      <c r="C623" s="34"/>
+      <c r="C623" s="46"/>
     </row>
     <row r="624">
       <c r="B624" s="2"/>
-      <c r="C624" s="34"/>
+      <c r="C624" s="46"/>
     </row>
     <row r="625">
       <c r="B625" s="2"/>
-      <c r="C625" s="34"/>
+      <c r="C625" s="46"/>
     </row>
     <row r="626">
       <c r="B626" s="2"/>
-      <c r="C626" s="34"/>
+      <c r="C626" s="46"/>
     </row>
     <row r="627">
       <c r="B627" s="2"/>
-      <c r="C627" s="34"/>
+      <c r="C627" s="46"/>
     </row>
     <row r="628">
       <c r="B628" s="2"/>
-      <c r="C628" s="34"/>
+      <c r="C628" s="46"/>
     </row>
     <row r="629">
       <c r="B629" s="2"/>
-      <c r="C629" s="34"/>
+      <c r="C629" s="46"/>
     </row>
     <row r="630">
       <c r="B630" s="2"/>
-      <c r="C630" s="34"/>
+      <c r="C630" s="46"/>
     </row>
     <row r="631">
       <c r="B631" s="2"/>
-      <c r="C631" s="34"/>
+      <c r="C631" s="46"/>
     </row>
     <row r="632">
       <c r="B632" s="2"/>
-      <c r="C632" s="34"/>
+      <c r="C632" s="46"/>
     </row>
     <row r="633">
       <c r="B633" s="2"/>
-      <c r="C633" s="34"/>
+      <c r="C633" s="46"/>
     </row>
     <row r="634">
       <c r="B634" s="2"/>
-      <c r="C634" s="34"/>
+      <c r="C634" s="46"/>
     </row>
     <row r="635">
       <c r="B635" s="2"/>
-      <c r="C635" s="34"/>
+      <c r="C635" s="46"/>
     </row>
     <row r="636">
       <c r="B636" s="2"/>
-      <c r="C636" s="34"/>
+      <c r="C636" s="46"/>
     </row>
     <row r="637">
       <c r="B637" s="2"/>
-      <c r="C637" s="34"/>
+      <c r="C637" s="46"/>
     </row>
     <row r="638">
       <c r="B638" s="2"/>
-      <c r="C638" s="34"/>
+      <c r="C638" s="46"/>
     </row>
     <row r="639">
       <c r="B639" s="2"/>
-      <c r="C639" s="34"/>
+      <c r="C639" s="46"/>
     </row>
     <row r="640">
       <c r="B640" s="2"/>
-      <c r="C640" s="34"/>
+      <c r="C640" s="46"/>
     </row>
     <row r="641">
       <c r="B641" s="2"/>
-      <c r="C641" s="34"/>
+      <c r="C641" s="46"/>
     </row>
     <row r="642">
       <c r="B642" s="2"/>
-      <c r="C642" s="34"/>
+      <c r="C642" s="46"/>
     </row>
     <row r="643">
       <c r="B643" s="2"/>
-      <c r="C643" s="34"/>
+      <c r="C643" s="46"/>
     </row>
     <row r="644">
       <c r="B644" s="2"/>
-      <c r="C644" s="34"/>
+      <c r="C644" s="46"/>
     </row>
     <row r="645">
       <c r="B645" s="2"/>
-      <c r="C645" s="34"/>
+      <c r="C645" s="46"/>
     </row>
     <row r="646">
       <c r="B646" s="2"/>
-      <c r="C646" s="34"/>
+      <c r="C646" s="46"/>
     </row>
     <row r="647">
       <c r="B647" s="2"/>
-      <c r="C647" s="34"/>
+      <c r="C647" s="46"/>
     </row>
     <row r="648">
       <c r="B648" s="2"/>
-      <c r="C648" s="34"/>
+      <c r="C648" s="46"/>
     </row>
     <row r="649">
       <c r="B649" s="2"/>
-      <c r="C649" s="34"/>
+      <c r="C649" s="46"/>
     </row>
     <row r="650">
       <c r="B650" s="2"/>
-      <c r="C650" s="34"/>
+      <c r="C650" s="46"/>
     </row>
     <row r="651">
       <c r="B651" s="2"/>
-      <c r="C651" s="34"/>
+      <c r="C651" s="46"/>
     </row>
     <row r="652">
       <c r="B652" s="2"/>
-      <c r="C652" s="34"/>
+      <c r="C652" s="46"/>
     </row>
     <row r="653">
       <c r="B653" s="2"/>
-      <c r="C653" s="34"/>
+      <c r="C653" s="46"/>
     </row>
     <row r="654">
       <c r="B654" s="2"/>
-      <c r="C654" s="34"/>
+      <c r="C654" s="46"/>
     </row>
     <row r="655">
       <c r="B655" s="2"/>
-      <c r="C655" s="34"/>
+      <c r="C655" s="46"/>
     </row>
     <row r="656">
       <c r="B656" s="2"/>
-      <c r="C656" s="34"/>
+      <c r="C656" s="46"/>
     </row>
     <row r="657">
       <c r="B657" s="2"/>
-      <c r="C657" s="34"/>
+      <c r="C657" s="46"/>
     </row>
     <row r="658">
       <c r="B658" s="2"/>
-      <c r="C658" s="34"/>
+      <c r="C658" s="46"/>
     </row>
     <row r="659">
       <c r="B659" s="2"/>
-      <c r="C659" s="34"/>
+      <c r="C659" s="46"/>
     </row>
     <row r="660">
       <c r="B660" s="2"/>
-      <c r="C660" s="34"/>
+      <c r="C660" s="46"/>
     </row>
     <row r="661">
       <c r="B661" s="2"/>
-      <c r="C661" s="34"/>
+      <c r="C661" s="46"/>
     </row>
     <row r="662">
       <c r="B662" s="2"/>
-      <c r="C662" s="34"/>
+      <c r="C662" s="46"/>
     </row>
     <row r="663">
       <c r="B663" s="2"/>
-      <c r="C663" s="34"/>
+      <c r="C663" s="46"/>
     </row>
     <row r="664">
       <c r="B664" s="2"/>
-      <c r="C664" s="34"/>
+      <c r="C664" s="46"/>
     </row>
     <row r="665">
       <c r="B665" s="2"/>
-      <c r="C665" s="34"/>
+      <c r="C665" s="46"/>
     </row>
     <row r="666">
       <c r="B666" s="2"/>
-      <c r="C666" s="34"/>
+      <c r="C666" s="46"/>
     </row>
     <row r="667">
       <c r="B667" s="2"/>
-      <c r="C667" s="34"/>
+      <c r="C667" s="46"/>
     </row>
     <row r="668">
       <c r="B668" s="2"/>
-      <c r="C668" s="34"/>
+      <c r="C668" s="46"/>
     </row>
     <row r="669">
       <c r="B669" s="2"/>
-      <c r="C669" s="34"/>
+      <c r="C669" s="46"/>
     </row>
     <row r="670">
       <c r="B670" s="2"/>
-      <c r="C670" s="34"/>
+      <c r="C670" s="46"/>
     </row>
     <row r="671">
       <c r="B671" s="2"/>
-      <c r="C671" s="34"/>
+      <c r="C671" s="46"/>
     </row>
     <row r="672">
       <c r="B672" s="2"/>
-      <c r="C672" s="34"/>
+      <c r="C672" s="46"/>
     </row>
     <row r="673">
       <c r="B673" s="2"/>
-      <c r="C673" s="34"/>
+      <c r="C673" s="46"/>
     </row>
     <row r="674">
       <c r="B674" s="2"/>
-      <c r="C674" s="34"/>
+      <c r="C674" s="46"/>
     </row>
     <row r="675">
       <c r="B675" s="2"/>
-      <c r="C675" s="34"/>
+      <c r="C675" s="46"/>
     </row>
     <row r="676">
       <c r="B676" s="2"/>
-      <c r="C676" s="34"/>
+      <c r="C676" s="46"/>
     </row>
     <row r="677">
       <c r="B677" s="2"/>
-      <c r="C677" s="34"/>
+      <c r="C677" s="46"/>
     </row>
     <row r="678">
       <c r="B678" s="2"/>
-      <c r="C678" s="34"/>
+      <c r="C678" s="46"/>
     </row>
     <row r="679">
       <c r="B679" s="2"/>
-      <c r="C679" s="34"/>
+      <c r="C679" s="46"/>
     </row>
     <row r="680">
       <c r="B680" s="2"/>
-      <c r="C680" s="34"/>
+      <c r="C680" s="46"/>
     </row>
     <row r="681">
       <c r="B681" s="2"/>
-      <c r="C681" s="34"/>
+      <c r="C681" s="46"/>
     </row>
     <row r="682">
       <c r="B682" s="2"/>
-      <c r="C682" s="34"/>
+      <c r="C682" s="46"/>
     </row>
     <row r="683">
       <c r="B683" s="2"/>
-      <c r="C683" s="34"/>
+      <c r="C683" s="46"/>
     </row>
     <row r="684">
       <c r="B684" s="2"/>
-      <c r="C684" s="34"/>
+      <c r="C684" s="46"/>
     </row>
     <row r="685">
       <c r="B685" s="2"/>
-      <c r="C685" s="34"/>
+      <c r="C685" s="46"/>
     </row>
     <row r="686">
       <c r="B686" s="2"/>
-      <c r="C686" s="34"/>
+      <c r="C686" s="46"/>
     </row>
     <row r="687">
       <c r="B687" s="2"/>
-      <c r="C687" s="34"/>
+      <c r="C687" s="46"/>
     </row>
     <row r="688">
       <c r="B688" s="2"/>
-      <c r="C688" s="34"/>
+      <c r="C688" s="46"/>
     </row>
     <row r="689">
       <c r="B689" s="2"/>
-      <c r="C689" s="34"/>
+      <c r="C689" s="46"/>
     </row>
     <row r="690">
       <c r="B690" s="2"/>
-      <c r="C690" s="34"/>
+      <c r="C690" s="46"/>
     </row>
     <row r="691">
       <c r="B691" s="2"/>
-      <c r="C691" s="34"/>
+      <c r="C691" s="46"/>
     </row>
     <row r="692">
       <c r="B692" s="2"/>
-      <c r="C692" s="34"/>
+      <c r="C692" s="46"/>
     </row>
     <row r="693">
       <c r="B693" s="2"/>
-      <c r="C693" s="34"/>
+      <c r="C693" s="46"/>
     </row>
     <row r="694">
       <c r="B694" s="2"/>
-      <c r="C694" s="34"/>
+      <c r="C694" s="46"/>
     </row>
     <row r="695">
       <c r="B695" s="2"/>
-      <c r="C695" s="34"/>
+      <c r="C695" s="46"/>
     </row>
     <row r="696">
       <c r="B696" s="2"/>
-      <c r="C696" s="34"/>
+      <c r="C696" s="46"/>
     </row>
     <row r="697">
       <c r="B697" s="2"/>
-      <c r="C697" s="34"/>
+      <c r="C697" s="46"/>
     </row>
     <row r="698">
       <c r="B698" s="2"/>
-      <c r="C698" s="34"/>
+      <c r="C698" s="46"/>
     </row>
     <row r="699">
       <c r="B699" s="2"/>
-      <c r="C699" s="34"/>
+      <c r="C699" s="46"/>
     </row>
     <row r="700">
       <c r="B700" s="2"/>
-      <c r="C700" s="34"/>
+      <c r="C700" s="46"/>
     </row>
     <row r="701">
       <c r="B701" s="2"/>
-      <c r="C701" s="34"/>
+      <c r="C701" s="46"/>
     </row>
     <row r="702">
       <c r="B702" s="2"/>
-      <c r="C702" s="34"/>
+      <c r="C702" s="46"/>
     </row>
     <row r="703">
       <c r="B703" s="2"/>
-      <c r="C703" s="34"/>
+      <c r="C703" s="46"/>
     </row>
     <row r="704">
       <c r="B704" s="2"/>
-      <c r="C704" s="34"/>
+      <c r="C704" s="46"/>
     </row>
     <row r="705">
       <c r="B705" s="2"/>
-      <c r="C705" s="34"/>
+      <c r="C705" s="46"/>
     </row>
     <row r="706">
       <c r="B706" s="2"/>
-      <c r="C706" s="34"/>
+      <c r="C706" s="46"/>
     </row>
     <row r="707">
       <c r="B707" s="2"/>
-      <c r="C707" s="34"/>
+      <c r="C707" s="46"/>
     </row>
     <row r="708">
       <c r="B708" s="2"/>
-      <c r="C708" s="34"/>
+      <c r="C708" s="46"/>
     </row>
     <row r="709">
       <c r="B709" s="2"/>
-      <c r="C709" s="34"/>
+      <c r="C709" s="46"/>
     </row>
     <row r="710">
       <c r="B710" s="2"/>
-      <c r="C710" s="34"/>
+      <c r="C710" s="46"/>
     </row>
     <row r="711">
       <c r="B711" s="2"/>
-      <c r="C711" s="34"/>
+      <c r="C711" s="46"/>
     </row>
     <row r="712">
       <c r="B712" s="2"/>
-      <c r="C712" s="34"/>
+      <c r="C712" s="46"/>
     </row>
     <row r="713">
       <c r="B713" s="2"/>
-      <c r="C713" s="34"/>
+      <c r="C713" s="46"/>
     </row>
     <row r="714">
       <c r="B714" s="2"/>
-      <c r="C714" s="34"/>
+      <c r="C714" s="46"/>
     </row>
     <row r="715">
       <c r="B715" s="2"/>
-      <c r="C715" s="34"/>
+      <c r="C715" s="46"/>
     </row>
     <row r="716">
       <c r="B716" s="2"/>
-      <c r="C716" s="34"/>
+      <c r="C716" s="46"/>
     </row>
     <row r="717">
       <c r="B717" s="2"/>
-      <c r="C717" s="34"/>
+      <c r="C717" s="46"/>
     </row>
     <row r="718">
       <c r="B718" s="2"/>
-      <c r="C718" s="34"/>
+      <c r="C718" s="46"/>
     </row>
     <row r="719">
       <c r="B719" s="2"/>
-      <c r="C719" s="34"/>
+      <c r="C719" s="46"/>
     </row>
     <row r="720">
       <c r="B720" s="2"/>
-      <c r="C720" s="34"/>
+      <c r="C720" s="46"/>
     </row>
     <row r="721">
       <c r="B721" s="2"/>
-      <c r="C721" s="34"/>
+      <c r="C721" s="46"/>
     </row>
     <row r="722">
       <c r="B722" s="2"/>
-      <c r="C722" s="34"/>
+      <c r="C722" s="46"/>
     </row>
     <row r="723">
       <c r="B723" s="2"/>
-      <c r="C723" s="34"/>
+      <c r="C723" s="46"/>
     </row>
     <row r="724">
       <c r="B724" s="2"/>
-      <c r="C724" s="34"/>
+      <c r="C724" s="46"/>
     </row>
     <row r="725">
       <c r="B725" s="2"/>
-      <c r="C725" s="34"/>
+      <c r="C725" s="46"/>
     </row>
     <row r="726">
       <c r="B726" s="2"/>
-      <c r="C726" s="34"/>
+      <c r="C726" s="46"/>
     </row>
     <row r="727">
       <c r="B727" s="2"/>
-      <c r="C727" s="34"/>
+      <c r="C727" s="46"/>
     </row>
     <row r="728">
       <c r="B728" s="2"/>
-      <c r="C728" s="34"/>
+      <c r="C728" s="46"/>
     </row>
     <row r="729">
       <c r="B729" s="2"/>
-      <c r="C729" s="34"/>
+      <c r="C729" s="46"/>
     </row>
     <row r="730">
       <c r="B730" s="2"/>
-      <c r="C730" s="34"/>
+      <c r="C730" s="46"/>
     </row>
     <row r="731">
       <c r="B731" s="2"/>
-      <c r="C731" s="34"/>
+      <c r="C731" s="46"/>
     </row>
     <row r="732">
       <c r="B732" s="2"/>
-      <c r="C732" s="34"/>
+      <c r="C732" s="46"/>
     </row>
     <row r="733">
       <c r="B733" s="2"/>
-      <c r="C733" s="34"/>
+      <c r="C733" s="46"/>
     </row>
     <row r="734">
       <c r="B734" s="2"/>
-      <c r="C734" s="34"/>
+      <c r="C734" s="46"/>
     </row>
     <row r="735">
       <c r="B735" s="2"/>
-      <c r="C735" s="34"/>
+      <c r="C735" s="46"/>
     </row>
     <row r="736">
       <c r="B736" s="2"/>
-      <c r="C736" s="34"/>
+      <c r="C736" s="46"/>
     </row>
     <row r="737">
       <c r="B737" s="2"/>
-      <c r="C737" s="34"/>
+      <c r="C737" s="46"/>
     </row>
     <row r="738">
       <c r="B738" s="2"/>
-      <c r="C738" s="34"/>
+      <c r="C738" s="46"/>
     </row>
     <row r="739">
       <c r="B739" s="2"/>
-      <c r="C739" s="34"/>
+      <c r="C739" s="46"/>
     </row>
     <row r="740">
       <c r="B740" s="2"/>
-      <c r="C740" s="34"/>
+      <c r="C740" s="46"/>
     </row>
     <row r="741">
       <c r="B741" s="2"/>
-      <c r="C741" s="34"/>
+      <c r="C741" s="46"/>
     </row>
     <row r="742">
       <c r="B742" s="2"/>
-      <c r="C742" s="34"/>
+      <c r="C742" s="46"/>
     </row>
     <row r="743">
       <c r="B743" s="2"/>
-      <c r="C743" s="34"/>
+      <c r="C743" s="46"/>
     </row>
     <row r="744">
       <c r="B744" s="2"/>
-      <c r="C744" s="34"/>
+      <c r="C744" s="46"/>
     </row>
     <row r="745">
       <c r="B745" s="2"/>
-      <c r="C745" s="34"/>
+      <c r="C745" s="46"/>
     </row>
     <row r="746">
       <c r="B746" s="2"/>
-      <c r="C746" s="34"/>
+      <c r="C746" s="46"/>
     </row>
     <row r="747">
       <c r="B747" s="2"/>
-      <c r="C747" s="34"/>
+      <c r="C747" s="46"/>
     </row>
     <row r="748">
       <c r="B748" s="2"/>
-      <c r="C748" s="34"/>
+      <c r="C748" s="46"/>
     </row>
     <row r="749">
       <c r="B749" s="2"/>
-      <c r="C749" s="34"/>
+      <c r="C749" s="46"/>
     </row>
     <row r="750">
       <c r="B750" s="2"/>
-      <c r="C750" s="34"/>
+      <c r="C750" s="46"/>
     </row>
     <row r="751">
       <c r="B751" s="2"/>
-      <c r="C751" s="34"/>
+      <c r="C751" s="46"/>
     </row>
     <row r="752">
       <c r="B752" s="2"/>
-      <c r="C752" s="34"/>
+      <c r="C752" s="46"/>
     </row>
     <row r="753">
       <c r="B753" s="2"/>
-      <c r="C753" s="34"/>
+      <c r="C753" s="46"/>
     </row>
     <row r="754">
       <c r="B754" s="2"/>
-      <c r="C754" s="34"/>
+      <c r="C754" s="46"/>
     </row>
     <row r="755">
       <c r="B755" s="2"/>
-      <c r="C755" s="34"/>
+      <c r="C755" s="46"/>
     </row>
     <row r="756">
       <c r="B756" s="2"/>
-      <c r="C756" s="34"/>
+      <c r="C756" s="46"/>
     </row>
     <row r="757">
       <c r="B757" s="2"/>
-      <c r="C757" s="34"/>
+      <c r="C757" s="46"/>
     </row>
     <row r="758">
       <c r="B758" s="2"/>
-      <c r="C758" s="34"/>
+      <c r="C758" s="46"/>
     </row>
     <row r="759">
       <c r="B759" s="2"/>
-      <c r="C759" s="34"/>
+      <c r="C759" s="46"/>
     </row>
     <row r="760">
       <c r="B760" s="2"/>
-      <c r="C760" s="34"/>
+      <c r="C760" s="46"/>
     </row>
     <row r="761">
       <c r="B761" s="2"/>
-      <c r="C761" s="34"/>
+      <c r="C761" s="46"/>
     </row>
     <row r="762">
       <c r="B762" s="2"/>
-      <c r="C762" s="34"/>
+      <c r="C762" s="46"/>
     </row>
     <row r="763">
       <c r="B763" s="2"/>
-      <c r="C763" s="34"/>
+      <c r="C763" s="46"/>
     </row>
     <row r="764">
       <c r="B764" s="2"/>
-      <c r="C764" s="34"/>
+      <c r="C764" s="46"/>
     </row>
     <row r="765">
       <c r="B765" s="2"/>
-      <c r="C765" s="34"/>
+      <c r="C765" s="46"/>
     </row>
     <row r="766">
       <c r="B766" s="2"/>
-      <c r="C766" s="34"/>
+      <c r="C766" s="46"/>
     </row>
     <row r="767">
       <c r="B767" s="2"/>
-      <c r="C767" s="34"/>
+      <c r="C767" s="46"/>
     </row>
     <row r="768">
       <c r="B768" s="2"/>
-      <c r="C768" s="34"/>
+      <c r="C768" s="46"/>
     </row>
     <row r="769">
       <c r="B769" s="2"/>
-      <c r="C769" s="34"/>
+      <c r="C769" s="46"/>
     </row>
     <row r="770">
       <c r="B770" s="2"/>
-      <c r="C770" s="34"/>
+      <c r="C770" s="46"/>
     </row>
     <row r="771">
       <c r="B771" s="2"/>
-      <c r="C771" s="34"/>
+      <c r="C771" s="46"/>
     </row>
     <row r="772">
       <c r="B772" s="2"/>
-      <c r="C772" s="34"/>
+      <c r="C772" s="46"/>
     </row>
     <row r="773">
       <c r="B773" s="2"/>
-      <c r="C773" s="34"/>
+      <c r="C773" s="46"/>
     </row>
     <row r="774">
       <c r="B774" s="2"/>
-      <c r="C774" s="34"/>
+      <c r="C774" s="46"/>
     </row>
     <row r="775">
       <c r="B775" s="2"/>
-      <c r="C775" s="34"/>
+      <c r="C775" s="46"/>
     </row>
     <row r="776">
       <c r="B776" s="2"/>
-      <c r="C776" s="34"/>
+      <c r="C776" s="46"/>
     </row>
     <row r="777">
       <c r="B777" s="2"/>
-      <c r="C777" s="34"/>
+      <c r="C777" s="46"/>
     </row>
     <row r="778">
       <c r="B778" s="2"/>
-      <c r="C778" s="34"/>
+      <c r="C778" s="46"/>
     </row>
     <row r="779">
       <c r="B779" s="2"/>
-      <c r="C779" s="34"/>
+      <c r="C779" s="46"/>
     </row>
     <row r="780">
       <c r="B780" s="2"/>
-      <c r="C780" s="34"/>
+      <c r="C780" s="46"/>
     </row>
     <row r="781">
       <c r="B781" s="2"/>
-      <c r="C781" s="34"/>
+      <c r="C781" s="46"/>
     </row>
     <row r="782">
       <c r="B782" s="2"/>
-      <c r="C782" s="34"/>
+      <c r="C782" s="46"/>
     </row>
     <row r="783">
       <c r="B783" s="2"/>
-      <c r="C783" s="34"/>
+      <c r="C783" s="46"/>
     </row>
     <row r="784">
       <c r="B784" s="2"/>
-      <c r="C784" s="34"/>
+      <c r="C784" s="46"/>
     </row>
     <row r="785">
       <c r="B785" s="2"/>
-      <c r="C785" s="34"/>
+      <c r="C785" s="46"/>
     </row>
     <row r="786">
       <c r="B786" s="2"/>
-      <c r="C786" s="34"/>
+      <c r="C786" s="46"/>
     </row>
     <row r="787">
       <c r="B787" s="2"/>
-      <c r="C787" s="34"/>
+      <c r="C787" s="46"/>
     </row>
     <row r="788">
       <c r="B788" s="2"/>
-      <c r="C788" s="34"/>
+      <c r="C788" s="46"/>
     </row>
     <row r="789">
       <c r="B789" s="2"/>
-      <c r="C789" s="34"/>
+      <c r="C789" s="46"/>
     </row>
     <row r="790">
       <c r="B790" s="2"/>
-      <c r="C790" s="34"/>
+      <c r="C790" s="46"/>
     </row>
     <row r="791">
       <c r="B791" s="2"/>
-      <c r="C791" s="34"/>
+      <c r="C791" s="46"/>
     </row>
     <row r="792">
       <c r="B792" s="2"/>
-      <c r="C792" s="34"/>
+      <c r="C792" s="46"/>
     </row>
     <row r="793">
       <c r="B793" s="2"/>
-      <c r="C793" s="34"/>
+      <c r="C793" s="46"/>
     </row>
     <row r="794">
       <c r="B794" s="2"/>
-      <c r="C794" s="34"/>
+      <c r="C794" s="46"/>
     </row>
     <row r="795">
       <c r="B795" s="2"/>
-      <c r="C795" s="34"/>
+      <c r="C795" s="46"/>
     </row>
     <row r="796">
       <c r="B796" s="2"/>
-      <c r="C796" s="34"/>
+      <c r="C796" s="46"/>
     </row>
     <row r="797">
       <c r="B797" s="2"/>
-      <c r="C797" s="34"/>
+      <c r="C797" s="46"/>
     </row>
     <row r="798">
       <c r="B798" s="2"/>
-      <c r="C798" s="34"/>
+      <c r="C798" s="46"/>
     </row>
     <row r="799">
       <c r="B799" s="2"/>
-      <c r="C799" s="34"/>
+      <c r="C799" s="46"/>
     </row>
     <row r="800">
       <c r="B800" s="2"/>
-      <c r="C800" s="34"/>
+      <c r="C800" s="46"/>
     </row>
     <row r="801">
       <c r="B801" s="2"/>
-      <c r="C801" s="34"/>
+      <c r="C801" s="46"/>
     </row>
     <row r="802">
       <c r="B802" s="2"/>
-      <c r="C802" s="34"/>
+      <c r="C802" s="46"/>
     </row>
     <row r="803">
       <c r="B803" s="2"/>
-      <c r="C803" s="34"/>
+      <c r="C803" s="46"/>
     </row>
     <row r="804">
       <c r="B804" s="2"/>
-      <c r="C804" s="34"/>
+      <c r="C804" s="46"/>
     </row>
     <row r="805">
       <c r="B805" s="2"/>
-      <c r="C805" s="34"/>
+      <c r="C805" s="46"/>
     </row>
     <row r="806">
       <c r="B806" s="2"/>
-      <c r="C806" s="34"/>
+      <c r="C806" s="46"/>
     </row>
     <row r="807">
       <c r="B807" s="2"/>
-      <c r="C807" s="34"/>
+      <c r="C807" s="46"/>
     </row>
     <row r="808">
       <c r="B808" s="2"/>
-      <c r="C808" s="34"/>
+      <c r="C808" s="46"/>
     </row>
     <row r="809">
       <c r="B809" s="2"/>
-      <c r="C809" s="34"/>
+      <c r="C809" s="46"/>
     </row>
     <row r="810">
       <c r="B810" s="2"/>
-      <c r="C810" s="34"/>
+      <c r="C810" s="46"/>
     </row>
     <row r="811">
       <c r="B811" s="2"/>
-      <c r="C811" s="34"/>
+      <c r="C811" s="46"/>
     </row>
     <row r="812">
       <c r="B812" s="2"/>
-      <c r="C812" s="34"/>
+      <c r="C812" s="46"/>
     </row>
     <row r="813">
       <c r="B813" s="2"/>
-      <c r="C813" s="34"/>
+      <c r="C813" s="46"/>
     </row>
     <row r="814">
       <c r="B814" s="2"/>
-      <c r="C814" s="34"/>
+      <c r="C814" s="46"/>
     </row>
     <row r="815">
       <c r="B815" s="2"/>
-      <c r="C815" s="34"/>
+      <c r="C815" s="46"/>
     </row>
     <row r="816">
       <c r="B816" s="2"/>
-      <c r="C816" s="34"/>
+      <c r="C816" s="46"/>
     </row>
     <row r="817">
       <c r="B817" s="2"/>
-      <c r="C817" s="34"/>
+      <c r="C817" s="46"/>
     </row>
     <row r="818">
       <c r="B818" s="2"/>
-      <c r="C818" s="34"/>
+      <c r="C818" s="46"/>
     </row>
     <row r="819">
       <c r="B819" s="2"/>
-      <c r="C819" s="34"/>
+      <c r="C819" s="46"/>
     </row>
     <row r="820">
       <c r="B820" s="2"/>
-      <c r="C820" s="34"/>
+      <c r="C820" s="46"/>
     </row>
     <row r="821">
       <c r="B821" s="2"/>
-      <c r="C821" s="34"/>
+      <c r="C821" s="46"/>
     </row>
     <row r="822">
       <c r="B822" s="2"/>
-      <c r="C822" s="34"/>
+      <c r="C822" s="46"/>
     </row>
     <row r="823">
       <c r="B823" s="2"/>
-      <c r="C823" s="34"/>
+      <c r="C823" s="46"/>
     </row>
     <row r="824">
       <c r="B824" s="2"/>
-      <c r="C824" s="34"/>
+      <c r="C824" s="46"/>
     </row>
     <row r="825">
       <c r="B825" s="2"/>
-      <c r="C825" s="34"/>
+      <c r="C825" s="46"/>
     </row>
     <row r="826">
       <c r="B826" s="2"/>
-      <c r="C826" s="34"/>
+      <c r="C826" s="46"/>
     </row>
     <row r="827">
       <c r="B827" s="2"/>
-      <c r="C827" s="34"/>
+      <c r="C827" s="46"/>
     </row>
     <row r="828">
       <c r="B828" s="2"/>
-      <c r="C828" s="34"/>
+      <c r="C828" s="46"/>
     </row>
     <row r="829">
       <c r="B829" s="2"/>
-      <c r="C829" s="34"/>
+      <c r="C829" s="46"/>
     </row>
     <row r="830">
       <c r="B830" s="2"/>
-      <c r="C830" s="34"/>
+      <c r="C830" s="46"/>
     </row>
     <row r="831">
       <c r="B831" s="2"/>
-      <c r="C831" s="34"/>
+      <c r="C831" s="46"/>
     </row>
     <row r="832">
       <c r="B832" s="2"/>
-      <c r="C832" s="34"/>
+      <c r="C832" s="46"/>
     </row>
     <row r="833">
       <c r="B833" s="2"/>
-      <c r="C833" s="34"/>
+      <c r="C833" s="46"/>
     </row>
     <row r="834">
       <c r="B834" s="2"/>
-      <c r="C834" s="34"/>
+      <c r="C834" s="46"/>
     </row>
     <row r="835">
       <c r="B835" s="2"/>
-      <c r="C835" s="34"/>
+      <c r="C835" s="46"/>
     </row>
     <row r="836">
       <c r="B836" s="2"/>
-      <c r="C836" s="34"/>
+      <c r="C836" s="46"/>
     </row>
     <row r="837">
       <c r="B837" s="2"/>
-      <c r="C837" s="34"/>
+      <c r="C837" s="46"/>
     </row>
     <row r="838">
       <c r="B838" s="2"/>
-      <c r="C838" s="34"/>
+      <c r="C838" s="46"/>
     </row>
     <row r="839">
       <c r="B839" s="2"/>
-      <c r="C839" s="34"/>
+      <c r="C839" s="46"/>
     </row>
     <row r="840">
       <c r="B840" s="2"/>
-      <c r="C840" s="34"/>
+      <c r="C840" s="46"/>
     </row>
     <row r="841">
       <c r="B841" s="2"/>
-      <c r="C841" s="34"/>
+      <c r="C841" s="46"/>
     </row>
     <row r="842">
       <c r="B842" s="2"/>
-      <c r="C842" s="34"/>
+      <c r="C842" s="46"/>
     </row>
     <row r="843">
       <c r="B843" s="2"/>
-      <c r="C843" s="34"/>
+      <c r="C843" s="46"/>
     </row>
     <row r="844">
       <c r="B844" s="2"/>
-      <c r="C844" s="34"/>
+      <c r="C844" s="46"/>
     </row>
     <row r="845">
       <c r="B845" s="2"/>
-      <c r="C845" s="34"/>
+      <c r="C845" s="46"/>
     </row>
     <row r="846">
       <c r="B846" s="2"/>
-      <c r="C846" s="34"/>
+      <c r="C846" s="46"/>
     </row>
     <row r="847">
       <c r="B847" s="2"/>
-      <c r="C847" s="34"/>
+      <c r="C847" s="46"/>
     </row>
     <row r="848">
       <c r="B848" s="2"/>
-      <c r="C848" s="34"/>
+      <c r="C848" s="46"/>
     </row>
     <row r="849">
       <c r="B849" s="2"/>
-      <c r="C849" s="34"/>
+      <c r="C849" s="46"/>
     </row>
     <row r="850">
       <c r="B850" s="2"/>
-      <c r="C850" s="34"/>
+      <c r="C850" s="46"/>
     </row>
     <row r="851">
       <c r="B851" s="2"/>
-      <c r="C851" s="34"/>
+      <c r="C851" s="46"/>
     </row>
     <row r="852">
       <c r="B852" s="2"/>
-      <c r="C852" s="34"/>
+      <c r="C852" s="46"/>
     </row>
     <row r="853">
       <c r="B853" s="2"/>
-      <c r="C853" s="34"/>
+      <c r="C853" s="46"/>
     </row>
     <row r="854">
       <c r="B854" s="2"/>
-      <c r="C854" s="34"/>
+      <c r="C854" s="46"/>
     </row>
     <row r="855">
       <c r="B855" s="2"/>
-      <c r="C855" s="34"/>
+      <c r="C855" s="46"/>
     </row>
     <row r="856">
       <c r="B856" s="2"/>
-      <c r="C856" s="34"/>
+      <c r="C856" s="46"/>
     </row>
     <row r="857">
       <c r="B857" s="2"/>
-      <c r="C857" s="34"/>
+      <c r="C857" s="46"/>
     </row>
     <row r="858">
       <c r="B858" s="2"/>
-      <c r="C858" s="34"/>
+      <c r="C858" s="46"/>
     </row>
     <row r="859">
       <c r="B859" s="2"/>
-      <c r="C859" s="34"/>
+      <c r="C859" s="46"/>
     </row>
     <row r="860">
       <c r="B860" s="2"/>
-      <c r="C860" s="34"/>
+      <c r="C860" s="46"/>
     </row>
     <row r="861">
       <c r="B861" s="2"/>
-      <c r="C861" s="34"/>
+      <c r="C861" s="46"/>
     </row>
     <row r="862">
       <c r="B862" s="2"/>
-      <c r="C862" s="34"/>
+      <c r="C862" s="46"/>
     </row>
     <row r="863">
       <c r="B863" s="2"/>
-      <c r="C863" s="34"/>
+      <c r="C863" s="46"/>
     </row>
     <row r="864">
       <c r="B864" s="2"/>
-      <c r="C864" s="34"/>
+      <c r="C864" s="46"/>
     </row>
     <row r="865">
       <c r="B865" s="2"/>
-      <c r="C865" s="34"/>
+      <c r="C865" s="46"/>
     </row>
     <row r="866">
       <c r="B866" s="2"/>
-      <c r="C866" s="34"/>
+      <c r="C866" s="46"/>
     </row>
     <row r="867">
       <c r="B867" s="2"/>
-      <c r="C867" s="34"/>
+      <c r="C867" s="46"/>
     </row>
     <row r="868">
       <c r="B868" s="2"/>
-      <c r="C868" s="34"/>
+      <c r="C868" s="46"/>
     </row>
     <row r="869">
       <c r="B869" s="2"/>
-      <c r="C869" s="34"/>
+      <c r="C869" s="46"/>
     </row>
     <row r="870">
       <c r="B870" s="2"/>
-      <c r="C870" s="34"/>
+      <c r="C870" s="46"/>
     </row>
     <row r="871">
       <c r="B871" s="2"/>
-      <c r="C871" s="34"/>
+      <c r="C871" s="46"/>
     </row>
     <row r="872">
       <c r="B872" s="2"/>
-      <c r="C872" s="34"/>
+      <c r="C872" s="46"/>
     </row>
     <row r="873">
       <c r="B873" s="2"/>
-      <c r="C873" s="34"/>
+      <c r="C873" s="46"/>
     </row>
     <row r="874">
       <c r="B874" s="2"/>
-      <c r="C874" s="34"/>
+      <c r="C874" s="46"/>
     </row>
     <row r="875">
       <c r="B875" s="2"/>
-      <c r="C875" s="34"/>
+      <c r="C875" s="46"/>
     </row>
     <row r="876">
       <c r="B876" s="2"/>
-      <c r="C876" s="34"/>
+      <c r="C876" s="46"/>
     </row>
     <row r="877">
       <c r="B877" s="2"/>
-      <c r="C877" s="34"/>
+      <c r="C877" s="46"/>
     </row>
     <row r="878">
       <c r="B878" s="2"/>
-      <c r="C878" s="34"/>
+      <c r="C878" s="46"/>
     </row>
     <row r="879">
       <c r="B879" s="2"/>
-      <c r="C879" s="34"/>
+      <c r="C879" s="46"/>
     </row>
     <row r="880">
       <c r="B880" s="2"/>
-      <c r="C880" s="34"/>
+      <c r="C880" s="46"/>
     </row>
     <row r="881">
       <c r="B881" s="2"/>
-      <c r="C881" s="34"/>
+      <c r="C881" s="46"/>
     </row>
     <row r="882">
       <c r="B882" s="2"/>
-      <c r="C882" s="34"/>
+      <c r="C882" s="46"/>
     </row>
     <row r="883">
       <c r="B883" s="2"/>
-      <c r="C883" s="34"/>
+      <c r="C883" s="46"/>
     </row>
     <row r="884">
       <c r="B884" s="2"/>
-      <c r="C884" s="34"/>
+      <c r="C884" s="46"/>
     </row>
     <row r="885">
       <c r="B885" s="2"/>
-      <c r="C885" s="34"/>
+      <c r="C885" s="46"/>
     </row>
     <row r="886">
       <c r="B886" s="2"/>
-      <c r="C886" s="34"/>
+      <c r="C886" s="46"/>
     </row>
     <row r="887">
       <c r="B887" s="2"/>
-      <c r="C887" s="34"/>
+      <c r="C887" s="46"/>
     </row>
     <row r="888">
       <c r="B888" s="2"/>
-      <c r="C888" s="34"/>
+      <c r="C888" s="46"/>
     </row>
     <row r="889">
       <c r="B889" s="2"/>
-      <c r="C889" s="34"/>
+      <c r="C889" s="46"/>
     </row>
     <row r="890">
       <c r="B890" s="2"/>
-      <c r="C890" s="34"/>
+      <c r="C890" s="46"/>
     </row>
     <row r="891">
       <c r="B891" s="2"/>
-      <c r="C891" s="34"/>
+      <c r="C891" s="46"/>
     </row>
     <row r="892">
       <c r="B892" s="2"/>
-      <c r="C892" s="34"/>
+      <c r="C892" s="46"/>
     </row>
     <row r="893">
       <c r="B893" s="2"/>
-      <c r="C893" s="34"/>
+      <c r="C893" s="46"/>
     </row>
     <row r="894">
       <c r="B894" s="2"/>
-      <c r="C894" s="34"/>
+      <c r="C894" s="46"/>
     </row>
     <row r="895">
       <c r="B895" s="2"/>
-      <c r="C895" s="34"/>
+      <c r="C895" s="46"/>
     </row>
     <row r="896">
       <c r="B896" s="2"/>
-      <c r="C896" s="34"/>
+      <c r="C896" s="46"/>
     </row>
     <row r="897">
       <c r="B897" s="2"/>
-      <c r="C897" s="34"/>
+      <c r="C897" s="46"/>
     </row>
     <row r="898">
       <c r="B898" s="2"/>
-      <c r="C898" s="34"/>
+      <c r="C898" s="46"/>
     </row>
     <row r="899">
       <c r="B899" s="2"/>
-      <c r="C899" s="34"/>
+      <c r="C899" s="46"/>
     </row>
     <row r="900">
       <c r="B900" s="2"/>
-      <c r="C900" s="34"/>
+      <c r="C900" s="46"/>
     </row>
     <row r="901">
       <c r="B901" s="2"/>
-      <c r="C901" s="34"/>
+      <c r="C901" s="46"/>
     </row>
     <row r="902">
       <c r="B902" s="2"/>
-      <c r="C902" s="34"/>
+      <c r="C902" s="46"/>
     </row>
     <row r="903">
       <c r="B903" s="2"/>
-      <c r="C903" s="34"/>
+      <c r="C903" s="46"/>
     </row>
     <row r="904">
       <c r="B904" s="2"/>
-      <c r="C904" s="34"/>
+      <c r="C904" s="46"/>
     </row>
     <row r="905">
       <c r="B905" s="2"/>
-      <c r="C905" s="34"/>
+      <c r="C905" s="46"/>
     </row>
     <row r="906">
       <c r="B906" s="2"/>
-      <c r="C906" s="34"/>
+      <c r="C906" s="46"/>
     </row>
     <row r="907">
       <c r="B907" s="2"/>
-      <c r="C907" s="34"/>
+      <c r="C907" s="46"/>
     </row>
     <row r="908">
       <c r="B908" s="2"/>
-      <c r="C908" s="34"/>
+      <c r="C908" s="46"/>
     </row>
     <row r="909">
       <c r="B909" s="2"/>
-      <c r="C909" s="34"/>
+      <c r="C909" s="46"/>
     </row>
     <row r="910">
       <c r="B910" s="2"/>
-      <c r="C910" s="34"/>
+      <c r="C910" s="46"/>
     </row>
     <row r="911">
       <c r="B911" s="2"/>
-      <c r="C911" s="34"/>
+      <c r="C911" s="46"/>
     </row>
     <row r="912">
       <c r="B912" s="2"/>
-      <c r="C912" s="34"/>
+      <c r="C912" s="46"/>
     </row>
     <row r="913">
       <c r="B913" s="2"/>
-      <c r="C913" s="34"/>
+      <c r="C913" s="46"/>
     </row>
     <row r="914">
       <c r="B914" s="2"/>
-      <c r="C914" s="34"/>
+      <c r="C914" s="46"/>
     </row>
     <row r="915">
       <c r="B915" s="2"/>
-      <c r="C915" s="34"/>
+      <c r="C915" s="46"/>
     </row>
     <row r="916">
       <c r="B916" s="2"/>
-      <c r="C916" s="34"/>
+      <c r="C916" s="46"/>
     </row>
     <row r="917">
       <c r="B917" s="2"/>
-      <c r="C917" s="34"/>
+      <c r="C917" s="46"/>
     </row>
     <row r="918">
       <c r="B918" s="2"/>
-      <c r="C918" s="34"/>
+      <c r="C918" s="46"/>
     </row>
     <row r="919">
       <c r="B919" s="2"/>
-      <c r="C919" s="34"/>
+      <c r="C919" s="46"/>
     </row>
     <row r="920">
       <c r="B920" s="2"/>
-      <c r="C920" s="34"/>
+      <c r="C920" s="46"/>
     </row>
     <row r="921">
       <c r="B921" s="2"/>
-      <c r="C921" s="34"/>
+      <c r="C921" s="46"/>
     </row>
     <row r="922">
       <c r="B922" s="2"/>
-      <c r="C922" s="34"/>
+      <c r="C922" s="46"/>
     </row>
     <row r="923">
       <c r="B923" s="2"/>
-      <c r="C923" s="34"/>
+      <c r="C923" s="46"/>
     </row>
     <row r="924">
       <c r="B924" s="2"/>
-      <c r="C924" s="34"/>
+      <c r="C924" s="46"/>
     </row>
     <row r="925">
       <c r="B925" s="2"/>
-      <c r="C925" s="34"/>
+      <c r="C925" s="46"/>
     </row>
     <row r="926">
       <c r="B926" s="2"/>
-      <c r="C926" s="34"/>
+      <c r="C926" s="46"/>
     </row>
     <row r="927">
       <c r="B927" s="2"/>
-      <c r="C927" s="34"/>
+      <c r="C927" s="46"/>
     </row>
     <row r="928">
       <c r="B928" s="2"/>
-      <c r="C928" s="34"/>
+      <c r="C928" s="46"/>
     </row>
     <row r="929">
       <c r="B929" s="2"/>
-      <c r="C929" s="34"/>
+      <c r="C929" s="46"/>
     </row>
     <row r="930">
       <c r="B930" s="2"/>
-      <c r="C930" s="34"/>
+      <c r="C930" s="46"/>
     </row>
     <row r="931">
       <c r="B931" s="2"/>
-      <c r="C931" s="34"/>
+      <c r="C931" s="46"/>
     </row>
     <row r="932">
       <c r="B932" s="2"/>
-      <c r="C932" s="34"/>
+      <c r="C932" s="46"/>
     </row>
     <row r="933">
       <c r="B933" s="2"/>
-      <c r="C933" s="34"/>
+      <c r="C933" s="46"/>
     </row>
     <row r="934">
       <c r="B934" s="2"/>
-      <c r="C934" s="34"/>
+      <c r="C934" s="46"/>
     </row>
     <row r="935">
       <c r="B935" s="2"/>
-      <c r="C935" s="34"/>
+      <c r="C935" s="46"/>
     </row>
     <row r="936">
       <c r="B936" s="2"/>
-      <c r="C936" s="34"/>
+      <c r="C936" s="46"/>
     </row>
     <row r="937">
       <c r="B937" s="2"/>
-      <c r="C937" s="34"/>
+      <c r="C937" s="46"/>
     </row>
     <row r="938">
       <c r="B938" s="2"/>
-      <c r="C938" s="34"/>
+      <c r="C938" s="46"/>
     </row>
     <row r="939">
       <c r="B939" s="2"/>
-      <c r="C939" s="34"/>
+      <c r="C939" s="46"/>
     </row>
     <row r="940">
       <c r="B940" s="2"/>
-      <c r="C940" s="34"/>
+      <c r="C940" s="46"/>
     </row>
     <row r="941">
       <c r="B941" s="2"/>
-      <c r="C941" s="34"/>
+      <c r="C941" s="46"/>
     </row>
     <row r="942">
       <c r="B942" s="2"/>
-      <c r="C942" s="34"/>
+      <c r="C942" s="46"/>
     </row>
     <row r="943">
       <c r="B943" s="2"/>
-      <c r="C943" s="34"/>
+      <c r="C943" s="46"/>
     </row>
     <row r="944">
       <c r="B944" s="2"/>
-      <c r="C944" s="34"/>
+      <c r="C944" s="46"/>
     </row>
     <row r="945">
       <c r="B945" s="2"/>
-      <c r="C945" s="34"/>
+      <c r="C945" s="46"/>
     </row>
     <row r="946">
       <c r="B946" s="2"/>
-      <c r="C946" s="34"/>
+      <c r="C946" s="46"/>
     </row>
     <row r="947">
       <c r="B947" s="2"/>
-      <c r="C947" s="34"/>
+      <c r="C947" s="46"/>
     </row>
     <row r="948">
       <c r="B948" s="2"/>
-      <c r="C948" s="34"/>
+      <c r="C948" s="46"/>
     </row>
     <row r="949">
       <c r="B949" s="2"/>
-      <c r="C949" s="34"/>
+      <c r="C949" s="46"/>
     </row>
     <row r="950">
       <c r="B950" s="2"/>
-      <c r="C950" s="34"/>
+      <c r="C950" s="46"/>
     </row>
     <row r="951">
       <c r="B951" s="2"/>
-      <c r="C951" s="34"/>
+      <c r="C951" s="46"/>
     </row>
     <row r="952">
       <c r="B952" s="2"/>
-      <c r="C952" s="34"/>
+      <c r="C952" s="46"/>
     </row>
     <row r="953">
       <c r="B953" s="2"/>
-      <c r="C953" s="34"/>
+      <c r="C953" s="46"/>
     </row>
     <row r="954">
       <c r="B954" s="2"/>
-      <c r="C954" s="34"/>
+      <c r="C954" s="46"/>
     </row>
     <row r="955">
       <c r="B955" s="2"/>
-      <c r="C955" s="34"/>
+      <c r="C955" s="46"/>
     </row>
     <row r="956">
       <c r="B956" s="2"/>
-      <c r="C956" s="34"/>
+      <c r="C956" s="46"/>
     </row>
     <row r="957">
       <c r="B957" s="2"/>
-      <c r="C957" s="34"/>
+      <c r="C957" s="46"/>
     </row>
     <row r="958">
       <c r="B958" s="2"/>
-      <c r="C958" s="34"/>
+      <c r="C958" s="46"/>
     </row>
     <row r="959">
       <c r="B959" s="2"/>
-      <c r="C959" s="34"/>
+      <c r="C959" s="46"/>
     </row>
     <row r="960">
       <c r="B960" s="2"/>
-      <c r="C960" s="34"/>
+      <c r="C960" s="46"/>
     </row>
     <row r="961">
       <c r="B961" s="2"/>
-      <c r="C961" s="34"/>
+      <c r="C961" s="46"/>
     </row>
     <row r="962">
       <c r="B962" s="2"/>
-      <c r="C962" s="34"/>
+      <c r="C962" s="46"/>
     </row>
     <row r="963">
       <c r="B963" s="2"/>
-      <c r="C963" s="34"/>
+      <c r="C963" s="46"/>
     </row>
     <row r="964">
       <c r="B964" s="2"/>
-      <c r="C964" s="34"/>
+      <c r="C964" s="46"/>
     </row>
     <row r="965">
       <c r="B965" s="2"/>
-      <c r="C965" s="34"/>
+      <c r="C965" s="46"/>
     </row>
     <row r="966">
       <c r="B966" s="2"/>
-      <c r="C966" s="34"/>
+      <c r="C966" s="46"/>
     </row>
     <row r="967">
       <c r="B967" s="2"/>
-      <c r="C967" s="34"/>
+      <c r="C967" s="46"/>
     </row>
     <row r="968">
       <c r="B968" s="2"/>
-      <c r="C968" s="34"/>
+      <c r="C968" s="46"/>
     </row>
     <row r="969">
       <c r="B969" s="2"/>
-      <c r="C969" s="34"/>
+      <c r="C969" s="46"/>
     </row>
     <row r="970">
       <c r="B970" s="2"/>
-      <c r="C970" s="34"/>
+      <c r="C970" s="46"/>
     </row>
     <row r="971">
       <c r="B971" s="2"/>
-      <c r="C971" s="34"/>
+      <c r="C971" s="46"/>
     </row>
     <row r="972">
       <c r="B972" s="2"/>
-      <c r="C972" s="34"/>
+      <c r="C972" s="46"/>
     </row>
     <row r="973">
       <c r="B973" s="2"/>
-      <c r="C973" s="34"/>
+      <c r="C973" s="46"/>
     </row>
     <row r="974">
       <c r="B974" s="2"/>
-      <c r="C974" s="34"/>
+      <c r="C974" s="46"/>
     </row>
     <row r="975">
       <c r="B975" s="2"/>
-      <c r="C975" s="34"/>
+      <c r="C975" s="46"/>
     </row>
     <row r="976">
       <c r="B976" s="2"/>
-      <c r="C976" s="34"/>
+      <c r="C976" s="46"/>
     </row>
     <row r="977">
       <c r="B977" s="2"/>
-      <c r="C977" s="34"/>
+      <c r="C977" s="46"/>
     </row>
     <row r="978">
       <c r="B978" s="2"/>
-      <c r="C978" s="34"/>
+      <c r="C978" s="46"/>
     </row>
     <row r="979">
       <c r="B979" s="2"/>
-      <c r="C979" s="34"/>
+      <c r="C979" s="46"/>
     </row>
     <row r="980">
       <c r="B980" s="2"/>
-      <c r="C980" s="34"/>
+      <c r="C980" s="46"/>
     </row>
     <row r="981">
       <c r="B981" s="2"/>
-      <c r="C981" s="34"/>
+      <c r="C981" s="46"/>
     </row>
     <row r="982">
       <c r="B982" s="2"/>
-      <c r="C982" s="34"/>
+      <c r="C982" s="46"/>
     </row>
     <row r="983">
       <c r="B983" s="2"/>
-      <c r="C983" s="34"/>
+      <c r="C983" s="46"/>
     </row>
     <row r="984">
       <c r="B984" s="2"/>
-      <c r="C984" s="34"/>
+      <c r="C984" s="46"/>
     </row>
     <row r="985">
       <c r="B985" s="2"/>
-      <c r="C985" s="34"/>
+      <c r="C985" s="46"/>
     </row>
     <row r="986">
       <c r="B986" s="2"/>
-      <c r="C986" s="34"/>
+      <c r="C986" s="46"/>
     </row>
     <row r="987">
       <c r="B987" s="2"/>
-      <c r="C987" s="34"/>
+      <c r="C987" s="46"/>
     </row>
     <row r="988">
       <c r="B988" s="2"/>
-      <c r="C988" s="34"/>
+      <c r="C988" s="46"/>
     </row>
     <row r="989">
       <c r="B989" s="2"/>
-      <c r="C989" s="34"/>
+      <c r="C989" s="46"/>
     </row>
     <row r="990">
       <c r="B990" s="2"/>
-      <c r="C990" s="34"/>
+      <c r="C990" s="46"/>
     </row>
     <row r="991">
       <c r="B991" s="2"/>
-      <c r="C991" s="34"/>
+      <c r="C991" s="46"/>
     </row>
     <row r="992">
       <c r="B992" s="2"/>
-      <c r="C992" s="34"/>
+      <c r="C992" s="46"/>
     </row>
     <row r="993">
       <c r="B993" s="2"/>
-      <c r="C993" s="34"/>
+      <c r="C993" s="46"/>
     </row>
     <row r="994">
       <c r="B994" s="2"/>
-      <c r="C994" s="34"/>
+      <c r="C994" s="46"/>
     </row>
     <row r="995">
       <c r="B995" s="2"/>
-      <c r="C995" s="34"/>
+      <c r="C995" s="46"/>
     </row>
     <row r="996">
       <c r="B996" s="2"/>
-      <c r="C996" s="34"/>
+      <c r="C996" s="46"/>
     </row>
     <row r="997">
       <c r="B997" s="2"/>
-      <c r="C997" s="34"/>
+      <c r="C997" s="46"/>
     </row>
     <row r="998">
       <c r="B998" s="2"/>
-      <c r="C998" s="34"/>
+      <c r="C998" s="46"/>
     </row>
     <row r="999">
       <c r="B999" s="2"/>
-      <c r="C999" s="34"/>
+      <c r="C999" s="46"/>
     </row>
     <row r="1000">
       <c r="B1000" s="2"/>
-      <c r="C1000" s="34"/>
+      <c r="C1000" s="46"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/public/templates/monthly-treatment-report-template.xlsx
+++ b/public/templates/monthly-treatment-report-template.xlsx
@@ -114,7 +114,7 @@
     <numFmt numFmtId="164" formatCode="[$-409]mmmm\-yy"/>
     <numFmt numFmtId="165" formatCode="m/d/yy"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <sz val="12.0"/>
       <color theme="1"/>
@@ -161,6 +161,12 @@
       <sz val="12.0"/>
       <color theme="1"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="12.0"/>
@@ -212,7 +218,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="18">
+  <borders count="15">
     <border/>
     <border>
       <left style="thin">
@@ -286,20 +292,6 @@
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF9A9A9A"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
@@ -321,39 +313,11 @@
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF9A9A9A"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF9A9A9A"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
     </border>
     <border>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF9A9A9A"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
     </border>
     <border>
       <left style="thin">
@@ -380,7 +344,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="50">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -474,29 +438,26 @@
     <xf borderId="1" fillId="6" fontId="4" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="7" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="8" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="7" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
+    <xf borderId="8" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="9" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
     <xf borderId="10" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="11" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="bottom"/>
+    <xf borderId="11" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="12" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="13" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="14" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="15" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="16" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="17" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="14" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -729,7 +690,7 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="24.33"/>
+    <col customWidth="1" min="1" max="1" width="28.89"/>
     <col customWidth="1" min="2" max="2" width="21.89"/>
     <col customWidth="1" min="3" max="4" width="14.67"/>
     <col customWidth="1" min="5" max="8" width="10.67"/>
@@ -1075,7 +1036,7 @@
       <c r="H28" s="39"/>
     </row>
     <row r="29">
-      <c r="A29" s="40" t="s">
+      <c r="A29" s="37" t="s">
         <v>23</v>
       </c>
       <c r="B29" s="2"/>
@@ -1083,13 +1044,13 @@
       <c r="H29" s="39"/>
     </row>
     <row r="30">
-      <c r="A30" s="41"/>
+      <c r="A30" s="40"/>
       <c r="B30" s="2"/>
-      <c r="D30" s="42"/>
-      <c r="E30" s="43"/>
-      <c r="F30" s="43"/>
-      <c r="G30" s="43"/>
-      <c r="H30" s="44"/>
+      <c r="D30" s="41"/>
+      <c r="E30" s="42"/>
+      <c r="F30" s="42"/>
+      <c r="G30" s="42"/>
+      <c r="H30" s="43"/>
     </row>
     <row r="31">
       <c r="B31" s="2"/>
@@ -9860,8 +9821,8 @@
       </c>
     </row>
     <row r="3" ht="7.5" customHeight="1">
-      <c r="B3" s="45"/>
-      <c r="C3" s="45"/>
+      <c r="B3" s="44"/>
+      <c r="C3" s="44"/>
     </row>
     <row r="4">
       <c r="B4" s="3" t="s">
@@ -9873,10 +9834,10 @@
     </row>
     <row r="5" ht="6.75" customHeight="1">
       <c r="B5" s="2"/>
-      <c r="C5" s="46"/>
+      <c r="C5" s="45"/>
     </row>
     <row r="6">
-      <c r="B6" s="47" t="s">
+      <c r="B6" s="46" t="s">
         <v>27</v>
       </c>
       <c r="C6" s="6" t="s">
@@ -9884,4185 +9845,4185 @@
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="48">
+      <c r="B7" s="47">
         <v>46113.0</v>
       </c>
-      <c r="C7" s="49">
+      <c r="C7" s="48">
         <v>33.75</v>
       </c>
-      <c r="D7" s="50"/>
+      <c r="D7" s="49"/>
     </row>
     <row r="8">
-      <c r="B8" s="48">
+      <c r="B8" s="47">
         <f t="shared" ref="B8:B36" si="1">B7+1</f>
         <v>46114</v>
       </c>
-      <c r="C8" s="49">
+      <c r="C8" s="48">
         <v>33.5</v>
       </c>
-      <c r="D8" s="50"/>
+      <c r="D8" s="49"/>
     </row>
     <row r="9">
-      <c r="B9" s="48">
+      <c r="B9" s="47">
         <f t="shared" si="1"/>
         <v>46115</v>
       </c>
-      <c r="C9" s="49">
+      <c r="C9" s="48">
         <v>33.75</v>
       </c>
-      <c r="D9" s="50"/>
-      <c r="E9" s="50"/>
+      <c r="D9" s="49"/>
+      <c r="E9" s="49"/>
     </row>
     <row r="10">
-      <c r="B10" s="48">
+      <c r="B10" s="47">
         <f t="shared" si="1"/>
         <v>46116</v>
       </c>
-      <c r="C10" s="49">
+      <c r="C10" s="48">
         <v>32.5</v>
       </c>
-      <c r="D10" s="50"/>
-      <c r="E10" s="50"/>
+      <c r="D10" s="49"/>
+      <c r="E10" s="49"/>
     </row>
     <row r="11">
-      <c r="B11" s="48">
+      <c r="B11" s="47">
         <f t="shared" si="1"/>
         <v>46117</v>
       </c>
-      <c r="C11" s="49">
+      <c r="C11" s="48">
         <v>32.25</v>
       </c>
-      <c r="D11" s="50"/>
-      <c r="E11" s="50"/>
+      <c r="D11" s="49"/>
+      <c r="E11" s="49"/>
     </row>
     <row r="12">
-      <c r="B12" s="48">
+      <c r="B12" s="47">
         <f t="shared" si="1"/>
         <v>46118</v>
       </c>
-      <c r="C12" s="49">
+      <c r="C12" s="48">
         <v>31.75</v>
       </c>
-      <c r="D12" s="50"/>
-      <c r="E12" s="50"/>
+      <c r="D12" s="49"/>
+      <c r="E12" s="49"/>
     </row>
     <row r="13">
-      <c r="B13" s="48">
+      <c r="B13" s="47">
         <f t="shared" si="1"/>
         <v>46119</v>
       </c>
-      <c r="C13" s="49">
+      <c r="C13" s="48">
         <v>31.75</v>
       </c>
-      <c r="D13" s="50"/>
-      <c r="E13" s="50"/>
+      <c r="D13" s="49"/>
+      <c r="E13" s="49"/>
     </row>
     <row r="14">
-      <c r="B14" s="48">
+      <c r="B14" s="47">
         <f t="shared" si="1"/>
         <v>46120</v>
       </c>
-      <c r="C14" s="49">
+      <c r="C14" s="48">
         <v>30.75</v>
       </c>
-      <c r="D14" s="50"/>
-      <c r="E14" s="50"/>
+      <c r="D14" s="49"/>
+      <c r="E14" s="49"/>
     </row>
     <row r="15">
-      <c r="B15" s="48">
+      <c r="B15" s="47">
         <f t="shared" si="1"/>
         <v>46121</v>
       </c>
-      <c r="C15" s="49">
+      <c r="C15" s="48">
         <v>30.5</v>
       </c>
-      <c r="D15" s="50"/>
-      <c r="E15" s="50"/>
+      <c r="D15" s="49"/>
+      <c r="E15" s="49"/>
     </row>
     <row r="16">
-      <c r="B16" s="48">
+      <c r="B16" s="47">
         <f t="shared" si="1"/>
         <v>46122</v>
       </c>
-      <c r="C16" s="49">
+      <c r="C16" s="48">
         <v>30.0</v>
       </c>
-      <c r="D16" s="50"/>
-      <c r="E16" s="50"/>
+      <c r="D16" s="49"/>
+      <c r="E16" s="49"/>
     </row>
     <row r="17">
-      <c r="B17" s="48">
+      <c r="B17" s="47">
         <f t="shared" si="1"/>
         <v>46123</v>
       </c>
-      <c r="C17" s="49">
+      <c r="C17" s="48">
         <v>29.5</v>
       </c>
-      <c r="D17" s="50"/>
-      <c r="E17" s="50"/>
+      <c r="D17" s="49"/>
+      <c r="E17" s="49"/>
     </row>
     <row r="18">
-      <c r="B18" s="48">
+      <c r="B18" s="47">
         <f t="shared" si="1"/>
         <v>46124</v>
       </c>
-      <c r="C18" s="49">
+      <c r="C18" s="48">
         <v>28.75</v>
       </c>
-      <c r="D18" s="50"/>
-      <c r="E18" s="50"/>
+      <c r="D18" s="49"/>
+      <c r="E18" s="49"/>
     </row>
     <row r="19">
-      <c r="B19" s="48">
+      <c r="B19" s="47">
         <f t="shared" si="1"/>
         <v>46125</v>
       </c>
-      <c r="C19" s="49">
+      <c r="C19" s="48">
         <v>28.5</v>
       </c>
-      <c r="D19" s="50"/>
-      <c r="E19" s="50"/>
+      <c r="D19" s="49"/>
+      <c r="E19" s="49"/>
     </row>
     <row r="20">
-      <c r="B20" s="48">
+      <c r="B20" s="47">
         <f t="shared" si="1"/>
         <v>46126</v>
       </c>
-      <c r="C20" s="49">
+      <c r="C20" s="48">
         <v>28.0</v>
       </c>
-      <c r="D20" s="50"/>
-      <c r="E20" s="50"/>
+      <c r="D20" s="49"/>
+      <c r="E20" s="49"/>
     </row>
     <row r="21">
-      <c r="B21" s="48">
+      <c r="B21" s="47">
         <f t="shared" si="1"/>
         <v>46127</v>
       </c>
-      <c r="C21" s="49">
+      <c r="C21" s="48">
         <v>27.5</v>
       </c>
-      <c r="D21" s="50"/>
-      <c r="E21" s="50"/>
+      <c r="D21" s="49"/>
+      <c r="E21" s="49"/>
     </row>
     <row r="22">
-      <c r="B22" s="48">
+      <c r="B22" s="47">
         <f t="shared" si="1"/>
         <v>46128</v>
       </c>
-      <c r="C22" s="49">
+      <c r="C22" s="48">
         <v>27.0</v>
       </c>
-      <c r="D22" s="50"/>
-      <c r="E22" s="50"/>
+      <c r="D22" s="49"/>
+      <c r="E22" s="49"/>
     </row>
     <row r="23">
-      <c r="B23" s="48">
+      <c r="B23" s="47">
         <f t="shared" si="1"/>
         <v>46129</v>
       </c>
-      <c r="C23" s="49">
+      <c r="C23" s="48">
         <v>26.5</v>
       </c>
-      <c r="D23" s="50"/>
-      <c r="E23" s="50"/>
+      <c r="D23" s="49"/>
+      <c r="E23" s="49"/>
     </row>
     <row r="24">
-      <c r="B24" s="48">
+      <c r="B24" s="47">
         <f t="shared" si="1"/>
         <v>46130</v>
       </c>
-      <c r="C24" s="49">
+      <c r="C24" s="48">
         <v>24.75</v>
       </c>
-      <c r="D24" s="50"/>
-      <c r="E24" s="50"/>
+      <c r="D24" s="49"/>
+      <c r="E24" s="49"/>
     </row>
     <row r="25">
-      <c r="B25" s="48">
+      <c r="B25" s="47">
         <f t="shared" si="1"/>
         <v>46131</v>
       </c>
-      <c r="C25" s="49">
+      <c r="C25" s="48">
         <v>25.375</v>
       </c>
-      <c r="D25" s="50"/>
-      <c r="E25" s="50"/>
+      <c r="D25" s="49"/>
+      <c r="E25" s="49"/>
     </row>
     <row r="26">
-      <c r="B26" s="48">
+      <c r="B26" s="47">
         <f t="shared" si="1"/>
         <v>46132</v>
       </c>
-      <c r="C26" s="49">
+      <c r="C26" s="48">
         <v>24.75</v>
       </c>
-      <c r="D26" s="50"/>
-      <c r="E26" s="50"/>
+      <c r="D26" s="49"/>
+      <c r="E26" s="49"/>
     </row>
     <row r="27">
-      <c r="B27" s="48">
+      <c r="B27" s="47">
         <f t="shared" si="1"/>
         <v>46133</v>
       </c>
-      <c r="C27" s="49">
+      <c r="C27" s="48">
         <v>24.25</v>
       </c>
-      <c r="D27" s="50"/>
-      <c r="E27" s="50"/>
+      <c r="D27" s="49"/>
+      <c r="E27" s="49"/>
     </row>
     <row r="28">
-      <c r="B28" s="48">
+      <c r="B28" s="47">
         <f t="shared" si="1"/>
         <v>46134</v>
       </c>
-      <c r="C28" s="49">
+      <c r="C28" s="48">
         <v>23.75</v>
       </c>
-      <c r="D28" s="50"/>
-      <c r="E28" s="50"/>
+      <c r="D28" s="49"/>
+      <c r="E28" s="49"/>
     </row>
     <row r="29">
-      <c r="B29" s="48">
+      <c r="B29" s="47">
         <f t="shared" si="1"/>
         <v>46135</v>
       </c>
-      <c r="C29" s="49">
+      <c r="C29" s="48">
         <v>23.25</v>
       </c>
-      <c r="D29" s="50"/>
-      <c r="E29" s="50"/>
+      <c r="D29" s="49"/>
+      <c r="E29" s="49"/>
     </row>
     <row r="30">
-      <c r="B30" s="48">
+      <c r="B30" s="47">
         <f t="shared" si="1"/>
         <v>46136</v>
       </c>
-      <c r="C30" s="49">
+      <c r="C30" s="48">
         <v>22.5</v>
       </c>
-      <c r="D30" s="50"/>
-      <c r="E30" s="50"/>
+      <c r="D30" s="49"/>
+      <c r="E30" s="49"/>
     </row>
     <row r="31">
-      <c r="B31" s="48">
+      <c r="B31" s="47">
         <f t="shared" si="1"/>
         <v>46137</v>
       </c>
-      <c r="C31" s="49">
+      <c r="C31" s="48">
         <v>22.0</v>
       </c>
-      <c r="D31" s="50"/>
-      <c r="E31" s="50"/>
+      <c r="D31" s="49"/>
+      <c r="E31" s="49"/>
     </row>
     <row r="32">
-      <c r="B32" s="48">
+      <c r="B32" s="47">
         <f t="shared" si="1"/>
         <v>46138</v>
       </c>
-      <c r="C32" s="49">
+      <c r="C32" s="48">
         <v>21.5</v>
       </c>
-      <c r="D32" s="50"/>
-      <c r="E32" s="50"/>
+      <c r="D32" s="49"/>
+      <c r="E32" s="49"/>
     </row>
     <row r="33">
-      <c r="B33" s="48">
+      <c r="B33" s="47">
         <f t="shared" si="1"/>
         <v>46139</v>
       </c>
-      <c r="C33" s="49">
+      <c r="C33" s="48">
         <v>21.0</v>
       </c>
-      <c r="D33" s="50"/>
-      <c r="E33" s="50"/>
+      <c r="D33" s="49"/>
+      <c r="E33" s="49"/>
     </row>
     <row r="34">
-      <c r="B34" s="48">
+      <c r="B34" s="47">
         <f t="shared" si="1"/>
         <v>46140</v>
       </c>
-      <c r="C34" s="49">
+      <c r="C34" s="48">
         <v>20.5</v>
       </c>
-      <c r="D34" s="50"/>
-      <c r="E34" s="50"/>
+      <c r="D34" s="49"/>
+      <c r="E34" s="49"/>
     </row>
     <row r="35">
-      <c r="B35" s="48">
+      <c r="B35" s="47">
         <f t="shared" si="1"/>
         <v>46141</v>
       </c>
-      <c r="C35" s="49">
+      <c r="C35" s="48">
         <v>19.5</v>
       </c>
-      <c r="D35" s="50"/>
-      <c r="E35" s="50"/>
+      <c r="D35" s="49"/>
+      <c r="E35" s="49"/>
     </row>
     <row r="36">
-      <c r="B36" s="48">
+      <c r="B36" s="47">
         <f t="shared" si="1"/>
         <v>46142</v>
       </c>
-      <c r="C36" s="49">
+      <c r="C36" s="48">
         <v>18.75</v>
       </c>
     </row>
     <row r="37">
       <c r="B37" s="2"/>
-      <c r="C37" s="46"/>
+      <c r="C37" s="45"/>
     </row>
     <row r="38">
       <c r="B38" s="2"/>
-      <c r="C38" s="46"/>
+      <c r="C38" s="45"/>
     </row>
     <row r="39">
       <c r="B39" s="2"/>
-      <c r="C39" s="46"/>
+      <c r="C39" s="45"/>
     </row>
     <row r="40">
       <c r="B40" s="2"/>
-      <c r="C40" s="46"/>
+      <c r="C40" s="45"/>
     </row>
     <row r="41">
       <c r="B41" s="2"/>
-      <c r="C41" s="46"/>
+      <c r="C41" s="45"/>
     </row>
     <row r="42">
       <c r="B42" s="2"/>
-      <c r="C42" s="46"/>
+      <c r="C42" s="45"/>
     </row>
     <row r="43">
       <c r="B43" s="2"/>
-      <c r="C43" s="46"/>
+      <c r="C43" s="45"/>
     </row>
     <row r="44">
       <c r="B44" s="2"/>
-      <c r="C44" s="46"/>
+      <c r="C44" s="45"/>
     </row>
     <row r="45">
       <c r="B45" s="2"/>
-      <c r="C45" s="46"/>
+      <c r="C45" s="45"/>
     </row>
     <row r="46">
       <c r="B46" s="2"/>
-      <c r="C46" s="46"/>
+      <c r="C46" s="45"/>
     </row>
     <row r="47">
       <c r="B47" s="2"/>
-      <c r="C47" s="46"/>
+      <c r="C47" s="45"/>
     </row>
     <row r="48">
       <c r="B48" s="2"/>
-      <c r="C48" s="46"/>
+      <c r="C48" s="45"/>
     </row>
     <row r="49">
       <c r="B49" s="2"/>
-      <c r="C49" s="46"/>
+      <c r="C49" s="45"/>
     </row>
     <row r="50">
       <c r="B50" s="2"/>
-      <c r="C50" s="46"/>
+      <c r="C50" s="45"/>
     </row>
     <row r="51">
       <c r="B51" s="2"/>
-      <c r="C51" s="46"/>
+      <c r="C51" s="45"/>
     </row>
     <row r="52">
       <c r="B52" s="2"/>
-      <c r="C52" s="46"/>
+      <c r="C52" s="45"/>
     </row>
     <row r="53">
       <c r="B53" s="2"/>
-      <c r="C53" s="46"/>
+      <c r="C53" s="45"/>
     </row>
     <row r="54">
       <c r="B54" s="2"/>
-      <c r="C54" s="46"/>
+      <c r="C54" s="45"/>
     </row>
     <row r="55">
       <c r="B55" s="2"/>
-      <c r="C55" s="46"/>
+      <c r="C55" s="45"/>
     </row>
     <row r="56">
       <c r="B56" s="2"/>
-      <c r="C56" s="46"/>
+      <c r="C56" s="45"/>
     </row>
     <row r="57">
       <c r="B57" s="2"/>
-      <c r="C57" s="46"/>
+      <c r="C57" s="45"/>
     </row>
     <row r="58">
       <c r="B58" s="2"/>
-      <c r="C58" s="46"/>
+      <c r="C58" s="45"/>
     </row>
     <row r="59">
       <c r="B59" s="2"/>
-      <c r="C59" s="46"/>
+      <c r="C59" s="45"/>
     </row>
     <row r="60">
       <c r="B60" s="2"/>
-      <c r="C60" s="46"/>
+      <c r="C60" s="45"/>
     </row>
     <row r="61">
       <c r="B61" s="2"/>
-      <c r="C61" s="46"/>
+      <c r="C61" s="45"/>
     </row>
     <row r="62">
       <c r="B62" s="2"/>
-      <c r="C62" s="46"/>
+      <c r="C62" s="45"/>
     </row>
     <row r="63">
       <c r="B63" s="2"/>
-      <c r="C63" s="46"/>
+      <c r="C63" s="45"/>
     </row>
     <row r="64">
       <c r="B64" s="2"/>
-      <c r="C64" s="46"/>
+      <c r="C64" s="45"/>
     </row>
     <row r="65">
       <c r="B65" s="2"/>
-      <c r="C65" s="46"/>
+      <c r="C65" s="45"/>
     </row>
     <row r="66">
       <c r="B66" s="2"/>
-      <c r="C66" s="46"/>
+      <c r="C66" s="45"/>
     </row>
     <row r="67">
       <c r="B67" s="2"/>
-      <c r="C67" s="46"/>
+      <c r="C67" s="45"/>
     </row>
     <row r="68">
       <c r="B68" s="2"/>
-      <c r="C68" s="46"/>
+      <c r="C68" s="45"/>
     </row>
     <row r="69">
       <c r="B69" s="2"/>
-      <c r="C69" s="46"/>
+      <c r="C69" s="45"/>
     </row>
     <row r="70">
       <c r="B70" s="2"/>
-      <c r="C70" s="46"/>
+      <c r="C70" s="45"/>
     </row>
     <row r="71">
       <c r="B71" s="2"/>
-      <c r="C71" s="46"/>
+      <c r="C71" s="45"/>
     </row>
     <row r="72">
       <c r="B72" s="2"/>
-      <c r="C72" s="46"/>
+      <c r="C72" s="45"/>
     </row>
     <row r="73">
       <c r="B73" s="2"/>
-      <c r="C73" s="46"/>
+      <c r="C73" s="45"/>
     </row>
     <row r="74">
       <c r="B74" s="2"/>
-      <c r="C74" s="46"/>
+      <c r="C74" s="45"/>
     </row>
     <row r="75">
       <c r="B75" s="2"/>
-      <c r="C75" s="46"/>
+      <c r="C75" s="45"/>
     </row>
     <row r="76">
       <c r="B76" s="2"/>
-      <c r="C76" s="46"/>
+      <c r="C76" s="45"/>
     </row>
     <row r="77">
       <c r="B77" s="2"/>
-      <c r="C77" s="46"/>
+      <c r="C77" s="45"/>
     </row>
     <row r="78">
       <c r="B78" s="2"/>
-      <c r="C78" s="46"/>
+      <c r="C78" s="45"/>
     </row>
     <row r="79">
       <c r="B79" s="2"/>
-      <c r="C79" s="46"/>
+      <c r="C79" s="45"/>
     </row>
     <row r="80">
       <c r="B80" s="2"/>
-      <c r="C80" s="46"/>
+      <c r="C80" s="45"/>
     </row>
     <row r="81">
       <c r="B81" s="2"/>
-      <c r="C81" s="46"/>
+      <c r="C81" s="45"/>
     </row>
     <row r="82">
       <c r="B82" s="2"/>
-      <c r="C82" s="46"/>
+      <c r="C82" s="45"/>
     </row>
     <row r="83">
       <c r="B83" s="2"/>
-      <c r="C83" s="46"/>
+      <c r="C83" s="45"/>
     </row>
     <row r="84">
       <c r="B84" s="2"/>
-      <c r="C84" s="46"/>
+      <c r="C84" s="45"/>
     </row>
     <row r="85">
       <c r="B85" s="2"/>
-      <c r="C85" s="46"/>
+      <c r="C85" s="45"/>
     </row>
     <row r="86">
       <c r="B86" s="2"/>
-      <c r="C86" s="46"/>
+      <c r="C86" s="45"/>
     </row>
     <row r="87">
       <c r="B87" s="2"/>
-      <c r="C87" s="46"/>
+      <c r="C87" s="45"/>
     </row>
     <row r="88">
       <c r="B88" s="2"/>
-      <c r="C88" s="46"/>
+      <c r="C88" s="45"/>
     </row>
     <row r="89">
       <c r="B89" s="2"/>
-      <c r="C89" s="46"/>
+      <c r="C89" s="45"/>
     </row>
     <row r="90">
       <c r="B90" s="2"/>
-      <c r="C90" s="46"/>
+      <c r="C90" s="45"/>
     </row>
     <row r="91">
       <c r="B91" s="2"/>
-      <c r="C91" s="46"/>
+      <c r="C91" s="45"/>
     </row>
     <row r="92">
       <c r="B92" s="2"/>
-      <c r="C92" s="46"/>
+      <c r="C92" s="45"/>
     </row>
     <row r="93">
       <c r="B93" s="2"/>
-      <c r="C93" s="46"/>
+      <c r="C93" s="45"/>
     </row>
     <row r="94">
       <c r="B94" s="2"/>
-      <c r="C94" s="46"/>
+      <c r="C94" s="45"/>
     </row>
     <row r="95">
       <c r="B95" s="2"/>
-      <c r="C95" s="46"/>
+      <c r="C95" s="45"/>
     </row>
     <row r="96">
       <c r="B96" s="2"/>
-      <c r="C96" s="46"/>
+      <c r="C96" s="45"/>
     </row>
     <row r="97">
       <c r="B97" s="2"/>
-      <c r="C97" s="46"/>
+      <c r="C97" s="45"/>
     </row>
     <row r="98">
       <c r="B98" s="2"/>
-      <c r="C98" s="46"/>
+      <c r="C98" s="45"/>
     </row>
     <row r="99">
       <c r="B99" s="2"/>
-      <c r="C99" s="46"/>
+      <c r="C99" s="45"/>
     </row>
     <row r="100">
       <c r="B100" s="2"/>
-      <c r="C100" s="46"/>
+      <c r="C100" s="45"/>
     </row>
     <row r="101">
       <c r="B101" s="2"/>
-      <c r="C101" s="46"/>
+      <c r="C101" s="45"/>
     </row>
     <row r="102">
       <c r="B102" s="2"/>
-      <c r="C102" s="46"/>
+      <c r="C102" s="45"/>
     </row>
     <row r="103">
       <c r="B103" s="2"/>
-      <c r="C103" s="46"/>
+      <c r="C103" s="45"/>
     </row>
     <row r="104">
       <c r="B104" s="2"/>
-      <c r="C104" s="46"/>
+      <c r="C104" s="45"/>
     </row>
     <row r="105">
       <c r="B105" s="2"/>
-      <c r="C105" s="46"/>
+      <c r="C105" s="45"/>
     </row>
     <row r="106">
       <c r="B106" s="2"/>
-      <c r="C106" s="46"/>
+      <c r="C106" s="45"/>
     </row>
     <row r="107">
       <c r="B107" s="2"/>
-      <c r="C107" s="46"/>
+      <c r="C107" s="45"/>
     </row>
     <row r="108">
       <c r="B108" s="2"/>
-      <c r="C108" s="46"/>
+      <c r="C108" s="45"/>
     </row>
     <row r="109">
       <c r="B109" s="2"/>
-      <c r="C109" s="46"/>
+      <c r="C109" s="45"/>
     </row>
     <row r="110">
       <c r="B110" s="2"/>
-      <c r="C110" s="46"/>
+      <c r="C110" s="45"/>
     </row>
     <row r="111">
       <c r="B111" s="2"/>
-      <c r="C111" s="46"/>
+      <c r="C111" s="45"/>
     </row>
     <row r="112">
       <c r="B112" s="2"/>
-      <c r="C112" s="46"/>
+      <c r="C112" s="45"/>
     </row>
     <row r="113">
       <c r="B113" s="2"/>
-      <c r="C113" s="46"/>
+      <c r="C113" s="45"/>
     </row>
     <row r="114">
       <c r="B114" s="2"/>
-      <c r="C114" s="46"/>
+      <c r="C114" s="45"/>
     </row>
     <row r="115">
       <c r="B115" s="2"/>
-      <c r="C115" s="46"/>
+      <c r="C115" s="45"/>
     </row>
     <row r="116">
       <c r="B116" s="2"/>
-      <c r="C116" s="46"/>
+      <c r="C116" s="45"/>
     </row>
     <row r="117">
       <c r="B117" s="2"/>
-      <c r="C117" s="46"/>
+      <c r="C117" s="45"/>
     </row>
     <row r="118">
       <c r="B118" s="2"/>
-      <c r="C118" s="46"/>
+      <c r="C118" s="45"/>
     </row>
     <row r="119">
       <c r="B119" s="2"/>
-      <c r="C119" s="46"/>
+      <c r="C119" s="45"/>
     </row>
     <row r="120">
       <c r="B120" s="2"/>
-      <c r="C120" s="46"/>
+      <c r="C120" s="45"/>
     </row>
     <row r="121">
       <c r="B121" s="2"/>
-      <c r="C121" s="46"/>
+      <c r="C121" s="45"/>
     </row>
     <row r="122">
       <c r="B122" s="2"/>
-      <c r="C122" s="46"/>
+      <c r="C122" s="45"/>
     </row>
     <row r="123">
       <c r="B123" s="2"/>
-      <c r="C123" s="46"/>
+      <c r="C123" s="45"/>
     </row>
     <row r="124">
       <c r="B124" s="2"/>
-      <c r="C124" s="46"/>
+      <c r="C124" s="45"/>
     </row>
     <row r="125">
       <c r="B125" s="2"/>
-      <c r="C125" s="46"/>
+      <c r="C125" s="45"/>
     </row>
     <row r="126">
       <c r="B126" s="2"/>
-      <c r="C126" s="46"/>
+      <c r="C126" s="45"/>
     </row>
     <row r="127">
       <c r="B127" s="2"/>
-      <c r="C127" s="46"/>
+      <c r="C127" s="45"/>
     </row>
     <row r="128">
       <c r="B128" s="2"/>
-      <c r="C128" s="46"/>
+      <c r="C128" s="45"/>
     </row>
     <row r="129">
       <c r="B129" s="2"/>
-      <c r="C129" s="46"/>
+      <c r="C129" s="45"/>
     </row>
     <row r="130">
       <c r="B130" s="2"/>
-      <c r="C130" s="46"/>
+      <c r="C130" s="45"/>
     </row>
     <row r="131">
       <c r="B131" s="2"/>
-      <c r="C131" s="46"/>
+      <c r="C131" s="45"/>
     </row>
     <row r="132">
       <c r="B132" s="2"/>
-      <c r="C132" s="46"/>
+      <c r="C132" s="45"/>
     </row>
     <row r="133">
       <c r="B133" s="2"/>
-      <c r="C133" s="46"/>
+      <c r="C133" s="45"/>
     </row>
     <row r="134">
       <c r="B134" s="2"/>
-      <c r="C134" s="46"/>
+      <c r="C134" s="45"/>
     </row>
     <row r="135">
       <c r="B135" s="2"/>
-      <c r="C135" s="46"/>
+      <c r="C135" s="45"/>
     </row>
     <row r="136">
       <c r="B136" s="2"/>
-      <c r="C136" s="46"/>
+      <c r="C136" s="45"/>
     </row>
     <row r="137">
       <c r="B137" s="2"/>
-      <c r="C137" s="46"/>
+      <c r="C137" s="45"/>
     </row>
     <row r="138">
       <c r="B138" s="2"/>
-      <c r="C138" s="46"/>
+      <c r="C138" s="45"/>
     </row>
     <row r="139">
       <c r="B139" s="2"/>
-      <c r="C139" s="46"/>
+      <c r="C139" s="45"/>
     </row>
     <row r="140">
       <c r="B140" s="2"/>
-      <c r="C140" s="46"/>
+      <c r="C140" s="45"/>
     </row>
     <row r="141">
       <c r="B141" s="2"/>
-      <c r="C141" s="46"/>
+      <c r="C141" s="45"/>
     </row>
     <row r="142">
       <c r="B142" s="2"/>
-      <c r="C142" s="46"/>
+      <c r="C142" s="45"/>
     </row>
     <row r="143">
       <c r="B143" s="2"/>
-      <c r="C143" s="46"/>
+      <c r="C143" s="45"/>
     </row>
     <row r="144">
       <c r="B144" s="2"/>
-      <c r="C144" s="46"/>
+      <c r="C144" s="45"/>
     </row>
     <row r="145">
       <c r="B145" s="2"/>
-      <c r="C145" s="46"/>
+      <c r="C145" s="45"/>
     </row>
     <row r="146">
       <c r="B146" s="2"/>
-      <c r="C146" s="46"/>
+      <c r="C146" s="45"/>
     </row>
     <row r="147">
       <c r="B147" s="2"/>
-      <c r="C147" s="46"/>
+      <c r="C147" s="45"/>
     </row>
     <row r="148">
       <c r="B148" s="2"/>
-      <c r="C148" s="46"/>
+      <c r="C148" s="45"/>
     </row>
     <row r="149">
       <c r="B149" s="2"/>
-      <c r="C149" s="46"/>
+      <c r="C149" s="45"/>
     </row>
     <row r="150">
       <c r="B150" s="2"/>
-      <c r="C150" s="46"/>
+      <c r="C150" s="45"/>
     </row>
     <row r="151">
       <c r="B151" s="2"/>
-      <c r="C151" s="46"/>
+      <c r="C151" s="45"/>
     </row>
     <row r="152">
       <c r="B152" s="2"/>
-      <c r="C152" s="46"/>
+      <c r="C152" s="45"/>
     </row>
     <row r="153">
       <c r="B153" s="2"/>
-      <c r="C153" s="46"/>
+      <c r="C153" s="45"/>
     </row>
     <row r="154">
       <c r="B154" s="2"/>
-      <c r="C154" s="46"/>
+      <c r="C154" s="45"/>
     </row>
     <row r="155">
       <c r="B155" s="2"/>
-      <c r="C155" s="46"/>
+      <c r="C155" s="45"/>
     </row>
     <row r="156">
       <c r="B156" s="2"/>
-      <c r="C156" s="46"/>
+      <c r="C156" s="45"/>
     </row>
     <row r="157">
       <c r="B157" s="2"/>
-      <c r="C157" s="46"/>
+      <c r="C157" s="45"/>
     </row>
     <row r="158">
       <c r="B158" s="2"/>
-      <c r="C158" s="46"/>
+      <c r="C158" s="45"/>
     </row>
     <row r="159">
       <c r="B159" s="2"/>
-      <c r="C159" s="46"/>
+      <c r="C159" s="45"/>
     </row>
     <row r="160">
       <c r="B160" s="2"/>
-      <c r="C160" s="46"/>
+      <c r="C160" s="45"/>
     </row>
     <row r="161">
       <c r="B161" s="2"/>
-      <c r="C161" s="46"/>
+      <c r="C161" s="45"/>
     </row>
     <row r="162">
       <c r="B162" s="2"/>
-      <c r="C162" s="46"/>
+      <c r="C162" s="45"/>
     </row>
     <row r="163">
       <c r="B163" s="2"/>
-      <c r="C163" s="46"/>
+      <c r="C163" s="45"/>
     </row>
     <row r="164">
       <c r="B164" s="2"/>
-      <c r="C164" s="46"/>
+      <c r="C164" s="45"/>
     </row>
     <row r="165">
       <c r="B165" s="2"/>
-      <c r="C165" s="46"/>
+      <c r="C165" s="45"/>
     </row>
     <row r="166">
       <c r="B166" s="2"/>
-      <c r="C166" s="46"/>
+      <c r="C166" s="45"/>
     </row>
     <row r="167">
       <c r="B167" s="2"/>
-      <c r="C167" s="46"/>
+      <c r="C167" s="45"/>
     </row>
     <row r="168">
       <c r="B168" s="2"/>
-      <c r="C168" s="46"/>
+      <c r="C168" s="45"/>
     </row>
     <row r="169">
       <c r="B169" s="2"/>
-      <c r="C169" s="46"/>
+      <c r="C169" s="45"/>
     </row>
     <row r="170">
       <c r="B170" s="2"/>
-      <c r="C170" s="46"/>
+      <c r="C170" s="45"/>
     </row>
     <row r="171">
       <c r="B171" s="2"/>
-      <c r="C171" s="46"/>
+      <c r="C171" s="45"/>
     </row>
     <row r="172">
       <c r="B172" s="2"/>
-      <c r="C172" s="46"/>
+      <c r="C172" s="45"/>
     </row>
     <row r="173">
       <c r="B173" s="2"/>
-      <c r="C173" s="46"/>
+      <c r="C173" s="45"/>
     </row>
     <row r="174">
       <c r="B174" s="2"/>
-      <c r="C174" s="46"/>
+      <c r="C174" s="45"/>
     </row>
     <row r="175">
       <c r="B175" s="2"/>
-      <c r="C175" s="46"/>
+      <c r="C175" s="45"/>
     </row>
     <row r="176">
       <c r="B176" s="2"/>
-      <c r="C176" s="46"/>
+      <c r="C176" s="45"/>
     </row>
     <row r="177">
       <c r="B177" s="2"/>
-      <c r="C177" s="46"/>
+      <c r="C177" s="45"/>
     </row>
     <row r="178">
       <c r="B178" s="2"/>
-      <c r="C178" s="46"/>
+      <c r="C178" s="45"/>
     </row>
     <row r="179">
       <c r="B179" s="2"/>
-      <c r="C179" s="46"/>
+      <c r="C179" s="45"/>
     </row>
     <row r="180">
       <c r="B180" s="2"/>
-      <c r="C180" s="46"/>
+      <c r="C180" s="45"/>
     </row>
     <row r="181">
       <c r="B181" s="2"/>
-      <c r="C181" s="46"/>
+      <c r="C181" s="45"/>
     </row>
     <row r="182">
       <c r="B182" s="2"/>
-      <c r="C182" s="46"/>
+      <c r="C182" s="45"/>
     </row>
     <row r="183">
       <c r="B183" s="2"/>
-      <c r="C183" s="46"/>
+      <c r="C183" s="45"/>
     </row>
     <row r="184">
       <c r="B184" s="2"/>
-      <c r="C184" s="46"/>
+      <c r="C184" s="45"/>
     </row>
     <row r="185">
       <c r="B185" s="2"/>
-      <c r="C185" s="46"/>
+      <c r="C185" s="45"/>
     </row>
     <row r="186">
       <c r="B186" s="2"/>
-      <c r="C186" s="46"/>
+      <c r="C186" s="45"/>
     </row>
     <row r="187">
       <c r="B187" s="2"/>
-      <c r="C187" s="46"/>
+      <c r="C187" s="45"/>
     </row>
     <row r="188">
       <c r="B188" s="2"/>
-      <c r="C188" s="46"/>
+      <c r="C188" s="45"/>
     </row>
     <row r="189">
       <c r="B189" s="2"/>
-      <c r="C189" s="46"/>
+      <c r="C189" s="45"/>
     </row>
     <row r="190">
       <c r="B190" s="2"/>
-      <c r="C190" s="46"/>
+      <c r="C190" s="45"/>
     </row>
     <row r="191">
       <c r="B191" s="2"/>
-      <c r="C191" s="46"/>
+      <c r="C191" s="45"/>
     </row>
     <row r="192">
       <c r="B192" s="2"/>
-      <c r="C192" s="46"/>
+      <c r="C192" s="45"/>
     </row>
     <row r="193">
       <c r="B193" s="2"/>
-      <c r="C193" s="46"/>
+      <c r="C193" s="45"/>
     </row>
     <row r="194">
       <c r="B194" s="2"/>
-      <c r="C194" s="46"/>
+      <c r="C194" s="45"/>
     </row>
     <row r="195">
       <c r="B195" s="2"/>
-      <c r="C195" s="46"/>
+      <c r="C195" s="45"/>
     </row>
     <row r="196">
       <c r="B196" s="2"/>
-      <c r="C196" s="46"/>
+      <c r="C196" s="45"/>
     </row>
     <row r="197">
       <c r="B197" s="2"/>
-      <c r="C197" s="46"/>
+      <c r="C197" s="45"/>
     </row>
     <row r="198">
       <c r="B198" s="2"/>
-      <c r="C198" s="46"/>
+      <c r="C198" s="45"/>
     </row>
     <row r="199">
       <c r="B199" s="2"/>
-      <c r="C199" s="46"/>
+      <c r="C199" s="45"/>
     </row>
     <row r="200">
       <c r="B200" s="2"/>
-      <c r="C200" s="46"/>
+      <c r="C200" s="45"/>
     </row>
     <row r="201">
       <c r="B201" s="2"/>
-      <c r="C201" s="46"/>
+      <c r="C201" s="45"/>
     </row>
     <row r="202">
       <c r="B202" s="2"/>
-      <c r="C202" s="46"/>
+      <c r="C202" s="45"/>
     </row>
     <row r="203">
       <c r="B203" s="2"/>
-      <c r="C203" s="46"/>
+      <c r="C203" s="45"/>
     </row>
     <row r="204">
       <c r="B204" s="2"/>
-      <c r="C204" s="46"/>
+      <c r="C204" s="45"/>
     </row>
     <row r="205">
       <c r="B205" s="2"/>
-      <c r="C205" s="46"/>
+      <c r="C205" s="45"/>
     </row>
     <row r="206">
       <c r="B206" s="2"/>
-      <c r="C206" s="46"/>
+      <c r="C206" s="45"/>
     </row>
     <row r="207">
       <c r="B207" s="2"/>
-      <c r="C207" s="46"/>
+      <c r="C207" s="45"/>
     </row>
     <row r="208">
       <c r="B208" s="2"/>
-      <c r="C208" s="46"/>
+      <c r="C208" s="45"/>
     </row>
     <row r="209">
       <c r="B209" s="2"/>
-      <c r="C209" s="46"/>
+      <c r="C209" s="45"/>
     </row>
     <row r="210">
       <c r="B210" s="2"/>
-      <c r="C210" s="46"/>
+      <c r="C210" s="45"/>
     </row>
     <row r="211">
       <c r="B211" s="2"/>
-      <c r="C211" s="46"/>
+      <c r="C211" s="45"/>
     </row>
     <row r="212">
       <c r="B212" s="2"/>
-      <c r="C212" s="46"/>
+      <c r="C212" s="45"/>
     </row>
     <row r="213">
       <c r="B213" s="2"/>
-      <c r="C213" s="46"/>
+      <c r="C213" s="45"/>
     </row>
     <row r="214">
       <c r="B214" s="2"/>
-      <c r="C214" s="46"/>
+      <c r="C214" s="45"/>
     </row>
     <row r="215">
       <c r="B215" s="2"/>
-      <c r="C215" s="46"/>
+      <c r="C215" s="45"/>
     </row>
     <row r="216">
       <c r="B216" s="2"/>
-      <c r="C216" s="46"/>
+      <c r="C216" s="45"/>
     </row>
     <row r="217">
       <c r="B217" s="2"/>
-      <c r="C217" s="46"/>
+      <c r="C217" s="45"/>
     </row>
     <row r="218">
       <c r="B218" s="2"/>
-      <c r="C218" s="46"/>
+      <c r="C218" s="45"/>
     </row>
     <row r="219">
       <c r="B219" s="2"/>
-      <c r="C219" s="46"/>
+      <c r="C219" s="45"/>
     </row>
     <row r="220">
       <c r="B220" s="2"/>
-      <c r="C220" s="46"/>
+      <c r="C220" s="45"/>
     </row>
     <row r="221">
       <c r="B221" s="2"/>
-      <c r="C221" s="46"/>
+      <c r="C221" s="45"/>
     </row>
     <row r="222">
       <c r="B222" s="2"/>
-      <c r="C222" s="46"/>
+      <c r="C222" s="45"/>
     </row>
     <row r="223">
       <c r="B223" s="2"/>
-      <c r="C223" s="46"/>
+      <c r="C223" s="45"/>
     </row>
     <row r="224">
       <c r="B224" s="2"/>
-      <c r="C224" s="46"/>
+      <c r="C224" s="45"/>
     </row>
     <row r="225">
       <c r="B225" s="2"/>
-      <c r="C225" s="46"/>
+      <c r="C225" s="45"/>
     </row>
     <row r="226">
       <c r="B226" s="2"/>
-      <c r="C226" s="46"/>
+      <c r="C226" s="45"/>
     </row>
     <row r="227">
       <c r="B227" s="2"/>
-      <c r="C227" s="46"/>
+      <c r="C227" s="45"/>
     </row>
     <row r="228">
       <c r="B228" s="2"/>
-      <c r="C228" s="46"/>
+      <c r="C228" s="45"/>
     </row>
     <row r="229">
       <c r="B229" s="2"/>
-      <c r="C229" s="46"/>
+      <c r="C229" s="45"/>
     </row>
     <row r="230">
       <c r="B230" s="2"/>
-      <c r="C230" s="46"/>
+      <c r="C230" s="45"/>
     </row>
     <row r="231">
       <c r="B231" s="2"/>
-      <c r="C231" s="46"/>
+      <c r="C231" s="45"/>
     </row>
     <row r="232">
       <c r="B232" s="2"/>
-      <c r="C232" s="46"/>
+      <c r="C232" s="45"/>
     </row>
     <row r="233">
       <c r="B233" s="2"/>
-      <c r="C233" s="46"/>
+      <c r="C233" s="45"/>
     </row>
     <row r="234">
       <c r="B234" s="2"/>
-      <c r="C234" s="46"/>
+      <c r="C234" s="45"/>
     </row>
     <row r="235">
       <c r="B235" s="2"/>
-      <c r="C235" s="46"/>
+      <c r="C235" s="45"/>
     </row>
     <row r="236">
       <c r="B236" s="2"/>
-      <c r="C236" s="46"/>
+      <c r="C236" s="45"/>
     </row>
     <row r="237">
       <c r="B237" s="2"/>
-      <c r="C237" s="46"/>
+      <c r="C237" s="45"/>
     </row>
     <row r="238">
       <c r="B238" s="2"/>
-      <c r="C238" s="46"/>
+      <c r="C238" s="45"/>
     </row>
     <row r="239">
       <c r="B239" s="2"/>
-      <c r="C239" s="46"/>
+      <c r="C239" s="45"/>
     </row>
     <row r="240">
       <c r="B240" s="2"/>
-      <c r="C240" s="46"/>
+      <c r="C240" s="45"/>
     </row>
     <row r="241">
       <c r="B241" s="2"/>
-      <c r="C241" s="46"/>
+      <c r="C241" s="45"/>
     </row>
     <row r="242">
       <c r="B242" s="2"/>
-      <c r="C242" s="46"/>
+      <c r="C242" s="45"/>
     </row>
     <row r="243">
       <c r="B243" s="2"/>
-      <c r="C243" s="46"/>
+      <c r="C243" s="45"/>
     </row>
     <row r="244">
       <c r="B244" s="2"/>
-      <c r="C244" s="46"/>
+      <c r="C244" s="45"/>
     </row>
     <row r="245">
       <c r="B245" s="2"/>
-      <c r="C245" s="46"/>
+      <c r="C245" s="45"/>
     </row>
     <row r="246">
       <c r="B246" s="2"/>
-      <c r="C246" s="46"/>
+      <c r="C246" s="45"/>
     </row>
     <row r="247">
       <c r="B247" s="2"/>
-      <c r="C247" s="46"/>
+      <c r="C247" s="45"/>
     </row>
     <row r="248">
       <c r="B248" s="2"/>
-      <c r="C248" s="46"/>
+      <c r="C248" s="45"/>
     </row>
     <row r="249">
       <c r="B249" s="2"/>
-      <c r="C249" s="46"/>
+      <c r="C249" s="45"/>
     </row>
     <row r="250">
       <c r="B250" s="2"/>
-      <c r="C250" s="46"/>
+      <c r="C250" s="45"/>
     </row>
     <row r="251">
       <c r="B251" s="2"/>
-      <c r="C251" s="46"/>
+      <c r="C251" s="45"/>
     </row>
     <row r="252">
       <c r="B252" s="2"/>
-      <c r="C252" s="46"/>
+      <c r="C252" s="45"/>
     </row>
     <row r="253">
       <c r="B253" s="2"/>
-      <c r="C253" s="46"/>
+      <c r="C253" s="45"/>
     </row>
     <row r="254">
       <c r="B254" s="2"/>
-      <c r="C254" s="46"/>
+      <c r="C254" s="45"/>
     </row>
     <row r="255">
       <c r="B255" s="2"/>
-      <c r="C255" s="46"/>
+      <c r="C255" s="45"/>
     </row>
     <row r="256">
       <c r="B256" s="2"/>
-      <c r="C256" s="46"/>
+      <c r="C256" s="45"/>
     </row>
     <row r="257">
       <c r="B257" s="2"/>
-      <c r="C257" s="46"/>
+      <c r="C257" s="45"/>
     </row>
     <row r="258">
       <c r="B258" s="2"/>
-      <c r="C258" s="46"/>
+      <c r="C258" s="45"/>
     </row>
     <row r="259">
       <c r="B259" s="2"/>
-      <c r="C259" s="46"/>
+      <c r="C259" s="45"/>
     </row>
     <row r="260">
       <c r="B260" s="2"/>
-      <c r="C260" s="46"/>
+      <c r="C260" s="45"/>
     </row>
     <row r="261">
       <c r="B261" s="2"/>
-      <c r="C261" s="46"/>
+      <c r="C261" s="45"/>
     </row>
     <row r="262">
       <c r="B262" s="2"/>
-      <c r="C262" s="46"/>
+      <c r="C262" s="45"/>
     </row>
     <row r="263">
       <c r="B263" s="2"/>
-      <c r="C263" s="46"/>
+      <c r="C263" s="45"/>
     </row>
     <row r="264">
       <c r="B264" s="2"/>
-      <c r="C264" s="46"/>
+      <c r="C264" s="45"/>
     </row>
     <row r="265">
       <c r="B265" s="2"/>
-      <c r="C265" s="46"/>
+      <c r="C265" s="45"/>
     </row>
     <row r="266">
       <c r="B266" s="2"/>
-      <c r="C266" s="46"/>
+      <c r="C266" s="45"/>
     </row>
     <row r="267">
       <c r="B267" s="2"/>
-      <c r="C267" s="46"/>
+      <c r="C267" s="45"/>
     </row>
     <row r="268">
       <c r="B268" s="2"/>
-      <c r="C268" s="46"/>
+      <c r="C268" s="45"/>
     </row>
     <row r="269">
       <c r="B269" s="2"/>
-      <c r="C269" s="46"/>
+      <c r="C269" s="45"/>
     </row>
     <row r="270">
       <c r="B270" s="2"/>
-      <c r="C270" s="46"/>
+      <c r="C270" s="45"/>
     </row>
     <row r="271">
       <c r="B271" s="2"/>
-      <c r="C271" s="46"/>
+      <c r="C271" s="45"/>
     </row>
     <row r="272">
       <c r="B272" s="2"/>
-      <c r="C272" s="46"/>
+      <c r="C272" s="45"/>
     </row>
     <row r="273">
       <c r="B273" s="2"/>
-      <c r="C273" s="46"/>
+      <c r="C273" s="45"/>
     </row>
     <row r="274">
       <c r="B274" s="2"/>
-      <c r="C274" s="46"/>
+      <c r="C274" s="45"/>
     </row>
     <row r="275">
       <c r="B275" s="2"/>
-      <c r="C275" s="46"/>
+      <c r="C275" s="45"/>
     </row>
     <row r="276">
       <c r="B276" s="2"/>
-      <c r="C276" s="46"/>
+      <c r="C276" s="45"/>
     </row>
     <row r="277">
       <c r="B277" s="2"/>
-      <c r="C277" s="46"/>
+      <c r="C277" s="45"/>
     </row>
     <row r="278">
       <c r="B278" s="2"/>
-      <c r="C278" s="46"/>
+      <c r="C278" s="45"/>
     </row>
     <row r="279">
       <c r="B279" s="2"/>
-      <c r="C279" s="46"/>
+      <c r="C279" s="45"/>
     </row>
     <row r="280">
       <c r="B280" s="2"/>
-      <c r="C280" s="46"/>
+      <c r="C280" s="45"/>
     </row>
     <row r="281">
       <c r="B281" s="2"/>
-      <c r="C281" s="46"/>
+      <c r="C281" s="45"/>
     </row>
     <row r="282">
       <c r="B282" s="2"/>
-      <c r="C282" s="46"/>
+      <c r="C282" s="45"/>
     </row>
     <row r="283">
       <c r="B283" s="2"/>
-      <c r="C283" s="46"/>
+      <c r="C283" s="45"/>
     </row>
     <row r="284">
       <c r="B284" s="2"/>
-      <c r="C284" s="46"/>
+      <c r="C284" s="45"/>
     </row>
     <row r="285">
       <c r="B285" s="2"/>
-      <c r="C285" s="46"/>
+      <c r="C285" s="45"/>
     </row>
     <row r="286">
       <c r="B286" s="2"/>
-      <c r="C286" s="46"/>
+      <c r="C286" s="45"/>
     </row>
     <row r="287">
       <c r="B287" s="2"/>
-      <c r="C287" s="46"/>
+      <c r="C287" s="45"/>
     </row>
     <row r="288">
       <c r="B288" s="2"/>
-      <c r="C288" s="46"/>
+      <c r="C288" s="45"/>
     </row>
     <row r="289">
       <c r="B289" s="2"/>
-      <c r="C289" s="46"/>
+      <c r="C289" s="45"/>
     </row>
     <row r="290">
       <c r="B290" s="2"/>
-      <c r="C290" s="46"/>
+      <c r="C290" s="45"/>
     </row>
     <row r="291">
       <c r="B291" s="2"/>
-      <c r="C291" s="46"/>
+      <c r="C291" s="45"/>
     </row>
     <row r="292">
       <c r="B292" s="2"/>
-      <c r="C292" s="46"/>
+      <c r="C292" s="45"/>
     </row>
     <row r="293">
       <c r="B293" s="2"/>
-      <c r="C293" s="46"/>
+      <c r="C293" s="45"/>
     </row>
     <row r="294">
       <c r="B294" s="2"/>
-      <c r="C294" s="46"/>
+      <c r="C294" s="45"/>
     </row>
     <row r="295">
       <c r="B295" s="2"/>
-      <c r="C295" s="46"/>
+      <c r="C295" s="45"/>
     </row>
     <row r="296">
       <c r="B296" s="2"/>
-      <c r="C296" s="46"/>
+      <c r="C296" s="45"/>
     </row>
     <row r="297">
       <c r="B297" s="2"/>
-      <c r="C297" s="46"/>
+      <c r="C297" s="45"/>
     </row>
     <row r="298">
       <c r="B298" s="2"/>
-      <c r="C298" s="46"/>
+      <c r="C298" s="45"/>
     </row>
     <row r="299">
       <c r="B299" s="2"/>
-      <c r="C299" s="46"/>
+      <c r="C299" s="45"/>
     </row>
     <row r="300">
       <c r="B300" s="2"/>
-      <c r="C300" s="46"/>
+      <c r="C300" s="45"/>
     </row>
     <row r="301">
       <c r="B301" s="2"/>
-      <c r="C301" s="46"/>
+      <c r="C301" s="45"/>
     </row>
     <row r="302">
       <c r="B302" s="2"/>
-      <c r="C302" s="46"/>
+      <c r="C302" s="45"/>
     </row>
     <row r="303">
       <c r="B303" s="2"/>
-      <c r="C303" s="46"/>
+      <c r="C303" s="45"/>
     </row>
     <row r="304">
       <c r="B304" s="2"/>
-      <c r="C304" s="46"/>
+      <c r="C304" s="45"/>
     </row>
     <row r="305">
       <c r="B305" s="2"/>
-      <c r="C305" s="46"/>
+      <c r="C305" s="45"/>
     </row>
     <row r="306">
       <c r="B306" s="2"/>
-      <c r="C306" s="46"/>
+      <c r="C306" s="45"/>
     </row>
     <row r="307">
       <c r="B307" s="2"/>
-      <c r="C307" s="46"/>
+      <c r="C307" s="45"/>
     </row>
     <row r="308">
       <c r="B308" s="2"/>
-      <c r="C308" s="46"/>
+      <c r="C308" s="45"/>
     </row>
     <row r="309">
       <c r="B309" s="2"/>
-      <c r="C309" s="46"/>
+      <c r="C309" s="45"/>
     </row>
     <row r="310">
       <c r="B310" s="2"/>
-      <c r="C310" s="46"/>
+      <c r="C310" s="45"/>
     </row>
     <row r="311">
       <c r="B311" s="2"/>
-      <c r="C311" s="46"/>
+      <c r="C311" s="45"/>
     </row>
     <row r="312">
       <c r="B312" s="2"/>
-      <c r="C312" s="46"/>
+      <c r="C312" s="45"/>
     </row>
     <row r="313">
       <c r="B313" s="2"/>
-      <c r="C313" s="46"/>
+      <c r="C313" s="45"/>
     </row>
     <row r="314">
       <c r="B314" s="2"/>
-      <c r="C314" s="46"/>
+      <c r="C314" s="45"/>
     </row>
     <row r="315">
       <c r="B315" s="2"/>
-      <c r="C315" s="46"/>
+      <c r="C315" s="45"/>
     </row>
     <row r="316">
       <c r="B316" s="2"/>
-      <c r="C316" s="46"/>
+      <c r="C316" s="45"/>
     </row>
     <row r="317">
       <c r="B317" s="2"/>
-      <c r="C317" s="46"/>
+      <c r="C317" s="45"/>
     </row>
     <row r="318">
       <c r="B318" s="2"/>
-      <c r="C318" s="46"/>
+      <c r="C318" s="45"/>
     </row>
     <row r="319">
       <c r="B319" s="2"/>
-      <c r="C319" s="46"/>
+      <c r="C319" s="45"/>
     </row>
     <row r="320">
       <c r="B320" s="2"/>
-      <c r="C320" s="46"/>
+      <c r="C320" s="45"/>
     </row>
     <row r="321">
       <c r="B321" s="2"/>
-      <c r="C321" s="46"/>
+      <c r="C321" s="45"/>
     </row>
     <row r="322">
       <c r="B322" s="2"/>
-      <c r="C322" s="46"/>
+      <c r="C322" s="45"/>
     </row>
     <row r="323">
       <c r="B323" s="2"/>
-      <c r="C323" s="46"/>
+      <c r="C323" s="45"/>
     </row>
     <row r="324">
       <c r="B324" s="2"/>
-      <c r="C324" s="46"/>
+      <c r="C324" s="45"/>
     </row>
     <row r="325">
       <c r="B325" s="2"/>
-      <c r="C325" s="46"/>
+      <c r="C325" s="45"/>
     </row>
     <row r="326">
       <c r="B326" s="2"/>
-      <c r="C326" s="46"/>
+      <c r="C326" s="45"/>
     </row>
     <row r="327">
       <c r="B327" s="2"/>
-      <c r="C327" s="46"/>
+      <c r="C327" s="45"/>
     </row>
     <row r="328">
       <c r="B328" s="2"/>
-      <c r="C328" s="46"/>
+      <c r="C328" s="45"/>
     </row>
     <row r="329">
       <c r="B329" s="2"/>
-      <c r="C329" s="46"/>
+      <c r="C329" s="45"/>
     </row>
     <row r="330">
       <c r="B330" s="2"/>
-      <c r="C330" s="46"/>
+      <c r="C330" s="45"/>
     </row>
     <row r="331">
       <c r="B331" s="2"/>
-      <c r="C331" s="46"/>
+      <c r="C331" s="45"/>
     </row>
     <row r="332">
       <c r="B332" s="2"/>
-      <c r="C332" s="46"/>
+      <c r="C332" s="45"/>
     </row>
     <row r="333">
       <c r="B333" s="2"/>
-      <c r="C333" s="46"/>
+      <c r="C333" s="45"/>
     </row>
     <row r="334">
       <c r="B334" s="2"/>
-      <c r="C334" s="46"/>
+      <c r="C334" s="45"/>
     </row>
     <row r="335">
       <c r="B335" s="2"/>
-      <c r="C335" s="46"/>
+      <c r="C335" s="45"/>
     </row>
     <row r="336">
       <c r="B336" s="2"/>
-      <c r="C336" s="46"/>
+      <c r="C336" s="45"/>
     </row>
     <row r="337">
       <c r="B337" s="2"/>
-      <c r="C337" s="46"/>
+      <c r="C337" s="45"/>
     </row>
     <row r="338">
       <c r="B338" s="2"/>
-      <c r="C338" s="46"/>
+      <c r="C338" s="45"/>
     </row>
     <row r="339">
       <c r="B339" s="2"/>
-      <c r="C339" s="46"/>
+      <c r="C339" s="45"/>
     </row>
     <row r="340">
       <c r="B340" s="2"/>
-      <c r="C340" s="46"/>
+      <c r="C340" s="45"/>
     </row>
     <row r="341">
       <c r="B341" s="2"/>
-      <c r="C341" s="46"/>
+      <c r="C341" s="45"/>
     </row>
     <row r="342">
       <c r="B342" s="2"/>
-      <c r="C342" s="46"/>
+      <c r="C342" s="45"/>
     </row>
     <row r="343">
       <c r="B343" s="2"/>
-      <c r="C343" s="46"/>
+      <c r="C343" s="45"/>
     </row>
     <row r="344">
       <c r="B344" s="2"/>
-      <c r="C344" s="46"/>
+      <c r="C344" s="45"/>
     </row>
     <row r="345">
       <c r="B345" s="2"/>
-      <c r="C345" s="46"/>
+      <c r="C345" s="45"/>
     </row>
     <row r="346">
       <c r="B346" s="2"/>
-      <c r="C346" s="46"/>
+      <c r="C346" s="45"/>
     </row>
     <row r="347">
       <c r="B347" s="2"/>
-      <c r="C347" s="46"/>
+      <c r="C347" s="45"/>
     </row>
     <row r="348">
       <c r="B348" s="2"/>
-      <c r="C348" s="46"/>
+      <c r="C348" s="45"/>
     </row>
     <row r="349">
       <c r="B349" s="2"/>
-      <c r="C349" s="46"/>
+      <c r="C349" s="45"/>
     </row>
     <row r="350">
       <c r="B350" s="2"/>
-      <c r="C350" s="46"/>
+      <c r="C350" s="45"/>
     </row>
     <row r="351">
       <c r="B351" s="2"/>
-      <c r="C351" s="46"/>
+      <c r="C351" s="45"/>
     </row>
     <row r="352">
       <c r="B352" s="2"/>
-      <c r="C352" s="46"/>
+      <c r="C352" s="45"/>
     </row>
     <row r="353">
       <c r="B353" s="2"/>
-      <c r="C353" s="46"/>
+      <c r="C353" s="45"/>
     </row>
     <row r="354">
       <c r="B354" s="2"/>
-      <c r="C354" s="46"/>
+      <c r="C354" s="45"/>
     </row>
     <row r="355">
       <c r="B355" s="2"/>
-      <c r="C355" s="46"/>
+      <c r="C355" s="45"/>
     </row>
     <row r="356">
       <c r="B356" s="2"/>
-      <c r="C356" s="46"/>
+      <c r="C356" s="45"/>
     </row>
     <row r="357">
       <c r="B357" s="2"/>
-      <c r="C357" s="46"/>
+      <c r="C357" s="45"/>
     </row>
     <row r="358">
       <c r="B358" s="2"/>
-      <c r="C358" s="46"/>
+      <c r="C358" s="45"/>
     </row>
     <row r="359">
       <c r="B359" s="2"/>
-      <c r="C359" s="46"/>
+      <c r="C359" s="45"/>
     </row>
     <row r="360">
       <c r="B360" s="2"/>
-      <c r="C360" s="46"/>
+      <c r="C360" s="45"/>
     </row>
     <row r="361">
       <c r="B361" s="2"/>
-      <c r="C361" s="46"/>
+      <c r="C361" s="45"/>
     </row>
     <row r="362">
       <c r="B362" s="2"/>
-      <c r="C362" s="46"/>
+      <c r="C362" s="45"/>
     </row>
     <row r="363">
       <c r="B363" s="2"/>
-      <c r="C363" s="46"/>
+      <c r="C363" s="45"/>
     </row>
     <row r="364">
       <c r="B364" s="2"/>
-      <c r="C364" s="46"/>
+      <c r="C364" s="45"/>
     </row>
     <row r="365">
       <c r="B365" s="2"/>
-      <c r="C365" s="46"/>
+      <c r="C365" s="45"/>
     </row>
     <row r="366">
       <c r="B366" s="2"/>
-      <c r="C366" s="46"/>
+      <c r="C366" s="45"/>
     </row>
     <row r="367">
       <c r="B367" s="2"/>
-      <c r="C367" s="46"/>
+      <c r="C367" s="45"/>
     </row>
     <row r="368">
       <c r="B368" s="2"/>
-      <c r="C368" s="46"/>
+      <c r="C368" s="45"/>
     </row>
     <row r="369">
       <c r="B369" s="2"/>
-      <c r="C369" s="46"/>
+      <c r="C369" s="45"/>
     </row>
     <row r="370">
       <c r="B370" s="2"/>
-      <c r="C370" s="46"/>
+      <c r="C370" s="45"/>
     </row>
     <row r="371">
       <c r="B371" s="2"/>
-      <c r="C371" s="46"/>
+      <c r="C371" s="45"/>
     </row>
     <row r="372">
       <c r="B372" s="2"/>
-      <c r="C372" s="46"/>
+      <c r="C372" s="45"/>
     </row>
     <row r="373">
       <c r="B373" s="2"/>
-      <c r="C373" s="46"/>
+      <c r="C373" s="45"/>
     </row>
     <row r="374">
       <c r="B374" s="2"/>
-      <c r="C374" s="46"/>
+      <c r="C374" s="45"/>
     </row>
     <row r="375">
       <c r="B375" s="2"/>
-      <c r="C375" s="46"/>
+      <c r="C375" s="45"/>
     </row>
     <row r="376">
       <c r="B376" s="2"/>
-      <c r="C376" s="46"/>
+      <c r="C376" s="45"/>
     </row>
     <row r="377">
       <c r="B377" s="2"/>
-      <c r="C377" s="46"/>
+      <c r="C377" s="45"/>
     </row>
     <row r="378">
       <c r="B378" s="2"/>
-      <c r="C378" s="46"/>
+      <c r="C378" s="45"/>
     </row>
     <row r="379">
       <c r="B379" s="2"/>
-      <c r="C379" s="46"/>
+      <c r="C379" s="45"/>
     </row>
     <row r="380">
       <c r="B380" s="2"/>
-      <c r="C380" s="46"/>
+      <c r="C380" s="45"/>
     </row>
     <row r="381">
       <c r="B381" s="2"/>
-      <c r="C381" s="46"/>
+      <c r="C381" s="45"/>
     </row>
     <row r="382">
       <c r="B382" s="2"/>
-      <c r="C382" s="46"/>
+      <c r="C382" s="45"/>
     </row>
     <row r="383">
       <c r="B383" s="2"/>
-      <c r="C383" s="46"/>
+      <c r="C383" s="45"/>
     </row>
     <row r="384">
       <c r="B384" s="2"/>
-      <c r="C384" s="46"/>
+      <c r="C384" s="45"/>
     </row>
     <row r="385">
       <c r="B385" s="2"/>
-      <c r="C385" s="46"/>
+      <c r="C385" s="45"/>
     </row>
     <row r="386">
       <c r="B386" s="2"/>
-      <c r="C386" s="46"/>
+      <c r="C386" s="45"/>
     </row>
     <row r="387">
       <c r="B387" s="2"/>
-      <c r="C387" s="46"/>
+      <c r="C387" s="45"/>
     </row>
     <row r="388">
       <c r="B388" s="2"/>
-      <c r="C388" s="46"/>
+      <c r="C388" s="45"/>
     </row>
     <row r="389">
       <c r="B389" s="2"/>
-      <c r="C389" s="46"/>
+      <c r="C389" s="45"/>
     </row>
     <row r="390">
       <c r="B390" s="2"/>
-      <c r="C390" s="46"/>
+      <c r="C390" s="45"/>
     </row>
     <row r="391">
       <c r="B391" s="2"/>
-      <c r="C391" s="46"/>
+      <c r="C391" s="45"/>
     </row>
     <row r="392">
       <c r="B392" s="2"/>
-      <c r="C392" s="46"/>
+      <c r="C392" s="45"/>
     </row>
     <row r="393">
       <c r="B393" s="2"/>
-      <c r="C393" s="46"/>
+      <c r="C393" s="45"/>
     </row>
     <row r="394">
       <c r="B394" s="2"/>
-      <c r="C394" s="46"/>
+      <c r="C394" s="45"/>
     </row>
     <row r="395">
       <c r="B395" s="2"/>
-      <c r="C395" s="46"/>
+      <c r="C395" s="45"/>
     </row>
     <row r="396">
       <c r="B396" s="2"/>
-      <c r="C396" s="46"/>
+      <c r="C396" s="45"/>
     </row>
     <row r="397">
       <c r="B397" s="2"/>
-      <c r="C397" s="46"/>
+      <c r="C397" s="45"/>
     </row>
     <row r="398">
       <c r="B398" s="2"/>
-      <c r="C398" s="46"/>
+      <c r="C398" s="45"/>
     </row>
     <row r="399">
       <c r="B399" s="2"/>
-      <c r="C399" s="46"/>
+      <c r="C399" s="45"/>
     </row>
     <row r="400">
       <c r="B400" s="2"/>
-      <c r="C400" s="46"/>
+      <c r="C400" s="45"/>
     </row>
     <row r="401">
       <c r="B401" s="2"/>
-      <c r="C401" s="46"/>
+      <c r="C401" s="45"/>
     </row>
     <row r="402">
       <c r="B402" s="2"/>
-      <c r="C402" s="46"/>
+      <c r="C402" s="45"/>
     </row>
     <row r="403">
       <c r="B403" s="2"/>
-      <c r="C403" s="46"/>
+      <c r="C403" s="45"/>
     </row>
     <row r="404">
       <c r="B404" s="2"/>
-      <c r="C404" s="46"/>
+      <c r="C404" s="45"/>
     </row>
     <row r="405">
       <c r="B405" s="2"/>
-      <c r="C405" s="46"/>
+      <c r="C405" s="45"/>
     </row>
     <row r="406">
       <c r="B406" s="2"/>
-      <c r="C406" s="46"/>
+      <c r="C406" s="45"/>
     </row>
     <row r="407">
       <c r="B407" s="2"/>
-      <c r="C407" s="46"/>
+      <c r="C407" s="45"/>
     </row>
     <row r="408">
       <c r="B408" s="2"/>
-      <c r="C408" s="46"/>
+      <c r="C408" s="45"/>
     </row>
     <row r="409">
       <c r="B409" s="2"/>
-      <c r="C409" s="46"/>
+      <c r="C409" s="45"/>
     </row>
     <row r="410">
       <c r="B410" s="2"/>
-      <c r="C410" s="46"/>
+      <c r="C410" s="45"/>
     </row>
     <row r="411">
       <c r="B411" s="2"/>
-      <c r="C411" s="46"/>
+      <c r="C411" s="45"/>
     </row>
     <row r="412">
       <c r="B412" s="2"/>
-      <c r="C412" s="46"/>
+      <c r="C412" s="45"/>
     </row>
     <row r="413">
       <c r="B413" s="2"/>
-      <c r="C413" s="46"/>
+      <c r="C413" s="45"/>
     </row>
     <row r="414">
       <c r="B414" s="2"/>
-      <c r="C414" s="46"/>
+      <c r="C414" s="45"/>
     </row>
     <row r="415">
       <c r="B415" s="2"/>
-      <c r="C415" s="46"/>
+      <c r="C415" s="45"/>
     </row>
     <row r="416">
       <c r="B416" s="2"/>
-      <c r="C416" s="46"/>
+      <c r="C416" s="45"/>
     </row>
     <row r="417">
       <c r="B417" s="2"/>
-      <c r="C417" s="46"/>
+      <c r="C417" s="45"/>
     </row>
     <row r="418">
       <c r="B418" s="2"/>
-      <c r="C418" s="46"/>
+      <c r="C418" s="45"/>
     </row>
     <row r="419">
       <c r="B419" s="2"/>
-      <c r="C419" s="46"/>
+      <c r="C419" s="45"/>
     </row>
     <row r="420">
       <c r="B420" s="2"/>
-      <c r="C420" s="46"/>
+      <c r="C420" s="45"/>
     </row>
     <row r="421">
       <c r="B421" s="2"/>
-      <c r="C421" s="46"/>
+      <c r="C421" s="45"/>
     </row>
     <row r="422">
       <c r="B422" s="2"/>
-      <c r="C422" s="46"/>
+      <c r="C422" s="45"/>
     </row>
     <row r="423">
       <c r="B423" s="2"/>
-      <c r="C423" s="46"/>
+      <c r="C423" s="45"/>
     </row>
     <row r="424">
       <c r="B424" s="2"/>
-      <c r="C424" s="46"/>
+      <c r="C424" s="45"/>
     </row>
     <row r="425">
       <c r="B425" s="2"/>
-      <c r="C425" s="46"/>
+      <c r="C425" s="45"/>
     </row>
     <row r="426">
       <c r="B426" s="2"/>
-      <c r="C426" s="46"/>
+      <c r="C426" s="45"/>
     </row>
     <row r="427">
       <c r="B427" s="2"/>
-      <c r="C427" s="46"/>
+      <c r="C427" s="45"/>
     </row>
     <row r="428">
       <c r="B428" s="2"/>
-      <c r="C428" s="46"/>
+      <c r="C428" s="45"/>
     </row>
     <row r="429">
       <c r="B429" s="2"/>
-      <c r="C429" s="46"/>
+      <c r="C429" s="45"/>
     </row>
     <row r="430">
       <c r="B430" s="2"/>
-      <c r="C430" s="46"/>
+      <c r="C430" s="45"/>
     </row>
     <row r="431">
       <c r="B431" s="2"/>
-      <c r="C431" s="46"/>
+      <c r="C431" s="45"/>
     </row>
     <row r="432">
       <c r="B432" s="2"/>
-      <c r="C432" s="46"/>
+      <c r="C432" s="45"/>
     </row>
     <row r="433">
       <c r="B433" s="2"/>
-      <c r="C433" s="46"/>
+      <c r="C433" s="45"/>
     </row>
     <row r="434">
       <c r="B434" s="2"/>
-      <c r="C434" s="46"/>
+      <c r="C434" s="45"/>
     </row>
     <row r="435">
       <c r="B435" s="2"/>
-      <c r="C435" s="46"/>
+      <c r="C435" s="45"/>
     </row>
     <row r="436">
       <c r="B436" s="2"/>
-      <c r="C436" s="46"/>
+      <c r="C436" s="45"/>
     </row>
     <row r="437">
       <c r="B437" s="2"/>
-      <c r="C437" s="46"/>
+      <c r="C437" s="45"/>
     </row>
     <row r="438">
       <c r="B438" s="2"/>
-      <c r="C438" s="46"/>
+      <c r="C438" s="45"/>
     </row>
     <row r="439">
       <c r="B439" s="2"/>
-      <c r="C439" s="46"/>
+      <c r="C439" s="45"/>
     </row>
     <row r="440">
       <c r="B440" s="2"/>
-      <c r="C440" s="46"/>
+      <c r="C440" s="45"/>
     </row>
     <row r="441">
       <c r="B441" s="2"/>
-      <c r="C441" s="46"/>
+      <c r="C441" s="45"/>
     </row>
     <row r="442">
       <c r="B442" s="2"/>
-      <c r="C442" s="46"/>
+      <c r="C442" s="45"/>
     </row>
     <row r="443">
       <c r="B443" s="2"/>
-      <c r="C443" s="46"/>
+      <c r="C443" s="45"/>
     </row>
     <row r="444">
       <c r="B444" s="2"/>
-      <c r="C444" s="46"/>
+      <c r="C444" s="45"/>
     </row>
     <row r="445">
       <c r="B445" s="2"/>
-      <c r="C445" s="46"/>
+      <c r="C445" s="45"/>
     </row>
     <row r="446">
       <c r="B446" s="2"/>
-      <c r="C446" s="46"/>
+      <c r="C446" s="45"/>
     </row>
     <row r="447">
       <c r="B447" s="2"/>
-      <c r="C447" s="46"/>
+      <c r="C447" s="45"/>
     </row>
     <row r="448">
       <c r="B448" s="2"/>
-      <c r="C448" s="46"/>
+      <c r="C448" s="45"/>
     </row>
     <row r="449">
       <c r="B449" s="2"/>
-      <c r="C449" s="46"/>
+      <c r="C449" s="45"/>
     </row>
     <row r="450">
       <c r="B450" s="2"/>
-      <c r="C450" s="46"/>
+      <c r="C450" s="45"/>
     </row>
     <row r="451">
       <c r="B451" s="2"/>
-      <c r="C451" s="46"/>
+      <c r="C451" s="45"/>
     </row>
     <row r="452">
       <c r="B452" s="2"/>
-      <c r="C452" s="46"/>
+      <c r="C452" s="45"/>
     </row>
     <row r="453">
       <c r="B453" s="2"/>
-      <c r="C453" s="46"/>
+      <c r="C453" s="45"/>
     </row>
     <row r="454">
       <c r="B454" s="2"/>
-      <c r="C454" s="46"/>
+      <c r="C454" s="45"/>
     </row>
     <row r="455">
       <c r="B455" s="2"/>
-      <c r="C455" s="46"/>
+      <c r="C455" s="45"/>
     </row>
     <row r="456">
       <c r="B456" s="2"/>
-      <c r="C456" s="46"/>
+      <c r="C456" s="45"/>
     </row>
     <row r="457">
       <c r="B457" s="2"/>
-      <c r="C457" s="46"/>
+      <c r="C457" s="45"/>
     </row>
     <row r="458">
       <c r="B458" s="2"/>
-      <c r="C458" s="46"/>
+      <c r="C458" s="45"/>
     </row>
     <row r="459">
       <c r="B459" s="2"/>
-      <c r="C459" s="46"/>
+      <c r="C459" s="45"/>
     </row>
     <row r="460">
       <c r="B460" s="2"/>
-      <c r="C460" s="46"/>
+      <c r="C460" s="45"/>
     </row>
     <row r="461">
       <c r="B461" s="2"/>
-      <c r="C461" s="46"/>
+      <c r="C461" s="45"/>
     </row>
     <row r="462">
       <c r="B462" s="2"/>
-      <c r="C462" s="46"/>
+      <c r="C462" s="45"/>
     </row>
     <row r="463">
       <c r="B463" s="2"/>
-      <c r="C463" s="46"/>
+      <c r="C463" s="45"/>
     </row>
     <row r="464">
       <c r="B464" s="2"/>
-      <c r="C464" s="46"/>
+      <c r="C464" s="45"/>
     </row>
     <row r="465">
       <c r="B465" s="2"/>
-      <c r="C465" s="46"/>
+      <c r="C465" s="45"/>
     </row>
     <row r="466">
       <c r="B466" s="2"/>
-      <c r="C466" s="46"/>
+      <c r="C466" s="45"/>
     </row>
     <row r="467">
       <c r="B467" s="2"/>
-      <c r="C467" s="46"/>
+      <c r="C467" s="45"/>
     </row>
     <row r="468">
       <c r="B468" s="2"/>
-      <c r="C468" s="46"/>
+      <c r="C468" s="45"/>
     </row>
     <row r="469">
       <c r="B469" s="2"/>
-      <c r="C469" s="46"/>
+      <c r="C469" s="45"/>
     </row>
     <row r="470">
       <c r="B470" s="2"/>
-      <c r="C470" s="46"/>
+      <c r="C470" s="45"/>
     </row>
     <row r="471">
       <c r="B471" s="2"/>
-      <c r="C471" s="46"/>
+      <c r="C471" s="45"/>
     </row>
     <row r="472">
       <c r="B472" s="2"/>
-      <c r="C472" s="46"/>
+      <c r="C472" s="45"/>
     </row>
     <row r="473">
       <c r="B473" s="2"/>
-      <c r="C473" s="46"/>
+      <c r="C473" s="45"/>
     </row>
     <row r="474">
       <c r="B474" s="2"/>
-      <c r="C474" s="46"/>
+      <c r="C474" s="45"/>
     </row>
     <row r="475">
       <c r="B475" s="2"/>
-      <c r="C475" s="46"/>
+      <c r="C475" s="45"/>
     </row>
     <row r="476">
       <c r="B476" s="2"/>
-      <c r="C476" s="46"/>
+      <c r="C476" s="45"/>
     </row>
     <row r="477">
       <c r="B477" s="2"/>
-      <c r="C477" s="46"/>
+      <c r="C477" s="45"/>
     </row>
     <row r="478">
       <c r="B478" s="2"/>
-      <c r="C478" s="46"/>
+      <c r="C478" s="45"/>
     </row>
     <row r="479">
       <c r="B479" s="2"/>
-      <c r="C479" s="46"/>
+      <c r="C479" s="45"/>
     </row>
     <row r="480">
       <c r="B480" s="2"/>
-      <c r="C480" s="46"/>
+      <c r="C480" s="45"/>
     </row>
     <row r="481">
       <c r="B481" s="2"/>
-      <c r="C481" s="46"/>
+      <c r="C481" s="45"/>
     </row>
     <row r="482">
       <c r="B482" s="2"/>
-      <c r="C482" s="46"/>
+      <c r="C482" s="45"/>
     </row>
     <row r="483">
       <c r="B483" s="2"/>
-      <c r="C483" s="46"/>
+      <c r="C483" s="45"/>
     </row>
     <row r="484">
       <c r="B484" s="2"/>
-      <c r="C484" s="46"/>
+      <c r="C484" s="45"/>
     </row>
     <row r="485">
       <c r="B485" s="2"/>
-      <c r="C485" s="46"/>
+      <c r="C485" s="45"/>
     </row>
     <row r="486">
       <c r="B486" s="2"/>
-      <c r="C486" s="46"/>
+      <c r="C486" s="45"/>
     </row>
     <row r="487">
       <c r="B487" s="2"/>
-      <c r="C487" s="46"/>
+      <c r="C487" s="45"/>
     </row>
     <row r="488">
       <c r="B488" s="2"/>
-      <c r="C488" s="46"/>
+      <c r="C488" s="45"/>
     </row>
     <row r="489">
       <c r="B489" s="2"/>
-      <c r="C489" s="46"/>
+      <c r="C489" s="45"/>
     </row>
     <row r="490">
       <c r="B490" s="2"/>
-      <c r="C490" s="46"/>
+      <c r="C490" s="45"/>
     </row>
     <row r="491">
       <c r="B491" s="2"/>
-      <c r="C491" s="46"/>
+      <c r="C491" s="45"/>
     </row>
     <row r="492">
       <c r="B492" s="2"/>
-      <c r="C492" s="46"/>
+      <c r="C492" s="45"/>
     </row>
     <row r="493">
       <c r="B493" s="2"/>
-      <c r="C493" s="46"/>
+      <c r="C493" s="45"/>
     </row>
     <row r="494">
       <c r="B494" s="2"/>
-      <c r="C494" s="46"/>
+      <c r="C494" s="45"/>
     </row>
     <row r="495">
       <c r="B495" s="2"/>
-      <c r="C495" s="46"/>
+      <c r="C495" s="45"/>
     </row>
     <row r="496">
       <c r="B496" s="2"/>
-      <c r="C496" s="46"/>
+      <c r="C496" s="45"/>
     </row>
     <row r="497">
       <c r="B497" s="2"/>
-      <c r="C497" s="46"/>
+      <c r="C497" s="45"/>
     </row>
     <row r="498">
       <c r="B498" s="2"/>
-      <c r="C498" s="46"/>
+      <c r="C498" s="45"/>
     </row>
     <row r="499">
       <c r="B499" s="2"/>
-      <c r="C499" s="46"/>
+      <c r="C499" s="45"/>
     </row>
     <row r="500">
       <c r="B500" s="2"/>
-      <c r="C500" s="46"/>
+      <c r="C500" s="45"/>
     </row>
     <row r="501">
       <c r="B501" s="2"/>
-      <c r="C501" s="46"/>
+      <c r="C501" s="45"/>
     </row>
     <row r="502">
       <c r="B502" s="2"/>
-      <c r="C502" s="46"/>
+      <c r="C502" s="45"/>
     </row>
     <row r="503">
       <c r="B503" s="2"/>
-      <c r="C503" s="46"/>
+      <c r="C503" s="45"/>
     </row>
     <row r="504">
       <c r="B504" s="2"/>
-      <c r="C504" s="46"/>
+      <c r="C504" s="45"/>
     </row>
     <row r="505">
       <c r="B505" s="2"/>
-      <c r="C505" s="46"/>
+      <c r="C505" s="45"/>
     </row>
     <row r="506">
       <c r="B506" s="2"/>
-      <c r="C506" s="46"/>
+      <c r="C506" s="45"/>
     </row>
     <row r="507">
       <c r="B507" s="2"/>
-      <c r="C507" s="46"/>
+      <c r="C507" s="45"/>
     </row>
     <row r="508">
       <c r="B508" s="2"/>
-      <c r="C508" s="46"/>
+      <c r="C508" s="45"/>
     </row>
     <row r="509">
       <c r="B509" s="2"/>
-      <c r="C509" s="46"/>
+      <c r="C509" s="45"/>
     </row>
     <row r="510">
       <c r="B510" s="2"/>
-      <c r="C510" s="46"/>
+      <c r="C510" s="45"/>
     </row>
     <row r="511">
       <c r="B511" s="2"/>
-      <c r="C511" s="46"/>
+      <c r="C511" s="45"/>
     </row>
     <row r="512">
       <c r="B512" s="2"/>
-      <c r="C512" s="46"/>
+      <c r="C512" s="45"/>
     </row>
     <row r="513">
       <c r="B513" s="2"/>
-      <c r="C513" s="46"/>
+      <c r="C513" s="45"/>
     </row>
     <row r="514">
       <c r="B514" s="2"/>
-      <c r="C514" s="46"/>
+      <c r="C514" s="45"/>
     </row>
     <row r="515">
       <c r="B515" s="2"/>
-      <c r="C515" s="46"/>
+      <c r="C515" s="45"/>
     </row>
     <row r="516">
       <c r="B516" s="2"/>
-      <c r="C516" s="46"/>
+      <c r="C516" s="45"/>
     </row>
     <row r="517">
       <c r="B517" s="2"/>
-      <c r="C517" s="46"/>
+      <c r="C517" s="45"/>
     </row>
     <row r="518">
       <c r="B518" s="2"/>
-      <c r="C518" s="46"/>
+      <c r="C518" s="45"/>
     </row>
     <row r="519">
       <c r="B519" s="2"/>
-      <c r="C519" s="46"/>
+      <c r="C519" s="45"/>
     </row>
     <row r="520">
       <c r="B520" s="2"/>
-      <c r="C520" s="46"/>
+      <c r="C520" s="45"/>
     </row>
     <row r="521">
       <c r="B521" s="2"/>
-      <c r="C521" s="46"/>
+      <c r="C521" s="45"/>
     </row>
     <row r="522">
       <c r="B522" s="2"/>
-      <c r="C522" s="46"/>
+      <c r="C522" s="45"/>
     </row>
     <row r="523">
       <c r="B523" s="2"/>
-      <c r="C523" s="46"/>
+      <c r="C523" s="45"/>
     </row>
     <row r="524">
       <c r="B524" s="2"/>
-      <c r="C524" s="46"/>
+      <c r="C524" s="45"/>
     </row>
     <row r="525">
       <c r="B525" s="2"/>
-      <c r="C525" s="46"/>
+      <c r="C525" s="45"/>
     </row>
     <row r="526">
       <c r="B526" s="2"/>
-      <c r="C526" s="46"/>
+      <c r="C526" s="45"/>
     </row>
     <row r="527">
       <c r="B527" s="2"/>
-      <c r="C527" s="46"/>
+      <c r="C527" s="45"/>
     </row>
     <row r="528">
       <c r="B528" s="2"/>
-      <c r="C528" s="46"/>
+      <c r="C528" s="45"/>
     </row>
     <row r="529">
       <c r="B529" s="2"/>
-      <c r="C529" s="46"/>
+      <c r="C529" s="45"/>
     </row>
     <row r="530">
       <c r="B530" s="2"/>
-      <c r="C530" s="46"/>
+      <c r="C530" s="45"/>
     </row>
     <row r="531">
       <c r="B531" s="2"/>
-      <c r="C531" s="46"/>
+      <c r="C531" s="45"/>
     </row>
     <row r="532">
       <c r="B532" s="2"/>
-      <c r="C532" s="46"/>
+      <c r="C532" s="45"/>
     </row>
     <row r="533">
       <c r="B533" s="2"/>
-      <c r="C533" s="46"/>
+      <c r="C533" s="45"/>
     </row>
     <row r="534">
       <c r="B534" s="2"/>
-      <c r="C534" s="46"/>
+      <c r="C534" s="45"/>
     </row>
     <row r="535">
       <c r="B535" s="2"/>
-      <c r="C535" s="46"/>
+      <c r="C535" s="45"/>
     </row>
     <row r="536">
       <c r="B536" s="2"/>
-      <c r="C536" s="46"/>
+      <c r="C536" s="45"/>
     </row>
     <row r="537">
       <c r="B537" s="2"/>
-      <c r="C537" s="46"/>
+      <c r="C537" s="45"/>
     </row>
     <row r="538">
       <c r="B538" s="2"/>
-      <c r="C538" s="46"/>
+      <c r="C538" s="45"/>
     </row>
     <row r="539">
       <c r="B539" s="2"/>
-      <c r="C539" s="46"/>
+      <c r="C539" s="45"/>
     </row>
     <row r="540">
       <c r="B540" s="2"/>
-      <c r="C540" s="46"/>
+      <c r="C540" s="45"/>
     </row>
     <row r="541">
       <c r="B541" s="2"/>
-      <c r="C541" s="46"/>
+      <c r="C541" s="45"/>
     </row>
     <row r="542">
       <c r="B542" s="2"/>
-      <c r="C542" s="46"/>
+      <c r="C542" s="45"/>
     </row>
     <row r="543">
       <c r="B543" s="2"/>
-      <c r="C543" s="46"/>
+      <c r="C543" s="45"/>
     </row>
     <row r="544">
       <c r="B544" s="2"/>
-      <c r="C544" s="46"/>
+      <c r="C544" s="45"/>
     </row>
     <row r="545">
       <c r="B545" s="2"/>
-      <c r="C545" s="46"/>
+      <c r="C545" s="45"/>
     </row>
     <row r="546">
       <c r="B546" s="2"/>
-      <c r="C546" s="46"/>
+      <c r="C546" s="45"/>
     </row>
     <row r="547">
       <c r="B547" s="2"/>
-      <c r="C547" s="46"/>
+      <c r="C547" s="45"/>
     </row>
     <row r="548">
       <c r="B548" s="2"/>
-      <c r="C548" s="46"/>
+      <c r="C548" s="45"/>
     </row>
     <row r="549">
       <c r="B549" s="2"/>
-      <c r="C549" s="46"/>
+      <c r="C549" s="45"/>
     </row>
     <row r="550">
       <c r="B550" s="2"/>
-      <c r="C550" s="46"/>
+      <c r="C550" s="45"/>
     </row>
     <row r="551">
       <c r="B551" s="2"/>
-      <c r="C551" s="46"/>
+      <c r="C551" s="45"/>
     </row>
     <row r="552">
       <c r="B552" s="2"/>
-      <c r="C552" s="46"/>
+      <c r="C552" s="45"/>
     </row>
     <row r="553">
       <c r="B553" s="2"/>
-      <c r="C553" s="46"/>
+      <c r="C553" s="45"/>
     </row>
     <row r="554">
       <c r="B554" s="2"/>
-      <c r="C554" s="46"/>
+      <c r="C554" s="45"/>
     </row>
     <row r="555">
       <c r="B555" s="2"/>
-      <c r="C555" s="46"/>
+      <c r="C555" s="45"/>
     </row>
     <row r="556">
       <c r="B556" s="2"/>
-      <c r="C556" s="46"/>
+      <c r="C556" s="45"/>
     </row>
     <row r="557">
       <c r="B557" s="2"/>
-      <c r="C557" s="46"/>
+      <c r="C557" s="45"/>
     </row>
     <row r="558">
       <c r="B558" s="2"/>
-      <c r="C558" s="46"/>
+      <c r="C558" s="45"/>
     </row>
     <row r="559">
       <c r="B559" s="2"/>
-      <c r="C559" s="46"/>
+      <c r="C559" s="45"/>
     </row>
     <row r="560">
       <c r="B560" s="2"/>
-      <c r="C560" s="46"/>
+      <c r="C560" s="45"/>
     </row>
     <row r="561">
       <c r="B561" s="2"/>
-      <c r="C561" s="46"/>
+      <c r="C561" s="45"/>
     </row>
     <row r="562">
       <c r="B562" s="2"/>
-      <c r="C562" s="46"/>
+      <c r="C562" s="45"/>
     </row>
     <row r="563">
       <c r="B563" s="2"/>
-      <c r="C563" s="46"/>
+      <c r="C563" s="45"/>
     </row>
     <row r="564">
       <c r="B564" s="2"/>
-      <c r="C564" s="46"/>
+      <c r="C564" s="45"/>
     </row>
     <row r="565">
       <c r="B565" s="2"/>
-      <c r="C565" s="46"/>
+      <c r="C565" s="45"/>
     </row>
     <row r="566">
       <c r="B566" s="2"/>
-      <c r="C566" s="46"/>
+      <c r="C566" s="45"/>
     </row>
     <row r="567">
       <c r="B567" s="2"/>
-      <c r="C567" s="46"/>
+      <c r="C567" s="45"/>
     </row>
     <row r="568">
       <c r="B568" s="2"/>
-      <c r="C568" s="46"/>
+      <c r="C568" s="45"/>
     </row>
     <row r="569">
       <c r="B569" s="2"/>
-      <c r="C569" s="46"/>
+      <c r="C569" s="45"/>
     </row>
     <row r="570">
       <c r="B570" s="2"/>
-      <c r="C570" s="46"/>
+      <c r="C570" s="45"/>
     </row>
     <row r="571">
       <c r="B571" s="2"/>
-      <c r="C571" s="46"/>
+      <c r="C571" s="45"/>
     </row>
     <row r="572">
       <c r="B572" s="2"/>
-      <c r="C572" s="46"/>
+      <c r="C572" s="45"/>
     </row>
     <row r="573">
       <c r="B573" s="2"/>
-      <c r="C573" s="46"/>
+      <c r="C573" s="45"/>
     </row>
     <row r="574">
       <c r="B574" s="2"/>
-      <c r="C574" s="46"/>
+      <c r="C574" s="45"/>
     </row>
     <row r="575">
       <c r="B575" s="2"/>
-      <c r="C575" s="46"/>
+      <c r="C575" s="45"/>
     </row>
     <row r="576">
       <c r="B576" s="2"/>
-      <c r="C576" s="46"/>
+      <c r="C576" s="45"/>
     </row>
     <row r="577">
       <c r="B577" s="2"/>
-      <c r="C577" s="46"/>
+      <c r="C577" s="45"/>
     </row>
     <row r="578">
       <c r="B578" s="2"/>
-      <c r="C578" s="46"/>
+      <c r="C578" s="45"/>
     </row>
     <row r="579">
       <c r="B579" s="2"/>
-      <c r="C579" s="46"/>
+      <c r="C579" s="45"/>
     </row>
     <row r="580">
       <c r="B580" s="2"/>
-      <c r="C580" s="46"/>
+      <c r="C580" s="45"/>
     </row>
     <row r="581">
       <c r="B581" s="2"/>
-      <c r="C581" s="46"/>
+      <c r="C581" s="45"/>
     </row>
     <row r="582">
       <c r="B582" s="2"/>
-      <c r="C582" s="46"/>
+      <c r="C582" s="45"/>
     </row>
     <row r="583">
       <c r="B583" s="2"/>
-      <c r="C583" s="46"/>
+      <c r="C583" s="45"/>
     </row>
     <row r="584">
       <c r="B584" s="2"/>
-      <c r="C584" s="46"/>
+      <c r="C584" s="45"/>
     </row>
     <row r="585">
       <c r="B585" s="2"/>
-      <c r="C585" s="46"/>
+      <c r="C585" s="45"/>
     </row>
     <row r="586">
       <c r="B586" s="2"/>
-      <c r="C586" s="46"/>
+      <c r="C586" s="45"/>
     </row>
     <row r="587">
       <c r="B587" s="2"/>
-      <c r="C587" s="46"/>
+      <c r="C587" s="45"/>
     </row>
     <row r="588">
       <c r="B588" s="2"/>
-      <c r="C588" s="46"/>
+      <c r="C588" s="45"/>
     </row>
     <row r="589">
       <c r="B589" s="2"/>
-      <c r="C589" s="46"/>
+      <c r="C589" s="45"/>
     </row>
     <row r="590">
       <c r="B590" s="2"/>
-      <c r="C590" s="46"/>
+      <c r="C590" s="45"/>
     </row>
     <row r="591">
       <c r="B591" s="2"/>
-      <c r="C591" s="46"/>
+      <c r="C591" s="45"/>
     </row>
     <row r="592">
       <c r="B592" s="2"/>
-      <c r="C592" s="46"/>
+      <c r="C592" s="45"/>
     </row>
     <row r="593">
       <c r="B593" s="2"/>
-      <c r="C593" s="46"/>
+      <c r="C593" s="45"/>
     </row>
     <row r="594">
       <c r="B594" s="2"/>
-      <c r="C594" s="46"/>
+      <c r="C594" s="45"/>
     </row>
     <row r="595">
       <c r="B595" s="2"/>
-      <c r="C595" s="46"/>
+      <c r="C595" s="45"/>
     </row>
     <row r="596">
       <c r="B596" s="2"/>
-      <c r="C596" s="46"/>
+      <c r="C596" s="45"/>
     </row>
     <row r="597">
       <c r="B597" s="2"/>
-      <c r="C597" s="46"/>
+      <c r="C597" s="45"/>
     </row>
     <row r="598">
       <c r="B598" s="2"/>
-      <c r="C598" s="46"/>
+      <c r="C598" s="45"/>
     </row>
     <row r="599">
       <c r="B599" s="2"/>
-      <c r="C599" s="46"/>
+      <c r="C599" s="45"/>
     </row>
     <row r="600">
       <c r="B600" s="2"/>
-      <c r="C600" s="46"/>
+      <c r="C600" s="45"/>
     </row>
     <row r="601">
       <c r="B601" s="2"/>
-      <c r="C601" s="46"/>
+      <c r="C601" s="45"/>
     </row>
     <row r="602">
       <c r="B602" s="2"/>
-      <c r="C602" s="46"/>
+      <c r="C602" s="45"/>
     </row>
     <row r="603">
       <c r="B603" s="2"/>
-      <c r="C603" s="46"/>
+      <c r="C603" s="45"/>
     </row>
     <row r="604">
       <c r="B604" s="2"/>
-      <c r="C604" s="46"/>
+      <c r="C604" s="45"/>
     </row>
     <row r="605">
       <c r="B605" s="2"/>
-      <c r="C605" s="46"/>
+      <c r="C605" s="45"/>
     </row>
     <row r="606">
       <c r="B606" s="2"/>
-      <c r="C606" s="46"/>
+      <c r="C606" s="45"/>
     </row>
     <row r="607">
       <c r="B607" s="2"/>
-      <c r="C607" s="46"/>
+      <c r="C607" s="45"/>
     </row>
     <row r="608">
       <c r="B608" s="2"/>
-      <c r="C608" s="46"/>
+      <c r="C608" s="45"/>
     </row>
     <row r="609">
       <c r="B609" s="2"/>
-      <c r="C609" s="46"/>
+      <c r="C609" s="45"/>
     </row>
     <row r="610">
       <c r="B610" s="2"/>
-      <c r="C610" s="46"/>
+      <c r="C610" s="45"/>
     </row>
     <row r="611">
       <c r="B611" s="2"/>
-      <c r="C611" s="46"/>
+      <c r="C611" s="45"/>
     </row>
     <row r="612">
       <c r="B612" s="2"/>
-      <c r="C612" s="46"/>
+      <c r="C612" s="45"/>
     </row>
     <row r="613">
       <c r="B613" s="2"/>
-      <c r="C613" s="46"/>
+      <c r="C613" s="45"/>
     </row>
     <row r="614">
       <c r="B614" s="2"/>
-      <c r="C614" s="46"/>
+      <c r="C614" s="45"/>
     </row>
     <row r="615">
       <c r="B615" s="2"/>
-      <c r="C615" s="46"/>
+      <c r="C615" s="45"/>
     </row>
     <row r="616">
       <c r="B616" s="2"/>
-      <c r="C616" s="46"/>
+      <c r="C616" s="45"/>
     </row>
     <row r="617">
       <c r="B617" s="2"/>
-      <c r="C617" s="46"/>
+      <c r="C617" s="45"/>
     </row>
     <row r="618">
       <c r="B618" s="2"/>
-      <c r="C618" s="46"/>
+      <c r="C618" s="45"/>
     </row>
     <row r="619">
       <c r="B619" s="2"/>
-      <c r="C619" s="46"/>
+      <c r="C619" s="45"/>
     </row>
     <row r="620">
       <c r="B620" s="2"/>
-      <c r="C620" s="46"/>
+      <c r="C620" s="45"/>
     </row>
     <row r="621">
       <c r="B621" s="2"/>
-      <c r="C621" s="46"/>
+      <c r="C621" s="45"/>
     </row>
     <row r="622">
       <c r="B622" s="2"/>
-      <c r="C622" s="46"/>
+      <c r="C622" s="45"/>
     </row>
     <row r="623">
       <c r="B623" s="2"/>
-      <c r="C623" s="46"/>
+      <c r="C623" s="45"/>
     </row>
     <row r="624">
       <c r="B624" s="2"/>
-      <c r="C624" s="46"/>
+      <c r="C624" s="45"/>
     </row>
     <row r="625">
       <c r="B625" s="2"/>
-      <c r="C625" s="46"/>
+      <c r="C625" s="45"/>
     </row>
     <row r="626">
       <c r="B626" s="2"/>
-      <c r="C626" s="46"/>
+      <c r="C626" s="45"/>
     </row>
     <row r="627">
       <c r="B627" s="2"/>
-      <c r="C627" s="46"/>
+      <c r="C627" s="45"/>
     </row>
     <row r="628">
       <c r="B628" s="2"/>
-      <c r="C628" s="46"/>
+      <c r="C628" s="45"/>
     </row>
     <row r="629">
       <c r="B629" s="2"/>
-      <c r="C629" s="46"/>
+      <c r="C629" s="45"/>
     </row>
     <row r="630">
       <c r="B630" s="2"/>
-      <c r="C630" s="46"/>
+      <c r="C630" s="45"/>
     </row>
     <row r="631">
       <c r="B631" s="2"/>
-      <c r="C631" s="46"/>
+      <c r="C631" s="45"/>
     </row>
     <row r="632">
       <c r="B632" s="2"/>
-      <c r="C632" s="46"/>
+      <c r="C632" s="45"/>
     </row>
     <row r="633">
       <c r="B633" s="2"/>
-      <c r="C633" s="46"/>
+      <c r="C633" s="45"/>
     </row>
     <row r="634">
       <c r="B634" s="2"/>
-      <c r="C634" s="46"/>
+      <c r="C634" s="45"/>
     </row>
     <row r="635">
       <c r="B635" s="2"/>
-      <c r="C635" s="46"/>
+      <c r="C635" s="45"/>
     </row>
     <row r="636">
       <c r="B636" s="2"/>
-      <c r="C636" s="46"/>
+      <c r="C636" s="45"/>
     </row>
     <row r="637">
       <c r="B637" s="2"/>
-      <c r="C637" s="46"/>
+      <c r="C637" s="45"/>
     </row>
     <row r="638">
       <c r="B638" s="2"/>
-      <c r="C638" s="46"/>
+      <c r="C638" s="45"/>
     </row>
     <row r="639">
       <c r="B639" s="2"/>
-      <c r="C639" s="46"/>
+      <c r="C639" s="45"/>
     </row>
     <row r="640">
       <c r="B640" s="2"/>
-      <c r="C640" s="46"/>
+      <c r="C640" s="45"/>
     </row>
     <row r="641">
       <c r="B641" s="2"/>
-      <c r="C641" s="46"/>
+      <c r="C641" s="45"/>
     </row>
     <row r="642">
       <c r="B642" s="2"/>
-      <c r="C642" s="46"/>
+      <c r="C642" s="45"/>
     </row>
     <row r="643">
       <c r="B643" s="2"/>
-      <c r="C643" s="46"/>
+      <c r="C643" s="45"/>
     </row>
     <row r="644">
       <c r="B644" s="2"/>
-      <c r="C644" s="46"/>
+      <c r="C644" s="45"/>
     </row>
     <row r="645">
       <c r="B645" s="2"/>
-      <c r="C645" s="46"/>
+      <c r="C645" s="45"/>
     </row>
     <row r="646">
       <c r="B646" s="2"/>
-      <c r="C646" s="46"/>
+      <c r="C646" s="45"/>
     </row>
     <row r="647">
       <c r="B647" s="2"/>
-      <c r="C647" s="46"/>
+      <c r="C647" s="45"/>
     </row>
     <row r="648">
       <c r="B648" s="2"/>
-      <c r="C648" s="46"/>
+      <c r="C648" s="45"/>
     </row>
     <row r="649">
       <c r="B649" s="2"/>
-      <c r="C649" s="46"/>
+      <c r="C649" s="45"/>
     </row>
     <row r="650">
       <c r="B650" s="2"/>
-      <c r="C650" s="46"/>
+      <c r="C650" s="45"/>
     </row>
     <row r="651">
       <c r="B651" s="2"/>
-      <c r="C651" s="46"/>
+      <c r="C651" s="45"/>
     </row>
     <row r="652">
       <c r="B652" s="2"/>
-      <c r="C652" s="46"/>
+      <c r="C652" s="45"/>
     </row>
     <row r="653">
       <c r="B653" s="2"/>
-      <c r="C653" s="46"/>
+      <c r="C653" s="45"/>
     </row>
     <row r="654">
       <c r="B654" s="2"/>
-      <c r="C654" s="46"/>
+      <c r="C654" s="45"/>
     </row>
     <row r="655">
       <c r="B655" s="2"/>
-      <c r="C655" s="46"/>
+      <c r="C655" s="45"/>
     </row>
     <row r="656">
       <c r="B656" s="2"/>
-      <c r="C656" s="46"/>
+      <c r="C656" s="45"/>
     </row>
     <row r="657">
       <c r="B657" s="2"/>
-      <c r="C657" s="46"/>
+      <c r="C657" s="45"/>
     </row>
     <row r="658">
       <c r="B658" s="2"/>
-      <c r="C658" s="46"/>
+      <c r="C658" s="45"/>
     </row>
     <row r="659">
       <c r="B659" s="2"/>
-      <c r="C659" s="46"/>
+      <c r="C659" s="45"/>
     </row>
     <row r="660">
       <c r="B660" s="2"/>
-      <c r="C660" s="46"/>
+      <c r="C660" s="45"/>
     </row>
     <row r="661">
       <c r="B661" s="2"/>
-      <c r="C661" s="46"/>
+      <c r="C661" s="45"/>
     </row>
     <row r="662">
       <c r="B662" s="2"/>
-      <c r="C662" s="46"/>
+      <c r="C662" s="45"/>
     </row>
     <row r="663">
       <c r="B663" s="2"/>
-      <c r="C663" s="46"/>
+      <c r="C663" s="45"/>
     </row>
     <row r="664">
       <c r="B664" s="2"/>
-      <c r="C664" s="46"/>
+      <c r="C664" s="45"/>
     </row>
     <row r="665">
       <c r="B665" s="2"/>
-      <c r="C665" s="46"/>
+      <c r="C665" s="45"/>
     </row>
     <row r="666">
       <c r="B666" s="2"/>
-      <c r="C666" s="46"/>
+      <c r="C666" s="45"/>
     </row>
     <row r="667">
       <c r="B667" s="2"/>
-      <c r="C667" s="46"/>
+      <c r="C667" s="45"/>
     </row>
     <row r="668">
       <c r="B668" s="2"/>
-      <c r="C668" s="46"/>
+      <c r="C668" s="45"/>
     </row>
     <row r="669">
       <c r="B669" s="2"/>
-      <c r="C669" s="46"/>
+      <c r="C669" s="45"/>
     </row>
     <row r="670">
       <c r="B670" s="2"/>
-      <c r="C670" s="46"/>
+      <c r="C670" s="45"/>
     </row>
     <row r="671">
       <c r="B671" s="2"/>
-      <c r="C671" s="46"/>
+      <c r="C671" s="45"/>
     </row>
     <row r="672">
       <c r="B672" s="2"/>
-      <c r="C672" s="46"/>
+      <c r="C672" s="45"/>
     </row>
     <row r="673">
       <c r="B673" s="2"/>
-      <c r="C673" s="46"/>
+      <c r="C673" s="45"/>
     </row>
     <row r="674">
       <c r="B674" s="2"/>
-      <c r="C674" s="46"/>
+      <c r="C674" s="45"/>
     </row>
     <row r="675">
       <c r="B675" s="2"/>
-      <c r="C675" s="46"/>
+      <c r="C675" s="45"/>
     </row>
     <row r="676">
       <c r="B676" s="2"/>
-      <c r="C676" s="46"/>
+      <c r="C676" s="45"/>
     </row>
     <row r="677">
       <c r="B677" s="2"/>
-      <c r="C677" s="46"/>
+      <c r="C677" s="45"/>
     </row>
     <row r="678">
       <c r="B678" s="2"/>
-      <c r="C678" s="46"/>
+      <c r="C678" s="45"/>
     </row>
     <row r="679">
       <c r="B679" s="2"/>
-      <c r="C679" s="46"/>
+      <c r="C679" s="45"/>
     </row>
     <row r="680">
       <c r="B680" s="2"/>
-      <c r="C680" s="46"/>
+      <c r="C680" s="45"/>
     </row>
     <row r="681">
       <c r="B681" s="2"/>
-      <c r="C681" s="46"/>
+      <c r="C681" s="45"/>
     </row>
     <row r="682">
       <c r="B682" s="2"/>
-      <c r="C682" s="46"/>
+      <c r="C682" s="45"/>
     </row>
     <row r="683">
       <c r="B683" s="2"/>
-      <c r="C683" s="46"/>
+      <c r="C683" s="45"/>
     </row>
     <row r="684">
       <c r="B684" s="2"/>
-      <c r="C684" s="46"/>
+      <c r="C684" s="45"/>
     </row>
     <row r="685">
       <c r="B685" s="2"/>
-      <c r="C685" s="46"/>
+      <c r="C685" s="45"/>
     </row>
     <row r="686">
       <c r="B686" s="2"/>
-      <c r="C686" s="46"/>
+      <c r="C686" s="45"/>
     </row>
     <row r="687">
       <c r="B687" s="2"/>
-      <c r="C687" s="46"/>
+      <c r="C687" s="45"/>
     </row>
     <row r="688">
       <c r="B688" s="2"/>
-      <c r="C688" s="46"/>
+      <c r="C688" s="45"/>
     </row>
     <row r="689">
       <c r="B689" s="2"/>
-      <c r="C689" s="46"/>
+      <c r="C689" s="45"/>
     </row>
     <row r="690">
       <c r="B690" s="2"/>
-      <c r="C690" s="46"/>
+      <c r="C690" s="45"/>
     </row>
     <row r="691">
       <c r="B691" s="2"/>
-      <c r="C691" s="46"/>
+      <c r="C691" s="45"/>
     </row>
     <row r="692">
       <c r="B692" s="2"/>
-      <c r="C692" s="46"/>
+      <c r="C692" s="45"/>
     </row>
     <row r="693">
       <c r="B693" s="2"/>
-      <c r="C693" s="46"/>
+      <c r="C693" s="45"/>
     </row>
     <row r="694">
       <c r="B694" s="2"/>
-      <c r="C694" s="46"/>
+      <c r="C694" s="45"/>
     </row>
     <row r="695">
       <c r="B695" s="2"/>
-      <c r="C695" s="46"/>
+      <c r="C695" s="45"/>
     </row>
     <row r="696">
       <c r="B696" s="2"/>
-      <c r="C696" s="46"/>
+      <c r="C696" s="45"/>
     </row>
     <row r="697">
       <c r="B697" s="2"/>
-      <c r="C697" s="46"/>
+      <c r="C697" s="45"/>
     </row>
     <row r="698">
       <c r="B698" s="2"/>
-      <c r="C698" s="46"/>
+      <c r="C698" s="45"/>
     </row>
     <row r="699">
       <c r="B699" s="2"/>
-      <c r="C699" s="46"/>
+      <c r="C699" s="45"/>
     </row>
     <row r="700">
       <c r="B700" s="2"/>
-      <c r="C700" s="46"/>
+      <c r="C700" s="45"/>
     </row>
     <row r="701">
       <c r="B701" s="2"/>
-      <c r="C701" s="46"/>
+      <c r="C701" s="45"/>
     </row>
     <row r="702">
       <c r="B702" s="2"/>
-      <c r="C702" s="46"/>
+      <c r="C702" s="45"/>
     </row>
     <row r="703">
       <c r="B703" s="2"/>
-      <c r="C703" s="46"/>
+      <c r="C703" s="45"/>
     </row>
     <row r="704">
       <c r="B704" s="2"/>
-      <c r="C704" s="46"/>
+      <c r="C704" s="45"/>
     </row>
     <row r="705">
       <c r="B705" s="2"/>
-      <c r="C705" s="46"/>
+      <c r="C705" s="45"/>
     </row>
     <row r="706">
       <c r="B706" s="2"/>
-      <c r="C706" s="46"/>
+      <c r="C706" s="45"/>
     </row>
     <row r="707">
       <c r="B707" s="2"/>
-      <c r="C707" s="46"/>
+      <c r="C707" s="45"/>
     </row>
     <row r="708">
       <c r="B708" s="2"/>
-      <c r="C708" s="46"/>
+      <c r="C708" s="45"/>
     </row>
     <row r="709">
       <c r="B709" s="2"/>
-      <c r="C709" s="46"/>
+      <c r="C709" s="45"/>
     </row>
     <row r="710">
       <c r="B710" s="2"/>
-      <c r="C710" s="46"/>
+      <c r="C710" s="45"/>
     </row>
     <row r="711">
       <c r="B711" s="2"/>
-      <c r="C711" s="46"/>
+      <c r="C711" s="45"/>
     </row>
     <row r="712">
       <c r="B712" s="2"/>
-      <c r="C712" s="46"/>
+      <c r="C712" s="45"/>
     </row>
     <row r="713">
       <c r="B713" s="2"/>
-      <c r="C713" s="46"/>
+      <c r="C713" s="45"/>
     </row>
     <row r="714">
       <c r="B714" s="2"/>
-      <c r="C714" s="46"/>
+      <c r="C714" s="45"/>
     </row>
     <row r="715">
       <c r="B715" s="2"/>
-      <c r="C715" s="46"/>
+      <c r="C715" s="45"/>
     </row>
     <row r="716">
       <c r="B716" s="2"/>
-      <c r="C716" s="46"/>
+      <c r="C716" s="45"/>
     </row>
     <row r="717">
       <c r="B717" s="2"/>
-      <c r="C717" s="46"/>
+      <c r="C717" s="45"/>
     </row>
     <row r="718">
       <c r="B718" s="2"/>
-      <c r="C718" s="46"/>
+      <c r="C718" s="45"/>
     </row>
     <row r="719">
       <c r="B719" s="2"/>
-      <c r="C719" s="46"/>
+      <c r="C719" s="45"/>
     </row>
     <row r="720">
       <c r="B720" s="2"/>
-      <c r="C720" s="46"/>
+      <c r="C720" s="45"/>
     </row>
     <row r="721">
       <c r="B721" s="2"/>
-      <c r="C721" s="46"/>
+      <c r="C721" s="45"/>
     </row>
     <row r="722">
       <c r="B722" s="2"/>
-      <c r="C722" s="46"/>
+      <c r="C722" s="45"/>
     </row>
     <row r="723">
       <c r="B723" s="2"/>
-      <c r="C723" s="46"/>
+      <c r="C723" s="45"/>
     </row>
     <row r="724">
       <c r="B724" s="2"/>
-      <c r="C724" s="46"/>
+      <c r="C724" s="45"/>
     </row>
     <row r="725">
       <c r="B725" s="2"/>
-      <c r="C725" s="46"/>
+      <c r="C725" s="45"/>
     </row>
     <row r="726">
       <c r="B726" s="2"/>
-      <c r="C726" s="46"/>
+      <c r="C726" s="45"/>
     </row>
     <row r="727">
       <c r="B727" s="2"/>
-      <c r="C727" s="46"/>
+      <c r="C727" s="45"/>
     </row>
     <row r="728">
       <c r="B728" s="2"/>
-      <c r="C728" s="46"/>
+      <c r="C728" s="45"/>
     </row>
     <row r="729">
       <c r="B729" s="2"/>
-      <c r="C729" s="46"/>
+      <c r="C729" s="45"/>
     </row>
     <row r="730">
       <c r="B730" s="2"/>
-      <c r="C730" s="46"/>
+      <c r="C730" s="45"/>
     </row>
     <row r="731">
       <c r="B731" s="2"/>
-      <c r="C731" s="46"/>
+      <c r="C731" s="45"/>
     </row>
     <row r="732">
       <c r="B732" s="2"/>
-      <c r="C732" s="46"/>
+      <c r="C732" s="45"/>
     </row>
     <row r="733">
       <c r="B733" s="2"/>
-      <c r="C733" s="46"/>
+      <c r="C733" s="45"/>
     </row>
     <row r="734">
       <c r="B734" s="2"/>
-      <c r="C734" s="46"/>
+      <c r="C734" s="45"/>
     </row>
     <row r="735">
       <c r="B735" s="2"/>
-      <c r="C735" s="46"/>
+      <c r="C735" s="45"/>
     </row>
     <row r="736">
       <c r="B736" s="2"/>
-      <c r="C736" s="46"/>
+      <c r="C736" s="45"/>
     </row>
     <row r="737">
       <c r="B737" s="2"/>
-      <c r="C737" s="46"/>
+      <c r="C737" s="45"/>
     </row>
     <row r="738">
       <c r="B738" s="2"/>
-      <c r="C738" s="46"/>
+      <c r="C738" s="45"/>
     </row>
     <row r="739">
       <c r="B739" s="2"/>
-      <c r="C739" s="46"/>
+      <c r="C739" s="45"/>
     </row>
     <row r="740">
       <c r="B740" s="2"/>
-      <c r="C740" s="46"/>
+      <c r="C740" s="45"/>
     </row>
     <row r="741">
       <c r="B741" s="2"/>
-      <c r="C741" s="46"/>
+      <c r="C741" s="45"/>
     </row>
     <row r="742">
       <c r="B742" s="2"/>
-      <c r="C742" s="46"/>
+      <c r="C742" s="45"/>
     </row>
     <row r="743">
       <c r="B743" s="2"/>
-      <c r="C743" s="46"/>
+      <c r="C743" s="45"/>
     </row>
     <row r="744">
       <c r="B744" s="2"/>
-      <c r="C744" s="46"/>
+      <c r="C744" s="45"/>
     </row>
     <row r="745">
       <c r="B745" s="2"/>
-      <c r="C745" s="46"/>
+      <c r="C745" s="45"/>
     </row>
     <row r="746">
       <c r="B746" s="2"/>
-      <c r="C746" s="46"/>
+      <c r="C746" s="45"/>
     </row>
     <row r="747">
       <c r="B747" s="2"/>
-      <c r="C747" s="46"/>
+      <c r="C747" s="45"/>
     </row>
     <row r="748">
       <c r="B748" s="2"/>
-      <c r="C748" s="46"/>
+      <c r="C748" s="45"/>
     </row>
     <row r="749">
       <c r="B749" s="2"/>
-      <c r="C749" s="46"/>
+      <c r="C749" s="45"/>
     </row>
     <row r="750">
       <c r="B750" s="2"/>
-      <c r="C750" s="46"/>
+      <c r="C750" s="45"/>
     </row>
     <row r="751">
       <c r="B751" s="2"/>
-      <c r="C751" s="46"/>
+      <c r="C751" s="45"/>
     </row>
     <row r="752">
       <c r="B752" s="2"/>
-      <c r="C752" s="46"/>
+      <c r="C752" s="45"/>
     </row>
     <row r="753">
       <c r="B753" s="2"/>
-      <c r="C753" s="46"/>
+      <c r="C753" s="45"/>
     </row>
     <row r="754">
       <c r="B754" s="2"/>
-      <c r="C754" s="46"/>
+      <c r="C754" s="45"/>
     </row>
     <row r="755">
       <c r="B755" s="2"/>
-      <c r="C755" s="46"/>
+      <c r="C755" s="45"/>
     </row>
     <row r="756">
       <c r="B756" s="2"/>
-      <c r="C756" s="46"/>
+      <c r="C756" s="45"/>
     </row>
     <row r="757">
       <c r="B757" s="2"/>
-      <c r="C757" s="46"/>
+      <c r="C757" s="45"/>
     </row>
     <row r="758">
       <c r="B758" s="2"/>
-      <c r="C758" s="46"/>
+      <c r="C758" s="45"/>
     </row>
     <row r="759">
       <c r="B759" s="2"/>
-      <c r="C759" s="46"/>
+      <c r="C759" s="45"/>
     </row>
     <row r="760">
       <c r="B760" s="2"/>
-      <c r="C760" s="46"/>
+      <c r="C760" s="45"/>
     </row>
     <row r="761">
       <c r="B761" s="2"/>
-      <c r="C761" s="46"/>
+      <c r="C761" s="45"/>
     </row>
     <row r="762">
       <c r="B762" s="2"/>
-      <c r="C762" s="46"/>
+      <c r="C762" s="45"/>
     </row>
     <row r="763">
       <c r="B763" s="2"/>
-      <c r="C763" s="46"/>
+      <c r="C763" s="45"/>
     </row>
     <row r="764">
       <c r="B764" s="2"/>
-      <c r="C764" s="46"/>
+      <c r="C764" s="45"/>
     </row>
     <row r="765">
       <c r="B765" s="2"/>
-      <c r="C765" s="46"/>
+      <c r="C765" s="45"/>
     </row>
     <row r="766">
       <c r="B766" s="2"/>
-      <c r="C766" s="46"/>
+      <c r="C766" s="45"/>
     </row>
     <row r="767">
       <c r="B767" s="2"/>
-      <c r="C767" s="46"/>
+      <c r="C767" s="45"/>
     </row>
     <row r="768">
       <c r="B768" s="2"/>
-      <c r="C768" s="46"/>
+      <c r="C768" s="45"/>
     </row>
     <row r="769">
       <c r="B769" s="2"/>
-      <c r="C769" s="46"/>
+      <c r="C769" s="45"/>
     </row>
     <row r="770">
       <c r="B770" s="2"/>
-      <c r="C770" s="46"/>
+      <c r="C770" s="45"/>
     </row>
     <row r="771">
       <c r="B771" s="2"/>
-      <c r="C771" s="46"/>
+      <c r="C771" s="45"/>
     </row>
     <row r="772">
       <c r="B772" s="2"/>
-      <c r="C772" s="46"/>
+      <c r="C772" s="45"/>
     </row>
     <row r="773">
       <c r="B773" s="2"/>
-      <c r="C773" s="46"/>
+      <c r="C773" s="45"/>
     </row>
     <row r="774">
       <c r="B774" s="2"/>
-      <c r="C774" s="46"/>
+      <c r="C774" s="45"/>
     </row>
     <row r="775">
       <c r="B775" s="2"/>
-      <c r="C775" s="46"/>
+      <c r="C775" s="45"/>
     </row>
     <row r="776">
       <c r="B776" s="2"/>
-      <c r="C776" s="46"/>
+      <c r="C776" s="45"/>
     </row>
     <row r="777">
       <c r="B777" s="2"/>
-      <c r="C777" s="46"/>
+      <c r="C777" s="45"/>
     </row>
     <row r="778">
       <c r="B778" s="2"/>
-      <c r="C778" s="46"/>
+      <c r="C778" s="45"/>
     </row>
     <row r="779">
       <c r="B779" s="2"/>
-      <c r="C779" s="46"/>
+      <c r="C779" s="45"/>
     </row>
     <row r="780">
       <c r="B780" s="2"/>
-      <c r="C780" s="46"/>
+      <c r="C780" s="45"/>
     </row>
     <row r="781">
       <c r="B781" s="2"/>
-      <c r="C781" s="46"/>
+      <c r="C781" s="45"/>
     </row>
     <row r="782">
       <c r="B782" s="2"/>
-      <c r="C782" s="46"/>
+      <c r="C782" s="45"/>
     </row>
     <row r="783">
       <c r="B783" s="2"/>
-      <c r="C783" s="46"/>
+      <c r="C783" s="45"/>
     </row>
     <row r="784">
       <c r="B784" s="2"/>
-      <c r="C784" s="46"/>
+      <c r="C784" s="45"/>
     </row>
     <row r="785">
       <c r="B785" s="2"/>
-      <c r="C785" s="46"/>
+      <c r="C785" s="45"/>
     </row>
     <row r="786">
       <c r="B786" s="2"/>
-      <c r="C786" s="46"/>
+      <c r="C786" s="45"/>
     </row>
     <row r="787">
       <c r="B787" s="2"/>
-      <c r="C787" s="46"/>
+      <c r="C787" s="45"/>
     </row>
     <row r="788">
       <c r="B788" s="2"/>
-      <c r="C788" s="46"/>
+      <c r="C788" s="45"/>
     </row>
     <row r="789">
       <c r="B789" s="2"/>
-      <c r="C789" s="46"/>
+      <c r="C789" s="45"/>
     </row>
     <row r="790">
       <c r="B790" s="2"/>
-      <c r="C790" s="46"/>
+      <c r="C790" s="45"/>
     </row>
     <row r="791">
       <c r="B791" s="2"/>
-      <c r="C791" s="46"/>
+      <c r="C791" s="45"/>
     </row>
     <row r="792">
       <c r="B792" s="2"/>
-      <c r="C792" s="46"/>
+      <c r="C792" s="45"/>
     </row>
     <row r="793">
       <c r="B793" s="2"/>
-      <c r="C793" s="46"/>
+      <c r="C793" s="45"/>
     </row>
     <row r="794">
       <c r="B794" s="2"/>
-      <c r="C794" s="46"/>
+      <c r="C794" s="45"/>
     </row>
     <row r="795">
       <c r="B795" s="2"/>
-      <c r="C795" s="46"/>
+      <c r="C795" s="45"/>
     </row>
     <row r="796">
       <c r="B796" s="2"/>
-      <c r="C796" s="46"/>
+      <c r="C796" s="45"/>
     </row>
     <row r="797">
       <c r="B797" s="2"/>
-      <c r="C797" s="46"/>
+      <c r="C797" s="45"/>
     </row>
     <row r="798">
       <c r="B798" s="2"/>
-      <c r="C798" s="46"/>
+      <c r="C798" s="45"/>
     </row>
     <row r="799">
       <c r="B799" s="2"/>
-      <c r="C799" s="46"/>
+      <c r="C799" s="45"/>
     </row>
     <row r="800">
       <c r="B800" s="2"/>
-      <c r="C800" s="46"/>
+      <c r="C800" s="45"/>
     </row>
     <row r="801">
       <c r="B801" s="2"/>
-      <c r="C801" s="46"/>
+      <c r="C801" s="45"/>
     </row>
     <row r="802">
       <c r="B802" s="2"/>
-      <c r="C802" s="46"/>
+      <c r="C802" s="45"/>
     </row>
     <row r="803">
       <c r="B803" s="2"/>
-      <c r="C803" s="46"/>
+      <c r="C803" s="45"/>
     </row>
     <row r="804">
       <c r="B804" s="2"/>
-      <c r="C804" s="46"/>
+      <c r="C804" s="45"/>
     </row>
     <row r="805">
       <c r="B805" s="2"/>
-      <c r="C805" s="46"/>
+      <c r="C805" s="45"/>
     </row>
     <row r="806">
       <c r="B806" s="2"/>
-      <c r="C806" s="46"/>
+      <c r="C806" s="45"/>
     </row>
     <row r="807">
       <c r="B807" s="2"/>
-      <c r="C807" s="46"/>
+      <c r="C807" s="45"/>
     </row>
     <row r="808">
       <c r="B808" s="2"/>
-      <c r="C808" s="46"/>
+      <c r="C808" s="45"/>
     </row>
     <row r="809">
       <c r="B809" s="2"/>
-      <c r="C809" s="46"/>
+      <c r="C809" s="45"/>
     </row>
     <row r="810">
       <c r="B810" s="2"/>
-      <c r="C810" s="46"/>
+      <c r="C810" s="45"/>
     </row>
     <row r="811">
       <c r="B811" s="2"/>
-      <c r="C811" s="46"/>
+      <c r="C811" s="45"/>
     </row>
     <row r="812">
       <c r="B812" s="2"/>
-      <c r="C812" s="46"/>
+      <c r="C812" s="45"/>
     </row>
     <row r="813">
       <c r="B813" s="2"/>
-      <c r="C813" s="46"/>
+      <c r="C813" s="45"/>
     </row>
     <row r="814">
       <c r="B814" s="2"/>
-      <c r="C814" s="46"/>
+      <c r="C814" s="45"/>
     </row>
     <row r="815">
       <c r="B815" s="2"/>
-      <c r="C815" s="46"/>
+      <c r="C815" s="45"/>
     </row>
     <row r="816">
       <c r="B816" s="2"/>
-      <c r="C816" s="46"/>
+      <c r="C816" s="45"/>
     </row>
     <row r="817">
       <c r="B817" s="2"/>
-      <c r="C817" s="46"/>
+      <c r="C817" s="45"/>
     </row>
     <row r="818">
       <c r="B818" s="2"/>
-      <c r="C818" s="46"/>
+      <c r="C818" s="45"/>
     </row>
     <row r="819">
       <c r="B819" s="2"/>
-      <c r="C819" s="46"/>
+      <c r="C819" s="45"/>
     </row>
     <row r="820">
       <c r="B820" s="2"/>
-      <c r="C820" s="46"/>
+      <c r="C820" s="45"/>
     </row>
     <row r="821">
       <c r="B821" s="2"/>
-      <c r="C821" s="46"/>
+      <c r="C821" s="45"/>
     </row>
     <row r="822">
       <c r="B822" s="2"/>
-      <c r="C822" s="46"/>
+      <c r="C822" s="45"/>
     </row>
     <row r="823">
       <c r="B823" s="2"/>
-      <c r="C823" s="46"/>
+      <c r="C823" s="45"/>
     </row>
     <row r="824">
       <c r="B824" s="2"/>
-      <c r="C824" s="46"/>
+      <c r="C824" s="45"/>
     </row>
     <row r="825">
       <c r="B825" s="2"/>
-      <c r="C825" s="46"/>
+      <c r="C825" s="45"/>
     </row>
     <row r="826">
       <c r="B826" s="2"/>
-      <c r="C826" s="46"/>
+      <c r="C826" s="45"/>
     </row>
     <row r="827">
       <c r="B827" s="2"/>
-      <c r="C827" s="46"/>
+      <c r="C827" s="45"/>
     </row>
     <row r="828">
       <c r="B828" s="2"/>
-      <c r="C828" s="46"/>
+      <c r="C828" s="45"/>
     </row>
     <row r="829">
       <c r="B829" s="2"/>
-      <c r="C829" s="46"/>
+      <c r="C829" s="45"/>
     </row>
     <row r="830">
       <c r="B830" s="2"/>
-      <c r="C830" s="46"/>
+      <c r="C830" s="45"/>
     </row>
     <row r="831">
       <c r="B831" s="2"/>
-      <c r="C831" s="46"/>
+      <c r="C831" s="45"/>
     </row>
     <row r="832">
       <c r="B832" s="2"/>
-      <c r="C832" s="46"/>
+      <c r="C832" s="45"/>
     </row>
     <row r="833">
       <c r="B833" s="2"/>
-      <c r="C833" s="46"/>
+      <c r="C833" s="45"/>
     </row>
     <row r="834">
       <c r="B834" s="2"/>
-      <c r="C834" s="46"/>
+      <c r="C834" s="45"/>
     </row>
     <row r="835">
       <c r="B835" s="2"/>
-      <c r="C835" s="46"/>
+      <c r="C835" s="45"/>
     </row>
     <row r="836">
       <c r="B836" s="2"/>
-      <c r="C836" s="46"/>
+      <c r="C836" s="45"/>
     </row>
     <row r="837">
       <c r="B837" s="2"/>
-      <c r="C837" s="46"/>
+      <c r="C837" s="45"/>
     </row>
     <row r="838">
       <c r="B838" s="2"/>
-      <c r="C838" s="46"/>
+      <c r="C838" s="45"/>
     </row>
     <row r="839">
       <c r="B839" s="2"/>
-      <c r="C839" s="46"/>
+      <c r="C839" s="45"/>
     </row>
     <row r="840">
       <c r="B840" s="2"/>
-      <c r="C840" s="46"/>
+      <c r="C840" s="45"/>
     </row>
     <row r="841">
       <c r="B841" s="2"/>
-      <c r="C841" s="46"/>
+      <c r="C841" s="45"/>
     </row>
     <row r="842">
       <c r="B842" s="2"/>
-      <c r="C842" s="46"/>
+      <c r="C842" s="45"/>
     </row>
     <row r="843">
       <c r="B843" s="2"/>
-      <c r="C843" s="46"/>
+      <c r="C843" s="45"/>
     </row>
     <row r="844">
       <c r="B844" s="2"/>
-      <c r="C844" s="46"/>
+      <c r="C844" s="45"/>
     </row>
     <row r="845">
       <c r="B845" s="2"/>
-      <c r="C845" s="46"/>
+      <c r="C845" s="45"/>
     </row>
     <row r="846">
       <c r="B846" s="2"/>
-      <c r="C846" s="46"/>
+      <c r="C846" s="45"/>
     </row>
     <row r="847">
       <c r="B847" s="2"/>
-      <c r="C847" s="46"/>
+      <c r="C847" s="45"/>
     </row>
     <row r="848">
       <c r="B848" s="2"/>
-      <c r="C848" s="46"/>
+      <c r="C848" s="45"/>
     </row>
     <row r="849">
       <c r="B849" s="2"/>
-      <c r="C849" s="46"/>
+      <c r="C849" s="45"/>
     </row>
     <row r="850">
       <c r="B850" s="2"/>
-      <c r="C850" s="46"/>
+      <c r="C850" s="45"/>
     </row>
     <row r="851">
       <c r="B851" s="2"/>
-      <c r="C851" s="46"/>
+      <c r="C851" s="45"/>
     </row>
     <row r="852">
       <c r="B852" s="2"/>
-      <c r="C852" s="46"/>
+      <c r="C852" s="45"/>
     </row>
     <row r="853">
       <c r="B853" s="2"/>
-      <c r="C853" s="46"/>
+      <c r="C853" s="45"/>
     </row>
     <row r="854">
       <c r="B854" s="2"/>
-      <c r="C854" s="46"/>
+      <c r="C854" s="45"/>
     </row>
     <row r="855">
       <c r="B855" s="2"/>
-      <c r="C855" s="46"/>
+      <c r="C855" s="45"/>
     </row>
     <row r="856">
       <c r="B856" s="2"/>
-      <c r="C856" s="46"/>
+      <c r="C856" s="45"/>
     </row>
     <row r="857">
       <c r="B857" s="2"/>
-      <c r="C857" s="46"/>
+      <c r="C857" s="45"/>
     </row>
     <row r="858">
       <c r="B858" s="2"/>
-      <c r="C858" s="46"/>
+      <c r="C858" s="45"/>
     </row>
     <row r="859">
       <c r="B859" s="2"/>
-      <c r="C859" s="46"/>
+      <c r="C859" s="45"/>
     </row>
     <row r="860">
       <c r="B860" s="2"/>
-      <c r="C860" s="46"/>
+      <c r="C860" s="45"/>
     </row>
     <row r="861">
       <c r="B861" s="2"/>
-      <c r="C861" s="46"/>
+      <c r="C861" s="45"/>
     </row>
     <row r="862">
       <c r="B862" s="2"/>
-      <c r="C862" s="46"/>
+      <c r="C862" s="45"/>
     </row>
     <row r="863">
       <c r="B863" s="2"/>
-      <c r="C863" s="46"/>
+      <c r="C863" s="45"/>
     </row>
     <row r="864">
       <c r="B864" s="2"/>
-      <c r="C864" s="46"/>
+      <c r="C864" s="45"/>
     </row>
     <row r="865">
       <c r="B865" s="2"/>
-      <c r="C865" s="46"/>
+      <c r="C865" s="45"/>
     </row>
     <row r="866">
       <c r="B866" s="2"/>
-      <c r="C866" s="46"/>
+      <c r="C866" s="45"/>
     </row>
     <row r="867">
       <c r="B867" s="2"/>
-      <c r="C867" s="46"/>
+      <c r="C867" s="45"/>
     </row>
     <row r="868">
       <c r="B868" s="2"/>
-      <c r="C868" s="46"/>
+      <c r="C868" s="45"/>
     </row>
     <row r="869">
       <c r="B869" s="2"/>
-      <c r="C869" s="46"/>
+      <c r="C869" s="45"/>
     </row>
     <row r="870">
       <c r="B870" s="2"/>
-      <c r="C870" s="46"/>
+      <c r="C870" s="45"/>
     </row>
     <row r="871">
       <c r="B871" s="2"/>
-      <c r="C871" s="46"/>
+      <c r="C871" s="45"/>
     </row>
     <row r="872">
       <c r="B872" s="2"/>
-      <c r="C872" s="46"/>
+      <c r="C872" s="45"/>
     </row>
     <row r="873">
       <c r="B873" s="2"/>
-      <c r="C873" s="46"/>
+      <c r="C873" s="45"/>
     </row>
     <row r="874">
       <c r="B874" s="2"/>
-      <c r="C874" s="46"/>
+      <c r="C874" s="45"/>
     </row>
     <row r="875">
       <c r="B875" s="2"/>
-      <c r="C875" s="46"/>
+      <c r="C875" s="45"/>
     </row>
     <row r="876">
       <c r="B876" s="2"/>
-      <c r="C876" s="46"/>
+      <c r="C876" s="45"/>
     </row>
     <row r="877">
       <c r="B877" s="2"/>
-      <c r="C877" s="46"/>
+      <c r="C877" s="45"/>
     </row>
     <row r="878">
       <c r="B878" s="2"/>
-      <c r="C878" s="46"/>
+      <c r="C878" s="45"/>
     </row>
     <row r="879">
       <c r="B879" s="2"/>
-      <c r="C879" s="46"/>
+      <c r="C879" s="45"/>
     </row>
     <row r="880">
       <c r="B880" s="2"/>
-      <c r="C880" s="46"/>
+      <c r="C880" s="45"/>
     </row>
     <row r="881">
       <c r="B881" s="2"/>
-      <c r="C881" s="46"/>
+      <c r="C881" s="45"/>
     </row>
     <row r="882">
       <c r="B882" s="2"/>
-      <c r="C882" s="46"/>
+      <c r="C882" s="45"/>
     </row>
     <row r="883">
       <c r="B883" s="2"/>
-      <c r="C883" s="46"/>
+      <c r="C883" s="45"/>
     </row>
     <row r="884">
       <c r="B884" s="2"/>
-      <c r="C884" s="46"/>
+      <c r="C884" s="45"/>
     </row>
     <row r="885">
       <c r="B885" s="2"/>
-      <c r="C885" s="46"/>
+      <c r="C885" s="45"/>
     </row>
     <row r="886">
       <c r="B886" s="2"/>
-      <c r="C886" s="46"/>
+      <c r="C886" s="45"/>
     </row>
     <row r="887">
       <c r="B887" s="2"/>
-      <c r="C887" s="46"/>
+      <c r="C887" s="45"/>
     </row>
     <row r="888">
       <c r="B888" s="2"/>
-      <c r="C888" s="46"/>
+      <c r="C888" s="45"/>
     </row>
     <row r="889">
       <c r="B889" s="2"/>
-      <c r="C889" s="46"/>
+      <c r="C889" s="45"/>
     </row>
     <row r="890">
       <c r="B890" s="2"/>
-      <c r="C890" s="46"/>
+      <c r="C890" s="45"/>
     </row>
     <row r="891">
       <c r="B891" s="2"/>
-      <c r="C891" s="46"/>
+      <c r="C891" s="45"/>
     </row>
     <row r="892">
       <c r="B892" s="2"/>
-      <c r="C892" s="46"/>
+      <c r="C892" s="45"/>
     </row>
     <row r="893">
       <c r="B893" s="2"/>
-      <c r="C893" s="46"/>
+      <c r="C893" s="45"/>
     </row>
     <row r="894">
       <c r="B894" s="2"/>
-      <c r="C894" s="46"/>
+      <c r="C894" s="45"/>
     </row>
     <row r="895">
       <c r="B895" s="2"/>
-      <c r="C895" s="46"/>
+      <c r="C895" s="45"/>
     </row>
     <row r="896">
       <c r="B896" s="2"/>
-      <c r="C896" s="46"/>
+      <c r="C896" s="45"/>
     </row>
     <row r="897">
       <c r="B897" s="2"/>
-      <c r="C897" s="46"/>
+      <c r="C897" s="45"/>
     </row>
     <row r="898">
       <c r="B898" s="2"/>
-      <c r="C898" s="46"/>
+      <c r="C898" s="45"/>
     </row>
     <row r="899">
       <c r="B899" s="2"/>
-      <c r="C899" s="46"/>
+      <c r="C899" s="45"/>
     </row>
     <row r="900">
       <c r="B900" s="2"/>
-      <c r="C900" s="46"/>
+      <c r="C900" s="45"/>
     </row>
     <row r="901">
       <c r="B901" s="2"/>
-      <c r="C901" s="46"/>
+      <c r="C901" s="45"/>
     </row>
     <row r="902">
       <c r="B902" s="2"/>
-      <c r="C902" s="46"/>
+      <c r="C902" s="45"/>
     </row>
     <row r="903">
       <c r="B903" s="2"/>
-      <c r="C903" s="46"/>
+      <c r="C903" s="45"/>
     </row>
     <row r="904">
       <c r="B904" s="2"/>
-      <c r="C904" s="46"/>
+      <c r="C904" s="45"/>
     </row>
     <row r="905">
       <c r="B905" s="2"/>
-      <c r="C905" s="46"/>
+      <c r="C905" s="45"/>
     </row>
     <row r="906">
       <c r="B906" s="2"/>
-      <c r="C906" s="46"/>
+      <c r="C906" s="45"/>
     </row>
     <row r="907">
       <c r="B907" s="2"/>
-      <c r="C907" s="46"/>
+      <c r="C907" s="45"/>
     </row>
     <row r="908">
       <c r="B908" s="2"/>
-      <c r="C908" s="46"/>
+      <c r="C908" s="45"/>
     </row>
     <row r="909">
       <c r="B909" s="2"/>
-      <c r="C909" s="46"/>
+      <c r="C909" s="45"/>
     </row>
     <row r="910">
       <c r="B910" s="2"/>
-      <c r="C910" s="46"/>
+      <c r="C910" s="45"/>
     </row>
     <row r="911">
       <c r="B911" s="2"/>
-      <c r="C911" s="46"/>
+      <c r="C911" s="45"/>
     </row>
     <row r="912">
       <c r="B912" s="2"/>
-      <c r="C912" s="46"/>
+      <c r="C912" s="45"/>
     </row>
     <row r="913">
       <c r="B913" s="2"/>
-      <c r="C913" s="46"/>
+      <c r="C913" s="45"/>
     </row>
     <row r="914">
       <c r="B914" s="2"/>
-      <c r="C914" s="46"/>
+      <c r="C914" s="45"/>
     </row>
     <row r="915">
       <c r="B915" s="2"/>
-      <c r="C915" s="46"/>
+      <c r="C915" s="45"/>
     </row>
     <row r="916">
       <c r="B916" s="2"/>
-      <c r="C916" s="46"/>
+      <c r="C916" s="45"/>
     </row>
     <row r="917">
       <c r="B917" s="2"/>
-      <c r="C917" s="46"/>
+      <c r="C917" s="45"/>
     </row>
     <row r="918">
       <c r="B918" s="2"/>
-      <c r="C918" s="46"/>
+      <c r="C918" s="45"/>
     </row>
     <row r="919">
       <c r="B919" s="2"/>
-      <c r="C919" s="46"/>
+      <c r="C919" s="45"/>
     </row>
     <row r="920">
       <c r="B920" s="2"/>
-      <c r="C920" s="46"/>
+      <c r="C920" s="45"/>
     </row>
     <row r="921">
       <c r="B921" s="2"/>
-      <c r="C921" s="46"/>
+      <c r="C921" s="45"/>
     </row>
     <row r="922">
       <c r="B922" s="2"/>
-      <c r="C922" s="46"/>
+      <c r="C922" s="45"/>
     </row>
     <row r="923">
       <c r="B923" s="2"/>
-      <c r="C923" s="46"/>
+      <c r="C923" s="45"/>
     </row>
     <row r="924">
       <c r="B924" s="2"/>
-      <c r="C924" s="46"/>
+      <c r="C924" s="45"/>
     </row>
     <row r="925">
       <c r="B925" s="2"/>
-      <c r="C925" s="46"/>
+      <c r="C925" s="45"/>
     </row>
     <row r="926">
       <c r="B926" s="2"/>
-      <c r="C926" s="46"/>
+      <c r="C926" s="45"/>
     </row>
     <row r="927">
       <c r="B927" s="2"/>
-      <c r="C927" s="46"/>
+      <c r="C927" s="45"/>
     </row>
     <row r="928">
       <c r="B928" s="2"/>
-      <c r="C928" s="46"/>
+      <c r="C928" s="45"/>
     </row>
     <row r="929">
       <c r="B929" s="2"/>
-      <c r="C929" s="46"/>
+      <c r="C929" s="45"/>
     </row>
     <row r="930">
       <c r="B930" s="2"/>
-      <c r="C930" s="46"/>
+      <c r="C930" s="45"/>
     </row>
     <row r="931">
       <c r="B931" s="2"/>
-      <c r="C931" s="46"/>
+      <c r="C931" s="45"/>
     </row>
     <row r="932">
       <c r="B932" s="2"/>
-      <c r="C932" s="46"/>
+      <c r="C932" s="45"/>
     </row>
     <row r="933">
       <c r="B933" s="2"/>
-      <c r="C933" s="46"/>
+      <c r="C933" s="45"/>
     </row>
     <row r="934">
       <c r="B934" s="2"/>
-      <c r="C934" s="46"/>
+      <c r="C934" s="45"/>
     </row>
     <row r="935">
       <c r="B935" s="2"/>
-      <c r="C935" s="46"/>
+      <c r="C935" s="45"/>
     </row>
     <row r="936">
       <c r="B936" s="2"/>
-      <c r="C936" s="46"/>
+      <c r="C936" s="45"/>
     </row>
     <row r="937">
       <c r="B937" s="2"/>
-      <c r="C937" s="46"/>
+      <c r="C937" s="45"/>
     </row>
     <row r="938">
       <c r="B938" s="2"/>
-      <c r="C938" s="46"/>
+      <c r="C938" s="45"/>
     </row>
     <row r="939">
       <c r="B939" s="2"/>
-      <c r="C939" s="46"/>
+      <c r="C939" s="45"/>
     </row>
     <row r="940">
       <c r="B940" s="2"/>
-      <c r="C940" s="46"/>
+      <c r="C940" s="45"/>
     </row>
     <row r="941">
       <c r="B941" s="2"/>
-      <c r="C941" s="46"/>
+      <c r="C941" s="45"/>
     </row>
     <row r="942">
       <c r="B942" s="2"/>
-      <c r="C942" s="46"/>
+      <c r="C942" s="45"/>
     </row>
     <row r="943">
       <c r="B943" s="2"/>
-      <c r="C943" s="46"/>
+      <c r="C943" s="45"/>
     </row>
     <row r="944">
       <c r="B944" s="2"/>
-      <c r="C944" s="46"/>
+      <c r="C944" s="45"/>
     </row>
     <row r="945">
       <c r="B945" s="2"/>
-      <c r="C945" s="46"/>
+      <c r="C945" s="45"/>
     </row>
     <row r="946">
       <c r="B946" s="2"/>
-      <c r="C946" s="46"/>
+      <c r="C946" s="45"/>
     </row>
     <row r="947">
       <c r="B947" s="2"/>
-      <c r="C947" s="46"/>
+      <c r="C947" s="45"/>
     </row>
     <row r="948">
       <c r="B948" s="2"/>
-      <c r="C948" s="46"/>
+      <c r="C948" s="45"/>
     </row>
     <row r="949">
       <c r="B949" s="2"/>
-      <c r="C949" s="46"/>
+      <c r="C949" s="45"/>
     </row>
     <row r="950">
       <c r="B950" s="2"/>
-      <c r="C950" s="46"/>
+      <c r="C950" s="45"/>
     </row>
     <row r="951">
       <c r="B951" s="2"/>
-      <c r="C951" s="46"/>
+      <c r="C951" s="45"/>
     </row>
     <row r="952">
       <c r="B952" s="2"/>
-      <c r="C952" s="46"/>
+      <c r="C952" s="45"/>
     </row>
     <row r="953">
       <c r="B953" s="2"/>
-      <c r="C953" s="46"/>
+      <c r="C953" s="45"/>
     </row>
     <row r="954">
       <c r="B954" s="2"/>
-      <c r="C954" s="46"/>
+      <c r="C954" s="45"/>
     </row>
     <row r="955">
       <c r="B955" s="2"/>
-      <c r="C955" s="46"/>
+      <c r="C955" s="45"/>
     </row>
     <row r="956">
       <c r="B956" s="2"/>
-      <c r="C956" s="46"/>
+      <c r="C956" s="45"/>
     </row>
     <row r="957">
       <c r="B957" s="2"/>
-      <c r="C957" s="46"/>
+      <c r="C957" s="45"/>
     </row>
     <row r="958">
       <c r="B958" s="2"/>
-      <c r="C958" s="46"/>
+      <c r="C958" s="45"/>
     </row>
     <row r="959">
       <c r="B959" s="2"/>
-      <c r="C959" s="46"/>
+      <c r="C959" s="45"/>
     </row>
     <row r="960">
       <c r="B960" s="2"/>
-      <c r="C960" s="46"/>
+      <c r="C960" s="45"/>
     </row>
     <row r="961">
       <c r="B961" s="2"/>
-      <c r="C961" s="46"/>
+      <c r="C961" s="45"/>
     </row>
     <row r="962">
       <c r="B962" s="2"/>
-      <c r="C962" s="46"/>
+      <c r="C962" s="45"/>
     </row>
     <row r="963">
       <c r="B963" s="2"/>
-      <c r="C963" s="46"/>
+      <c r="C963" s="45"/>
     </row>
     <row r="964">
       <c r="B964" s="2"/>
-      <c r="C964" s="46"/>
+      <c r="C964" s="45"/>
     </row>
     <row r="965">
       <c r="B965" s="2"/>
-      <c r="C965" s="46"/>
+      <c r="C965" s="45"/>
     </row>
     <row r="966">
       <c r="B966" s="2"/>
-      <c r="C966" s="46"/>
+      <c r="C966" s="45"/>
     </row>
     <row r="967">
       <c r="B967" s="2"/>
-      <c r="C967" s="46"/>
+      <c r="C967" s="45"/>
     </row>
     <row r="968">
       <c r="B968" s="2"/>
-      <c r="C968" s="46"/>
+      <c r="C968" s="45"/>
     </row>
     <row r="969">
       <c r="B969" s="2"/>
-      <c r="C969" s="46"/>
+      <c r="C969" s="45"/>
     </row>
     <row r="970">
       <c r="B970" s="2"/>
-      <c r="C970" s="46"/>
+      <c r="C970" s="45"/>
     </row>
     <row r="971">
       <c r="B971" s="2"/>
-      <c r="C971" s="46"/>
+      <c r="C971" s="45"/>
     </row>
     <row r="972">
       <c r="B972" s="2"/>
-      <c r="C972" s="46"/>
+      <c r="C972" s="45"/>
     </row>
     <row r="973">
       <c r="B973" s="2"/>
-      <c r="C973" s="46"/>
+      <c r="C973" s="45"/>
     </row>
     <row r="974">
       <c r="B974" s="2"/>
-      <c r="C974" s="46"/>
+      <c r="C974" s="45"/>
     </row>
     <row r="975">
       <c r="B975" s="2"/>
-      <c r="C975" s="46"/>
+      <c r="C975" s="45"/>
     </row>
     <row r="976">
       <c r="B976" s="2"/>
-      <c r="C976" s="46"/>
+      <c r="C976" s="45"/>
     </row>
     <row r="977">
       <c r="B977" s="2"/>
-      <c r="C977" s="46"/>
+      <c r="C977" s="45"/>
     </row>
     <row r="978">
       <c r="B978" s="2"/>
-      <c r="C978" s="46"/>
+      <c r="C978" s="45"/>
     </row>
     <row r="979">
       <c r="B979" s="2"/>
-      <c r="C979" s="46"/>
+      <c r="C979" s="45"/>
     </row>
     <row r="980">
       <c r="B980" s="2"/>
-      <c r="C980" s="46"/>
+      <c r="C980" s="45"/>
     </row>
     <row r="981">
       <c r="B981" s="2"/>
-      <c r="C981" s="46"/>
+      <c r="C981" s="45"/>
     </row>
     <row r="982">
       <c r="B982" s="2"/>
-      <c r="C982" s="46"/>
+      <c r="C982" s="45"/>
     </row>
     <row r="983">
       <c r="B983" s="2"/>
-      <c r="C983" s="46"/>
+      <c r="C983" s="45"/>
     </row>
     <row r="984">
       <c r="B984" s="2"/>
-      <c r="C984" s="46"/>
+      <c r="C984" s="45"/>
     </row>
     <row r="985">
       <c r="B985" s="2"/>
-      <c r="C985" s="46"/>
+      <c r="C985" s="45"/>
     </row>
     <row r="986">
       <c r="B986" s="2"/>
-      <c r="C986" s="46"/>
+      <c r="C986" s="45"/>
     </row>
     <row r="987">
       <c r="B987" s="2"/>
-      <c r="C987" s="46"/>
+      <c r="C987" s="45"/>
     </row>
     <row r="988">
       <c r="B988" s="2"/>
-      <c r="C988" s="46"/>
+      <c r="C988" s="45"/>
     </row>
     <row r="989">
       <c r="B989" s="2"/>
-      <c r="C989" s="46"/>
+      <c r="C989" s="45"/>
     </row>
     <row r="990">
       <c r="B990" s="2"/>
-      <c r="C990" s="46"/>
+      <c r="C990" s="45"/>
     </row>
     <row r="991">
       <c r="B991" s="2"/>
-      <c r="C991" s="46"/>
+      <c r="C991" s="45"/>
     </row>
     <row r="992">
       <c r="B992" s="2"/>
-      <c r="C992" s="46"/>
+      <c r="C992" s="45"/>
     </row>
     <row r="993">
       <c r="B993" s="2"/>
-      <c r="C993" s="46"/>
+      <c r="C993" s="45"/>
     </row>
     <row r="994">
       <c r="B994" s="2"/>
-      <c r="C994" s="46"/>
+      <c r="C994" s="45"/>
     </row>
     <row r="995">
       <c r="B995" s="2"/>
-      <c r="C995" s="46"/>
+      <c r="C995" s="45"/>
     </row>
     <row r="996">
       <c r="B996" s="2"/>
-      <c r="C996" s="46"/>
+      <c r="C996" s="45"/>
     </row>
     <row r="997">
       <c r="B997" s="2"/>
-      <c r="C997" s="46"/>
+      <c r="C997" s="45"/>
     </row>
     <row r="998">
       <c r="B998" s="2"/>
-      <c r="C998" s="46"/>
+      <c r="C998" s="45"/>
     </row>
     <row r="999">
       <c r="B999" s="2"/>
-      <c r="C999" s="46"/>
+      <c r="C999" s="45"/>
     </row>
     <row r="1000">
       <c r="B1000" s="2"/>
-      <c r="C1000" s="46"/>
+      <c r="C1000" s="45"/>
     </row>
   </sheetData>
   <mergeCells count="2">
